--- a/16기_스타트캠프_강사 가이드 문서.xlsx
+++ b/16기_스타트캠프_강사 가이드 문서.xlsx
@@ -5,20 +5,21 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SSAFY\16g_Local\00_startcamp\git_onboarding\git_ai_onboarding\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ed\ai-onboarding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDF617A0-3480-4A13-A777-DC914BAE9909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{22DD5019-E82A-4B73-8349-EA8DBA0ADA4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34452" yWindow="-108" windowWidth="46296" windowHeight="25416" xr2:uid="{FD3BB604-1650-4EBB-871F-9010366B35B1}"/>
+    <workbookView xWindow="15" yWindow="15" windowWidth="28770" windowHeight="15450" activeTab="1" xr2:uid="{FD3BB604-1650-4EBB-871F-9010366B35B1}"/>
   </bookViews>
   <sheets>
-    <sheet name="전체 일정표" sheetId="6" r:id="rId1"/>
-    <sheet name="1일차" sheetId="1" r:id="rId2"/>
-    <sheet name="2일차" sheetId="2" r:id="rId3"/>
-    <sheet name="3일차" sheetId="3" r:id="rId4"/>
-    <sheet name="4일차" sheetId="4" r:id="rId5"/>
-    <sheet name="5일차" sheetId="5" r:id="rId6"/>
+    <sheet name="교육 목표 및 방향" sheetId="7" r:id="rId1"/>
+    <sheet name="전체 일정표" sheetId="6" r:id="rId2"/>
+    <sheet name="1일차" sheetId="1" r:id="rId3"/>
+    <sheet name="2일차" sheetId="2" r:id="rId4"/>
+    <sheet name="3일차" sheetId="3" r:id="rId5"/>
+    <sheet name="4일차" sheetId="4" r:id="rId6"/>
+    <sheet name="5일차" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="203">
   <si>
     <t>시간</t>
   </si>
@@ -782,9 +783,6 @@
   </si>
   <si>
     <t xml:space="preserve"> 비전공: https://check-sc16-spa.netlify.app/</t>
-  </si>
-  <si>
-    <t>전공 : https://check-sc16-mpa.netlify.app/</t>
   </si>
   <si>
     <t>개발 명세서</t>
@@ -1685,9 +1683,6 @@
     <t>팀 스크럼 회의</t>
   </si>
   <si>
-    <t>to do 항목 및 목표공유 시간</t>
-  </si>
-  <si>
     <t>비전공: https://localhub-sc16-1.netlify.app/</t>
   </si>
   <si>
@@ -1812,9 +1807,6 @@
   </si>
   <si>
     <t>AI Studio 활용</t>
-  </si>
-  <si>
-    <t>AI 스튜디오 활용 문서</t>
   </si>
   <si>
     <t>17:00 – 17:30</t>
@@ -5066,10 +5058,6 @@
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <t>render 배포 가이드 문서</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">( Copilot  </t>
     </r>
@@ -6763,6 +6751,1032 @@
       </rPr>
       <t>우수팀에게는 기프티콘 지급 예정이라고 합니다. (커피 X)</t>
     </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">* ask </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모드를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">통해 진행하므로 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제안하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내용을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자세히</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>읽어보고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>추가할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있도록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지도해주시기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바랍니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. 
+  - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비전공</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>트랙의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>경우</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ask </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모드로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개발이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어려울</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있으니</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>강사님들이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>옆에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>많이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>도와줄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있도록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부탁드립니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. 
+  - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>막히는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부분이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>배워야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부분이고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>것을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>알면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시킬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있다로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>교육생들</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마인드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>셋팅도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>진행해주세요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.
+* git </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사용을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잊지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않도록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>계속</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부탁드립니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>render 배포 가이드 문서(
+전공 : render 서비스를 활용
+비전공: netlify 서비스 활용)</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> WebEX</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
@@ -8072,7 +9086,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="296">
+  <cellXfs count="297">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -8415,347 +9429,377 @@
     <xf numFmtId="0" fontId="42" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="46" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="43" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -8784,12 +9828,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -8826,26 +9864,41 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="46" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="43" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
@@ -8859,15 +9912,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -8880,34 +9927,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -8934,18 +9963,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -8958,8 +9975,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -8977,6 +9994,99 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>58019</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>86614</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32AF8DB6-D745-ABEC-7417-FFD6A661132F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="209550"/>
+          <a:ext cx="6230219" cy="6373114"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>10386</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>77063</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFC00CAA-380C-CAD8-AC6E-150EFD33769C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7553325" y="600075"/>
+          <a:ext cx="6173061" cy="6182588"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9295,20 +10405,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F735B4F9-89DF-4562-B374-7F3189E766EF}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetData/>
+  <phoneticPr fontId="17" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2CBD596-7E3B-4236-AC37-387FA1537CFC}">
   <dimension ref="B1:I65"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="4" max="4" width="34.140625" customWidth="1"/>
-    <col min="5" max="5" width="41.42578125" customWidth="1"/>
-    <col min="6" max="6" width="71.640625" customWidth="1"/>
+    <col min="4" max="4" width="34.125" customWidth="1"/>
+    <col min="5" max="5" width="41.375" customWidth="1"/>
+    <col min="6" max="6" width="71.625" customWidth="1"/>
     <col min="7" max="7" width="53.5" customWidth="1"/>
-    <col min="8" max="8" width="41.140625" customWidth="1"/>
-    <col min="9" max="9" width="43.35546875" customWidth="1"/>
+    <col min="8" max="8" width="41.125" customWidth="1"/>
+    <col min="9" max="9" width="43.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="18" thickBot="1"/>
-    <row r="2" spans="2:9" ht="18" thickBot="1">
+    <row r="1" spans="2:9" ht="17.25" thickBot="1"/>
+    <row r="2" spans="2:9" ht="17.25" thickBot="1">
       <c r="B2" s="46"/>
       <c r="C2" s="47" t="s">
         <v>0</v>
@@ -9323,18 +10444,18 @@
         <v>3</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H2" s="47" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I2" s="106" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="35.15">
-      <c r="B3" s="158" t="s">
-        <v>169</v>
+    <row r="3" spans="2:9" ht="33">
+      <c r="B3" s="181" t="s">
+        <v>166</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>6</v>
@@ -9342,74 +10463,74 @@
       <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="192" t="s">
+      <c r="E3" s="140" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="193"/>
+      <c r="F3" s="141"/>
       <c r="G3" s="56" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H3" s="56"/>
       <c r="I3" s="53"/>
     </row>
-    <row r="4" spans="2:9" ht="17.600000000000001" customHeight="1">
-      <c r="B4" s="159"/>
-      <c r="C4" s="114" t="s">
+    <row r="4" spans="2:9" ht="17.649999999999999" customHeight="1">
+      <c r="B4" s="182"/>
+      <c r="C4" s="216" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="117" t="s">
+      <c r="D4" s="200" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="120" t="s">
+      <c r="F4" s="125" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="164" t="s">
-        <v>107</v>
-      </c>
-      <c r="H4" s="167"/>
-      <c r="I4" s="197"/>
-    </row>
-    <row r="5" spans="2:9" ht="17.600000000000001" customHeight="1">
-      <c r="B5" s="159"/>
-      <c r="C5" s="115"/>
-      <c r="D5" s="118"/>
+      <c r="G4" s="155" t="s">
+        <v>104</v>
+      </c>
+      <c r="H4" s="192"/>
+      <c r="I4" s="145"/>
+    </row>
+    <row r="5" spans="2:9" ht="17.649999999999999" customHeight="1">
+      <c r="B5" s="182"/>
+      <c r="C5" s="217"/>
+      <c r="D5" s="201"/>
       <c r="E5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="121"/>
-      <c r="G5" s="165"/>
-      <c r="H5" s="168"/>
-      <c r="I5" s="195"/>
+      <c r="F5" s="167"/>
+      <c r="G5" s="190"/>
+      <c r="H5" s="193"/>
+      <c r="I5" s="143"/>
     </row>
     <row r="6" spans="2:9">
-      <c r="B6" s="159"/>
-      <c r="C6" s="115"/>
-      <c r="D6" s="118"/>
+      <c r="B6" s="182"/>
+      <c r="C6" s="217"/>
+      <c r="D6" s="201"/>
       <c r="E6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="121"/>
-      <c r="G6" s="165"/>
-      <c r="H6" s="168"/>
-      <c r="I6" s="195"/>
+      <c r="F6" s="167"/>
+      <c r="G6" s="190"/>
+      <c r="H6" s="193"/>
+      <c r="I6" s="143"/>
     </row>
     <row r="7" spans="2:9">
-      <c r="B7" s="159"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="119"/>
+      <c r="B7" s="182"/>
+      <c r="C7" s="218"/>
+      <c r="D7" s="219"/>
       <c r="E7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="122"/>
-      <c r="G7" s="166"/>
-      <c r="H7" s="169"/>
-      <c r="I7" s="198"/>
-    </row>
-    <row r="8" spans="2:9" ht="53.15" customHeight="1">
-      <c r="B8" s="159"/>
+      <c r="F7" s="220"/>
+      <c r="G7" s="191"/>
+      <c r="H7" s="194"/>
+      <c r="I7" s="146"/>
+    </row>
+    <row r="8" spans="2:9" ht="53.1" customHeight="1">
+      <c r="B8" s="182"/>
       <c r="C8" s="7" t="s">
         <v>16</v>
       </c>
@@ -9419,48 +10540,48 @@
       <c r="E8" s="45"/>
       <c r="F8" s="9"/>
       <c r="G8" s="91" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H8" s="97"/>
-      <c r="I8" s="194" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" ht="17.600000000000001" customHeight="1">
-      <c r="B9" s="159"/>
-      <c r="C9" s="114" t="s">
+      <c r="I8" s="142" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="17.649999999999999" customHeight="1">
+      <c r="B9" s="182"/>
+      <c r="C9" s="216" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="134" t="s">
+      <c r="D9" s="223" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="120" t="s">
+      <c r="E9" s="125" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="216" t="s">
-        <v>180</v>
-      </c>
-      <c r="G9" s="178" t="s">
-        <v>123</v>
-      </c>
-      <c r="H9" s="211" t="s">
-        <v>114</v>
-      </c>
-      <c r="I9" s="195"/>
-    </row>
-    <row r="10" spans="2:9" ht="347.15" customHeight="1">
-      <c r="B10" s="159"/>
-      <c r="C10" s="133"/>
-      <c r="D10" s="135"/>
-      <c r="E10" s="136"/>
-      <c r="F10" s="217"/>
-      <c r="G10" s="180"/>
-      <c r="H10" s="212"/>
-      <c r="I10" s="195"/>
-    </row>
-    <row r="11" spans="2:9" ht="17.600000000000001" customHeight="1">
-      <c r="B11" s="159"/>
-      <c r="C11" s="114" t="s">
+      <c r="F9" s="118" t="s">
+        <v>176</v>
+      </c>
+      <c r="G9" s="165" t="s">
+        <v>120</v>
+      </c>
+      <c r="H9" s="163" t="s">
+        <v>111</v>
+      </c>
+      <c r="I9" s="143"/>
+    </row>
+    <row r="10" spans="2:9" ht="385.5" customHeight="1">
+      <c r="B10" s="182"/>
+      <c r="C10" s="222"/>
+      <c r="D10" s="224"/>
+      <c r="E10" s="126"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="166"/>
+      <c r="H10" s="164"/>
+      <c r="I10" s="143"/>
+    </row>
+    <row r="11" spans="2:9" ht="17.649999999999999" customHeight="1">
+      <c r="B11" s="182"/>
+      <c r="C11" s="216" t="s">
         <v>21</v>
       </c>
       <c r="D11" s="10" t="s">
@@ -9469,146 +10590,146 @@
       <c r="E11" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="181" t="s">
-        <v>176</v>
-      </c>
-      <c r="G11" s="178" t="s">
-        <v>121</v>
-      </c>
-      <c r="H11" s="183" t="s">
-        <v>117</v>
-      </c>
-      <c r="I11" s="195"/>
-    </row>
-    <row r="12" spans="2:9" ht="17.600000000000001" customHeight="1">
-      <c r="B12" s="159"/>
-      <c r="C12" s="115"/>
+      <c r="F11" s="170" t="s">
+        <v>173</v>
+      </c>
+      <c r="G11" s="165" t="s">
+        <v>118</v>
+      </c>
+      <c r="H11" s="172" t="s">
+        <v>114</v>
+      </c>
+      <c r="I11" s="143"/>
+    </row>
+    <row r="12" spans="2:9" ht="17.649999999999999" customHeight="1">
+      <c r="B12" s="182"/>
+      <c r="C12" s="217"/>
       <c r="D12" s="11" t="s">
         <v>23</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="F12" s="182"/>
-      <c r="G12" s="179"/>
-      <c r="H12" s="184"/>
-      <c r="I12" s="195"/>
-    </row>
-    <row r="13" spans="2:9" ht="123.9" customHeight="1">
-      <c r="B13" s="159"/>
-      <c r="C13" s="133"/>
+        <v>171</v>
+      </c>
+      <c r="F12" s="171"/>
+      <c r="G12" s="169"/>
+      <c r="H12" s="173"/>
+      <c r="I12" s="143"/>
+    </row>
+    <row r="13" spans="2:9" ht="123.95" customHeight="1">
+      <c r="B13" s="182"/>
+      <c r="C13" s="222"/>
       <c r="D13" s="11"/>
       <c r="E13" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F13" s="130"/>
-      <c r="G13" s="180"/>
-      <c r="H13" s="185"/>
-      <c r="I13" s="195"/>
-    </row>
-    <row r="14" spans="2:9" ht="17.600000000000001" customHeight="1">
-      <c r="B14" s="159"/>
-      <c r="C14" s="114" t="s">
+      <c r="F13" s="124"/>
+      <c r="G13" s="166"/>
+      <c r="H13" s="174"/>
+      <c r="I13" s="143"/>
+    </row>
+    <row r="14" spans="2:9" ht="17.649999999999999" customHeight="1">
+      <c r="B14" s="182"/>
+      <c r="C14" s="216" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="120" t="s">
-        <v>103</v>
+      <c r="D14" s="125" t="s">
+        <v>100</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G14" s="186" t="s">
-        <v>126</v>
-      </c>
-      <c r="H14" s="189" t="s">
-        <v>116</v>
-      </c>
-      <c r="I14" s="195"/>
-    </row>
-    <row r="15" spans="2:9" ht="35.15" customHeight="1">
-      <c r="B15" s="159"/>
-      <c r="C15" s="115"/>
-      <c r="D15" s="121"/>
+        <v>31</v>
+      </c>
+      <c r="G14" s="175" t="s">
+        <v>123</v>
+      </c>
+      <c r="H14" s="178" t="s">
+        <v>113</v>
+      </c>
+      <c r="I14" s="143"/>
+    </row>
+    <row r="15" spans="2:9" ht="35.1" customHeight="1">
+      <c r="B15" s="182"/>
+      <c r="C15" s="217"/>
+      <c r="D15" s="167"/>
       <c r="E15" s="13" t="s">
         <v>28</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="G15" s="187"/>
-      <c r="H15" s="190"/>
-      <c r="I15" s="195"/>
+        <v>172</v>
+      </c>
+      <c r="G15" s="176"/>
+      <c r="H15" s="179"/>
+      <c r="I15" s="143"/>
     </row>
     <row r="16" spans="2:9">
-      <c r="B16" s="159"/>
-      <c r="C16" s="115"/>
-      <c r="D16" s="121"/>
+      <c r="B16" s="182"/>
+      <c r="C16" s="217"/>
+      <c r="D16" s="167"/>
       <c r="E16" s="14"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="187"/>
-      <c r="H16" s="190"/>
-      <c r="I16" s="195"/>
-    </row>
-    <row r="17" spans="2:9" ht="52.75">
-      <c r="B17" s="159"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="121"/>
+      <c r="G16" s="176"/>
+      <c r="H16" s="179"/>
+      <c r="I16" s="143"/>
+    </row>
+    <row r="17" spans="2:9" ht="49.5">
+      <c r="B17" s="182"/>
+      <c r="C17" s="217"/>
+      <c r="D17" s="167"/>
       <c r="E17" s="13" t="s">
         <v>29</v>
       </c>
       <c r="F17" s="5"/>
-      <c r="G17" s="187"/>
-      <c r="H17" s="190"/>
-      <c r="I17" s="195"/>
+      <c r="G17" s="176"/>
+      <c r="H17" s="179"/>
+      <c r="I17" s="143"/>
     </row>
     <row r="18" spans="2:9">
-      <c r="B18" s="159"/>
-      <c r="C18" s="115"/>
-      <c r="D18" s="121"/>
+      <c r="B18" s="182"/>
+      <c r="C18" s="217"/>
+      <c r="D18" s="167"/>
       <c r="E18" s="14"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="187"/>
-      <c r="H18" s="190"/>
-      <c r="I18" s="195"/>
+      <c r="G18" s="176"/>
+      <c r="H18" s="179"/>
+      <c r="I18" s="143"/>
     </row>
     <row r="19" spans="2:9">
-      <c r="B19" s="159"/>
-      <c r="C19" s="115"/>
-      <c r="D19" s="121"/>
-      <c r="E19" s="13" t="s">
+      <c r="B19" s="182"/>
+      <c r="C19" s="217"/>
+      <c r="D19" s="167"/>
+      <c r="E19" s="296" t="s">
         <v>30</v>
       </c>
       <c r="F19" s="5"/>
-      <c r="G19" s="187"/>
-      <c r="H19" s="190"/>
-      <c r="I19" s="195"/>
+      <c r="G19" s="176"/>
+      <c r="H19" s="179"/>
+      <c r="I19" s="143"/>
     </row>
     <row r="20" spans="2:9">
-      <c r="B20" s="159"/>
-      <c r="C20" s="115"/>
-      <c r="D20" s="121"/>
-      <c r="E20" s="13" t="s">
-        <v>109</v>
+      <c r="B20" s="182"/>
+      <c r="C20" s="217"/>
+      <c r="D20" s="167"/>
+      <c r="E20" s="296" t="s">
+        <v>106</v>
       </c>
       <c r="F20" s="5"/>
-      <c r="G20" s="187"/>
-      <c r="H20" s="190"/>
-      <c r="I20" s="195"/>
-    </row>
-    <row r="21" spans="2:9" ht="84.45" customHeight="1" thickBot="1">
-      <c r="B21" s="160"/>
-      <c r="C21" s="126"/>
-      <c r="D21" s="177"/>
+      <c r="G20" s="176"/>
+      <c r="H20" s="179"/>
+      <c r="I20" s="143"/>
+    </row>
+    <row r="21" spans="2:9" ht="84.4" customHeight="1" thickBot="1">
+      <c r="B21" s="183"/>
+      <c r="C21" s="221"/>
+      <c r="D21" s="168"/>
       <c r="E21" s="50"/>
       <c r="F21" s="49"/>
-      <c r="G21" s="188"/>
-      <c r="H21" s="191"/>
-      <c r="I21" s="196"/>
-    </row>
-    <row r="22" spans="2:9" ht="18" thickBot="1">
+      <c r="G21" s="177"/>
+      <c r="H21" s="180"/>
+      <c r="I21" s="144"/>
+    </row>
+    <row r="22" spans="2:9" ht="17.25" thickBot="1">
       <c r="B22" s="107"/>
       <c r="C22" s="15"/>
       <c r="D22" s="16"/>
@@ -9618,223 +10739,223 @@
       <c r="H22" s="98"/>
       <c r="I22" s="108"/>
     </row>
-    <row r="23" spans="2:9" ht="32.15" customHeight="1">
-      <c r="B23" s="152" t="s">
-        <v>170</v>
-      </c>
-      <c r="C23" s="127" t="s">
+    <row r="23" spans="2:9" ht="32.1" customHeight="1">
+      <c r="B23" s="184" t="s">
+        <v>167</v>
+      </c>
+      <c r="C23" s="212" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="E23" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="E23" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="F23" s="129" t="s">
-        <v>181</v>
-      </c>
-      <c r="G23" s="201" t="s">
-        <v>137</v>
-      </c>
-      <c r="H23" s="129" t="s">
-        <v>136</v>
-      </c>
-      <c r="I23" s="123" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" ht="70.75" customHeight="1">
-      <c r="B24" s="153"/>
-      <c r="C24" s="128"/>
+      <c r="F23" s="123" t="s">
+        <v>177</v>
+      </c>
+      <c r="G23" s="151" t="s">
+        <v>134</v>
+      </c>
+      <c r="H23" s="123" t="s">
+        <v>133</v>
+      </c>
+      <c r="I23" s="133" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" ht="70.7" customHeight="1">
+      <c r="B24" s="185"/>
+      <c r="C24" s="196"/>
       <c r="D24" s="20" t="s">
         <v>23</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="F24" s="130"/>
-      <c r="G24" s="202"/>
-      <c r="H24" s="130"/>
-      <c r="I24" s="124"/>
-    </row>
-    <row r="25" spans="2:9" ht="35.15" customHeight="1">
-      <c r="B25" s="153"/>
-      <c r="C25" s="131" t="s">
+        <v>35</v>
+      </c>
+      <c r="F24" s="124"/>
+      <c r="G24" s="152"/>
+      <c r="H24" s="124"/>
+      <c r="I24" s="136"/>
+    </row>
+    <row r="25" spans="2:9" ht="35.1" customHeight="1">
+      <c r="B25" s="185"/>
+      <c r="C25" s="195" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="23" t="s">
+      <c r="E25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F25" s="120" t="s">
+        <v>179</v>
+      </c>
+      <c r="G25" s="147" t="s">
+        <v>124</v>
+      </c>
+      <c r="H25" s="228" t="s">
+        <v>180</v>
+      </c>
+      <c r="I25" s="136"/>
+    </row>
+    <row r="26" spans="2:9">
+      <c r="B26" s="185"/>
+      <c r="C26" s="199"/>
+      <c r="D26" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E26" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F25" s="218" t="s">
-        <v>183</v>
-      </c>
-      <c r="G25" s="139" t="s">
-        <v>127</v>
-      </c>
-      <c r="H25" s="142" t="s">
-        <v>184</v>
-      </c>
-      <c r="I25" s="124"/>
-    </row>
-    <row r="26" spans="2:9">
-      <c r="B26" s="153"/>
-      <c r="C26" s="132"/>
-      <c r="D26" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="F26" s="219"/>
-      <c r="G26" s="140"/>
-      <c r="H26" s="143"/>
-      <c r="I26" s="124"/>
+      <c r="F26" s="121"/>
+      <c r="G26" s="227"/>
+      <c r="H26" s="132"/>
+      <c r="I26" s="136"/>
     </row>
     <row r="27" spans="2:9">
-      <c r="B27" s="153"/>
-      <c r="C27" s="132"/>
+      <c r="B27" s="185"/>
+      <c r="C27" s="199"/>
       <c r="D27" s="24"/>
       <c r="E27" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="F27" s="219"/>
-      <c r="G27" s="140"/>
-      <c r="H27" s="143"/>
-      <c r="I27" s="124"/>
+        <v>42</v>
+      </c>
+      <c r="F27" s="121"/>
+      <c r="G27" s="227"/>
+      <c r="H27" s="132"/>
+      <c r="I27" s="136"/>
     </row>
     <row r="28" spans="2:9">
-      <c r="B28" s="153"/>
-      <c r="C28" s="132"/>
+      <c r="B28" s="185"/>
+      <c r="C28" s="199"/>
       <c r="D28" s="24"/>
       <c r="E28" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="F28" s="219"/>
-      <c r="G28" s="140"/>
-      <c r="H28" s="143"/>
-      <c r="I28" s="124"/>
+        <v>43</v>
+      </c>
+      <c r="F28" s="121"/>
+      <c r="G28" s="227"/>
+      <c r="H28" s="132"/>
+      <c r="I28" s="136"/>
     </row>
     <row r="29" spans="2:9">
-      <c r="B29" s="153"/>
-      <c r="C29" s="132"/>
+      <c r="B29" s="185"/>
+      <c r="C29" s="199"/>
       <c r="D29" s="24"/>
       <c r="E29" s="14"/>
-      <c r="F29" s="219"/>
-      <c r="G29" s="140"/>
-      <c r="H29" s="143"/>
-      <c r="I29" s="124"/>
+      <c r="F29" s="121"/>
+      <c r="G29" s="227"/>
+      <c r="H29" s="132"/>
+      <c r="I29" s="136"/>
     </row>
     <row r="30" spans="2:9">
-      <c r="B30" s="153"/>
-      <c r="C30" s="132"/>
+      <c r="B30" s="185"/>
+      <c r="C30" s="199"/>
       <c r="D30" s="24"/>
-      <c r="E30" s="13" t="s">
+      <c r="E30" s="296" t="s">
         <v>30</v>
       </c>
-      <c r="F30" s="219"/>
-      <c r="G30" s="140"/>
-      <c r="H30" s="143"/>
-      <c r="I30" s="124"/>
+      <c r="F30" s="121"/>
+      <c r="G30" s="227"/>
+      <c r="H30" s="132"/>
+      <c r="I30" s="136"/>
     </row>
     <row r="31" spans="2:9">
-      <c r="B31" s="153"/>
-      <c r="C31" s="132"/>
+      <c r="B31" s="185"/>
+      <c r="C31" s="199"/>
       <c r="D31" s="24"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="219"/>
-      <c r="G31" s="140"/>
-      <c r="H31" s="143"/>
-      <c r="I31" s="124"/>
+      <c r="E31" s="296" t="s">
+        <v>106</v>
+      </c>
+      <c r="F31" s="121"/>
+      <c r="G31" s="227"/>
+      <c r="H31" s="132"/>
+      <c r="I31" s="136"/>
     </row>
     <row r="32" spans="2:9">
-      <c r="B32" s="153"/>
-      <c r="C32" s="128"/>
+      <c r="B32" s="185"/>
+      <c r="C32" s="196"/>
       <c r="D32" s="25"/>
-      <c r="E32" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="F32" s="220"/>
-      <c r="G32" s="141"/>
-      <c r="H32" s="144"/>
-      <c r="I32" s="124"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="122"/>
+      <c r="G32" s="148"/>
+      <c r="H32" s="131"/>
+      <c r="I32" s="136"/>
     </row>
     <row r="33" spans="2:9">
-      <c r="B33" s="153"/>
-      <c r="C33" s="131" t="s">
+      <c r="B33" s="185"/>
+      <c r="C33" s="195" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="D33" s="23" t="s">
+      <c r="E33" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F33" s="225" t="s">
+        <v>178</v>
+      </c>
+      <c r="G33" s="208" t="s">
+        <v>127</v>
+      </c>
+      <c r="H33" s="130" t="s">
+        <v>130</v>
+      </c>
+      <c r="I33" s="136"/>
+    </row>
+    <row r="34" spans="2:9" ht="123.4" customHeight="1">
+      <c r="B34" s="185"/>
+      <c r="C34" s="196"/>
+      <c r="D34" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E34" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="F33" s="137" t="s">
-        <v>182</v>
-      </c>
-      <c r="G33" s="145" t="s">
-        <v>130</v>
-      </c>
-      <c r="H33" s="147" t="s">
-        <v>133</v>
-      </c>
-      <c r="I33" s="124"/>
-    </row>
-    <row r="34" spans="2:9" ht="123.45" customHeight="1">
-      <c r="B34" s="153"/>
-      <c r="C34" s="128"/>
-      <c r="D34" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="E34" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="F34" s="138"/>
-      <c r="G34" s="146"/>
-      <c r="H34" s="144"/>
-      <c r="I34" s="124"/>
+      <c r="F34" s="226"/>
+      <c r="G34" s="209"/>
+      <c r="H34" s="131"/>
+      <c r="I34" s="136"/>
     </row>
     <row r="35" spans="2:9" ht="141" customHeight="1">
-      <c r="B35" s="153"/>
+      <c r="B35" s="185"/>
       <c r="C35" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="D35" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="29" t="s">
+      <c r="E35" s="30" t="s">
         <v>52</v>
-      </c>
-      <c r="E35" s="30" t="s">
-        <v>53</v>
       </c>
       <c r="F35" s="9"/>
       <c r="G35" s="63" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H35" s="99" t="s">
-        <v>134</v>
-      </c>
-      <c r="I35" s="125"/>
-    </row>
-    <row r="36" spans="2:9" ht="35.6" thickBot="1">
-      <c r="B36" s="154"/>
+        <v>131</v>
+      </c>
+      <c r="I35" s="137"/>
+    </row>
+    <row r="36" spans="2:9" ht="33.75" thickBot="1">
+      <c r="B36" s="186"/>
       <c r="C36" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="D36" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="D36" s="32" t="s">
+      <c r="E36" s="60" t="s">
         <v>56</v>
-      </c>
-      <c r="E36" s="60" t="s">
-        <v>57</v>
       </c>
       <c r="F36" s="61"/>
       <c r="G36" s="88"/>
       <c r="H36" s="88"/>
       <c r="I36" s="110"/>
     </row>
-    <row r="37" spans="2:9" ht="18" thickBot="1">
+    <row r="37" spans="2:9" ht="17.25" thickBot="1">
       <c r="B37" s="82"/>
       <c r="C37" s="83"/>
       <c r="D37" s="84"/>
@@ -9845,226 +10966,226 @@
       <c r="I37" s="94"/>
     </row>
     <row r="38" spans="2:9">
-      <c r="B38" s="152" t="s">
+      <c r="B38" s="184" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" s="212" t="s">
         <v>58</v>
       </c>
-      <c r="C38" s="127" t="s">
+      <c r="D38" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="D38" s="33" t="s">
+      <c r="E38" s="213" t="s">
+        <v>61</v>
+      </c>
+      <c r="F38" s="123" t="s">
+        <v>181</v>
+      </c>
+      <c r="G38" s="151" t="s">
+        <v>144</v>
+      </c>
+      <c r="H38" s="153" t="s">
+        <v>146</v>
+      </c>
+      <c r="I38" s="133" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" ht="149.1" customHeight="1">
+      <c r="B39" s="185"/>
+      <c r="C39" s="199"/>
+      <c r="D39" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="E38" s="155" t="s">
+      <c r="E39" s="131"/>
+      <c r="F39" s="124"/>
+      <c r="G39" s="152"/>
+      <c r="H39" s="154"/>
+      <c r="I39" s="134"/>
+    </row>
+    <row r="40" spans="2:9">
+      <c r="B40" s="185"/>
+      <c r="C40" s="199"/>
+      <c r="D40" s="214" t="s">
         <v>62</v>
       </c>
-      <c r="F38" s="129" t="s">
+      <c r="E40" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F40" s="125" t="s">
+        <v>184</v>
+      </c>
+      <c r="G40" s="155" t="s">
+        <v>145</v>
+      </c>
+      <c r="H40" s="149" t="s">
+        <v>147</v>
+      </c>
+      <c r="I40" s="134"/>
+    </row>
+    <row r="41" spans="2:9" ht="119.65" customHeight="1">
+      <c r="B41" s="185"/>
+      <c r="C41" s="196"/>
+      <c r="D41" s="215"/>
+      <c r="E41" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="F41" s="126"/>
+      <c r="G41" s="156"/>
+      <c r="H41" s="150"/>
+      <c r="I41" s="134"/>
+    </row>
+    <row r="42" spans="2:9">
+      <c r="B42" s="185"/>
+      <c r="C42" s="195" t="s">
+        <v>65</v>
+      </c>
+      <c r="D42" s="206" t="s">
+        <v>66</v>
+      </c>
+      <c r="E42" s="120" t="s">
+        <v>140</v>
+      </c>
+      <c r="F42" s="125" t="s">
+        <v>183</v>
+      </c>
+      <c r="G42" s="155" t="s">
+        <v>141</v>
+      </c>
+      <c r="H42" s="157" t="s">
+        <v>148</v>
+      </c>
+      <c r="I42" s="134"/>
+    </row>
+    <row r="43" spans="2:9" ht="113.65" customHeight="1">
+      <c r="B43" s="185"/>
+      <c r="C43" s="199"/>
+      <c r="D43" s="207"/>
+      <c r="E43" s="122"/>
+      <c r="F43" s="126"/>
+      <c r="G43" s="156"/>
+      <c r="H43" s="157"/>
+      <c r="I43" s="134"/>
+    </row>
+    <row r="44" spans="2:9">
+      <c r="B44" s="185"/>
+      <c r="C44" s="199"/>
+      <c r="D44" s="197" t="s">
+        <v>67</v>
+      </c>
+      <c r="E44" s="125" t="s">
+        <v>182</v>
+      </c>
+      <c r="F44" s="210"/>
+      <c r="G44" s="138" t="s">
+        <v>189</v>
+      </c>
+      <c r="H44" s="157"/>
+      <c r="I44" s="134"/>
+    </row>
+    <row r="45" spans="2:9" ht="317.64999999999998" customHeight="1">
+      <c r="B45" s="185"/>
+      <c r="C45" s="196"/>
+      <c r="D45" s="198"/>
+      <c r="E45" s="126"/>
+      <c r="F45" s="211"/>
+      <c r="G45" s="139"/>
+      <c r="H45" s="150"/>
+      <c r="I45" s="134"/>
+    </row>
+    <row r="46" spans="2:9">
+      <c r="B46" s="185"/>
+      <c r="C46" s="195" t="s">
+        <v>68</v>
+      </c>
+      <c r="D46" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="E46" s="200" t="s">
+        <v>72</v>
+      </c>
+      <c r="F46" s="130" t="s">
         <v>185</v>
       </c>
-      <c r="G38" s="201" t="s">
-        <v>147</v>
-      </c>
-      <c r="H38" s="203" t="s">
-        <v>149</v>
-      </c>
-      <c r="I38" s="123" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="39" spans="2:9" ht="149.15" customHeight="1">
-      <c r="B39" s="153"/>
-      <c r="C39" s="132"/>
-      <c r="D39" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="E39" s="144"/>
-      <c r="F39" s="130"/>
-      <c r="G39" s="202"/>
-      <c r="H39" s="204"/>
-      <c r="I39" s="224"/>
-    </row>
-    <row r="40" spans="2:9">
-      <c r="B40" s="153"/>
-      <c r="C40" s="132"/>
-      <c r="D40" s="156" t="s">
-        <v>63</v>
-      </c>
-      <c r="E40" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F40" s="120" t="s">
-        <v>188</v>
-      </c>
-      <c r="G40" s="164" t="s">
-        <v>148</v>
-      </c>
-      <c r="H40" s="199" t="s">
-        <v>150</v>
-      </c>
-      <c r="I40" s="224"/>
-    </row>
-    <row r="41" spans="2:9" ht="119.6" customHeight="1">
-      <c r="B41" s="153"/>
-      <c r="C41" s="128"/>
-      <c r="D41" s="157"/>
-      <c r="E41" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="F41" s="136"/>
-      <c r="G41" s="174"/>
-      <c r="H41" s="200"/>
-      <c r="I41" s="224"/>
-    </row>
-    <row r="42" spans="2:9">
-      <c r="B42" s="153"/>
-      <c r="C42" s="131" t="s">
-        <v>66</v>
-      </c>
-      <c r="D42" s="175" t="s">
-        <v>67</v>
-      </c>
-      <c r="E42" s="218" t="s">
-        <v>143</v>
-      </c>
-      <c r="F42" s="120" t="s">
-        <v>187</v>
-      </c>
-      <c r="G42" s="164" t="s">
-        <v>144</v>
-      </c>
-      <c r="H42" s="205" t="s">
-        <v>151</v>
-      </c>
-      <c r="I42" s="224"/>
-    </row>
-    <row r="43" spans="2:9" ht="113.6" customHeight="1">
-      <c r="B43" s="153"/>
-      <c r="C43" s="132"/>
-      <c r="D43" s="176"/>
-      <c r="E43" s="220"/>
-      <c r="F43" s="136"/>
-      <c r="G43" s="174"/>
-      <c r="H43" s="205"/>
-      <c r="I43" s="224"/>
-    </row>
-    <row r="44" spans="2:9">
-      <c r="B44" s="153"/>
-      <c r="C44" s="132"/>
-      <c r="D44" s="148" t="s">
-        <v>68</v>
-      </c>
-      <c r="E44" s="120" t="s">
-        <v>186</v>
-      </c>
-      <c r="F44" s="150"/>
-      <c r="G44" s="226" t="s">
-        <v>193</v>
-      </c>
-      <c r="H44" s="205"/>
-      <c r="I44" s="224"/>
-    </row>
-    <row r="45" spans="2:9" ht="317.60000000000002" customHeight="1">
-      <c r="B45" s="153"/>
-      <c r="C45" s="128"/>
-      <c r="D45" s="149"/>
-      <c r="E45" s="136"/>
-      <c r="F45" s="151"/>
-      <c r="G45" s="227"/>
-      <c r="H45" s="200"/>
-      <c r="I45" s="224"/>
-    </row>
-    <row r="46" spans="2:9">
-      <c r="B46" s="153"/>
-      <c r="C46" s="131" t="s">
-        <v>69</v>
-      </c>
-      <c r="D46" s="36" t="s">
+      <c r="G46" s="158" t="s">
+        <v>199</v>
+      </c>
+      <c r="H46" s="161"/>
+      <c r="I46" s="134"/>
+    </row>
+    <row r="47" spans="2:9">
+      <c r="B47" s="185"/>
+      <c r="C47" s="199"/>
+      <c r="D47" s="37" t="s">
+        <v>175</v>
+      </c>
+      <c r="E47" s="201"/>
+      <c r="F47" s="132"/>
+      <c r="G47" s="159"/>
+      <c r="H47" s="161"/>
+      <c r="I47" s="134"/>
+    </row>
+    <row r="48" spans="2:9">
+      <c r="B48" s="185"/>
+      <c r="C48" s="199"/>
+      <c r="D48" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="E46" s="117" t="s">
+      <c r="E48" s="201"/>
+      <c r="F48" s="132"/>
+      <c r="G48" s="159"/>
+      <c r="H48" s="161"/>
+      <c r="I48" s="134"/>
+    </row>
+    <row r="49" spans="2:9">
+      <c r="B49" s="185"/>
+      <c r="C49" s="199"/>
+      <c r="D49" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="E49" s="201"/>
+      <c r="F49" s="132"/>
+      <c r="G49" s="159"/>
+      <c r="H49" s="161"/>
+      <c r="I49" s="134"/>
+    </row>
+    <row r="50" spans="2:9">
+      <c r="B50" s="185"/>
+      <c r="C50" s="199"/>
+      <c r="D50" s="37"/>
+      <c r="E50" s="201"/>
+      <c r="F50" s="132"/>
+      <c r="G50" s="159"/>
+      <c r="H50" s="161"/>
+      <c r="I50" s="134"/>
+    </row>
+    <row r="51" spans="2:9" ht="204.4" customHeight="1" thickBot="1">
+      <c r="B51" s="185"/>
+      <c r="C51" s="196"/>
+      <c r="D51" s="37"/>
+      <c r="E51" s="202"/>
+      <c r="F51" s="131"/>
+      <c r="G51" s="160"/>
+      <c r="H51" s="162"/>
+      <c r="I51" s="135"/>
+    </row>
+    <row r="52" spans="2:9" ht="30.75" thickBot="1">
+      <c r="B52" s="186"/>
+      <c r="C52" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="F46" s="147" t="s">
-        <v>189</v>
-      </c>
-      <c r="G46" s="206" t="s">
-        <v>203</v>
-      </c>
-      <c r="H46" s="209"/>
-      <c r="I46" s="224"/>
-    </row>
-    <row r="47" spans="2:9">
-      <c r="B47" s="153"/>
-      <c r="C47" s="132"/>
-      <c r="D47" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="E47" s="118"/>
-      <c r="F47" s="143"/>
-      <c r="G47" s="207"/>
-      <c r="H47" s="209"/>
-      <c r="I47" s="224"/>
-    </row>
-    <row r="48" spans="2:9">
-      <c r="B48" s="153"/>
-      <c r="C48" s="132"/>
-      <c r="D48" s="37" t="s">
-        <v>71</v>
-      </c>
-      <c r="E48" s="118"/>
-      <c r="F48" s="143"/>
-      <c r="G48" s="207"/>
-      <c r="H48" s="209"/>
-      <c r="I48" s="224"/>
-    </row>
-    <row r="49" spans="2:9">
-      <c r="B49" s="153"/>
-      <c r="C49" s="132"/>
-      <c r="D49" s="37" t="s">
-        <v>72</v>
-      </c>
-      <c r="E49" s="118"/>
-      <c r="F49" s="143"/>
-      <c r="G49" s="207"/>
-      <c r="H49" s="209"/>
-      <c r="I49" s="224"/>
-    </row>
-    <row r="50" spans="2:9">
-      <c r="B50" s="153"/>
-      <c r="C50" s="132"/>
-      <c r="D50" s="37"/>
-      <c r="E50" s="118"/>
-      <c r="F50" s="143"/>
-      <c r="G50" s="207"/>
-      <c r="H50" s="209"/>
-      <c r="I50" s="224"/>
-    </row>
-    <row r="51" spans="2:9" ht="204.45" customHeight="1" thickBot="1">
-      <c r="B51" s="153"/>
-      <c r="C51" s="128"/>
-      <c r="D51" s="37"/>
-      <c r="E51" s="170"/>
-      <c r="F51" s="144"/>
-      <c r="G51" s="208"/>
-      <c r="H51" s="210"/>
-      <c r="I51" s="225"/>
-    </row>
-    <row r="52" spans="2:9" ht="29.6" thickBot="1">
-      <c r="B52" s="154"/>
-      <c r="C52" s="38" t="s">
+      <c r="D52" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="D52" s="39" t="s">
-        <v>75</v>
-      </c>
-      <c r="E52" s="171" t="s">
-        <v>57</v>
-      </c>
-      <c r="F52" s="172"/>
-      <c r="G52" s="172"/>
-      <c r="H52" s="172"/>
-      <c r="I52" s="173"/>
-    </row>
-    <row r="53" spans="2:9" ht="18" thickBot="1">
+      <c r="E52" s="203" t="s">
+        <v>56</v>
+      </c>
+      <c r="F52" s="204"/>
+      <c r="G52" s="204"/>
+      <c r="H52" s="204"/>
+      <c r="I52" s="205"/>
+    </row>
+    <row r="53" spans="2:9" ht="17.25" thickBot="1">
       <c r="B53" s="82"/>
       <c r="C53" s="83"/>
       <c r="D53" s="84"/>
@@ -10074,99 +11195,99 @@
       <c r="H53" s="100"/>
       <c r="I53" s="95"/>
     </row>
-    <row r="54" spans="2:9" ht="94.75" customHeight="1">
-      <c r="B54" s="152" t="s">
+    <row r="54" spans="2:9" ht="94.7" customHeight="1">
+      <c r="B54" s="184" t="s">
+        <v>75</v>
+      </c>
+      <c r="C54" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="C54" s="40" t="s">
+      <c r="D54" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="D54" s="41" t="s">
+      <c r="E54" s="42" t="s">
         <v>78</v>
       </c>
-      <c r="E54" s="42" t="s">
+      <c r="F54" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G54" s="69" t="s">
+        <v>153</v>
+      </c>
+      <c r="H54" s="111" t="s">
+        <v>150</v>
+      </c>
+      <c r="I54" s="133" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9">
+      <c r="B55" s="185"/>
+      <c r="C55" s="195" t="s">
+        <v>16</v>
+      </c>
+      <c r="D55" s="197" t="s">
         <v>79</v>
       </c>
-      <c r="F54" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="G54" s="69" t="s">
-        <v>156</v>
-      </c>
-      <c r="H54" s="111" t="s">
-        <v>153</v>
-      </c>
-      <c r="I54" s="123" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="55" spans="2:9">
-      <c r="B55" s="153"/>
-      <c r="C55" s="131" t="s">
-        <v>16</v>
-      </c>
-      <c r="D55" s="148" t="s">
+      <c r="E55" s="130" t="s">
         <v>80</v>
       </c>
-      <c r="E55" s="147" t="s">
+      <c r="F55" s="130" t="s">
+        <v>186</v>
+      </c>
+      <c r="G55" s="147" t="s">
+        <v>155</v>
+      </c>
+      <c r="H55" s="149" t="s">
+        <v>187</v>
+      </c>
+      <c r="I55" s="134"/>
+    </row>
+    <row r="56" spans="2:9" ht="150.4" customHeight="1">
+      <c r="B56" s="185"/>
+      <c r="C56" s="196"/>
+      <c r="D56" s="198"/>
+      <c r="E56" s="131"/>
+      <c r="F56" s="131"/>
+      <c r="G56" s="148"/>
+      <c r="H56" s="150"/>
+      <c r="I56" s="134"/>
+    </row>
+    <row r="57" spans="2:9" ht="181.7" customHeight="1">
+      <c r="B57" s="185"/>
+      <c r="C57" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="F55" s="147" t="s">
-        <v>190</v>
-      </c>
-      <c r="G55" s="139" t="s">
-        <v>158</v>
-      </c>
-      <c r="H55" s="199" t="s">
-        <v>191</v>
-      </c>
-      <c r="I55" s="224"/>
-    </row>
-    <row r="56" spans="2:9" ht="150.44999999999999" customHeight="1">
-      <c r="B56" s="153"/>
-      <c r="C56" s="128"/>
-      <c r="D56" s="149"/>
-      <c r="E56" s="144"/>
-      <c r="F56" s="144"/>
-      <c r="G56" s="141"/>
-      <c r="H56" s="200"/>
-      <c r="I56" s="224"/>
-    </row>
-    <row r="57" spans="2:9" ht="181.75" customHeight="1">
-      <c r="B57" s="153"/>
-      <c r="C57" s="28" t="s">
+      <c r="D57" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="E57" s="9" t="s">
         <v>82</v>
-      </c>
-      <c r="D57" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="E57" s="9" t="s">
-        <v>83</v>
       </c>
       <c r="F57" s="9"/>
       <c r="G57" s="90" t="s">
-        <v>159</v>
+        <v>200</v>
       </c>
       <c r="H57" s="101"/>
-      <c r="I57" s="225"/>
-    </row>
-    <row r="58" spans="2:9" ht="35.6" thickBot="1">
-      <c r="B58" s="154"/>
+      <c r="I57" s="135"/>
+    </row>
+    <row r="58" spans="2:9" ht="33.75" thickBot="1">
+      <c r="B58" s="186"/>
       <c r="C58" s="31" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D58" s="43" t="s">
-        <v>84</v>
-      </c>
-      <c r="E58" s="221" t="s">
-        <v>57</v>
-      </c>
-      <c r="F58" s="222"/>
-      <c r="G58" s="222"/>
-      <c r="H58" s="222"/>
-      <c r="I58" s="223"/>
-    </row>
-    <row r="59" spans="2:9" ht="18" thickBot="1">
+        <v>83</v>
+      </c>
+      <c r="E58" s="127" t="s">
+        <v>56</v>
+      </c>
+      <c r="F58" s="128"/>
+      <c r="G58" s="128"/>
+      <c r="H58" s="128"/>
+      <c r="I58" s="129"/>
+    </row>
+    <row r="59" spans="2:9" ht="17.25" thickBot="1">
       <c r="B59" s="78"/>
       <c r="C59" s="79"/>
       <c r="D59" s="80"/>
@@ -10176,135 +11297,165 @@
       <c r="H59" s="100"/>
       <c r="I59" s="96"/>
     </row>
-    <row r="60" spans="2:9" ht="70.3">
-      <c r="B60" s="161" t="s">
-        <v>161</v>
+    <row r="60" spans="2:9" ht="66">
+      <c r="B60" s="187" t="s">
+        <v>158</v>
       </c>
       <c r="C60" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="D60" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="D60" s="44" t="s">
-        <v>86</v>
-      </c>
       <c r="E60" s="42" t="s">
-        <v>87</v>
+        <v>159</v>
       </c>
       <c r="F60" s="72"/>
       <c r="G60" s="72" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H60" s="102"/>
-      <c r="I60" s="123" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="61" spans="2:9" ht="158.15">
-      <c r="B61" s="162"/>
+      <c r="I60" s="133" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" ht="148.5">
+      <c r="B61" s="188"/>
       <c r="C61" s="28" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D61" s="29" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E61" s="30"/>
       <c r="F61" s="73"/>
       <c r="G61" s="73" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H61" s="103"/>
-      <c r="I61" s="124"/>
-    </row>
-    <row r="62" spans="2:9" ht="193.3">
-      <c r="B62" s="162"/>
+      <c r="I61" s="136"/>
+    </row>
+    <row r="62" spans="2:9" ht="181.5">
+      <c r="B62" s="188"/>
       <c r="C62" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="D62" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="E62" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="D62" s="29" t="s">
+      <c r="F62" s="109" t="s">
+        <v>201</v>
+      </c>
+      <c r="G62" s="87" t="s">
+        <v>196</v>
+      </c>
+      <c r="H62" s="112" t="s">
+        <v>188</v>
+      </c>
+      <c r="I62" s="136"/>
+    </row>
+    <row r="63" spans="2:9" ht="33">
+      <c r="B63" s="188"/>
+      <c r="C63" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="E62" s="30" t="s">
+      <c r="D63" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="F62" s="109" t="s">
-        <v>178</v>
-      </c>
-      <c r="G62" s="87" t="s">
-        <v>200</v>
-      </c>
-      <c r="H62" s="112" t="s">
-        <v>192</v>
-      </c>
-      <c r="I62" s="124"/>
-    </row>
-    <row r="63" spans="2:9" ht="35.15">
-      <c r="B63" s="162"/>
-      <c r="C63" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="D63" s="29" t="s">
+      <c r="E63" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="F63" s="30"/>
+      <c r="G63" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="H63" s="104"/>
+      <c r="I63" s="136"/>
+    </row>
+    <row r="64" spans="2:9" ht="82.5">
+      <c r="B64" s="188"/>
+      <c r="C64" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="E63" s="30" t="s">
+      <c r="D64" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="F63" s="30" t="s">
+      <c r="E64" s="30" t="s">
         <v>97</v>
-      </c>
-      <c r="G63" s="30" t="s">
-        <v>171</v>
-      </c>
-      <c r="H63" s="104"/>
-      <c r="I63" s="124"/>
-    </row>
-    <row r="64" spans="2:9" ht="87.9">
-      <c r="B64" s="162"/>
-      <c r="C64" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="D64" s="29" t="s">
-        <v>99</v>
-      </c>
-      <c r="E64" s="30" t="s">
-        <v>100</v>
       </c>
       <c r="F64" s="30"/>
       <c r="G64" s="76" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H64" s="105"/>
-      <c r="I64" s="125"/>
-    </row>
-    <row r="65" spans="2:9" ht="35.6" thickBot="1">
-      <c r="B65" s="163"/>
+      <c r="I64" s="137"/>
+    </row>
+    <row r="65" spans="2:9" ht="33.75" thickBot="1">
+      <c r="B65" s="189"/>
       <c r="C65" s="31" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D65" s="113" t="s">
-        <v>102</v>
-      </c>
-      <c r="E65" s="213" t="s">
-        <v>57</v>
-      </c>
-      <c r="F65" s="214"/>
-      <c r="G65" s="214"/>
-      <c r="H65" s="214"/>
-      <c r="I65" s="215"/>
+        <v>99</v>
+      </c>
+      <c r="E65" s="115" t="s">
+        <v>56</v>
+      </c>
+      <c r="F65" s="116"/>
+      <c r="G65" s="116"/>
+      <c r="H65" s="116"/>
+      <c r="I65" s="117"/>
     </row>
   </sheetData>
   <mergeCells count="76">
-    <mergeCell ref="E65:I65"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="F25:F32"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="E58:I58"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="F46:F51"/>
-    <mergeCell ref="I54:I57"/>
-    <mergeCell ref="I38:I51"/>
-    <mergeCell ref="I23:I35"/>
-    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="F4:F7"/>
+    <mergeCell ref="I60:I64"/>
+    <mergeCell ref="C14:C21"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="C25:C32"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="G25:G32"/>
+    <mergeCell ref="H25:H32"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="B38:B52"/>
+    <mergeCell ref="C38:C41"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="B3:B21"/>
+    <mergeCell ref="B23:B36"/>
+    <mergeCell ref="B60:B65"/>
+    <mergeCell ref="G4:G7"/>
+    <mergeCell ref="H4:H7"/>
+    <mergeCell ref="B54:B58"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="C46:C51"/>
+    <mergeCell ref="E46:E51"/>
+    <mergeCell ref="E52:I52"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="C42:C45"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="D14:D21"/>
+    <mergeCell ref="G11:G13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="H11:H13"/>
+    <mergeCell ref="G14:G21"/>
+    <mergeCell ref="H14:H21"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="I8:I21"/>
     <mergeCell ref="I4:I7"/>
@@ -10321,53 +11472,21 @@
     <mergeCell ref="G9:G10"/>
     <mergeCell ref="G23:G24"/>
     <mergeCell ref="H23:H24"/>
-    <mergeCell ref="D14:D21"/>
-    <mergeCell ref="G11:G13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="H11:H13"/>
-    <mergeCell ref="G14:G21"/>
-    <mergeCell ref="H14:H21"/>
-    <mergeCell ref="B3:B21"/>
-    <mergeCell ref="B23:B36"/>
-    <mergeCell ref="B60:B65"/>
-    <mergeCell ref="G4:G7"/>
-    <mergeCell ref="H4:H7"/>
-    <mergeCell ref="B54:B58"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="C46:C51"/>
-    <mergeCell ref="E46:E51"/>
-    <mergeCell ref="E52:I52"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="C42:C45"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="E65:I65"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="F25:F32"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="E58:I58"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="F46:F51"/>
+    <mergeCell ref="I54:I57"/>
+    <mergeCell ref="I38:I51"/>
+    <mergeCell ref="I23:I35"/>
+    <mergeCell ref="G44:G45"/>
     <mergeCell ref="G33:G34"/>
     <mergeCell ref="H33:H34"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="B38:B52"/>
-    <mergeCell ref="C38:C41"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="F4:F7"/>
-    <mergeCell ref="I60:I64"/>
-    <mergeCell ref="C14:C21"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="C25:C32"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="G25:G32"/>
-    <mergeCell ref="H25:H32"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <hyperlinks>
@@ -10375,24 +11494,28 @@
     <hyperlink ref="I23" r:id="rId2" xr:uid="{48C188C7-7A34-4753-891F-6AFB7AA82563}"/>
     <hyperlink ref="I38" r:id="rId3" xr:uid="{EC9FD26B-5901-42E8-BC47-4FA90402A688}"/>
     <hyperlink ref="I54" r:id="rId4" xr:uid="{DBCE87F3-DC8B-4CB2-B7E7-2C179D59A9DD}"/>
+    <hyperlink ref="E19" r:id="rId5" xr:uid="{E01D2651-D930-4355-A0F8-FA470948D355}"/>
+    <hyperlink ref="E20" r:id="rId6" xr:uid="{E640EF3B-D28F-4372-820C-21868F7D842B}"/>
+    <hyperlink ref="E30" r:id="rId7" xr:uid="{55CB4F8D-79D6-4086-834E-A7B97BDD0E0A}"/>
+    <hyperlink ref="E31" r:id="rId8" xr:uid="{AAAAFA55-A7A9-4D9F-AA48-6828AF2613D3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84E26AAC-33B4-4831-8771-3672B1AF7BF1}">
   <dimension ref="B3:G29"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="4" max="4" width="31.640625" customWidth="1"/>
-    <col min="5" max="5" width="61.78515625" customWidth="1"/>
-    <col min="6" max="6" width="72.640625" customWidth="1"/>
-    <col min="7" max="7" width="38.7109375" customWidth="1"/>
+    <col min="4" max="4" width="31.625" customWidth="1"/>
+    <col min="5" max="5" width="61.75" customWidth="1"/>
+    <col min="6" max="6" width="72.625" customWidth="1"/>
+    <col min="7" max="7" width="38.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:7" ht="18" thickBot="1"/>
-    <row r="4" spans="2:7" ht="18" thickBot="1">
+    <row r="3" spans="2:7" ht="17.25" thickBot="1"/>
+    <row r="4" spans="2:7" ht="17.25" thickBot="1">
       <c r="B4" s="46"/>
       <c r="C4" s="47" t="s">
         <v>0</v>
@@ -10401,17 +11524,17 @@
         <v>1</v>
       </c>
       <c r="E4" s="47" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F4" s="47" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G4" s="48" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="35.15">
-      <c r="B5" s="231" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="33">
+      <c r="B5" s="241" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="54" t="s">
@@ -10421,55 +11544,55 @@
         <v>7</v>
       </c>
       <c r="E5" s="55" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F5" s="56" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G5" s="57"/>
     </row>
     <row r="6" spans="2:7">
-      <c r="B6" s="232"/>
-      <c r="C6" s="239" t="s">
+      <c r="B6" s="242"/>
+      <c r="C6" s="247" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="117" t="s">
+      <c r="D6" s="200" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="120" t="s">
-        <v>106</v>
-      </c>
-      <c r="F6" s="164" t="s">
-        <v>107</v>
-      </c>
-      <c r="G6" s="228"/>
+      <c r="E6" s="125" t="s">
+        <v>103</v>
+      </c>
+      <c r="F6" s="155" t="s">
+        <v>104</v>
+      </c>
+      <c r="G6" s="238"/>
     </row>
     <row r="7" spans="2:7">
-      <c r="B7" s="232"/>
-      <c r="C7" s="240"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="121"/>
-      <c r="F7" s="165"/>
-      <c r="G7" s="229"/>
+      <c r="B7" s="242"/>
+      <c r="C7" s="248"/>
+      <c r="D7" s="201"/>
+      <c r="E7" s="167"/>
+      <c r="F7" s="190"/>
+      <c r="G7" s="239"/>
     </row>
     <row r="8" spans="2:7">
-      <c r="B8" s="232"/>
-      <c r="C8" s="240"/>
-      <c r="D8" s="118"/>
-      <c r="E8" s="121"/>
-      <c r="F8" s="165"/>
-      <c r="G8" s="229"/>
+      <c r="B8" s="242"/>
+      <c r="C8" s="248"/>
+      <c r="D8" s="201"/>
+      <c r="E8" s="167"/>
+      <c r="F8" s="190"/>
+      <c r="G8" s="239"/>
     </row>
     <row r="9" spans="2:7">
-      <c r="B9" s="232"/>
-      <c r="C9" s="244"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="136"/>
-      <c r="F9" s="166"/>
-      <c r="G9" s="230"/>
-    </row>
-    <row r="10" spans="2:7" ht="35.15">
-      <c r="B10" s="232"/>
+      <c r="B9" s="242"/>
+      <c r="C9" s="252"/>
+      <c r="D9" s="219"/>
+      <c r="E9" s="126"/>
+      <c r="F9" s="191"/>
+      <c r="G9" s="240"/>
+    </row>
+    <row r="10" spans="2:7" ht="33">
+      <c r="B10" s="242"/>
       <c r="C10" s="58" t="s">
         <v>16</v>
       </c>
@@ -10478,169 +11601,164 @@
       </c>
       <c r="E10" s="45"/>
       <c r="F10" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="G10" s="52"/>
+    </row>
+    <row r="11" spans="2:7">
+      <c r="B11" s="242"/>
+      <c r="C11" s="247" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="223" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="125" t="s">
+        <v>108</v>
+      </c>
+      <c r="F11" s="229" t="s">
+        <v>120</v>
+      </c>
+      <c r="G11" s="256" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7">
+      <c r="B12" s="242"/>
+      <c r="C12" s="248"/>
+      <c r="D12" s="251"/>
+      <c r="E12" s="167"/>
+      <c r="F12" s="230"/>
+      <c r="G12" s="257"/>
+    </row>
+    <row r="13" spans="2:7" ht="286.7" customHeight="1">
+      <c r="B13" s="242"/>
+      <c r="C13" s="250"/>
+      <c r="D13" s="224"/>
+      <c r="E13" s="126"/>
+      <c r="F13" s="152"/>
+      <c r="G13" s="258"/>
+    </row>
+    <row r="14" spans="2:7" ht="35.1" customHeight="1">
+      <c r="B14" s="242"/>
+      <c r="C14" s="247" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="244" t="s">
+        <v>117</v>
+      </c>
+      <c r="E14" s="125" t="s">
+        <v>109</v>
+      </c>
+      <c r="F14" s="229" t="s">
+        <v>118</v>
+      </c>
+      <c r="G14" s="231" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7">
+      <c r="B15" s="242"/>
+      <c r="C15" s="248"/>
+      <c r="D15" s="245"/>
+      <c r="E15" s="167"/>
+      <c r="F15" s="230"/>
+      <c r="G15" s="232"/>
+    </row>
+    <row r="16" spans="2:7" ht="134.65" customHeight="1">
+      <c r="B16" s="242"/>
+      <c r="C16" s="250"/>
+      <c r="D16" s="246"/>
+      <c r="E16" s="126"/>
+      <c r="F16" s="152"/>
+      <c r="G16" s="233"/>
+    </row>
+    <row r="17" spans="2:7" ht="35.1" customHeight="1">
+      <c r="B17" s="242"/>
+      <c r="C17" s="247" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="125" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" s="200" t="s">
+        <v>105</v>
+      </c>
+      <c r="F17" s="253" t="s">
+        <v>123</v>
+      </c>
+      <c r="G17" s="235" t="s">
         <v>113</v>
       </c>
-      <c r="G10" s="52"/>
-    </row>
-    <row r="11" spans="2:7">
-      <c r="B11" s="232"/>
-      <c r="C11" s="239" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="134" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="120" t="s">
-        <v>111</v>
-      </c>
-      <c r="F11" s="237" t="s">
-        <v>123</v>
-      </c>
-      <c r="G11" s="248" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7">
-      <c r="B12" s="232"/>
-      <c r="C12" s="240"/>
-      <c r="D12" s="243"/>
-      <c r="E12" s="121"/>
-      <c r="F12" s="238"/>
-      <c r="G12" s="249"/>
-    </row>
-    <row r="13" spans="2:7" ht="286.75" customHeight="1">
-      <c r="B13" s="232"/>
-      <c r="C13" s="242"/>
-      <c r="D13" s="135"/>
-      <c r="E13" s="136"/>
-      <c r="F13" s="202"/>
-      <c r="G13" s="250"/>
-    </row>
-    <row r="14" spans="2:7" ht="35.15" customHeight="1">
-      <c r="B14" s="232"/>
-      <c r="C14" s="239" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="234" t="s">
-        <v>120</v>
-      </c>
-      <c r="E14" s="120" t="s">
-        <v>112</v>
-      </c>
-      <c r="F14" s="237" t="s">
-        <v>121</v>
-      </c>
-      <c r="G14" s="251" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7">
-      <c r="B15" s="232"/>
-      <c r="C15" s="240"/>
-      <c r="D15" s="235"/>
-      <c r="E15" s="121"/>
-      <c r="F15" s="238"/>
-      <c r="G15" s="252"/>
-    </row>
-    <row r="16" spans="2:7" ht="134.6" customHeight="1">
-      <c r="B16" s="232"/>
-      <c r="C16" s="242"/>
-      <c r="D16" s="236"/>
-      <c r="E16" s="136"/>
-      <c r="F16" s="202"/>
-      <c r="G16" s="253"/>
-    </row>
-    <row r="17" spans="2:7" ht="35.15" customHeight="1">
-      <c r="B17" s="232"/>
-      <c r="C17" s="239" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="120" t="s">
-        <v>103</v>
-      </c>
-      <c r="E17" s="117" t="s">
-        <v>108</v>
-      </c>
-      <c r="F17" s="245" t="s">
-        <v>126</v>
-      </c>
-      <c r="G17" s="255" t="s">
-        <v>116</v>
-      </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="232"/>
-      <c r="C18" s="240"/>
-      <c r="D18" s="121"/>
-      <c r="E18" s="118"/>
-      <c r="F18" s="246"/>
-      <c r="G18" s="256"/>
+      <c r="B18" s="242"/>
+      <c r="C18" s="248"/>
+      <c r="D18" s="167"/>
+      <c r="E18" s="201"/>
+      <c r="F18" s="254"/>
+      <c r="G18" s="236"/>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="232"/>
-      <c r="C19" s="240"/>
-      <c r="D19" s="121"/>
-      <c r="E19" s="118"/>
-      <c r="F19" s="246"/>
-      <c r="G19" s="256"/>
+      <c r="B19" s="242"/>
+      <c r="C19" s="248"/>
+      <c r="D19" s="167"/>
+      <c r="E19" s="201"/>
+      <c r="F19" s="254"/>
+      <c r="G19" s="236"/>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="232"/>
-      <c r="C20" s="240"/>
-      <c r="D20" s="121"/>
-      <c r="E20" s="118"/>
-      <c r="F20" s="246"/>
-      <c r="G20" s="256"/>
+      <c r="B20" s="242"/>
+      <c r="C20" s="248"/>
+      <c r="D20" s="167"/>
+      <c r="E20" s="201"/>
+      <c r="F20" s="254"/>
+      <c r="G20" s="236"/>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="232"/>
-      <c r="C21" s="240"/>
-      <c r="D21" s="121"/>
-      <c r="E21" s="118"/>
-      <c r="F21" s="246"/>
-      <c r="G21" s="256"/>
+      <c r="B21" s="242"/>
+      <c r="C21" s="248"/>
+      <c r="D21" s="167"/>
+      <c r="E21" s="201"/>
+      <c r="F21" s="254"/>
+      <c r="G21" s="236"/>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="232"/>
-      <c r="C22" s="240"/>
-      <c r="D22" s="121"/>
-      <c r="E22" s="118"/>
-      <c r="F22" s="246"/>
-      <c r="G22" s="256"/>
+      <c r="B22" s="242"/>
+      <c r="C22" s="248"/>
+      <c r="D22" s="167"/>
+      <c r="E22" s="201"/>
+      <c r="F22" s="254"/>
+      <c r="G22" s="236"/>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="232"/>
-      <c r="C23" s="240"/>
-      <c r="D23" s="121"/>
-      <c r="E23" s="118"/>
-      <c r="F23" s="246"/>
-      <c r="G23" s="256"/>
-    </row>
-    <row r="24" spans="2:7" ht="85.75" customHeight="1" thickBot="1">
-      <c r="B24" s="233"/>
-      <c r="C24" s="241"/>
-      <c r="D24" s="177"/>
-      <c r="E24" s="254"/>
-      <c r="F24" s="247"/>
-      <c r="G24" s="257"/>
+      <c r="B23" s="242"/>
+      <c r="C23" s="248"/>
+      <c r="D23" s="167"/>
+      <c r="E23" s="201"/>
+      <c r="F23" s="254"/>
+      <c r="G23" s="236"/>
+    </row>
+    <row r="24" spans="2:7" ht="85.7" customHeight="1" thickBot="1">
+      <c r="B24" s="243"/>
+      <c r="C24" s="249"/>
+      <c r="D24" s="168"/>
+      <c r="E24" s="234"/>
+      <c r="F24" s="255"/>
+      <c r="G24" s="237"/>
     </row>
     <row r="28" spans="2:7">
       <c r="F28" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="2:7">
       <c r="F29" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="E17:E24"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="G17:G24"/>
     <mergeCell ref="G6:G9"/>
     <mergeCell ref="B5:B24"/>
     <mergeCell ref="D17:D24"/>
@@ -10657,27 +11775,32 @@
     <mergeCell ref="F6:F9"/>
     <mergeCell ref="F17:F24"/>
     <mergeCell ref="G11:G13"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="E17:E24"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="G17:G24"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A81E2051-FA1D-49F8-BE92-D7970D343145}">
   <dimension ref="B1:H46"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="3" max="3" width="33.140625" customWidth="1"/>
-    <col min="4" max="4" width="31.2109375" customWidth="1"/>
-    <col min="5" max="5" width="49.5703125" customWidth="1"/>
-    <col min="6" max="6" width="67.2109375" customWidth="1"/>
-    <col min="7" max="7" width="46.140625" customWidth="1"/>
-    <col min="8" max="8" width="63.0703125" customWidth="1"/>
+    <col min="3" max="3" width="33.125" customWidth="1"/>
+    <col min="4" max="4" width="31.25" customWidth="1"/>
+    <col min="5" max="5" width="49.625" customWidth="1"/>
+    <col min="6" max="6" width="67.25" customWidth="1"/>
+    <col min="7" max="7" width="46.125" customWidth="1"/>
+    <col min="8" max="8" width="63.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="18" thickBot="1"/>
-    <row r="2" spans="2:7" ht="18" thickBot="1">
+    <row r="1" spans="2:7" ht="17.25" thickBot="1"/>
+    <row r="2" spans="2:7" ht="17.25" thickBot="1">
       <c r="B2" s="46"/>
       <c r="C2" s="47" t="s">
         <v>0</v>
@@ -10686,226 +11809,232 @@
         <v>1</v>
       </c>
       <c r="E2" s="47" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F2" s="47" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G2" s="48" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" ht="70.3" customHeight="1">
-      <c r="B3" s="161" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="70.349999999999994" customHeight="1">
+      <c r="B3" s="187" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="260" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="271" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="274" t="s">
-        <v>119</v>
-      </c>
-      <c r="E3" s="276" t="s">
+      <c r="D3" s="264" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="266" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3" s="151" t="s">
+        <v>134</v>
+      </c>
+      <c r="G3" s="262" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="83.1" customHeight="1">
+      <c r="B4" s="188"/>
+      <c r="C4" s="261"/>
+      <c r="D4" s="265"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="152"/>
+      <c r="G4" s="263"/>
+    </row>
+    <row r="5" spans="2:7" ht="105.4" customHeight="1">
+      <c r="B5" s="188"/>
+      <c r="C5" s="267" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="206" t="s">
+        <v>122</v>
+      </c>
+      <c r="E5" s="271" t="s">
+        <v>128</v>
+      </c>
+      <c r="F5" s="147" t="s">
         <v>124</v>
       </c>
-      <c r="F3" s="201" t="s">
-        <v>137</v>
-      </c>
-      <c r="G3" s="272" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="83.15" customHeight="1">
-      <c r="B4" s="162"/>
-      <c r="C4" s="264"/>
-      <c r="D4" s="275"/>
-      <c r="E4" s="141"/>
-      <c r="F4" s="202"/>
-      <c r="G4" s="273"/>
-    </row>
-    <row r="5" spans="2:7" ht="105.45" customHeight="1">
-      <c r="B5" s="162"/>
-      <c r="C5" s="262" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="175" t="s">
+      <c r="G5" s="268" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7">
+      <c r="B6" s="188"/>
+      <c r="C6" s="275"/>
+      <c r="D6" s="274"/>
+      <c r="E6" s="272"/>
+      <c r="F6" s="227"/>
+      <c r="G6" s="269"/>
+    </row>
+    <row r="7" spans="2:7">
+      <c r="B7" s="188"/>
+      <c r="C7" s="275"/>
+      <c r="D7" s="274"/>
+      <c r="E7" s="272"/>
+      <c r="F7" s="227"/>
+      <c r="G7" s="269"/>
+    </row>
+    <row r="8" spans="2:7">
+      <c r="B8" s="188"/>
+      <c r="C8" s="275"/>
+      <c r="D8" s="274"/>
+      <c r="E8" s="272"/>
+      <c r="F8" s="227"/>
+      <c r="G8" s="269"/>
+    </row>
+    <row r="9" spans="2:7">
+      <c r="B9" s="188"/>
+      <c r="C9" s="275"/>
+      <c r="D9" s="274"/>
+      <c r="E9" s="272"/>
+      <c r="F9" s="227"/>
+      <c r="G9" s="269"/>
+    </row>
+    <row r="10" spans="2:7">
+      <c r="B10" s="188"/>
+      <c r="C10" s="275"/>
+      <c r="D10" s="274"/>
+      <c r="E10" s="272"/>
+      <c r="F10" s="227"/>
+      <c r="G10" s="269"/>
+    </row>
+    <row r="11" spans="2:7">
+      <c r="B11" s="188"/>
+      <c r="C11" s="275"/>
+      <c r="D11" s="274"/>
+      <c r="E11" s="272"/>
+      <c r="F11" s="227"/>
+      <c r="G11" s="269"/>
+    </row>
+    <row r="12" spans="2:7">
+      <c r="B12" s="188"/>
+      <c r="C12" s="261"/>
+      <c r="D12" s="207"/>
+      <c r="E12" s="273"/>
+      <c r="F12" s="148"/>
+      <c r="G12" s="270"/>
+    </row>
+    <row r="13" spans="2:7" ht="138.94999999999999" customHeight="1">
+      <c r="B13" s="188"/>
+      <c r="C13" s="267" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="206" t="s">
+        <v>126</v>
+      </c>
+      <c r="E13" s="200" t="s">
         <v>125</v>
       </c>
-      <c r="E5" s="258" t="s">
+      <c r="F13" s="208" t="s">
+        <v>127</v>
+      </c>
+      <c r="G13" s="279" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7">
+      <c r="B14" s="188"/>
+      <c r="C14" s="261"/>
+      <c r="D14" s="207"/>
+      <c r="E14" s="202"/>
+      <c r="F14" s="209"/>
+      <c r="G14" s="270"/>
+    </row>
+    <row r="15" spans="2:7" ht="95.65" customHeight="1">
+      <c r="B15" s="188"/>
+      <c r="C15" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="63" t="s">
+        <v>132</v>
+      </c>
+      <c r="G15" s="64" t="s">
         <v>131</v>
       </c>
-      <c r="F5" s="139" t="s">
-        <v>127</v>
-      </c>
-      <c r="G5" s="277" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7">
-      <c r="B6" s="162"/>
-      <c r="C6" s="263"/>
-      <c r="D6" s="261"/>
-      <c r="E6" s="259"/>
-      <c r="F6" s="140"/>
-      <c r="G6" s="278"/>
-    </row>
-    <row r="7" spans="2:7">
-      <c r="B7" s="162"/>
-      <c r="C7" s="263"/>
-      <c r="D7" s="261"/>
-      <c r="E7" s="259"/>
-      <c r="F7" s="140"/>
-      <c r="G7" s="278"/>
-    </row>
-    <row r="8" spans="2:7">
-      <c r="B8" s="162"/>
-      <c r="C8" s="263"/>
-      <c r="D8" s="261"/>
-      <c r="E8" s="259"/>
-      <c r="F8" s="140"/>
-      <c r="G8" s="278"/>
-    </row>
-    <row r="9" spans="2:7">
-      <c r="B9" s="162"/>
-      <c r="C9" s="263"/>
-      <c r="D9" s="261"/>
-      <c r="E9" s="259"/>
-      <c r="F9" s="140"/>
-      <c r="G9" s="278"/>
-    </row>
-    <row r="10" spans="2:7">
-      <c r="B10" s="162"/>
-      <c r="C10" s="263"/>
-      <c r="D10" s="261"/>
-      <c r="E10" s="259"/>
-      <c r="F10" s="140"/>
-      <c r="G10" s="278"/>
-    </row>
-    <row r="11" spans="2:7">
-      <c r="B11" s="162"/>
-      <c r="C11" s="263"/>
-      <c r="D11" s="261"/>
-      <c r="E11" s="259"/>
-      <c r="F11" s="140"/>
-      <c r="G11" s="278"/>
-    </row>
-    <row r="12" spans="2:7">
-      <c r="B12" s="162"/>
-      <c r="C12" s="264"/>
-      <c r="D12" s="176"/>
-      <c r="E12" s="260"/>
-      <c r="F12" s="141"/>
-      <c r="G12" s="269"/>
-    </row>
-    <row r="13" spans="2:7" ht="138.9" customHeight="1">
-      <c r="B13" s="162"/>
-      <c r="C13" s="262" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="175" t="s">
-        <v>129</v>
-      </c>
-      <c r="E13" s="117" t="s">
-        <v>128</v>
-      </c>
-      <c r="F13" s="145" t="s">
-        <v>130</v>
-      </c>
-      <c r="G13" s="268" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7">
-      <c r="B14" s="162"/>
-      <c r="C14" s="264"/>
-      <c r="D14" s="176"/>
-      <c r="E14" s="170"/>
-      <c r="F14" s="146"/>
-      <c r="G14" s="269"/>
-    </row>
-    <row r="15" spans="2:7" ht="95.6" customHeight="1">
-      <c r="B15" s="162"/>
-      <c r="C15" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="F15" s="63" t="s">
-        <v>135</v>
-      </c>
-      <c r="G15" s="64" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" ht="18" thickBot="1">
-      <c r="B16" s="163"/>
+    </row>
+    <row r="16" spans="2:7" ht="17.25" thickBot="1">
+      <c r="B16" s="189"/>
       <c r="C16" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="E16" s="276" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="265" t="s">
-        <v>57</v>
-      </c>
-      <c r="F16" s="266"/>
-      <c r="G16" s="267"/>
-    </row>
-    <row r="32" ht="18" thickBot="1"/>
+      <c r="F16" s="277"/>
+      <c r="G16" s="278"/>
+    </row>
+    <row r="32" ht="17.25" thickBot="1"/>
     <row r="33" spans="8:8">
-      <c r="H33" s="123" t="s">
-        <v>37</v>
+      <c r="H33" s="133" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="8:8">
-      <c r="H34" s="124"/>
+      <c r="H34" s="136"/>
     </row>
     <row r="35" spans="8:8">
-      <c r="H35" s="124"/>
+      <c r="H35" s="136"/>
     </row>
     <row r="36" spans="8:8">
-      <c r="H36" s="124"/>
+      <c r="H36" s="136"/>
     </row>
     <row r="37" spans="8:8">
-      <c r="H37" s="124"/>
+      <c r="H37" s="136"/>
     </row>
     <row r="38" spans="8:8">
-      <c r="H38" s="124"/>
+      <c r="H38" s="136"/>
     </row>
     <row r="39" spans="8:8">
-      <c r="H39" s="124"/>
+      <c r="H39" s="136"/>
     </row>
     <row r="40" spans="8:8">
-      <c r="H40" s="124"/>
+      <c r="H40" s="136"/>
     </row>
     <row r="41" spans="8:8">
-      <c r="H41" s="124"/>
+      <c r="H41" s="136"/>
     </row>
     <row r="42" spans="8:8">
-      <c r="H42" s="125"/>
+      <c r="H42" s="137"/>
     </row>
     <row r="43" spans="8:8">
-      <c r="H43" s="270" t="s">
-        <v>50</v>
+      <c r="H43" s="259" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="44" spans="8:8">
-      <c r="H44" s="125"/>
+      <c r="H44" s="137"/>
     </row>
     <row r="45" spans="8:8">
       <c r="H45" s="59" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="46" spans="8:8" ht="18" thickBot="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="46" spans="8:8" ht="17.25" thickBot="1">
       <c r="H46" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B3:B16"/>
+    <mergeCell ref="E5:E12"/>
+    <mergeCell ref="D5:D12"/>
+    <mergeCell ref="C5:C12"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="G13:G14"/>
     <mergeCell ref="H33:H42"/>
     <mergeCell ref="H43:H44"/>
     <mergeCell ref="C3:C4"/>
@@ -10919,12 +12048,6 @@
     <mergeCell ref="E13:E14"/>
     <mergeCell ref="F13:F14"/>
     <mergeCell ref="G5:G12"/>
-    <mergeCell ref="B3:B16"/>
-    <mergeCell ref="E5:E12"/>
-    <mergeCell ref="D5:D12"/>
-    <mergeCell ref="C5:C12"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="G13:G14"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <hyperlinks>
@@ -10936,19 +12059,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04021987-DBDC-46EB-B15B-B1DD935E8DAA}">
   <dimension ref="B1:G17"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="4" max="4" width="35.42578125" customWidth="1"/>
-    <col min="5" max="5" width="43.78515625" customWidth="1"/>
+    <col min="4" max="4" width="35.375" customWidth="1"/>
+    <col min="5" max="5" width="43.75" customWidth="1"/>
     <col min="6" max="6" width="81" customWidth="1"/>
-    <col min="7" max="7" width="59.42578125" customWidth="1"/>
+    <col min="7" max="7" width="59.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="18" thickBot="1"/>
-    <row r="2" spans="2:7" ht="18" thickBot="1">
+    <row r="1" spans="2:7" ht="17.25" thickBot="1"/>
+    <row r="2" spans="2:7" ht="17.25" thickBot="1">
       <c r="B2" s="46"/>
       <c r="C2" s="47" t="s">
         <v>0</v>
@@ -10957,184 +12080,174 @@
         <v>1</v>
       </c>
       <c r="E2" s="47" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F2" s="47" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G2" s="48" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" ht="35.15" customHeight="1">
-      <c r="B3" s="161" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="35.1" customHeight="1">
+      <c r="B3" s="187" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="260" t="s">
         <v>58</v>
       </c>
-      <c r="C3" s="271" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" s="281" t="s">
+      <c r="D3" s="286" t="s">
+        <v>139</v>
+      </c>
+      <c r="E3" s="213" t="s">
+        <v>135</v>
+      </c>
+      <c r="F3" s="151" t="s">
+        <v>144</v>
+      </c>
+      <c r="G3" s="284" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="182.1" customHeight="1">
+      <c r="B4" s="188"/>
+      <c r="C4" s="275"/>
+      <c r="D4" s="287"/>
+      <c r="E4" s="131"/>
+      <c r="F4" s="152"/>
+      <c r="G4" s="285"/>
+    </row>
+    <row r="5" spans="2:7">
+      <c r="B5" s="188"/>
+      <c r="C5" s="275"/>
+      <c r="D5" s="214" t="s">
+        <v>137</v>
+      </c>
+      <c r="E5" s="170" t="s">
+        <v>138</v>
+      </c>
+      <c r="F5" s="155" t="s">
+        <v>145</v>
+      </c>
+      <c r="G5" s="256" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="86.1" customHeight="1">
+      <c r="B6" s="188"/>
+      <c r="C6" s="261"/>
+      <c r="D6" s="215"/>
+      <c r="E6" s="124"/>
+      <c r="F6" s="156"/>
+      <c r="G6" s="291"/>
+    </row>
+    <row r="7" spans="2:7">
+      <c r="B7" s="188"/>
+      <c r="C7" s="267" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="206" t="s">
+        <v>136</v>
+      </c>
+      <c r="E7" s="120" t="s">
+        <v>140</v>
+      </c>
+      <c r="F7" s="155" t="s">
+        <v>141</v>
+      </c>
+      <c r="G7" s="290" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" ht="102.95" customHeight="1">
+      <c r="B8" s="188"/>
+      <c r="C8" s="275"/>
+      <c r="D8" s="207"/>
+      <c r="E8" s="122"/>
+      <c r="F8" s="156"/>
+      <c r="G8" s="290"/>
+    </row>
+    <row r="9" spans="2:7">
+      <c r="B9" s="188"/>
+      <c r="C9" s="275"/>
+      <c r="D9" s="197" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="125" t="s">
         <v>142</v>
       </c>
-      <c r="E3" s="155" t="s">
-        <v>138</v>
-      </c>
-      <c r="F3" s="201" t="s">
-        <v>147</v>
-      </c>
-      <c r="G3" s="279" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="182.15" customHeight="1">
-      <c r="B4" s="162"/>
-      <c r="C4" s="263"/>
-      <c r="D4" s="282"/>
-      <c r="E4" s="144"/>
-      <c r="F4" s="202"/>
-      <c r="G4" s="280"/>
-    </row>
-    <row r="5" spans="2:7">
-      <c r="B5" s="162"/>
-      <c r="C5" s="263"/>
-      <c r="D5" s="156" t="s">
-        <v>140</v>
-      </c>
-      <c r="E5" s="181" t="s">
-        <v>141</v>
-      </c>
-      <c r="F5" s="164" t="s">
-        <v>148</v>
-      </c>
-      <c r="G5" s="248" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="86.15" customHeight="1">
-      <c r="B6" s="162"/>
-      <c r="C6" s="264"/>
-      <c r="D6" s="157"/>
-      <c r="E6" s="130"/>
-      <c r="F6" s="174"/>
-      <c r="G6" s="286"/>
-    </row>
-    <row r="7" spans="2:7">
-      <c r="B7" s="162"/>
-      <c r="C7" s="262" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" s="175" t="s">
-        <v>139</v>
-      </c>
-      <c r="E7" s="218" t="s">
+      <c r="F9" s="138" t="s">
+        <v>190</v>
+      </c>
+      <c r="G9" s="290"/>
+    </row>
+    <row r="10" spans="2:7" ht="175.35" customHeight="1">
+      <c r="B10" s="188"/>
+      <c r="C10" s="261"/>
+      <c r="D10" s="198"/>
+      <c r="E10" s="126"/>
+      <c r="F10" s="139"/>
+      <c r="G10" s="291"/>
+    </row>
+    <row r="11" spans="2:7" ht="17.649999999999999" customHeight="1">
+      <c r="B11" s="188"/>
+      <c r="C11" s="267" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" s="280" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="200" t="s">
         <v>143</v>
       </c>
-      <c r="F7" s="164" t="s">
-        <v>144</v>
-      </c>
-      <c r="G7" s="285" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" ht="102.9" customHeight="1">
-      <c r="B8" s="162"/>
-      <c r="C8" s="263"/>
-      <c r="D8" s="176"/>
-      <c r="E8" s="220"/>
-      <c r="F8" s="174"/>
-      <c r="G8" s="285"/>
-    </row>
-    <row r="9" spans="2:7">
-      <c r="B9" s="162"/>
-      <c r="C9" s="263"/>
-      <c r="D9" s="148" t="s">
-        <v>68</v>
-      </c>
-      <c r="E9" s="120" t="s">
-        <v>145</v>
-      </c>
-      <c r="F9" s="226" t="s">
-        <v>194</v>
-      </c>
-      <c r="G9" s="285"/>
-    </row>
-    <row r="10" spans="2:7" ht="175.3" customHeight="1">
-      <c r="B10" s="162"/>
-      <c r="C10" s="264"/>
-      <c r="D10" s="149"/>
-      <c r="E10" s="136"/>
-      <c r="F10" s="227"/>
-      <c r="G10" s="286"/>
-    </row>
-    <row r="11" spans="2:7" ht="17.600000000000001" customHeight="1">
-      <c r="B11" s="162"/>
-      <c r="C11" s="262" t="s">
-        <v>69</v>
-      </c>
-      <c r="D11" s="287" t="s">
-        <v>70</v>
-      </c>
-      <c r="E11" s="117" t="s">
-        <v>146</v>
-      </c>
-      <c r="F11" s="206" t="s">
-        <v>202</v>
-      </c>
-      <c r="G11" s="283"/>
-    </row>
-    <row r="12" spans="2:7" ht="28.3" customHeight="1">
-      <c r="B12" s="162"/>
-      <c r="C12" s="263"/>
-      <c r="D12" s="288"/>
-      <c r="E12" s="118"/>
-      <c r="F12" s="207"/>
-      <c r="G12" s="283"/>
-    </row>
-    <row r="13" spans="2:7" ht="42.45" customHeight="1">
-      <c r="B13" s="162"/>
-      <c r="C13" s="263"/>
-      <c r="D13" s="288"/>
-      <c r="E13" s="118"/>
-      <c r="F13" s="207"/>
-      <c r="G13" s="283"/>
+      <c r="F11" s="158" t="s">
+        <v>198</v>
+      </c>
+      <c r="G11" s="288"/>
+    </row>
+    <row r="12" spans="2:7" ht="28.35" customHeight="1">
+      <c r="B12" s="188"/>
+      <c r="C12" s="275"/>
+      <c r="D12" s="281"/>
+      <c r="E12" s="201"/>
+      <c r="F12" s="159"/>
+      <c r="G12" s="288"/>
+    </row>
+    <row r="13" spans="2:7" ht="42.4" customHeight="1">
+      <c r="B13" s="188"/>
+      <c r="C13" s="275"/>
+      <c r="D13" s="281"/>
+      <c r="E13" s="201"/>
+      <c r="F13" s="159"/>
+      <c r="G13" s="288"/>
     </row>
     <row r="14" spans="2:7">
-      <c r="B14" s="162"/>
-      <c r="C14" s="263"/>
-      <c r="D14" s="288"/>
-      <c r="E14" s="118"/>
-      <c r="F14" s="207"/>
-      <c r="G14" s="283"/>
+      <c r="B14" s="188"/>
+      <c r="C14" s="275"/>
+      <c r="D14" s="281"/>
+      <c r="E14" s="201"/>
+      <c r="F14" s="159"/>
+      <c r="G14" s="288"/>
     </row>
     <row r="15" spans="2:7">
-      <c r="B15" s="162"/>
-      <c r="C15" s="263"/>
-      <c r="D15" s="288"/>
-      <c r="E15" s="118"/>
-      <c r="F15" s="207"/>
-      <c r="G15" s="283"/>
-    </row>
-    <row r="16" spans="2:7" ht="115.3" customHeight="1" thickBot="1">
-      <c r="B16" s="163"/>
-      <c r="C16" s="290"/>
-      <c r="D16" s="289"/>
-      <c r="E16" s="254"/>
-      <c r="F16" s="208"/>
-      <c r="G16" s="284"/>
-    </row>
-    <row r="17" ht="17.600000000000001" customHeight="1"/>
+      <c r="B15" s="188"/>
+      <c r="C15" s="275"/>
+      <c r="D15" s="281"/>
+      <c r="E15" s="201"/>
+      <c r="F15" s="159"/>
+      <c r="G15" s="288"/>
+    </row>
+    <row r="16" spans="2:7" ht="115.35" customHeight="1" thickBot="1">
+      <c r="B16" s="189"/>
+      <c r="C16" s="283"/>
+      <c r="D16" s="282"/>
+      <c r="E16" s="234"/>
+      <c r="F16" s="160"/>
+      <c r="G16" s="289"/>
+    </row>
+    <row r="17" ht="17.649999999999999" customHeight="1"/>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="B3:B16"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="D11:D16"/>
-    <mergeCell ref="F11:F16"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="C11:C16"/>
-    <mergeCell ref="C7:C10"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="F5:F6"/>
@@ -11148,26 +12261,36 @@
     <mergeCell ref="E11:E16"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="F7:F8"/>
+    <mergeCell ref="B3:B16"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="D11:D16"/>
+    <mergeCell ref="F11:F16"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="C11:C16"/>
+    <mergeCell ref="C7:C10"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70E3C3FB-0E54-4ECF-BDE5-7A10C9F7ACB4}">
   <dimension ref="B1:G7"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="3" max="3" width="13.5" customWidth="1"/>
-    <col min="4" max="4" width="34.140625" customWidth="1"/>
-    <col min="5" max="5" width="47.5703125" customWidth="1"/>
-    <col min="6" max="6" width="69.35546875" customWidth="1"/>
-    <col min="7" max="7" width="55.640625" customWidth="1"/>
+    <col min="4" max="4" width="34.125" customWidth="1"/>
+    <col min="5" max="5" width="47.625" customWidth="1"/>
+    <col min="6" max="6" width="69.375" customWidth="1"/>
+    <col min="7" max="7" width="55.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="18" thickBot="1"/>
-    <row r="2" spans="2:7" ht="18" thickBot="1">
+    <row r="1" spans="2:7" ht="17.25" thickBot="1"/>
+    <row r="2" spans="2:7" ht="17.25" thickBot="1">
       <c r="B2" s="46"/>
       <c r="C2" s="47" t="s">
         <v>0</v>
@@ -11176,86 +12299,86 @@
         <v>1</v>
       </c>
       <c r="E2" s="47" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F2" s="47" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G2" s="48" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" ht="103.3" customHeight="1">
-      <c r="B3" s="161" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="103.35" customHeight="1">
+      <c r="B3" s="187" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="D3" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="41" t="s">
+      <c r="E3" s="42" t="s">
         <v>78</v>
       </c>
-      <c r="E3" s="42" t="s">
-        <v>79</v>
-      </c>
       <c r="F3" s="69" t="s">
+        <v>153</v>
+      </c>
+      <c r="G3" s="70" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="69.95" customHeight="1">
+      <c r="B4" s="188"/>
+      <c r="C4" s="267" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="71" t="s">
+        <v>152</v>
+      </c>
+      <c r="E4" s="130" t="s">
+        <v>154</v>
+      </c>
+      <c r="F4" s="147" t="s">
+        <v>155</v>
+      </c>
+      <c r="G4" s="256" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="98.1" customHeight="1">
+      <c r="B5" s="188"/>
+      <c r="C5" s="261"/>
+      <c r="D5" s="67" t="s">
+        <v>151</v>
+      </c>
+      <c r="E5" s="131"/>
+      <c r="F5" s="148"/>
+      <c r="G5" s="291"/>
+    </row>
+    <row r="6" spans="2:7" ht="125.25" customHeight="1">
+      <c r="B6" s="188"/>
+      <c r="C6" s="267" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" s="280" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="292" t="s">
+        <v>163</v>
+      </c>
+      <c r="F6" s="147" t="s">
         <v>156</v>
       </c>
-      <c r="G3" s="70" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="69.900000000000006" customHeight="1">
-      <c r="B4" s="162"/>
-      <c r="C4" s="262" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="71" t="s">
-        <v>155</v>
-      </c>
-      <c r="E4" s="147" t="s">
-        <v>157</v>
-      </c>
-      <c r="F4" s="139" t="s">
-        <v>158</v>
-      </c>
-      <c r="G4" s="248" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="98.15" customHeight="1">
-      <c r="B5" s="162"/>
-      <c r="C5" s="264"/>
-      <c r="D5" s="67" t="s">
-        <v>154</v>
-      </c>
-      <c r="E5" s="144"/>
-      <c r="F5" s="141"/>
-      <c r="G5" s="286"/>
-    </row>
-    <row r="6" spans="2:7" ht="125.25" customHeight="1">
-      <c r="B6" s="162"/>
-      <c r="C6" s="262" t="s">
-        <v>82</v>
-      </c>
-      <c r="D6" s="287" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" s="291" t="s">
-        <v>166</v>
-      </c>
-      <c r="F6" s="139" t="s">
-        <v>159</v>
-      </c>
-      <c r="G6" s="293"/>
-    </row>
-    <row r="7" spans="2:7" ht="18" thickBot="1">
-      <c r="B7" s="163"/>
-      <c r="C7" s="290"/>
-      <c r="D7" s="289"/>
-      <c r="E7" s="171"/>
-      <c r="F7" s="292"/>
-      <c r="G7" s="294"/>
+      <c r="G6" s="294"/>
+    </row>
+    <row r="7" spans="2:7" ht="17.25" thickBot="1">
+      <c r="B7" s="189"/>
+      <c r="C7" s="283"/>
+      <c r="D7" s="282"/>
+      <c r="E7" s="203"/>
+      <c r="F7" s="293"/>
+      <c r="G7" s="295"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -11275,20 +12398,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECA8A220-10DE-488F-966E-CC2D9B9E3E1E}">
   <dimension ref="B1:G12"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="3" max="3" width="13.92578125" customWidth="1"/>
-    <col min="4" max="4" width="21.5703125" customWidth="1"/>
-    <col min="5" max="5" width="26.35546875" customWidth="1"/>
-    <col min="6" max="6" width="53.92578125" customWidth="1"/>
-    <col min="7" max="7" width="35.640625" customWidth="1"/>
+    <col min="3" max="3" width="13.875" customWidth="1"/>
+    <col min="4" max="4" width="21.625" customWidth="1"/>
+    <col min="5" max="5" width="26.375" customWidth="1"/>
+    <col min="6" max="6" width="53.875" customWidth="1"/>
+    <col min="7" max="7" width="35.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="18" thickBot="1"/>
-    <row r="2" spans="2:7" ht="18" thickBot="1">
+    <row r="1" spans="2:7" ht="17.25" thickBot="1"/>
+    <row r="2" spans="2:7" ht="17.25" thickBot="1">
       <c r="B2" s="46"/>
       <c r="C2" s="47" t="s">
         <v>0</v>
@@ -11297,121 +12420,121 @@
         <v>1</v>
       </c>
       <c r="E2" s="47" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F2" s="47" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G2" s="48" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" ht="165.45" customHeight="1">
-      <c r="B3" s="161" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="165.4" customHeight="1">
+      <c r="B3" s="187" t="s">
+        <v>158</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" s="42" t="s">
+        <v>159</v>
+      </c>
+      <c r="F3" s="72" t="s">
+        <v>170</v>
+      </c>
+      <c r="G3" s="68"/>
+    </row>
+    <row r="4" spans="2:7" ht="162.94999999999999" customHeight="1">
+      <c r="B4" s="188"/>
+      <c r="C4" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="77" t="s">
+        <v>165</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="F4" s="73" t="s">
+        <v>169</v>
+      </c>
+      <c r="G4" s="65"/>
+    </row>
+    <row r="5" spans="2:7" ht="176.65" customHeight="1">
+      <c r="B5" s="188"/>
+      <c r="C5" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="F5" s="87" t="s">
+        <v>196</v>
+      </c>
+      <c r="G5" s="114" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="94.35" customHeight="1">
+      <c r="B6" s="188"/>
+      <c r="C6" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="F6" s="75" t="s">
+        <v>197</v>
+      </c>
+      <c r="G6" s="66"/>
+    </row>
+    <row r="7" spans="2:7" ht="82.5">
+      <c r="B7" s="188"/>
+      <c r="C7" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="F7" s="76" t="s">
         <v>161</v>
       </c>
-      <c r="C3" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="D3" s="44" t="s">
-        <v>86</v>
-      </c>
-      <c r="E3" s="42" t="s">
-        <v>162</v>
-      </c>
-      <c r="F3" s="72" t="s">
-        <v>173</v>
-      </c>
-      <c r="G3" s="68"/>
-    </row>
-    <row r="4" spans="2:7" ht="162.9" customHeight="1">
-      <c r="B4" s="162"/>
-      <c r="C4" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" s="77" t="s">
-        <v>168</v>
-      </c>
-      <c r="E4" s="30" t="s">
-        <v>167</v>
-      </c>
-      <c r="F4" s="73" t="s">
-        <v>172</v>
-      </c>
-      <c r="G4" s="65"/>
-    </row>
-    <row r="5" spans="2:7" ht="176.6" customHeight="1">
-      <c r="B5" s="162"/>
-      <c r="C5" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="E5" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="F5" s="87" t="s">
-        <v>200</v>
-      </c>
-      <c r="G5" s="295" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="94.3" customHeight="1">
-      <c r="B6" s="162"/>
-      <c r="C6" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="E6" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="F6" s="75" t="s">
-        <v>201</v>
-      </c>
-      <c r="G6" s="66"/>
-    </row>
-    <row r="7" spans="2:7" ht="87.9">
-      <c r="B7" s="162"/>
-      <c r="C7" s="28" t="s">
+      <c r="G7" s="74"/>
+    </row>
+    <row r="8" spans="2:7" ht="17.25" thickBot="1">
+      <c r="B8" s="189"/>
+      <c r="C8" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="D7" s="29" t="s">
+      <c r="D8" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="E7" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="F7" s="76" t="s">
-        <v>164</v>
-      </c>
-      <c r="G7" s="74"/>
-    </row>
-    <row r="8" spans="2:7" ht="18" thickBot="1">
-      <c r="B8" s="163"/>
-      <c r="C8" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="D8" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="E8" s="213" t="s">
-        <v>57</v>
-      </c>
-      <c r="F8" s="214"/>
-      <c r="G8" s="215"/>
+      <c r="E8" s="115" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="116"/>
+      <c r="G8" s="117"/>
     </row>
     <row r="11" spans="2:7">
       <c r="F11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="2:7">
       <c r="F12" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/16기_스타트캠프_강사 가이드 문서.xlsx
+++ b/16기_스타트캠프_강사 가이드 문서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ed\ai-onboarding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{22DD5019-E82A-4B73-8349-EA8DBA0ADA4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8EEA616-8E1A-4528-80BC-9E1149844B97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="15" windowWidth="28770" windowHeight="15450" activeTab="1" xr2:uid="{FD3BB604-1650-4EBB-871F-9010366B35B1}"/>
+    <workbookView xWindow="30" yWindow="30" windowWidth="28770" windowHeight="15450" activeTab="1" xr2:uid="{FD3BB604-1650-4EBB-871F-9010366B35B1}"/>
   </bookViews>
   <sheets>
     <sheet name="교육 목표 및 방향" sheetId="7" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="204">
   <si>
     <t>시간</t>
   </si>
@@ -1627,40 +1627,6 @@
         <sz val="11"/>
         <color rgb="FF2B2E3A"/>
         <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>안내</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">OpenAI API Key </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사용</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
       </rPr>
@@ -4223,10 +4189,6 @@
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">* 발표 진행시 AI Studio의 화면 공유(Zoom) 을 활용해주세요. </t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">* </t>
     </r>
@@ -5460,10 +5422,6 @@
   </si>
   <si>
     <t>VS Code Copilot BYOK 설정 가이드</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Render 서비스 배포 가이드 문서</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
@@ -5601,179 +5559,6 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>개발 의뢰 문서에 언급된</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>정해진 스펙 외에는 사용할 수 없음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>을 안내해주세요.  (MySQL 불가, Flask 불가, Express.js 불가, React 불가 등)</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">* 욕심내서 많은 내용을 시도하려고 하진 않는지 확인 부탁드립니다. 
-* </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>왜 MVP를 이렇게 결정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">했는지, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>역할 분배는 어떻게 했는지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>일정에 있어 무리는 없는지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">를 각 팀들과 회의 하여 체크해주시기 바랍니다. 
-* 추가 데이터 수집은 하지 않고 주어진 데이터 기반으로 할 수 있도록 안내해주세요. 
-* 개발 진행하기 앞서 </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Copilot Ask모드 활용만 허가받은 상태</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">이기에 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>프로젝트를 어떻게 시작할지 ChatGPT로 확인하고 시작할 수 있도록 교육생들 안내</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 부탁드립니다. 
-  - AI 를 활용하여 프로젝트 시작하는 방법 (FastAPI 시작하는 방법, Vue 시작하는 방법 등등)을 조사하고 시작할 수 있도록 안내해주세요. 
-* Claude Code, Codex와 같은 툴로 한 번에 끝내려는 교육생이 없도록 감독이 필요합니다. 
-* </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>개발 의뢰 문서에 언급된 정해진 스펙 외에는 사용할 수 없음</t>
     </r>
     <r>
@@ -5803,10 +5588,6 @@
   </si>
   <si>
     <t>https://github.com/mulcamp-ed/ai-onboarding/tree/master/Day04</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://github.com/mulcamp-ed/ai-onboarding/tree/master/Day05/%EB%B0%B0%ED%8F%AC%EC%9A%A9/%EA%B0%80%EC%9D%B4%EB%93%9C%EB%AC%B8%EC%84%9C</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
@@ -6299,6 +6080,1195 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">* ask </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모드를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">통해 진행하므로 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제안하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내용을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자세히</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>읽어보고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>추가할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있도록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지도해주시기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>바랍니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. 
+  - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비전공</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>트랙의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>경우</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ask </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모드로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개발이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>어려울</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있으니</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>강사님들이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>옆에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>많이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>도와줄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있도록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부탁드립니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. 
+  - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>막히는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부분이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>배워야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부분이고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>것을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>알면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시킬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있다로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>교육생들</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마인드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>셋팅도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>진행해주세요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.
+* git </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사용을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잊지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않도록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>계속</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부탁드립니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">* 욕심내서 많은 내용을 시도하려고 하진 않는지 확인 부탁드립니다. 
+* </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>왜 MVP를 이렇게 결정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">했는지, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>역할 분배는 어떻게 했는지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>일정에 있어 무리는 없는지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">를 각 팀들과 회의 하여 체크해주시기 바랍니다. 
+* 추가 데이터 수집은 하지 않고 주어진 데이터 기반으로 할 수 있도록 안내해주세요. 
+* 개발 진행하기 앞서 </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Copilot Ask모드 활용만 허가받은 상태</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">이기에 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>프로젝트를 어떻게 시작할지 AI로 확인하고 시작할 수 있도록 교육생들 안내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 부탁드립니다. 
+  - AI 를 활용하여 프로젝트 시작하는 방법 (FastAPI 시작하는 방법, Vue 시작하는 방법 등등)을 조사하고 시작할 수 있도록 안내해주세요. 
+* Claude Code, Codex와 같은 툴로 한 번에 끝내려는 교육생이 없도록 감독이 필요합니다. 
+* </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>개발 의뢰 문서에 언급된</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>정해진 스펙 외에는 사용할 수 없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>을 안내해주세요.  (MySQL 불가, Flask 불가, Express.js 불가, React 불가 등)</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
@@ -6355,7 +7325,8 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">코드 스타일, 커뮤니케이션 방식) 에 대해 어느 정도 결정하고 진행할 수 있도록 유도 부탁해주세요. </t>
+      <t xml:space="preserve">코드 스타일, 커뮤니케이션 방식) 에 대해 어느 정도 결정하고 진행할 수 있도록 유도 부탁해주세요. 
+ </t>
     </r>
     <r>
       <rPr>
@@ -6673,7 +7644,7 @@
         <charset val="129"/>
       </rPr>
       <t xml:space="preserve">최대한 OpenAI API 키를 배포하지 않고 무료 사용량을 소모하도록 안내해주세요. 
-  - 무료 </t>
+ </t>
     </r>
     <r>
       <rPr>
@@ -6684,7 +7655,7 @@
         <charset val="129"/>
       </rPr>
       <t xml:space="preserve">
-  - 무료 사용량을 다 사용한 경우 개발한 내용을 문서로 정리할 수 있도록 유도 부탁드립니다. 
+  - 무료 사용량을 다 사용한 경우 지금까지 개발한 내용을 Readme 문서로 정리할 수 있도록 유도 부탁드립니다. 
   - Readme 문서 템플릿을 ChatGPT를 활용하여 안내 받고 그 곳에 내용을 채우는 방식으로 안내 부탁드립니다. </t>
     </r>
     <r>
@@ -6755,1028 +7726,337 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">* ask </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>모드를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">통해 진행하므로 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>제안하는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>내용을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>자세히</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>읽어보고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>추가할</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있도록</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지도해주시기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>바랍니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. 
-  - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>비전공</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>트랙의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>경우</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> ask </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>모드로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>개발이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>어려울</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있으니</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>강사님들이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>옆에서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>많이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>도와줄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있도록</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
+      <t xml:space="preserve">to do </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>항목</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>목표공유</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">시간 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">OpenAI API Key </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
         <charset val="129"/>
       </rPr>
       <t>안내</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>부탁드립니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. 
-  - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>막히는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>부분이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>배워야</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>하는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>부분이고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>것을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>알면</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>에게</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>일을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>더</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>잘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시킬</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있다로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>교육생들</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>마인드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>셋팅도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>진행해주세요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.
-* git </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사용을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>잊지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>않도록</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>계속</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>안내</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>부탁드립니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <t>render 배포 가이드 문서(
-전공 : render 서비스를 활용
+    <r>
+      <t xml:space="preserve">* </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">팀 스크럼 회의는 </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이슈 내용 공유, 오늘 해 야 할 내용 공유, 특이 사항 공유</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 등으로 진행하도록 안내부탁드립니다.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+* </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">OpenAI API </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>키는 추가 발급되거나 하지 않기 때문에 유출되지 않도록 잘 관리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">할 수 있도록 안내해주세요. 
+* </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최대 사용 금액은 $3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">이기 때문에 효율적인 토큰 사용이 될 수 있도록 지도 부탁드립니다. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+* </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">BYOK </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>용도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">와 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">필수 기능인 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">LLM </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>챗봇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">에 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">API Key </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">가 활용되니 팀 별로 잘 조절해서 사용할 수 있도록 안내해주세요. </t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>render 배포 가이드 문서
+(전공 : render 서비스를 활용
 비전공: netlify 서비스 활용)</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> WebEX</t>
+    <t xml:space="preserve"> Webex</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">* 발표 진행시 Webex 화면 공유를 활용해주세요. </t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://github.com/mulcamp-ed/ai-onboarding/tree/master/Day05</t>
+  </si>
+  <si>
+    <t>render 서비스 배포 가이드 문서</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
@@ -7784,7 +8064,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="44">
+  <fonts count="45">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8119,6 +8399,13 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -9432,6 +9719,300 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9456,18 +10037,6 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -9476,18 +10045,6 @@
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -9495,283 +10052,43 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -9780,6 +10097,42 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="46" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -9801,68 +10154,41 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="43" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -9870,9 +10196,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -9888,55 +10211,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -9963,6 +10241,18 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -9974,9 +10264,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -10444,18 +10731,18 @@
         <v>3</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H2" s="47" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I2" s="106" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="33">
-      <c r="B3" s="181" t="s">
-        <v>166</v>
+      <c r="B3" s="157" t="s">
+        <v>165</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>6</v>
@@ -10463,74 +10750,74 @@
       <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="140" t="s">
+      <c r="E3" s="192" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="141"/>
+      <c r="F3" s="193"/>
       <c r="G3" s="56" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H3" s="56"/>
       <c r="I3" s="53"/>
     </row>
     <row r="4" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B4" s="182"/>
-      <c r="C4" s="216" t="s">
+      <c r="B4" s="158"/>
+      <c r="C4" s="116" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="200" t="s">
+      <c r="D4" s="119" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="125" t="s">
+      <c r="F4" s="122" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="155" t="s">
-        <v>104</v>
-      </c>
-      <c r="H4" s="192"/>
-      <c r="I4" s="145"/>
+      <c r="G4" s="163" t="s">
+        <v>103</v>
+      </c>
+      <c r="H4" s="166"/>
+      <c r="I4" s="197"/>
     </row>
     <row r="5" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B5" s="182"/>
-      <c r="C5" s="217"/>
-      <c r="D5" s="201"/>
+      <c r="B5" s="158"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="120"/>
       <c r="E5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="167"/>
-      <c r="G5" s="190"/>
-      <c r="H5" s="193"/>
-      <c r="I5" s="143"/>
+      <c r="F5" s="123"/>
+      <c r="G5" s="164"/>
+      <c r="H5" s="167"/>
+      <c r="I5" s="195"/>
     </row>
     <row r="6" spans="2:9">
-      <c r="B6" s="182"/>
-      <c r="C6" s="217"/>
-      <c r="D6" s="201"/>
+      <c r="B6" s="158"/>
+      <c r="C6" s="117"/>
+      <c r="D6" s="120"/>
       <c r="E6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="167"/>
-      <c r="G6" s="190"/>
-      <c r="H6" s="193"/>
-      <c r="I6" s="143"/>
+      <c r="F6" s="123"/>
+      <c r="G6" s="164"/>
+      <c r="H6" s="167"/>
+      <c r="I6" s="195"/>
     </row>
     <row r="7" spans="2:9">
-      <c r="B7" s="182"/>
-      <c r="C7" s="218"/>
-      <c r="D7" s="219"/>
+      <c r="B7" s="158"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="121"/>
       <c r="E7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="220"/>
-      <c r="G7" s="191"/>
-      <c r="H7" s="194"/>
-      <c r="I7" s="146"/>
+      <c r="F7" s="124"/>
+      <c r="G7" s="165"/>
+      <c r="H7" s="168"/>
+      <c r="I7" s="198"/>
     </row>
     <row r="8" spans="2:9" ht="53.1" customHeight="1">
-      <c r="B8" s="182"/>
+      <c r="B8" s="158"/>
       <c r="C8" s="7" t="s">
         <v>16</v>
       </c>
@@ -10540,48 +10827,48 @@
       <c r="E8" s="45"/>
       <c r="F8" s="9"/>
       <c r="G8" s="91" t="s">
+        <v>109</v>
+      </c>
+      <c r="H8" s="97"/>
+      <c r="I8" s="194" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="17.649999999999999" customHeight="1">
+      <c r="B9" s="158"/>
+      <c r="C9" s="116" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="136" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="216" t="s">
+        <v>174</v>
+      </c>
+      <c r="G9" s="178" t="s">
+        <v>119</v>
+      </c>
+      <c r="H9" s="211" t="s">
         <v>110</v>
       </c>
-      <c r="H8" s="97"/>
-      <c r="I8" s="142" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B9" s="182"/>
-      <c r="C9" s="216" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="223" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="125" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="118" t="s">
-        <v>176</v>
-      </c>
-      <c r="G9" s="165" t="s">
-        <v>120</v>
-      </c>
-      <c r="H9" s="163" t="s">
-        <v>111</v>
-      </c>
-      <c r="I9" s="143"/>
+      <c r="I9" s="195"/>
     </row>
     <row r="10" spans="2:9" ht="385.5" customHeight="1">
-      <c r="B10" s="182"/>
-      <c r="C10" s="222"/>
-      <c r="D10" s="224"/>
-      <c r="E10" s="126"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="166"/>
-      <c r="H10" s="164"/>
-      <c r="I10" s="143"/>
+      <c r="B10" s="158"/>
+      <c r="C10" s="135"/>
+      <c r="D10" s="137"/>
+      <c r="E10" s="138"/>
+      <c r="F10" s="217"/>
+      <c r="G10" s="180"/>
+      <c r="H10" s="212"/>
+      <c r="I10" s="195"/>
     </row>
     <row r="11" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B11" s="182"/>
-      <c r="C11" s="216" t="s">
+      <c r="B11" s="158"/>
+      <c r="C11" s="116" t="s">
         <v>21</v>
       </c>
       <c r="D11" s="10" t="s">
@@ -10590,50 +10877,50 @@
       <c r="E11" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="170" t="s">
-        <v>173</v>
-      </c>
-      <c r="G11" s="165" t="s">
-        <v>118</v>
-      </c>
-      <c r="H11" s="172" t="s">
-        <v>114</v>
-      </c>
-      <c r="I11" s="143"/>
+      <c r="F11" s="181" t="s">
+        <v>171</v>
+      </c>
+      <c r="G11" s="178" t="s">
+        <v>117</v>
+      </c>
+      <c r="H11" s="183" t="s">
+        <v>113</v>
+      </c>
+      <c r="I11" s="195"/>
     </row>
     <row r="12" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B12" s="182"/>
-      <c r="C12" s="217"/>
+      <c r="B12" s="158"/>
+      <c r="C12" s="117"/>
       <c r="D12" s="11" t="s">
         <v>23</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="F12" s="171"/>
-      <c r="G12" s="169"/>
-      <c r="H12" s="173"/>
-      <c r="I12" s="143"/>
+        <v>169</v>
+      </c>
+      <c r="F12" s="182"/>
+      <c r="G12" s="179"/>
+      <c r="H12" s="184"/>
+      <c r="I12" s="195"/>
     </row>
     <row r="13" spans="2:9" ht="123.95" customHeight="1">
-      <c r="B13" s="182"/>
-      <c r="C13" s="222"/>
+      <c r="B13" s="158"/>
+      <c r="C13" s="135"/>
       <c r="D13" s="11"/>
       <c r="E13" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F13" s="124"/>
-      <c r="G13" s="166"/>
-      <c r="H13" s="174"/>
-      <c r="I13" s="143"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="180"/>
+      <c r="H13" s="185"/>
+      <c r="I13" s="195"/>
     </row>
     <row r="14" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B14" s="182"/>
-      <c r="C14" s="216" t="s">
+      <c r="B14" s="158"/>
+      <c r="C14" s="116" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="125" t="s">
-        <v>100</v>
+      <c r="D14" s="122" t="s">
+        <v>99</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>27</v>
@@ -10641,93 +10928,93 @@
       <c r="F14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="175" t="s">
-        <v>123</v>
-      </c>
-      <c r="H14" s="178" t="s">
-        <v>113</v>
-      </c>
-      <c r="I14" s="143"/>
+      <c r="G14" s="186" t="s">
+        <v>122</v>
+      </c>
+      <c r="H14" s="189" t="s">
+        <v>112</v>
+      </c>
+      <c r="I14" s="195"/>
     </row>
     <row r="15" spans="2:9" ht="35.1" customHeight="1">
-      <c r="B15" s="182"/>
-      <c r="C15" s="217"/>
-      <c r="D15" s="167"/>
+      <c r="B15" s="158"/>
+      <c r="C15" s="117"/>
+      <c r="D15" s="123"/>
       <c r="E15" s="13" t="s">
         <v>28</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G15" s="176"/>
-      <c r="H15" s="179"/>
-      <c r="I15" s="143"/>
+        <v>170</v>
+      </c>
+      <c r="G15" s="187"/>
+      <c r="H15" s="190"/>
+      <c r="I15" s="195"/>
     </row>
     <row r="16" spans="2:9">
-      <c r="B16" s="182"/>
-      <c r="C16" s="217"/>
-      <c r="D16" s="167"/>
+      <c r="B16" s="158"/>
+      <c r="C16" s="117"/>
+      <c r="D16" s="123"/>
       <c r="E16" s="14"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="176"/>
-      <c r="H16" s="179"/>
-      <c r="I16" s="143"/>
+      <c r="G16" s="187"/>
+      <c r="H16" s="190"/>
+      <c r="I16" s="195"/>
     </row>
     <row r="17" spans="2:9" ht="49.5">
-      <c r="B17" s="182"/>
-      <c r="C17" s="217"/>
-      <c r="D17" s="167"/>
+      <c r="B17" s="158"/>
+      <c r="C17" s="117"/>
+      <c r="D17" s="123"/>
       <c r="E17" s="13" t="s">
         <v>29</v>
       </c>
       <c r="F17" s="5"/>
-      <c r="G17" s="176"/>
-      <c r="H17" s="179"/>
-      <c r="I17" s="143"/>
+      <c r="G17" s="187"/>
+      <c r="H17" s="190"/>
+      <c r="I17" s="195"/>
     </row>
     <row r="18" spans="2:9">
-      <c r="B18" s="182"/>
-      <c r="C18" s="217"/>
-      <c r="D18" s="167"/>
+      <c r="B18" s="158"/>
+      <c r="C18" s="117"/>
+      <c r="D18" s="123"/>
       <c r="E18" s="14"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="176"/>
-      <c r="H18" s="179"/>
-      <c r="I18" s="143"/>
+      <c r="G18" s="187"/>
+      <c r="H18" s="190"/>
+      <c r="I18" s="195"/>
     </row>
     <row r="19" spans="2:9">
-      <c r="B19" s="182"/>
-      <c r="C19" s="217"/>
-      <c r="D19" s="167"/>
-      <c r="E19" s="296" t="s">
+      <c r="B19" s="158"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="123"/>
+      <c r="E19" s="115" t="s">
         <v>30</v>
       </c>
       <c r="F19" s="5"/>
-      <c r="G19" s="176"/>
-      <c r="H19" s="179"/>
-      <c r="I19" s="143"/>
+      <c r="G19" s="187"/>
+      <c r="H19" s="190"/>
+      <c r="I19" s="195"/>
     </row>
     <row r="20" spans="2:9">
-      <c r="B20" s="182"/>
-      <c r="C20" s="217"/>
-      <c r="D20" s="167"/>
-      <c r="E20" s="296" t="s">
-        <v>106</v>
+      <c r="B20" s="158"/>
+      <c r="C20" s="117"/>
+      <c r="D20" s="123"/>
+      <c r="E20" s="115" t="s">
+        <v>105</v>
       </c>
       <c r="F20" s="5"/>
-      <c r="G20" s="176"/>
-      <c r="H20" s="179"/>
-      <c r="I20" s="143"/>
+      <c r="G20" s="187"/>
+      <c r="H20" s="190"/>
+      <c r="I20" s="195"/>
     </row>
     <row r="21" spans="2:9" ht="84.4" customHeight="1" thickBot="1">
-      <c r="B21" s="183"/>
-      <c r="C21" s="221"/>
-      <c r="D21" s="168"/>
+      <c r="B21" s="159"/>
+      <c r="C21" s="128"/>
+      <c r="D21" s="177"/>
       <c r="E21" s="50"/>
       <c r="F21" s="49"/>
-      <c r="G21" s="177"/>
-      <c r="H21" s="180"/>
-      <c r="I21" s="144"/>
+      <c r="G21" s="188"/>
+      <c r="H21" s="191"/>
+      <c r="I21" s="196"/>
     </row>
     <row r="22" spans="2:9" ht="17.25" thickBot="1">
       <c r="B22" s="107"/>
@@ -10740,48 +11027,48 @@
       <c r="I22" s="108"/>
     </row>
     <row r="23" spans="2:9" ht="32.1" customHeight="1">
-      <c r="B23" s="184" t="s">
-        <v>167</v>
-      </c>
-      <c r="C23" s="212" t="s">
+      <c r="B23" s="151" t="s">
+        <v>166</v>
+      </c>
+      <c r="C23" s="129" t="s">
         <v>33</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E23" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="F23" s="123" t="s">
-        <v>177</v>
-      </c>
-      <c r="G23" s="151" t="s">
-        <v>134</v>
-      </c>
-      <c r="H23" s="123" t="s">
+      <c r="F23" s="131" t="s">
+        <v>175</v>
+      </c>
+      <c r="G23" s="201" t="s">
         <v>133</v>
       </c>
-      <c r="I23" s="133" t="s">
-        <v>192</v>
+      <c r="H23" s="131" t="s">
+        <v>132</v>
+      </c>
+      <c r="I23" s="125" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="24" spans="2:9" ht="70.7" customHeight="1">
-      <c r="B24" s="185"/>
-      <c r="C24" s="196"/>
+      <c r="B24" s="152"/>
+      <c r="C24" s="130"/>
       <c r="D24" s="20" t="s">
         <v>23</v>
       </c>
       <c r="E24" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="F24" s="124"/>
-      <c r="G24" s="152"/>
-      <c r="H24" s="124"/>
-      <c r="I24" s="136"/>
+      <c r="F24" s="132"/>
+      <c r="G24" s="202"/>
+      <c r="H24" s="132"/>
+      <c r="I24" s="126"/>
     </row>
     <row r="25" spans="2:9" ht="35.1" customHeight="1">
-      <c r="B25" s="185"/>
-      <c r="C25" s="195" t="s">
+      <c r="B25" s="152"/>
+      <c r="C25" s="133" t="s">
         <v>37</v>
       </c>
       <c r="D25" s="23" t="s">
@@ -10790,102 +11077,102 @@
       <c r="E25" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F25" s="120" t="s">
-        <v>179</v>
-      </c>
-      <c r="G25" s="147" t="s">
-        <v>124</v>
-      </c>
-      <c r="H25" s="228" t="s">
-        <v>180</v>
-      </c>
-      <c r="I25" s="136"/>
+      <c r="F25" s="218" t="s">
+        <v>177</v>
+      </c>
+      <c r="G25" s="141" t="s">
+        <v>123</v>
+      </c>
+      <c r="H25" s="144" t="s">
+        <v>178</v>
+      </c>
+      <c r="I25" s="126"/>
     </row>
     <row r="26" spans="2:9">
-      <c r="B26" s="185"/>
-      <c r="C26" s="199"/>
+      <c r="B26" s="152"/>
+      <c r="C26" s="134"/>
       <c r="D26" s="24" t="s">
         <v>39</v>
       </c>
       <c r="E26" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F26" s="121"/>
-      <c r="G26" s="227"/>
-      <c r="H26" s="132"/>
-      <c r="I26" s="136"/>
+      <c r="F26" s="219"/>
+      <c r="G26" s="142"/>
+      <c r="H26" s="145"/>
+      <c r="I26" s="126"/>
     </row>
     <row r="27" spans="2:9">
-      <c r="B27" s="185"/>
-      <c r="C27" s="199"/>
+      <c r="B27" s="152"/>
+      <c r="C27" s="134"/>
       <c r="D27" s="24"/>
       <c r="E27" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F27" s="121"/>
-      <c r="G27" s="227"/>
-      <c r="H27" s="132"/>
-      <c r="I27" s="136"/>
+      <c r="F27" s="219"/>
+      <c r="G27" s="142"/>
+      <c r="H27" s="145"/>
+      <c r="I27" s="126"/>
     </row>
     <row r="28" spans="2:9">
-      <c r="B28" s="185"/>
-      <c r="C28" s="199"/>
+      <c r="B28" s="152"/>
+      <c r="C28" s="134"/>
       <c r="D28" s="24"/>
       <c r="E28" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F28" s="121"/>
-      <c r="G28" s="227"/>
-      <c r="H28" s="132"/>
-      <c r="I28" s="136"/>
+      <c r="F28" s="219"/>
+      <c r="G28" s="142"/>
+      <c r="H28" s="145"/>
+      <c r="I28" s="126"/>
     </row>
     <row r="29" spans="2:9">
-      <c r="B29" s="185"/>
-      <c r="C29" s="199"/>
+      <c r="B29" s="152"/>
+      <c r="C29" s="134"/>
       <c r="D29" s="24"/>
       <c r="E29" s="14"/>
-      <c r="F29" s="121"/>
-      <c r="G29" s="227"/>
-      <c r="H29" s="132"/>
-      <c r="I29" s="136"/>
+      <c r="F29" s="219"/>
+      <c r="G29" s="142"/>
+      <c r="H29" s="145"/>
+      <c r="I29" s="126"/>
     </row>
     <row r="30" spans="2:9">
-      <c r="B30" s="185"/>
-      <c r="C30" s="199"/>
+      <c r="B30" s="152"/>
+      <c r="C30" s="134"/>
       <c r="D30" s="24"/>
-      <c r="E30" s="296" t="s">
+      <c r="E30" s="115" t="s">
         <v>30</v>
       </c>
-      <c r="F30" s="121"/>
-      <c r="G30" s="227"/>
-      <c r="H30" s="132"/>
-      <c r="I30" s="136"/>
+      <c r="F30" s="219"/>
+      <c r="G30" s="142"/>
+      <c r="H30" s="145"/>
+      <c r="I30" s="126"/>
     </row>
     <row r="31" spans="2:9">
-      <c r="B31" s="185"/>
-      <c r="C31" s="199"/>
+      <c r="B31" s="152"/>
+      <c r="C31" s="134"/>
       <c r="D31" s="24"/>
-      <c r="E31" s="296" t="s">
-        <v>106</v>
-      </c>
-      <c r="F31" s="121"/>
-      <c r="G31" s="227"/>
-      <c r="H31" s="132"/>
-      <c r="I31" s="136"/>
+      <c r="E31" s="115" t="s">
+        <v>105</v>
+      </c>
+      <c r="F31" s="219"/>
+      <c r="G31" s="142"/>
+      <c r="H31" s="145"/>
+      <c r="I31" s="126"/>
     </row>
     <row r="32" spans="2:9">
-      <c r="B32" s="185"/>
-      <c r="C32" s="196"/>
+      <c r="B32" s="152"/>
+      <c r="C32" s="130"/>
       <c r="D32" s="25"/>
       <c r="E32" s="26"/>
-      <c r="F32" s="122"/>
-      <c r="G32" s="148"/>
-      <c r="H32" s="131"/>
-      <c r="I32" s="136"/>
+      <c r="F32" s="220"/>
+      <c r="G32" s="143"/>
+      <c r="H32" s="146"/>
+      <c r="I32" s="126"/>
     </row>
     <row r="33" spans="2:9">
-      <c r="B33" s="185"/>
-      <c r="C33" s="195" t="s">
+      <c r="B33" s="152"/>
+      <c r="C33" s="133" t="s">
         <v>44</v>
       </c>
       <c r="D33" s="23" t="s">
@@ -10894,33 +11181,33 @@
       <c r="E33" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F33" s="225" t="s">
-        <v>178</v>
-      </c>
-      <c r="G33" s="208" t="s">
-        <v>127</v>
-      </c>
-      <c r="H33" s="130" t="s">
-        <v>130</v>
-      </c>
-      <c r="I33" s="136"/>
+      <c r="F33" s="139" t="s">
+        <v>176</v>
+      </c>
+      <c r="G33" s="228" t="s">
+        <v>126</v>
+      </c>
+      <c r="H33" s="169" t="s">
+        <v>129</v>
+      </c>
+      <c r="I33" s="126"/>
     </row>
     <row r="34" spans="2:9" ht="123.4" customHeight="1">
-      <c r="B34" s="185"/>
-      <c r="C34" s="196"/>
+      <c r="B34" s="152"/>
+      <c r="C34" s="130"/>
       <c r="D34" s="27" t="s">
         <v>46</v>
       </c>
       <c r="E34" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="F34" s="226"/>
-      <c r="G34" s="209"/>
-      <c r="H34" s="131"/>
-      <c r="I34" s="136"/>
+      <c r="F34" s="140"/>
+      <c r="G34" s="229"/>
+      <c r="H34" s="146"/>
+      <c r="I34" s="126"/>
     </row>
     <row r="35" spans="2:9" ht="141" customHeight="1">
-      <c r="B35" s="185"/>
+      <c r="B35" s="152"/>
       <c r="C35" s="28" t="s">
         <v>50</v>
       </c>
@@ -10932,15 +11219,15 @@
       </c>
       <c r="F35" s="9"/>
       <c r="G35" s="63" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H35" s="99" t="s">
-        <v>131</v>
-      </c>
-      <c r="I35" s="137"/>
+        <v>130</v>
+      </c>
+      <c r="I35" s="127"/>
     </row>
     <row r="36" spans="2:9" ht="33.75" thickBot="1">
-      <c r="B36" s="186"/>
+      <c r="B36" s="153"/>
       <c r="C36" s="31" t="s">
         <v>54</v>
       </c>
@@ -10966,224 +11253,224 @@
       <c r="I37" s="94"/>
     </row>
     <row r="38" spans="2:9">
-      <c r="B38" s="184" t="s">
+      <c r="B38" s="151" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="212" t="s">
+      <c r="C38" s="129" t="s">
         <v>58</v>
       </c>
       <c r="D38" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="E38" s="213" t="s">
+      <c r="E38" s="154" t="s">
         <v>61</v>
       </c>
-      <c r="F38" s="123" t="s">
-        <v>181</v>
-      </c>
-      <c r="G38" s="151" t="s">
-        <v>144</v>
-      </c>
-      <c r="H38" s="153" t="s">
-        <v>146</v>
-      </c>
-      <c r="I38" s="133" t="s">
-        <v>193</v>
+      <c r="F38" s="131" t="s">
+        <v>179</v>
+      </c>
+      <c r="G38" s="201" t="s">
+        <v>143</v>
+      </c>
+      <c r="H38" s="203" t="s">
+        <v>145</v>
+      </c>
+      <c r="I38" s="125" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="39" spans="2:9" ht="149.1" customHeight="1">
-      <c r="B39" s="185"/>
-      <c r="C39" s="199"/>
+      <c r="B39" s="152"/>
+      <c r="C39" s="134"/>
       <c r="D39" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="E39" s="131"/>
-      <c r="F39" s="124"/>
-      <c r="G39" s="152"/>
-      <c r="H39" s="154"/>
-      <c r="I39" s="134"/>
+      <c r="E39" s="146"/>
+      <c r="F39" s="132"/>
+      <c r="G39" s="202"/>
+      <c r="H39" s="204"/>
+      <c r="I39" s="224"/>
     </row>
     <row r="40" spans="2:9">
-      <c r="B40" s="185"/>
-      <c r="C40" s="199"/>
-      <c r="D40" s="214" t="s">
+      <c r="B40" s="152"/>
+      <c r="C40" s="134"/>
+      <c r="D40" s="155" t="s">
         <v>62</v>
       </c>
       <c r="E40" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F40" s="125" t="s">
-        <v>184</v>
-      </c>
-      <c r="G40" s="155" t="s">
-        <v>145</v>
-      </c>
-      <c r="H40" s="149" t="s">
-        <v>147</v>
-      </c>
-      <c r="I40" s="134"/>
+      <c r="F40" s="122" t="s">
+        <v>182</v>
+      </c>
+      <c r="G40" s="163" t="s">
+        <v>144</v>
+      </c>
+      <c r="H40" s="199" t="s">
+        <v>146</v>
+      </c>
+      <c r="I40" s="224"/>
     </row>
     <row r="41" spans="2:9" ht="119.65" customHeight="1">
-      <c r="B41" s="185"/>
-      <c r="C41" s="196"/>
-      <c r="D41" s="215"/>
+      <c r="B41" s="152"/>
+      <c r="C41" s="130"/>
+      <c r="D41" s="156"/>
       <c r="E41" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="F41" s="126"/>
-      <c r="G41" s="156"/>
-      <c r="H41" s="150"/>
-      <c r="I41" s="134"/>
+      <c r="F41" s="138"/>
+      <c r="G41" s="174"/>
+      <c r="H41" s="200"/>
+      <c r="I41" s="224"/>
     </row>
     <row r="42" spans="2:9">
-      <c r="B42" s="185"/>
-      <c r="C42" s="195" t="s">
+      <c r="B42" s="152"/>
+      <c r="C42" s="133" t="s">
         <v>65</v>
       </c>
-      <c r="D42" s="206" t="s">
+      <c r="D42" s="175" t="s">
         <v>66</v>
       </c>
-      <c r="E42" s="120" t="s">
+      <c r="E42" s="218" t="s">
+        <v>139</v>
+      </c>
+      <c r="F42" s="122" t="s">
+        <v>181</v>
+      </c>
+      <c r="G42" s="163" t="s">
         <v>140</v>
       </c>
-      <c r="F42" s="125" t="s">
-        <v>183</v>
-      </c>
-      <c r="G42" s="155" t="s">
-        <v>141</v>
-      </c>
-      <c r="H42" s="157" t="s">
-        <v>148</v>
-      </c>
-      <c r="I42" s="134"/>
+      <c r="H42" s="205" t="s">
+        <v>147</v>
+      </c>
+      <c r="I42" s="224"/>
     </row>
     <row r="43" spans="2:9" ht="113.65" customHeight="1">
-      <c r="B43" s="185"/>
-      <c r="C43" s="199"/>
-      <c r="D43" s="207"/>
-      <c r="E43" s="122"/>
-      <c r="F43" s="126"/>
-      <c r="G43" s="156"/>
-      <c r="H43" s="157"/>
-      <c r="I43" s="134"/>
+      <c r="B43" s="152"/>
+      <c r="C43" s="134"/>
+      <c r="D43" s="176"/>
+      <c r="E43" s="220"/>
+      <c r="F43" s="138"/>
+      <c r="G43" s="174"/>
+      <c r="H43" s="205"/>
+      <c r="I43" s="224"/>
     </row>
     <row r="44" spans="2:9">
-      <c r="B44" s="185"/>
-      <c r="C44" s="199"/>
-      <c r="D44" s="197" t="s">
+      <c r="B44" s="152"/>
+      <c r="C44" s="134"/>
+      <c r="D44" s="147" t="s">
         <v>67</v>
       </c>
-      <c r="E44" s="125" t="s">
-        <v>182</v>
-      </c>
-      <c r="F44" s="210"/>
-      <c r="G44" s="138" t="s">
-        <v>189</v>
-      </c>
-      <c r="H44" s="157"/>
-      <c r="I44" s="134"/>
+      <c r="E44" s="122" t="s">
+        <v>180</v>
+      </c>
+      <c r="F44" s="149"/>
+      <c r="G44" s="226" t="s">
+        <v>195</v>
+      </c>
+      <c r="H44" s="205"/>
+      <c r="I44" s="224"/>
     </row>
     <row r="45" spans="2:9" ht="317.64999999999998" customHeight="1">
-      <c r="B45" s="185"/>
-      <c r="C45" s="196"/>
-      <c r="D45" s="198"/>
-      <c r="E45" s="126"/>
-      <c r="F45" s="211"/>
-      <c r="G45" s="139"/>
-      <c r="H45" s="150"/>
-      <c r="I45" s="134"/>
+      <c r="B45" s="152"/>
+      <c r="C45" s="130"/>
+      <c r="D45" s="148"/>
+      <c r="E45" s="138"/>
+      <c r="F45" s="150"/>
+      <c r="G45" s="227"/>
+      <c r="H45" s="200"/>
+      <c r="I45" s="224"/>
     </row>
     <row r="46" spans="2:9">
-      <c r="B46" s="185"/>
-      <c r="C46" s="195" t="s">
+      <c r="B46" s="152"/>
+      <c r="C46" s="133" t="s">
         <v>68</v>
       </c>
       <c r="D46" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="E46" s="200" t="s">
+      <c r="E46" s="119" t="s">
         <v>72</v>
       </c>
-      <c r="F46" s="130" t="s">
-        <v>185</v>
-      </c>
-      <c r="G46" s="158" t="s">
-        <v>199</v>
-      </c>
-      <c r="H46" s="161"/>
-      <c r="I46" s="134"/>
+      <c r="F46" s="169" t="s">
+        <v>183</v>
+      </c>
+      <c r="G46" s="206" t="s">
+        <v>196</v>
+      </c>
+      <c r="H46" s="209"/>
+      <c r="I46" s="224"/>
     </row>
     <row r="47" spans="2:9">
-      <c r="B47" s="185"/>
-      <c r="C47" s="199"/>
+      <c r="B47" s="152"/>
+      <c r="C47" s="134"/>
       <c r="D47" s="37" t="s">
-        <v>175</v>
-      </c>
-      <c r="E47" s="201"/>
-      <c r="F47" s="132"/>
-      <c r="G47" s="159"/>
-      <c r="H47" s="161"/>
-      <c r="I47" s="134"/>
+        <v>173</v>
+      </c>
+      <c r="E47" s="120"/>
+      <c r="F47" s="145"/>
+      <c r="G47" s="207"/>
+      <c r="H47" s="209"/>
+      <c r="I47" s="224"/>
     </row>
     <row r="48" spans="2:9">
-      <c r="B48" s="185"/>
-      <c r="C48" s="199"/>
+      <c r="B48" s="152"/>
+      <c r="C48" s="134"/>
       <c r="D48" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="E48" s="201"/>
-      <c r="F48" s="132"/>
-      <c r="G48" s="159"/>
-      <c r="H48" s="161"/>
-      <c r="I48" s="134"/>
+      <c r="E48" s="120"/>
+      <c r="F48" s="145"/>
+      <c r="G48" s="207"/>
+      <c r="H48" s="209"/>
+      <c r="I48" s="224"/>
     </row>
     <row r="49" spans="2:9">
-      <c r="B49" s="185"/>
-      <c r="C49" s="199"/>
+      <c r="B49" s="152"/>
+      <c r="C49" s="134"/>
       <c r="D49" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="E49" s="201"/>
-      <c r="F49" s="132"/>
-      <c r="G49" s="159"/>
-      <c r="H49" s="161"/>
-      <c r="I49" s="134"/>
+      <c r="E49" s="120"/>
+      <c r="F49" s="145"/>
+      <c r="G49" s="207"/>
+      <c r="H49" s="209"/>
+      <c r="I49" s="224"/>
     </row>
     <row r="50" spans="2:9">
-      <c r="B50" s="185"/>
-      <c r="C50" s="199"/>
+      <c r="B50" s="152"/>
+      <c r="C50" s="134"/>
       <c r="D50" s="37"/>
-      <c r="E50" s="201"/>
-      <c r="F50" s="132"/>
-      <c r="G50" s="159"/>
-      <c r="H50" s="161"/>
-      <c r="I50" s="134"/>
+      <c r="E50" s="120"/>
+      <c r="F50" s="145"/>
+      <c r="G50" s="207"/>
+      <c r="H50" s="209"/>
+      <c r="I50" s="224"/>
     </row>
     <row r="51" spans="2:9" ht="204.4" customHeight="1" thickBot="1">
-      <c r="B51" s="185"/>
-      <c r="C51" s="196"/>
+      <c r="B51" s="152"/>
+      <c r="C51" s="130"/>
       <c r="D51" s="37"/>
-      <c r="E51" s="202"/>
-      <c r="F51" s="131"/>
-      <c r="G51" s="160"/>
-      <c r="H51" s="162"/>
-      <c r="I51" s="135"/>
+      <c r="E51" s="170"/>
+      <c r="F51" s="146"/>
+      <c r="G51" s="208"/>
+      <c r="H51" s="210"/>
+      <c r="I51" s="225"/>
     </row>
     <row r="52" spans="2:9" ht="30.75" thickBot="1">
-      <c r="B52" s="186"/>
+      <c r="B52" s="153"/>
       <c r="C52" s="38" t="s">
         <v>73</v>
       </c>
       <c r="D52" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="E52" s="203" t="s">
+      <c r="E52" s="171" t="s">
         <v>56</v>
       </c>
-      <c r="F52" s="204"/>
-      <c r="G52" s="204"/>
-      <c r="H52" s="204"/>
-      <c r="I52" s="205"/>
+      <c r="F52" s="172"/>
+      <c r="G52" s="172"/>
+      <c r="H52" s="172"/>
+      <c r="I52" s="173"/>
     </row>
     <row r="53" spans="2:9" ht="17.25" thickBot="1">
       <c r="B53" s="82"/>
@@ -11196,7 +11483,7 @@
       <c r="I53" s="95"/>
     </row>
     <row r="54" spans="2:9" ht="94.7" customHeight="1">
-      <c r="B54" s="184" t="s">
+      <c r="B54" s="151" t="s">
         <v>75</v>
       </c>
       <c r="C54" s="40" t="s">
@@ -11209,83 +11496,83 @@
         <v>78</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G54" s="69" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H54" s="111" t="s">
-        <v>150</v>
-      </c>
-      <c r="I54" s="133" t="s">
-        <v>194</v>
+        <v>149</v>
+      </c>
+      <c r="I54" s="125" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="55" spans="2:9">
-      <c r="B55" s="185"/>
-      <c r="C55" s="195" t="s">
+      <c r="B55" s="152"/>
+      <c r="C55" s="133" t="s">
         <v>16</v>
       </c>
-      <c r="D55" s="197" t="s">
+      <c r="D55" s="147" t="s">
         <v>79</v>
       </c>
-      <c r="E55" s="130" t="s">
+      <c r="E55" s="169" t="s">
+        <v>197</v>
+      </c>
+      <c r="F55" s="169" t="s">
+        <v>184</v>
+      </c>
+      <c r="G55" s="141" t="s">
+        <v>198</v>
+      </c>
+      <c r="H55" s="199" t="s">
+        <v>185</v>
+      </c>
+      <c r="I55" s="224"/>
+    </row>
+    <row r="56" spans="2:9" ht="150.4" customHeight="1">
+      <c r="B56" s="152"/>
+      <c r="C56" s="130"/>
+      <c r="D56" s="148"/>
+      <c r="E56" s="146"/>
+      <c r="F56" s="146"/>
+      <c r="G56" s="143"/>
+      <c r="H56" s="200"/>
+      <c r="I56" s="224"/>
+    </row>
+    <row r="57" spans="2:9" ht="181.7" customHeight="1">
+      <c r="B57" s="152"/>
+      <c r="C57" s="28" t="s">
         <v>80</v>
-      </c>
-      <c r="F55" s="130" t="s">
-        <v>186</v>
-      </c>
-      <c r="G55" s="147" t="s">
-        <v>155</v>
-      </c>
-      <c r="H55" s="149" t="s">
-        <v>187</v>
-      </c>
-      <c r="I55" s="134"/>
-    </row>
-    <row r="56" spans="2:9" ht="150.4" customHeight="1">
-      <c r="B56" s="185"/>
-      <c r="C56" s="196"/>
-      <c r="D56" s="198"/>
-      <c r="E56" s="131"/>
-      <c r="F56" s="131"/>
-      <c r="G56" s="148"/>
-      <c r="H56" s="150"/>
-      <c r="I56" s="134"/>
-    </row>
-    <row r="57" spans="2:9" ht="181.7" customHeight="1">
-      <c r="B57" s="185"/>
-      <c r="C57" s="28" t="s">
-        <v>81</v>
       </c>
       <c r="D57" s="29" t="s">
         <v>69</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F57" s="9"/>
       <c r="G57" s="90" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="H57" s="101"/>
-      <c r="I57" s="135"/>
+      <c r="I57" s="225"/>
     </row>
     <row r="58" spans="2:9" ht="33.75" thickBot="1">
-      <c r="B58" s="186"/>
+      <c r="B58" s="153"/>
       <c r="C58" s="31" t="s">
         <v>73</v>
       </c>
       <c r="D58" s="43" t="s">
-        <v>83</v>
-      </c>
-      <c r="E58" s="127" t="s">
+        <v>82</v>
+      </c>
+      <c r="E58" s="221" t="s">
         <v>56</v>
       </c>
-      <c r="F58" s="128"/>
-      <c r="G58" s="128"/>
-      <c r="H58" s="128"/>
-      <c r="I58" s="129"/>
+      <c r="F58" s="222"/>
+      <c r="G58" s="222"/>
+      <c r="H58" s="222"/>
+      <c r="I58" s="223"/>
     </row>
     <row r="59" spans="2:9" ht="17.25" thickBot="1">
       <c r="B59" s="78"/>
@@ -11298,119 +11585,179 @@
       <c r="I59" s="96"/>
     </row>
     <row r="60" spans="2:9" ht="66">
-      <c r="B60" s="187" t="s">
+      <c r="B60" s="160" t="s">
+        <v>157</v>
+      </c>
+      <c r="C60" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="D60" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="E60" s="42" t="s">
         <v>158</v>
-      </c>
-      <c r="C60" s="40" t="s">
-        <v>84</v>
-      </c>
-      <c r="D60" s="44" t="s">
-        <v>85</v>
-      </c>
-      <c r="E60" s="42" t="s">
-        <v>159</v>
       </c>
       <c r="F60" s="72"/>
       <c r="G60" s="72" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H60" s="102"/>
-      <c r="I60" s="133" t="s">
-        <v>195</v>
+      <c r="I60" s="125" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="61" spans="2:9" ht="148.5">
-      <c r="B61" s="188"/>
+      <c r="B61" s="161"/>
       <c r="C61" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="D61" s="29" t="s">
         <v>87</v>
-      </c>
-      <c r="D61" s="29" t="s">
-        <v>88</v>
       </c>
       <c r="E61" s="30"/>
       <c r="F61" s="73"/>
       <c r="G61" s="73" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H61" s="103"/>
-      <c r="I61" s="136"/>
+      <c r="I61" s="126"/>
     </row>
     <row r="62" spans="2:9" ht="181.5">
-      <c r="B62" s="188"/>
+      <c r="B62" s="161"/>
       <c r="C62" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="D62" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="D62" s="29" t="s">
+      <c r="E62" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="E62" s="30" t="s">
+      <c r="F62" s="109" t="s">
+        <v>199</v>
+      </c>
+      <c r="G62" s="87" t="s">
+        <v>191</v>
+      </c>
+      <c r="H62" s="112" t="s">
+        <v>203</v>
+      </c>
+      <c r="I62" s="126"/>
+    </row>
+    <row r="63" spans="2:9" ht="33">
+      <c r="B63" s="161"/>
+      <c r="C63" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="F62" s="109" t="s">
-        <v>201</v>
-      </c>
-      <c r="G62" s="87" t="s">
-        <v>196</v>
-      </c>
-      <c r="H62" s="112" t="s">
-        <v>188</v>
-      </c>
-      <c r="I62" s="136"/>
-    </row>
-    <row r="63" spans="2:9" ht="33">
-      <c r="B63" s="188"/>
-      <c r="C63" s="28" t="s">
+      <c r="D63" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="D63" s="29" t="s">
-        <v>93</v>
-      </c>
       <c r="E63" s="30" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F63" s="30"/>
       <c r="G63" s="30" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="H63" s="104"/>
-      <c r="I63" s="136"/>
+      <c r="I63" s="126"/>
     </row>
     <row r="64" spans="2:9" ht="82.5">
-      <c r="B64" s="188"/>
+      <c r="B64" s="161"/>
       <c r="C64" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="D64" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="D64" s="29" t="s">
+      <c r="E64" s="30" t="s">
         <v>96</v>
-      </c>
-      <c r="E64" s="30" t="s">
-        <v>97</v>
       </c>
       <c r="F64" s="30"/>
       <c r="G64" s="76" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H64" s="105"/>
-      <c r="I64" s="137"/>
+      <c r="I64" s="127"/>
     </row>
     <row r="65" spans="2:9" ht="33.75" thickBot="1">
-      <c r="B65" s="189"/>
+      <c r="B65" s="162"/>
       <c r="C65" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="D65" s="113" t="s">
         <v>98</v>
       </c>
-      <c r="D65" s="113" t="s">
-        <v>99</v>
-      </c>
-      <c r="E65" s="115" t="s">
+      <c r="E65" s="213" t="s">
         <v>56</v>
       </c>
-      <c r="F65" s="116"/>
-      <c r="G65" s="116"/>
-      <c r="H65" s="116"/>
-      <c r="I65" s="117"/>
+      <c r="F65" s="214"/>
+      <c r="G65" s="214"/>
+      <c r="H65" s="214"/>
+      <c r="I65" s="215"/>
     </row>
   </sheetData>
   <mergeCells count="76">
+    <mergeCell ref="E65:I65"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="F25:F32"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="E58:I58"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="F46:F51"/>
+    <mergeCell ref="I54:I57"/>
+    <mergeCell ref="I38:I51"/>
+    <mergeCell ref="I23:I35"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="I8:I21"/>
+    <mergeCell ref="I4:I7"/>
+    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="H55:H56"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="H42:H45"/>
+    <mergeCell ref="G46:G51"/>
+    <mergeCell ref="H46:H51"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="D14:D21"/>
+    <mergeCell ref="G11:G13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="H11:H13"/>
+    <mergeCell ref="G14:G21"/>
+    <mergeCell ref="H14:H21"/>
+    <mergeCell ref="B3:B21"/>
+    <mergeCell ref="B23:B36"/>
+    <mergeCell ref="B60:B65"/>
+    <mergeCell ref="G4:G7"/>
+    <mergeCell ref="H4:H7"/>
+    <mergeCell ref="B54:B58"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="C46:C51"/>
+    <mergeCell ref="E46:E51"/>
+    <mergeCell ref="E52:I52"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="C42:C45"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="B38:B52"/>
+    <mergeCell ref="C38:C41"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="F40:F41"/>
     <mergeCell ref="C4:C7"/>
     <mergeCell ref="D4:D7"/>
     <mergeCell ref="F4:F7"/>
@@ -11427,66 +11774,6 @@
     <mergeCell ref="F33:F34"/>
     <mergeCell ref="G25:G32"/>
     <mergeCell ref="H25:H32"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="B38:B52"/>
-    <mergeCell ref="C38:C41"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="B3:B21"/>
-    <mergeCell ref="B23:B36"/>
-    <mergeCell ref="B60:B65"/>
-    <mergeCell ref="G4:G7"/>
-    <mergeCell ref="H4:H7"/>
-    <mergeCell ref="B54:B58"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="C46:C51"/>
-    <mergeCell ref="E46:E51"/>
-    <mergeCell ref="E52:I52"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="C42:C45"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="D14:D21"/>
-    <mergeCell ref="G11:G13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="H11:H13"/>
-    <mergeCell ref="G14:G21"/>
-    <mergeCell ref="H14:H21"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="I8:I21"/>
-    <mergeCell ref="I4:I7"/>
-    <mergeCell ref="G55:G56"/>
-    <mergeCell ref="H55:H56"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="H40:H41"/>
-    <mergeCell ref="H42:H45"/>
-    <mergeCell ref="G46:G51"/>
-    <mergeCell ref="H46:H51"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="E65:I65"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="F25:F32"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="E58:I58"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="F46:F51"/>
-    <mergeCell ref="I54:I57"/>
-    <mergeCell ref="I38:I51"/>
-    <mergeCell ref="I23:I35"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="G33:G34"/>
-    <mergeCell ref="H33:H34"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <hyperlinks>
@@ -11498,6 +11785,7 @@
     <hyperlink ref="E20" r:id="rId6" xr:uid="{E640EF3B-D28F-4372-820C-21868F7D842B}"/>
     <hyperlink ref="E30" r:id="rId7" xr:uid="{55CB4F8D-79D6-4086-834E-A7B97BDD0E0A}"/>
     <hyperlink ref="E31" r:id="rId8" xr:uid="{AAAAFA55-A7A9-4D9F-AA48-6828AF2613D3}"/>
+    <hyperlink ref="I60:I64" r:id="rId9" display="https://github.com/mulcamp-ed/ai-onboarding/tree/master/Day05" xr:uid="{311D5629-79A4-40B8-9A92-B2A35AB221AD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11524,17 +11812,17 @@
         <v>1</v>
       </c>
       <c r="E4" s="47" t="s">
+        <v>100</v>
+      </c>
+      <c r="F4" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="F4" s="47" t="s">
-        <v>102</v>
-      </c>
       <c r="G4" s="48" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="2:7" ht="33">
-      <c r="B5" s="241" t="s">
+      <c r="B5" s="233" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="54" t="s">
@@ -11544,55 +11832,55 @@
         <v>7</v>
       </c>
       <c r="E5" s="55" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F5" s="56" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G5" s="57"/>
     </row>
     <row r="6" spans="2:7">
-      <c r="B6" s="242"/>
-      <c r="C6" s="247" t="s">
+      <c r="B6" s="234"/>
+      <c r="C6" s="241" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="200" t="s">
+      <c r="D6" s="119" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="125" t="s">
+      <c r="E6" s="122" t="s">
+        <v>102</v>
+      </c>
+      <c r="F6" s="163" t="s">
         <v>103</v>
       </c>
-      <c r="F6" s="155" t="s">
-        <v>104</v>
-      </c>
-      <c r="G6" s="238"/>
+      <c r="G6" s="230"/>
     </row>
     <row r="7" spans="2:7">
-      <c r="B7" s="242"/>
-      <c r="C7" s="248"/>
-      <c r="D7" s="201"/>
-      <c r="E7" s="167"/>
-      <c r="F7" s="190"/>
-      <c r="G7" s="239"/>
+      <c r="B7" s="234"/>
+      <c r="C7" s="242"/>
+      <c r="D7" s="120"/>
+      <c r="E7" s="123"/>
+      <c r="F7" s="164"/>
+      <c r="G7" s="231"/>
     </row>
     <row r="8" spans="2:7">
-      <c r="B8" s="242"/>
-      <c r="C8" s="248"/>
-      <c r="D8" s="201"/>
-      <c r="E8" s="167"/>
-      <c r="F8" s="190"/>
-      <c r="G8" s="239"/>
+      <c r="B8" s="234"/>
+      <c r="C8" s="242"/>
+      <c r="D8" s="120"/>
+      <c r="E8" s="123"/>
+      <c r="F8" s="164"/>
+      <c r="G8" s="231"/>
     </row>
     <row r="9" spans="2:7">
-      <c r="B9" s="242"/>
-      <c r="C9" s="252"/>
-      <c r="D9" s="219"/>
-      <c r="E9" s="126"/>
-      <c r="F9" s="191"/>
-      <c r="G9" s="240"/>
+      <c r="B9" s="234"/>
+      <c r="C9" s="246"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="138"/>
+      <c r="F9" s="165"/>
+      <c r="G9" s="232"/>
     </row>
     <row r="10" spans="2:7" ht="33">
-      <c r="B10" s="242"/>
+      <c r="B10" s="234"/>
       <c r="C10" s="58" t="s">
         <v>16</v>
       </c>
@@ -11601,164 +11889,169 @@
       </c>
       <c r="E10" s="45"/>
       <c r="F10" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="G10" s="52"/>
+    </row>
+    <row r="11" spans="2:7">
+      <c r="B11" s="234"/>
+      <c r="C11" s="241" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="136" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="122" t="s">
+        <v>107</v>
+      </c>
+      <c r="F11" s="239" t="s">
+        <v>119</v>
+      </c>
+      <c r="G11" s="250" t="s">
         <v>110</v>
       </c>
-      <c r="G10" s="52"/>
-    </row>
-    <row r="11" spans="2:7">
-      <c r="B11" s="242"/>
-      <c r="C11" s="247" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="223" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="125" t="s">
+    </row>
+    <row r="12" spans="2:7">
+      <c r="B12" s="234"/>
+      <c r="C12" s="242"/>
+      <c r="D12" s="245"/>
+      <c r="E12" s="123"/>
+      <c r="F12" s="240"/>
+      <c r="G12" s="251"/>
+    </row>
+    <row r="13" spans="2:7" ht="286.7" customHeight="1">
+      <c r="B13" s="234"/>
+      <c r="C13" s="244"/>
+      <c r="D13" s="137"/>
+      <c r="E13" s="138"/>
+      <c r="F13" s="202"/>
+      <c r="G13" s="252"/>
+    </row>
+    <row r="14" spans="2:7" ht="35.1" customHeight="1">
+      <c r="B14" s="234"/>
+      <c r="C14" s="241" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="236" t="s">
+        <v>116</v>
+      </c>
+      <c r="E14" s="122" t="s">
         <v>108</v>
       </c>
-      <c r="F11" s="229" t="s">
-        <v>120</v>
-      </c>
-      <c r="G11" s="256" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7">
-      <c r="B12" s="242"/>
-      <c r="C12" s="248"/>
-      <c r="D12" s="251"/>
-      <c r="E12" s="167"/>
-      <c r="F12" s="230"/>
-      <c r="G12" s="257"/>
-    </row>
-    <row r="13" spans="2:7" ht="286.7" customHeight="1">
-      <c r="B13" s="242"/>
-      <c r="C13" s="250"/>
-      <c r="D13" s="224"/>
-      <c r="E13" s="126"/>
-      <c r="F13" s="152"/>
-      <c r="G13" s="258"/>
-    </row>
-    <row r="14" spans="2:7" ht="35.1" customHeight="1">
-      <c r="B14" s="242"/>
-      <c r="C14" s="247" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="244" t="s">
+      <c r="F14" s="239" t="s">
         <v>117</v>
       </c>
-      <c r="E14" s="125" t="s">
-        <v>109</v>
-      </c>
-      <c r="F14" s="229" t="s">
-        <v>118</v>
-      </c>
-      <c r="G14" s="231" t="s">
-        <v>114</v>
+      <c r="G14" s="253" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="2:7">
-      <c r="B15" s="242"/>
-      <c r="C15" s="248"/>
-      <c r="D15" s="245"/>
-      <c r="E15" s="167"/>
-      <c r="F15" s="230"/>
-      <c r="G15" s="232"/>
+      <c r="B15" s="234"/>
+      <c r="C15" s="242"/>
+      <c r="D15" s="237"/>
+      <c r="E15" s="123"/>
+      <c r="F15" s="240"/>
+      <c r="G15" s="254"/>
     </row>
     <row r="16" spans="2:7" ht="134.65" customHeight="1">
-      <c r="B16" s="242"/>
-      <c r="C16" s="250"/>
-      <c r="D16" s="246"/>
-      <c r="E16" s="126"/>
-      <c r="F16" s="152"/>
-      <c r="G16" s="233"/>
+      <c r="B16" s="234"/>
+      <c r="C16" s="244"/>
+      <c r="D16" s="238"/>
+      <c r="E16" s="138"/>
+      <c r="F16" s="202"/>
+      <c r="G16" s="255"/>
     </row>
     <row r="17" spans="2:7" ht="35.1" customHeight="1">
-      <c r="B17" s="242"/>
-      <c r="C17" s="247" t="s">
+      <c r="B17" s="234"/>
+      <c r="C17" s="241" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="125" t="s">
-        <v>100</v>
-      </c>
-      <c r="E17" s="200" t="s">
-        <v>105</v>
-      </c>
-      <c r="F17" s="253" t="s">
-        <v>123</v>
-      </c>
-      <c r="G17" s="235" t="s">
-        <v>113</v>
+      <c r="D17" s="122" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17" s="119" t="s">
+        <v>104</v>
+      </c>
+      <c r="F17" s="247" t="s">
+        <v>122</v>
+      </c>
+      <c r="G17" s="257" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="242"/>
-      <c r="C18" s="248"/>
-      <c r="D18" s="167"/>
-      <c r="E18" s="201"/>
-      <c r="F18" s="254"/>
-      <c r="G18" s="236"/>
+      <c r="B18" s="234"/>
+      <c r="C18" s="242"/>
+      <c r="D18" s="123"/>
+      <c r="E18" s="120"/>
+      <c r="F18" s="248"/>
+      <c r="G18" s="258"/>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="242"/>
-      <c r="C19" s="248"/>
-      <c r="D19" s="167"/>
-      <c r="E19" s="201"/>
-      <c r="F19" s="254"/>
-      <c r="G19" s="236"/>
+      <c r="B19" s="234"/>
+      <c r="C19" s="242"/>
+      <c r="D19" s="123"/>
+      <c r="E19" s="120"/>
+      <c r="F19" s="248"/>
+      <c r="G19" s="258"/>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="242"/>
-      <c r="C20" s="248"/>
-      <c r="D20" s="167"/>
-      <c r="E20" s="201"/>
-      <c r="F20" s="254"/>
-      <c r="G20" s="236"/>
+      <c r="B20" s="234"/>
+      <c r="C20" s="242"/>
+      <c r="D20" s="123"/>
+      <c r="E20" s="120"/>
+      <c r="F20" s="248"/>
+      <c r="G20" s="258"/>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="242"/>
-      <c r="C21" s="248"/>
-      <c r="D21" s="167"/>
-      <c r="E21" s="201"/>
-      <c r="F21" s="254"/>
-      <c r="G21" s="236"/>
+      <c r="B21" s="234"/>
+      <c r="C21" s="242"/>
+      <c r="D21" s="123"/>
+      <c r="E21" s="120"/>
+      <c r="F21" s="248"/>
+      <c r="G21" s="258"/>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="242"/>
-      <c r="C22" s="248"/>
-      <c r="D22" s="167"/>
-      <c r="E22" s="201"/>
-      <c r="F22" s="254"/>
-      <c r="G22" s="236"/>
+      <c r="B22" s="234"/>
+      <c r="C22" s="242"/>
+      <c r="D22" s="123"/>
+      <c r="E22" s="120"/>
+      <c r="F22" s="248"/>
+      <c r="G22" s="258"/>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="242"/>
-      <c r="C23" s="248"/>
-      <c r="D23" s="167"/>
-      <c r="E23" s="201"/>
-      <c r="F23" s="254"/>
-      <c r="G23" s="236"/>
+      <c r="B23" s="234"/>
+      <c r="C23" s="242"/>
+      <c r="D23" s="123"/>
+      <c r="E23" s="120"/>
+      <c r="F23" s="248"/>
+      <c r="G23" s="258"/>
     </row>
     <row r="24" spans="2:7" ht="85.7" customHeight="1" thickBot="1">
-      <c r="B24" s="243"/>
-      <c r="C24" s="249"/>
-      <c r="D24" s="168"/>
-      <c r="E24" s="234"/>
-      <c r="F24" s="255"/>
-      <c r="G24" s="237"/>
+      <c r="B24" s="235"/>
+      <c r="C24" s="243"/>
+      <c r="D24" s="177"/>
+      <c r="E24" s="256"/>
+      <c r="F24" s="249"/>
+      <c r="G24" s="259"/>
     </row>
     <row r="28" spans="2:7">
       <c r="F28" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" spans="2:7">
       <c r="F29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="E17:E24"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="G17:G24"/>
     <mergeCell ref="G6:G9"/>
     <mergeCell ref="B5:B24"/>
     <mergeCell ref="D17:D24"/>
@@ -11775,11 +12068,6 @@
     <mergeCell ref="F6:F9"/>
     <mergeCell ref="F17:F24"/>
     <mergeCell ref="G11:G13"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="E17:E24"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="G17:G24"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11809,145 +12097,145 @@
         <v>1</v>
       </c>
       <c r="E2" s="47" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="47" t="s">
-        <v>102</v>
-      </c>
       <c r="G2" s="48" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="70.349999999999994" customHeight="1">
-      <c r="B3" s="187" t="s">
+      <c r="B3" s="160" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="260" t="s">
+      <c r="C3" s="273" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="264" t="s">
-        <v>116</v>
-      </c>
-      <c r="E3" s="266" t="s">
+      <c r="D3" s="276" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" s="278" t="s">
+        <v>120</v>
+      </c>
+      <c r="F3" s="201" t="s">
+        <v>133</v>
+      </c>
+      <c r="G3" s="274" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="83.1" customHeight="1">
+      <c r="B4" s="161"/>
+      <c r="C4" s="266"/>
+      <c r="D4" s="277"/>
+      <c r="E4" s="143"/>
+      <c r="F4" s="202"/>
+      <c r="G4" s="275"/>
+    </row>
+    <row r="5" spans="2:7" ht="105.4" customHeight="1">
+      <c r="B5" s="161"/>
+      <c r="C5" s="264" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="175" t="s">
         <v>121</v>
       </c>
-      <c r="F3" s="151" t="s">
-        <v>134</v>
-      </c>
-      <c r="G3" s="262" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="83.1" customHeight="1">
-      <c r="B4" s="188"/>
-      <c r="C4" s="261"/>
-      <c r="D4" s="265"/>
-      <c r="E4" s="148"/>
-      <c r="F4" s="152"/>
-      <c r="G4" s="263"/>
-    </row>
-    <row r="5" spans="2:7" ht="105.4" customHeight="1">
-      <c r="B5" s="188"/>
-      <c r="C5" s="267" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="206" t="s">
-        <v>122</v>
-      </c>
-      <c r="E5" s="271" t="s">
+      <c r="E5" s="260" t="s">
+        <v>127</v>
+      </c>
+      <c r="F5" s="141" t="s">
+        <v>123</v>
+      </c>
+      <c r="G5" s="279" t="s">
         <v>128</v>
       </c>
-      <c r="F5" s="147" t="s">
+    </row>
+    <row r="6" spans="2:7">
+      <c r="B6" s="161"/>
+      <c r="C6" s="265"/>
+      <c r="D6" s="263"/>
+      <c r="E6" s="261"/>
+      <c r="F6" s="142"/>
+      <c r="G6" s="280"/>
+    </row>
+    <row r="7" spans="2:7">
+      <c r="B7" s="161"/>
+      <c r="C7" s="265"/>
+      <c r="D7" s="263"/>
+      <c r="E7" s="261"/>
+      <c r="F7" s="142"/>
+      <c r="G7" s="280"/>
+    </row>
+    <row r="8" spans="2:7">
+      <c r="B8" s="161"/>
+      <c r="C8" s="265"/>
+      <c r="D8" s="263"/>
+      <c r="E8" s="261"/>
+      <c r="F8" s="142"/>
+      <c r="G8" s="280"/>
+    </row>
+    <row r="9" spans="2:7">
+      <c r="B9" s="161"/>
+      <c r="C9" s="265"/>
+      <c r="D9" s="263"/>
+      <c r="E9" s="261"/>
+      <c r="F9" s="142"/>
+      <c r="G9" s="280"/>
+    </row>
+    <row r="10" spans="2:7">
+      <c r="B10" s="161"/>
+      <c r="C10" s="265"/>
+      <c r="D10" s="263"/>
+      <c r="E10" s="261"/>
+      <c r="F10" s="142"/>
+      <c r="G10" s="280"/>
+    </row>
+    <row r="11" spans="2:7">
+      <c r="B11" s="161"/>
+      <c r="C11" s="265"/>
+      <c r="D11" s="263"/>
+      <c r="E11" s="261"/>
+      <c r="F11" s="142"/>
+      <c r="G11" s="280"/>
+    </row>
+    <row r="12" spans="2:7">
+      <c r="B12" s="161"/>
+      <c r="C12" s="266"/>
+      <c r="D12" s="176"/>
+      <c r="E12" s="262"/>
+      <c r="F12" s="143"/>
+      <c r="G12" s="271"/>
+    </row>
+    <row r="13" spans="2:7" ht="138.94999999999999" customHeight="1">
+      <c r="B13" s="161"/>
+      <c r="C13" s="264" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="175" t="s">
+        <v>125</v>
+      </c>
+      <c r="E13" s="119" t="s">
         <v>124</v>
       </c>
-      <c r="G5" s="268" t="s">
+      <c r="F13" s="228" t="s">
+        <v>126</v>
+      </c>
+      <c r="G13" s="270" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
-      <c r="B6" s="188"/>
-      <c r="C6" s="275"/>
-      <c r="D6" s="274"/>
-      <c r="E6" s="272"/>
-      <c r="F6" s="227"/>
-      <c r="G6" s="269"/>
-    </row>
-    <row r="7" spans="2:7">
-      <c r="B7" s="188"/>
-      <c r="C7" s="275"/>
-      <c r="D7" s="274"/>
-      <c r="E7" s="272"/>
-      <c r="F7" s="227"/>
-      <c r="G7" s="269"/>
-    </row>
-    <row r="8" spans="2:7">
-      <c r="B8" s="188"/>
-      <c r="C8" s="275"/>
-      <c r="D8" s="274"/>
-      <c r="E8" s="272"/>
-      <c r="F8" s="227"/>
-      <c r="G8" s="269"/>
-    </row>
-    <row r="9" spans="2:7">
-      <c r="B9" s="188"/>
-      <c r="C9" s="275"/>
-      <c r="D9" s="274"/>
-      <c r="E9" s="272"/>
-      <c r="F9" s="227"/>
-      <c r="G9" s="269"/>
-    </row>
-    <row r="10" spans="2:7">
-      <c r="B10" s="188"/>
-      <c r="C10" s="275"/>
-      <c r="D10" s="274"/>
-      <c r="E10" s="272"/>
-      <c r="F10" s="227"/>
-      <c r="G10" s="269"/>
-    </row>
-    <row r="11" spans="2:7">
-      <c r="B11" s="188"/>
-      <c r="C11" s="275"/>
-      <c r="D11" s="274"/>
-      <c r="E11" s="272"/>
-      <c r="F11" s="227"/>
-      <c r="G11" s="269"/>
-    </row>
-    <row r="12" spans="2:7">
-      <c r="B12" s="188"/>
-      <c r="C12" s="261"/>
-      <c r="D12" s="207"/>
-      <c r="E12" s="273"/>
-      <c r="F12" s="148"/>
-      <c r="G12" s="270"/>
-    </row>
-    <row r="13" spans="2:7" ht="138.94999999999999" customHeight="1">
-      <c r="B13" s="188"/>
-      <c r="C13" s="267" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="206" t="s">
-        <v>126</v>
-      </c>
-      <c r="E13" s="200" t="s">
-        <v>125</v>
-      </c>
-      <c r="F13" s="208" t="s">
-        <v>127</v>
-      </c>
-      <c r="G13" s="279" t="s">
-        <v>130</v>
-      </c>
-    </row>
     <row r="14" spans="2:7">
-      <c r="B14" s="188"/>
-      <c r="C14" s="261"/>
-      <c r="D14" s="207"/>
-      <c r="E14" s="202"/>
-      <c r="F14" s="209"/>
-      <c r="G14" s="270"/>
+      <c r="B14" s="161"/>
+      <c r="C14" s="266"/>
+      <c r="D14" s="176"/>
+      <c r="E14" s="170"/>
+      <c r="F14" s="229"/>
+      <c r="G14" s="271"/>
     </row>
     <row r="15" spans="2:7" ht="95.65" customHeight="1">
-      <c r="B15" s="188"/>
+      <c r="B15" s="161"/>
       <c r="C15" s="28" t="s">
         <v>50</v>
       </c>
@@ -11958,66 +12246,66 @@
         <v>52</v>
       </c>
       <c r="F15" s="63" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G15" s="64" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="17.25" thickBot="1">
-      <c r="B16" s="189"/>
+      <c r="B16" s="162"/>
       <c r="C16" s="31" t="s">
         <v>54</v>
       </c>
       <c r="D16" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="E16" s="276" t="s">
+      <c r="E16" s="267" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="277"/>
-      <c r="G16" s="278"/>
+      <c r="F16" s="268"/>
+      <c r="G16" s="269"/>
     </row>
     <row r="32" ht="17.25" thickBot="1"/>
     <row r="33" spans="8:8">
-      <c r="H33" s="133" t="s">
+      <c r="H33" s="125" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="34" spans="8:8">
-      <c r="H34" s="136"/>
+      <c r="H34" s="126"/>
     </row>
     <row r="35" spans="8:8">
-      <c r="H35" s="136"/>
+      <c r="H35" s="126"/>
     </row>
     <row r="36" spans="8:8">
-      <c r="H36" s="136"/>
+      <c r="H36" s="126"/>
     </row>
     <row r="37" spans="8:8">
-      <c r="H37" s="136"/>
+      <c r="H37" s="126"/>
     </row>
     <row r="38" spans="8:8">
-      <c r="H38" s="136"/>
+      <c r="H38" s="126"/>
     </row>
     <row r="39" spans="8:8">
-      <c r="H39" s="136"/>
+      <c r="H39" s="126"/>
     </row>
     <row r="40" spans="8:8">
-      <c r="H40" s="136"/>
+      <c r="H40" s="126"/>
     </row>
     <row r="41" spans="8:8">
-      <c r="H41" s="136"/>
+      <c r="H41" s="126"/>
     </row>
     <row r="42" spans="8:8">
-      <c r="H42" s="137"/>
+      <c r="H42" s="127"/>
     </row>
     <row r="43" spans="8:8">
-      <c r="H43" s="259" t="s">
+      <c r="H43" s="272" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="44" spans="8:8">
-      <c r="H44" s="137"/>
+      <c r="H44" s="127"/>
     </row>
     <row r="45" spans="8:8">
       <c r="H45" s="59" t="s">
@@ -12029,12 +12317,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B3:B16"/>
-    <mergeCell ref="E5:E12"/>
-    <mergeCell ref="D5:D12"/>
-    <mergeCell ref="C5:C12"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="G13:G14"/>
     <mergeCell ref="H33:H42"/>
     <mergeCell ref="H43:H44"/>
     <mergeCell ref="C3:C4"/>
@@ -12048,6 +12330,12 @@
     <mergeCell ref="E13:E14"/>
     <mergeCell ref="F13:F14"/>
     <mergeCell ref="G5:G12"/>
+    <mergeCell ref="B3:B16"/>
+    <mergeCell ref="E5:E12"/>
+    <mergeCell ref="D5:D12"/>
+    <mergeCell ref="C5:C12"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="G13:G14"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <hyperlinks>
@@ -12080,174 +12368,184 @@
         <v>1</v>
       </c>
       <c r="E2" s="47" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="47" t="s">
-        <v>102</v>
-      </c>
       <c r="G2" s="48" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="35.1" customHeight="1">
-      <c r="B3" s="187" t="s">
+      <c r="B3" s="160" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="260" t="s">
+      <c r="C3" s="273" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="286" t="s">
+      <c r="D3" s="283" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3" s="154" t="s">
+        <v>134</v>
+      </c>
+      <c r="F3" s="201" t="s">
+        <v>143</v>
+      </c>
+      <c r="G3" s="281" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="182.1" customHeight="1">
+      <c r="B4" s="161"/>
+      <c r="C4" s="265"/>
+      <c r="D4" s="284"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="202"/>
+      <c r="G4" s="282"/>
+    </row>
+    <row r="5" spans="2:7">
+      <c r="B5" s="161"/>
+      <c r="C5" s="265"/>
+      <c r="D5" s="155" t="s">
+        <v>136</v>
+      </c>
+      <c r="E5" s="181" t="s">
+        <v>137</v>
+      </c>
+      <c r="F5" s="163" t="s">
+        <v>144</v>
+      </c>
+      <c r="G5" s="250" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="86.1" customHeight="1">
+      <c r="B6" s="161"/>
+      <c r="C6" s="266"/>
+      <c r="D6" s="156"/>
+      <c r="E6" s="132"/>
+      <c r="F6" s="174"/>
+      <c r="G6" s="288"/>
+    </row>
+    <row r="7" spans="2:7">
+      <c r="B7" s="161"/>
+      <c r="C7" s="264" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="175" t="s">
+        <v>135</v>
+      </c>
+      <c r="E7" s="218" t="s">
         <v>139</v>
       </c>
-      <c r="E3" s="213" t="s">
-        <v>135</v>
-      </c>
-      <c r="F3" s="151" t="s">
-        <v>144</v>
-      </c>
-      <c r="G3" s="284" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="182.1" customHeight="1">
-      <c r="B4" s="188"/>
-      <c r="C4" s="275"/>
-      <c r="D4" s="287"/>
-      <c r="E4" s="131"/>
-      <c r="F4" s="152"/>
-      <c r="G4" s="285"/>
-    </row>
-    <row r="5" spans="2:7">
-      <c r="B5" s="188"/>
-      <c r="C5" s="275"/>
-      <c r="D5" s="214" t="s">
-        <v>137</v>
-      </c>
-      <c r="E5" s="170" t="s">
-        <v>138</v>
-      </c>
-      <c r="F5" s="155" t="s">
-        <v>145</v>
-      </c>
-      <c r="G5" s="256" t="s">
+      <c r="F7" s="163" t="s">
+        <v>140</v>
+      </c>
+      <c r="G7" s="287" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="86.1" customHeight="1">
-      <c r="B6" s="188"/>
-      <c r="C6" s="261"/>
-      <c r="D6" s="215"/>
-      <c r="E6" s="124"/>
-      <c r="F6" s="156"/>
-      <c r="G6" s="291"/>
-    </row>
-    <row r="7" spans="2:7">
-      <c r="B7" s="188"/>
-      <c r="C7" s="267" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="206" t="s">
-        <v>136</v>
-      </c>
-      <c r="E7" s="120" t="s">
-        <v>140</v>
-      </c>
-      <c r="F7" s="155" t="s">
+    <row r="8" spans="2:7" ht="102.95" customHeight="1">
+      <c r="B8" s="161"/>
+      <c r="C8" s="265"/>
+      <c r="D8" s="176"/>
+      <c r="E8" s="220"/>
+      <c r="F8" s="174"/>
+      <c r="G8" s="287"/>
+    </row>
+    <row r="9" spans="2:7">
+      <c r="B9" s="161"/>
+      <c r="C9" s="265"/>
+      <c r="D9" s="147" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="122" t="s">
         <v>141</v>
       </c>
-      <c r="G7" s="290" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" ht="102.95" customHeight="1">
-      <c r="B8" s="188"/>
-      <c r="C8" s="275"/>
-      <c r="D8" s="207"/>
-      <c r="E8" s="122"/>
-      <c r="F8" s="156"/>
-      <c r="G8" s="290"/>
-    </row>
-    <row r="9" spans="2:7">
-      <c r="B9" s="188"/>
-      <c r="C9" s="275"/>
-      <c r="D9" s="197" t="s">
-        <v>67</v>
-      </c>
-      <c r="E9" s="125" t="s">
+      <c r="F9" s="226" t="s">
+        <v>186</v>
+      </c>
+      <c r="G9" s="287"/>
+    </row>
+    <row r="10" spans="2:7" ht="175.35" customHeight="1">
+      <c r="B10" s="161"/>
+      <c r="C10" s="266"/>
+      <c r="D10" s="148"/>
+      <c r="E10" s="138"/>
+      <c r="F10" s="227"/>
+      <c r="G10" s="288"/>
+    </row>
+    <row r="11" spans="2:7" ht="17.649999999999999" customHeight="1">
+      <c r="B11" s="161"/>
+      <c r="C11" s="264" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" s="289" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="119" t="s">
         <v>142</v>
       </c>
-      <c r="F9" s="138" t="s">
-        <v>190</v>
-      </c>
-      <c r="G9" s="290"/>
-    </row>
-    <row r="10" spans="2:7" ht="175.35" customHeight="1">
-      <c r="B10" s="188"/>
-      <c r="C10" s="261"/>
-      <c r="D10" s="198"/>
-      <c r="E10" s="126"/>
-      <c r="F10" s="139"/>
-      <c r="G10" s="291"/>
-    </row>
-    <row r="11" spans="2:7" ht="17.649999999999999" customHeight="1">
-      <c r="B11" s="188"/>
-      <c r="C11" s="267" t="s">
-        <v>68</v>
-      </c>
-      <c r="D11" s="280" t="s">
-        <v>69</v>
-      </c>
-      <c r="E11" s="200" t="s">
-        <v>143</v>
-      </c>
-      <c r="F11" s="158" t="s">
-        <v>198</v>
-      </c>
-      <c r="G11" s="288"/>
+      <c r="F11" s="206" t="s">
+        <v>193</v>
+      </c>
+      <c r="G11" s="285"/>
     </row>
     <row r="12" spans="2:7" ht="28.35" customHeight="1">
-      <c r="B12" s="188"/>
-      <c r="C12" s="275"/>
-      <c r="D12" s="281"/>
-      <c r="E12" s="201"/>
-      <c r="F12" s="159"/>
-      <c r="G12" s="288"/>
+      <c r="B12" s="161"/>
+      <c r="C12" s="265"/>
+      <c r="D12" s="290"/>
+      <c r="E12" s="120"/>
+      <c r="F12" s="207"/>
+      <c r="G12" s="285"/>
     </row>
     <row r="13" spans="2:7" ht="42.4" customHeight="1">
-      <c r="B13" s="188"/>
-      <c r="C13" s="275"/>
-      <c r="D13" s="281"/>
-      <c r="E13" s="201"/>
-      <c r="F13" s="159"/>
-      <c r="G13" s="288"/>
+      <c r="B13" s="161"/>
+      <c r="C13" s="265"/>
+      <c r="D13" s="290"/>
+      <c r="E13" s="120"/>
+      <c r="F13" s="207"/>
+      <c r="G13" s="285"/>
     </row>
     <row r="14" spans="2:7">
-      <c r="B14" s="188"/>
-      <c r="C14" s="275"/>
-      <c r="D14" s="281"/>
-      <c r="E14" s="201"/>
-      <c r="F14" s="159"/>
-      <c r="G14" s="288"/>
+      <c r="B14" s="161"/>
+      <c r="C14" s="265"/>
+      <c r="D14" s="290"/>
+      <c r="E14" s="120"/>
+      <c r="F14" s="207"/>
+      <c r="G14" s="285"/>
     </row>
     <row r="15" spans="2:7">
-      <c r="B15" s="188"/>
-      <c r="C15" s="275"/>
-      <c r="D15" s="281"/>
-      <c r="E15" s="201"/>
-      <c r="F15" s="159"/>
-      <c r="G15" s="288"/>
+      <c r="B15" s="161"/>
+      <c r="C15" s="265"/>
+      <c r="D15" s="290"/>
+      <c r="E15" s="120"/>
+      <c r="F15" s="207"/>
+      <c r="G15" s="285"/>
     </row>
     <row r="16" spans="2:7" ht="115.35" customHeight="1" thickBot="1">
-      <c r="B16" s="189"/>
-      <c r="C16" s="283"/>
-      <c r="D16" s="282"/>
-      <c r="E16" s="234"/>
-      <c r="F16" s="160"/>
-      <c r="G16" s="289"/>
+      <c r="B16" s="162"/>
+      <c r="C16" s="292"/>
+      <c r="D16" s="291"/>
+      <c r="E16" s="256"/>
+      <c r="F16" s="208"/>
+      <c r="G16" s="286"/>
     </row>
     <row r="17" ht="17.649999999999999" customHeight="1"/>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="B3:B16"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="D11:D16"/>
+    <mergeCell ref="F11:F16"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="C11:C16"/>
+    <mergeCell ref="C7:C10"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="F5:F6"/>
@@ -12261,16 +12559,6 @@
     <mergeCell ref="E11:E16"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="B3:B16"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="D11:D16"/>
-    <mergeCell ref="F11:F16"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="C11:C16"/>
-    <mergeCell ref="C7:C10"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12299,17 +12587,17 @@
         <v>1</v>
       </c>
       <c r="E2" s="47" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="47" t="s">
-        <v>102</v>
-      </c>
       <c r="G2" s="48" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="103.35" customHeight="1">
-      <c r="B3" s="187" t="s">
+      <c r="B3" s="160" t="s">
         <v>75</v>
       </c>
       <c r="C3" s="40" t="s">
@@ -12322,63 +12610,63 @@
         <v>78</v>
       </c>
       <c r="F3" s="69" t="s">
+        <v>152</v>
+      </c>
+      <c r="G3" s="70" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="69.95" customHeight="1">
+      <c r="B4" s="161"/>
+      <c r="C4" s="264" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="71" t="s">
+        <v>151</v>
+      </c>
+      <c r="E4" s="169" t="s">
         <v>153</v>
       </c>
-      <c r="G3" s="70" t="s">
+      <c r="F4" s="141" t="s">
+        <v>154</v>
+      </c>
+      <c r="G4" s="250" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="98.1" customHeight="1">
+      <c r="B5" s="161"/>
+      <c r="C5" s="266"/>
+      <c r="D5" s="67" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="4" spans="2:7" ht="69.95" customHeight="1">
-      <c r="B4" s="188"/>
-      <c r="C4" s="267" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="71" t="s">
-        <v>152</v>
-      </c>
-      <c r="E4" s="130" t="s">
-        <v>154</v>
-      </c>
-      <c r="F4" s="147" t="s">
+      <c r="E5" s="146"/>
+      <c r="F5" s="143"/>
+      <c r="G5" s="288"/>
+    </row>
+    <row r="6" spans="2:7" ht="125.25" customHeight="1">
+      <c r="B6" s="161"/>
+      <c r="C6" s="264" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="289" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="293" t="s">
+        <v>162</v>
+      </c>
+      <c r="F6" s="141" t="s">
         <v>155</v>
       </c>
-      <c r="G4" s="256" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="98.1" customHeight="1">
-      <c r="B5" s="188"/>
-      <c r="C5" s="261"/>
-      <c r="D5" s="67" t="s">
-        <v>151</v>
-      </c>
-      <c r="E5" s="131"/>
-      <c r="F5" s="148"/>
-      <c r="G5" s="291"/>
-    </row>
-    <row r="6" spans="2:7" ht="125.25" customHeight="1">
-      <c r="B6" s="188"/>
-      <c r="C6" s="267" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" s="280" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" s="292" t="s">
-        <v>163</v>
-      </c>
-      <c r="F6" s="147" t="s">
-        <v>156</v>
-      </c>
-      <c r="G6" s="294"/>
+      <c r="G6" s="295"/>
     </row>
     <row r="7" spans="2:7" ht="17.25" thickBot="1">
-      <c r="B7" s="189"/>
-      <c r="C7" s="283"/>
-      <c r="D7" s="282"/>
-      <c r="E7" s="203"/>
-      <c r="F7" s="293"/>
-      <c r="G7" s="295"/>
+      <c r="B7" s="162"/>
+      <c r="C7" s="292"/>
+      <c r="D7" s="291"/>
+      <c r="E7" s="171"/>
+      <c r="F7" s="294"/>
+      <c r="G7" s="296"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -12420,121 +12708,121 @@
         <v>1</v>
       </c>
       <c r="E2" s="47" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="47" t="s">
-        <v>102</v>
-      </c>
       <c r="G2" s="48" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="165.4" customHeight="1">
-      <c r="B3" s="187" t="s">
+      <c r="B3" s="160" t="s">
+        <v>157</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="E3" s="42" t="s">
         <v>158</v>
       </c>
-      <c r="C3" s="40" t="s">
-        <v>84</v>
-      </c>
-      <c r="D3" s="44" t="s">
-        <v>85</v>
-      </c>
-      <c r="E3" s="42" t="s">
+      <c r="F3" s="72" t="s">
+        <v>168</v>
+      </c>
+      <c r="G3" s="68"/>
+    </row>
+    <row r="4" spans="2:7" ht="162.94999999999999" customHeight="1">
+      <c r="B4" s="161"/>
+      <c r="C4" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="77" t="s">
+        <v>164</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="F4" s="73" t="s">
+        <v>167</v>
+      </c>
+      <c r="G4" s="65"/>
+    </row>
+    <row r="5" spans="2:7" ht="176.65" customHeight="1">
+      <c r="B5" s="161"/>
+      <c r="C5" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="F5" s="87" t="s">
+        <v>191</v>
+      </c>
+      <c r="G5" s="114" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="94.35" customHeight="1">
+      <c r="B6" s="161"/>
+      <c r="C6" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="F6" s="75" t="s">
+        <v>192</v>
+      </c>
+      <c r="G6" s="66"/>
+    </row>
+    <row r="7" spans="2:7" ht="82.5">
+      <c r="B7" s="161"/>
+      <c r="C7" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="E7" s="30" t="s">
         <v>159</v>
       </c>
-      <c r="F3" s="72" t="s">
-        <v>170</v>
-      </c>
-      <c r="G3" s="68"/>
-    </row>
-    <row r="4" spans="2:7" ht="162.94999999999999" customHeight="1">
-      <c r="B4" s="188"/>
-      <c r="C4" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="D4" s="77" t="s">
-        <v>165</v>
-      </c>
-      <c r="E4" s="30" t="s">
-        <v>164</v>
-      </c>
-      <c r="F4" s="73" t="s">
-        <v>169</v>
-      </c>
-      <c r="G4" s="65"/>
-    </row>
-    <row r="5" spans="2:7" ht="176.65" customHeight="1">
-      <c r="B5" s="188"/>
-      <c r="C5" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>90</v>
-      </c>
-      <c r="E5" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="F5" s="87" t="s">
-        <v>196</v>
-      </c>
-      <c r="G5" s="114" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="94.35" customHeight="1">
-      <c r="B6" s="188"/>
-      <c r="C6" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>93</v>
-      </c>
-      <c r="E6" s="30" t="s">
-        <v>94</v>
-      </c>
-      <c r="F6" s="75" t="s">
-        <v>197</v>
-      </c>
-      <c r="G6" s="66"/>
-    </row>
-    <row r="7" spans="2:7" ht="82.5">
-      <c r="B7" s="188"/>
-      <c r="C7" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="E7" s="30" t="s">
+      <c r="F7" s="76" t="s">
         <v>160</v>
       </c>
-      <c r="F7" s="76" t="s">
-        <v>161</v>
-      </c>
       <c r="G7" s="74"/>
     </row>
     <row r="8" spans="2:7" ht="17.25" thickBot="1">
-      <c r="B8" s="189"/>
+      <c r="B8" s="162"/>
       <c r="C8" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" s="39" t="s">
         <v>98</v>
       </c>
-      <c r="D8" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="E8" s="115" t="s">
+      <c r="E8" s="213" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="116"/>
-      <c r="G8" s="117"/>
+      <c r="F8" s="214"/>
+      <c r="G8" s="215"/>
     </row>
     <row r="11" spans="2:7">
       <c r="F11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="2:7">
       <c r="F12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>

--- a/16기_스타트캠프_강사 가이드 문서.xlsx
+++ b/16기_스타트캠프_강사 가이드 문서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ed\ai-onboarding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8EEA616-8E1A-4528-80BC-9E1149844B97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB1C0B49-7033-4DA5-ADBE-7ECF870551E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="30" windowWidth="28770" windowHeight="15450" activeTab="1" xr2:uid="{FD3BB604-1650-4EBB-871F-9010366B35B1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FD3BB604-1650-4EBB-871F-9010366B35B1}"/>
   </bookViews>
   <sheets>
     <sheet name="교육 목표 및 방향" sheetId="7" r:id="rId1"/>
@@ -1433,9 +1433,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">- 첫 가입자 50크레딧  </t>
-  </si>
-  <si>
     <t>-  github 신규 계정 필요)</t>
   </si>
   <si>
@@ -8057,6 +8054,69 @@
   </si>
   <si>
     <t>render 서비스 배포 가이드 문서</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>첫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가입자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>크레딧</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
@@ -9373,7 +9433,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="297">
+  <cellXfs count="298">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -9722,347 +9782,374 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="46" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="43" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -10091,12 +10178,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -10133,26 +10214,41 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="46" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="43" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
@@ -10166,15 +10262,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -10187,34 +10277,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10241,18 +10313,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -10264,6 +10324,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -10731,18 +10794,18 @@
         <v>3</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H2" s="47" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I2" s="106" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="33">
-      <c r="B3" s="157" t="s">
-        <v>165</v>
+      <c r="B3" s="184" t="s">
+        <v>164</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>6</v>
@@ -10750,74 +10813,74 @@
       <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="192" t="s">
+      <c r="E3" s="143" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="193"/>
+      <c r="F3" s="144"/>
       <c r="G3" s="56" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H3" s="56"/>
       <c r="I3" s="53"/>
     </row>
     <row r="4" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B4" s="158"/>
-      <c r="C4" s="116" t="s">
+      <c r="B4" s="185"/>
+      <c r="C4" s="217" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="119" t="s">
+      <c r="D4" s="203" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="122" t="s">
+      <c r="F4" s="126" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="163" t="s">
-        <v>103</v>
-      </c>
-      <c r="H4" s="166"/>
-      <c r="I4" s="197"/>
+      <c r="G4" s="158" t="s">
+        <v>102</v>
+      </c>
+      <c r="H4" s="195"/>
+      <c r="I4" s="148"/>
     </row>
     <row r="5" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B5" s="158"/>
-      <c r="C5" s="117"/>
-      <c r="D5" s="120"/>
+      <c r="B5" s="185"/>
+      <c r="C5" s="218"/>
+      <c r="D5" s="204"/>
       <c r="E5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="123"/>
-      <c r="G5" s="164"/>
-      <c r="H5" s="167"/>
-      <c r="I5" s="195"/>
+      <c r="F5" s="170"/>
+      <c r="G5" s="193"/>
+      <c r="H5" s="196"/>
+      <c r="I5" s="146"/>
     </row>
     <row r="6" spans="2:9">
-      <c r="B6" s="158"/>
-      <c r="C6" s="117"/>
-      <c r="D6" s="120"/>
+      <c r="B6" s="185"/>
+      <c r="C6" s="218"/>
+      <c r="D6" s="204"/>
       <c r="E6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="123"/>
-      <c r="G6" s="164"/>
-      <c r="H6" s="167"/>
-      <c r="I6" s="195"/>
+      <c r="F6" s="170"/>
+      <c r="G6" s="193"/>
+      <c r="H6" s="196"/>
+      <c r="I6" s="146"/>
     </row>
     <row r="7" spans="2:9">
-      <c r="B7" s="158"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="121"/>
+      <c r="B7" s="185"/>
+      <c r="C7" s="219"/>
+      <c r="D7" s="220"/>
       <c r="E7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="124"/>
-      <c r="G7" s="165"/>
-      <c r="H7" s="168"/>
-      <c r="I7" s="198"/>
+      <c r="F7" s="221"/>
+      <c r="G7" s="194"/>
+      <c r="H7" s="197"/>
+      <c r="I7" s="149"/>
     </row>
     <row r="8" spans="2:9" ht="53.1" customHeight="1">
-      <c r="B8" s="158"/>
+      <c r="B8" s="185"/>
       <c r="C8" s="7" t="s">
         <v>16</v>
       </c>
@@ -10827,48 +10890,48 @@
       <c r="E8" s="45"/>
       <c r="F8" s="9"/>
       <c r="G8" s="91" t="s">
+        <v>108</v>
+      </c>
+      <c r="H8" s="97"/>
+      <c r="I8" s="145" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="17.649999999999999" customHeight="1">
+      <c r="B9" s="185"/>
+      <c r="C9" s="217" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="224" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="126" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="119" t="s">
+        <v>173</v>
+      </c>
+      <c r="G9" s="168" t="s">
+        <v>118</v>
+      </c>
+      <c r="H9" s="166" t="s">
         <v>109</v>
       </c>
-      <c r="H8" s="97"/>
-      <c r="I8" s="194" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B9" s="158"/>
-      <c r="C9" s="116" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="136" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="122" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="216" t="s">
-        <v>174</v>
-      </c>
-      <c r="G9" s="178" t="s">
-        <v>119</v>
-      </c>
-      <c r="H9" s="211" t="s">
-        <v>110</v>
-      </c>
-      <c r="I9" s="195"/>
+      <c r="I9" s="146"/>
     </row>
     <row r="10" spans="2:9" ht="385.5" customHeight="1">
-      <c r="B10" s="158"/>
-      <c r="C10" s="135"/>
-      <c r="D10" s="137"/>
-      <c r="E10" s="138"/>
-      <c r="F10" s="217"/>
-      <c r="G10" s="180"/>
-      <c r="H10" s="212"/>
-      <c r="I10" s="195"/>
+      <c r="B10" s="185"/>
+      <c r="C10" s="223"/>
+      <c r="D10" s="225"/>
+      <c r="E10" s="127"/>
+      <c r="F10" s="120"/>
+      <c r="G10" s="169"/>
+      <c r="H10" s="167"/>
+      <c r="I10" s="146"/>
     </row>
     <row r="11" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B11" s="158"/>
-      <c r="C11" s="116" t="s">
+      <c r="B11" s="185"/>
+      <c r="C11" s="217" t="s">
         <v>21</v>
       </c>
       <c r="D11" s="10" t="s">
@@ -10877,50 +10940,50 @@
       <c r="E11" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="181" t="s">
-        <v>171</v>
-      </c>
-      <c r="G11" s="178" t="s">
-        <v>117</v>
-      </c>
-      <c r="H11" s="183" t="s">
-        <v>113</v>
-      </c>
-      <c r="I11" s="195"/>
+      <c r="F11" s="173" t="s">
+        <v>170</v>
+      </c>
+      <c r="G11" s="168" t="s">
+        <v>116</v>
+      </c>
+      <c r="H11" s="175" t="s">
+        <v>112</v>
+      </c>
+      <c r="I11" s="146"/>
     </row>
     <row r="12" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B12" s="158"/>
-      <c r="C12" s="117"/>
+      <c r="B12" s="185"/>
+      <c r="C12" s="218"/>
       <c r="D12" s="11" t="s">
         <v>23</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="F12" s="182"/>
-      <c r="G12" s="179"/>
-      <c r="H12" s="184"/>
-      <c r="I12" s="195"/>
+        <v>168</v>
+      </c>
+      <c r="F12" s="174"/>
+      <c r="G12" s="172"/>
+      <c r="H12" s="176"/>
+      <c r="I12" s="146"/>
     </row>
     <row r="13" spans="2:9" ht="123.95" customHeight="1">
-      <c r="B13" s="158"/>
-      <c r="C13" s="135"/>
+      <c r="B13" s="185"/>
+      <c r="C13" s="223"/>
       <c r="D13" s="11"/>
       <c r="E13" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F13" s="132"/>
-      <c r="G13" s="180"/>
-      <c r="H13" s="185"/>
-      <c r="I13" s="195"/>
+      <c r="F13" s="125"/>
+      <c r="G13" s="169"/>
+      <c r="H13" s="177"/>
+      <c r="I13" s="146"/>
     </row>
     <row r="14" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B14" s="158"/>
-      <c r="C14" s="116" t="s">
+      <c r="B14" s="185"/>
+      <c r="C14" s="217" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="122" t="s">
-        <v>99</v>
+      <c r="D14" s="126" t="s">
+        <v>98</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>27</v>
@@ -10928,93 +10991,93 @@
       <c r="F14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="186" t="s">
-        <v>122</v>
-      </c>
-      <c r="H14" s="189" t="s">
-        <v>112</v>
-      </c>
-      <c r="I14" s="195"/>
+      <c r="G14" s="178" t="s">
+        <v>121</v>
+      </c>
+      <c r="H14" s="181" t="s">
+        <v>111</v>
+      </c>
+      <c r="I14" s="146"/>
     </row>
     <row r="15" spans="2:9" ht="35.1" customHeight="1">
-      <c r="B15" s="158"/>
-      <c r="C15" s="117"/>
-      <c r="D15" s="123"/>
+      <c r="B15" s="185"/>
+      <c r="C15" s="218"/>
+      <c r="D15" s="170"/>
       <c r="E15" s="13" t="s">
         <v>28</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="G15" s="187"/>
-      <c r="H15" s="190"/>
-      <c r="I15" s="195"/>
+        <v>169</v>
+      </c>
+      <c r="G15" s="179"/>
+      <c r="H15" s="182"/>
+      <c r="I15" s="146"/>
     </row>
     <row r="16" spans="2:9">
-      <c r="B16" s="158"/>
-      <c r="C16" s="117"/>
-      <c r="D16" s="123"/>
+      <c r="B16" s="185"/>
+      <c r="C16" s="218"/>
+      <c r="D16" s="170"/>
       <c r="E16" s="14"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="187"/>
-      <c r="H16" s="190"/>
-      <c r="I16" s="195"/>
+      <c r="G16" s="179"/>
+      <c r="H16" s="182"/>
+      <c r="I16" s="146"/>
     </row>
     <row r="17" spans="2:9" ht="49.5">
-      <c r="B17" s="158"/>
-      <c r="C17" s="117"/>
-      <c r="D17" s="123"/>
+      <c r="B17" s="185"/>
+      <c r="C17" s="218"/>
+      <c r="D17" s="170"/>
       <c r="E17" s="13" t="s">
         <v>29</v>
       </c>
       <c r="F17" s="5"/>
-      <c r="G17" s="187"/>
-      <c r="H17" s="190"/>
-      <c r="I17" s="195"/>
+      <c r="G17" s="179"/>
+      <c r="H17" s="182"/>
+      <c r="I17" s="146"/>
     </row>
     <row r="18" spans="2:9">
-      <c r="B18" s="158"/>
-      <c r="C18" s="117"/>
-      <c r="D18" s="123"/>
+      <c r="B18" s="185"/>
+      <c r="C18" s="218"/>
+      <c r="D18" s="170"/>
       <c r="E18" s="14"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="187"/>
-      <c r="H18" s="190"/>
-      <c r="I18" s="195"/>
+      <c r="G18" s="179"/>
+      <c r="H18" s="182"/>
+      <c r="I18" s="146"/>
     </row>
     <row r="19" spans="2:9">
-      <c r="B19" s="158"/>
-      <c r="C19" s="117"/>
-      <c r="D19" s="123"/>
+      <c r="B19" s="185"/>
+      <c r="C19" s="218"/>
+      <c r="D19" s="170"/>
       <c r="E19" s="115" t="s">
         <v>30</v>
       </c>
       <c r="F19" s="5"/>
-      <c r="G19" s="187"/>
-      <c r="H19" s="190"/>
-      <c r="I19" s="195"/>
+      <c r="G19" s="179"/>
+      <c r="H19" s="182"/>
+      <c r="I19" s="146"/>
     </row>
     <row r="20" spans="2:9">
-      <c r="B20" s="158"/>
-      <c r="C20" s="117"/>
-      <c r="D20" s="123"/>
+      <c r="B20" s="185"/>
+      <c r="C20" s="218"/>
+      <c r="D20" s="170"/>
       <c r="E20" s="115" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F20" s="5"/>
-      <c r="G20" s="187"/>
-      <c r="H20" s="190"/>
-      <c r="I20" s="195"/>
+      <c r="G20" s="179"/>
+      <c r="H20" s="182"/>
+      <c r="I20" s="146"/>
     </row>
     <row r="21" spans="2:9" ht="84.4" customHeight="1" thickBot="1">
-      <c r="B21" s="159"/>
-      <c r="C21" s="128"/>
-      <c r="D21" s="177"/>
+      <c r="B21" s="186"/>
+      <c r="C21" s="222"/>
+      <c r="D21" s="171"/>
       <c r="E21" s="50"/>
       <c r="F21" s="49"/>
-      <c r="G21" s="188"/>
-      <c r="H21" s="191"/>
-      <c r="I21" s="196"/>
+      <c r="G21" s="180"/>
+      <c r="H21" s="183"/>
+      <c r="I21" s="147"/>
     </row>
     <row r="22" spans="2:9" ht="17.25" thickBot="1">
       <c r="B22" s="107"/>
@@ -11027,48 +11090,48 @@
       <c r="I22" s="108"/>
     </row>
     <row r="23" spans="2:9" ht="32.1" customHeight="1">
-      <c r="B23" s="151" t="s">
-        <v>166</v>
-      </c>
-      <c r="C23" s="129" t="s">
+      <c r="B23" s="187" t="s">
+        <v>165</v>
+      </c>
+      <c r="C23" s="213" t="s">
         <v>33</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E23" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="F23" s="131" t="s">
-        <v>175</v>
-      </c>
-      <c r="G23" s="201" t="s">
-        <v>133</v>
-      </c>
-      <c r="H23" s="131" t="s">
+      <c r="F23" s="124" t="s">
+        <v>174</v>
+      </c>
+      <c r="G23" s="154" t="s">
         <v>132</v>
       </c>
-      <c r="I23" s="125" t="s">
-        <v>188</v>
+      <c r="H23" s="124" t="s">
+        <v>131</v>
+      </c>
+      <c r="I23" s="134" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="2:9" ht="70.7" customHeight="1">
-      <c r="B24" s="152"/>
-      <c r="C24" s="130"/>
+      <c r="B24" s="188"/>
+      <c r="C24" s="199"/>
       <c r="D24" s="20" t="s">
         <v>23</v>
       </c>
       <c r="E24" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="F24" s="132"/>
-      <c r="G24" s="202"/>
-      <c r="H24" s="132"/>
-      <c r="I24" s="126"/>
+      <c r="F24" s="125"/>
+      <c r="G24" s="155"/>
+      <c r="H24" s="125"/>
+      <c r="I24" s="137"/>
     </row>
     <row r="25" spans="2:9" ht="35.1" customHeight="1">
-      <c r="B25" s="152"/>
-      <c r="C25" s="133" t="s">
+      <c r="B25" s="188"/>
+      <c r="C25" s="198" t="s">
         <v>37</v>
       </c>
       <c r="D25" s="23" t="s">
@@ -11077,102 +11140,102 @@
       <c r="E25" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F25" s="218" t="s">
+      <c r="F25" s="121" t="s">
+        <v>176</v>
+      </c>
+      <c r="G25" s="150" t="s">
+        <v>122</v>
+      </c>
+      <c r="H25" s="229" t="s">
         <v>177</v>
       </c>
-      <c r="G25" s="141" t="s">
-        <v>123</v>
-      </c>
-      <c r="H25" s="144" t="s">
-        <v>178</v>
-      </c>
-      <c r="I25" s="126"/>
+      <c r="I25" s="137"/>
     </row>
     <row r="26" spans="2:9">
-      <c r="B26" s="152"/>
-      <c r="C26" s="134"/>
+      <c r="B26" s="188"/>
+      <c r="C26" s="202"/>
       <c r="D26" s="24" t="s">
         <v>39</v>
       </c>
       <c r="E26" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F26" s="219"/>
-      <c r="G26" s="142"/>
-      <c r="H26" s="145"/>
-      <c r="I26" s="126"/>
+      <c r="F26" s="122"/>
+      <c r="G26" s="228"/>
+      <c r="H26" s="133"/>
+      <c r="I26" s="137"/>
     </row>
     <row r="27" spans="2:9">
-      <c r="B27" s="152"/>
-      <c r="C27" s="134"/>
+      <c r="B27" s="188"/>
+      <c r="C27" s="202"/>
       <c r="D27" s="24"/>
       <c r="E27" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F27" s="219"/>
-      <c r="G27" s="142"/>
-      <c r="H27" s="145"/>
-      <c r="I27" s="126"/>
+      <c r="F27" s="122"/>
+      <c r="G27" s="228"/>
+      <c r="H27" s="133"/>
+      <c r="I27" s="137"/>
     </row>
     <row r="28" spans="2:9">
-      <c r="B28" s="152"/>
-      <c r="C28" s="134"/>
+      <c r="B28" s="188"/>
+      <c r="C28" s="202"/>
       <c r="D28" s="24"/>
       <c r="E28" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F28" s="219"/>
-      <c r="G28" s="142"/>
-      <c r="H28" s="145"/>
-      <c r="I28" s="126"/>
+      <c r="F28" s="122"/>
+      <c r="G28" s="228"/>
+      <c r="H28" s="133"/>
+      <c r="I28" s="137"/>
     </row>
     <row r="29" spans="2:9">
-      <c r="B29" s="152"/>
-      <c r="C29" s="134"/>
+      <c r="B29" s="188"/>
+      <c r="C29" s="202"/>
       <c r="D29" s="24"/>
       <c r="E29" s="14"/>
-      <c r="F29" s="219"/>
-      <c r="G29" s="142"/>
-      <c r="H29" s="145"/>
-      <c r="I29" s="126"/>
+      <c r="F29" s="122"/>
+      <c r="G29" s="228"/>
+      <c r="H29" s="133"/>
+      <c r="I29" s="137"/>
     </row>
     <row r="30" spans="2:9">
-      <c r="B30" s="152"/>
-      <c r="C30" s="134"/>
+      <c r="B30" s="188"/>
+      <c r="C30" s="202"/>
       <c r="D30" s="24"/>
       <c r="E30" s="115" t="s">
         <v>30</v>
       </c>
-      <c r="F30" s="219"/>
-      <c r="G30" s="142"/>
-      <c r="H30" s="145"/>
-      <c r="I30" s="126"/>
+      <c r="F30" s="122"/>
+      <c r="G30" s="228"/>
+      <c r="H30" s="133"/>
+      <c r="I30" s="137"/>
     </row>
     <row r="31" spans="2:9">
-      <c r="B31" s="152"/>
-      <c r="C31" s="134"/>
+      <c r="B31" s="188"/>
+      <c r="C31" s="202"/>
       <c r="D31" s="24"/>
       <c r="E31" s="115" t="s">
-        <v>105</v>
-      </c>
-      <c r="F31" s="219"/>
-      <c r="G31" s="142"/>
-      <c r="H31" s="145"/>
-      <c r="I31" s="126"/>
+        <v>104</v>
+      </c>
+      <c r="F31" s="122"/>
+      <c r="G31" s="228"/>
+      <c r="H31" s="133"/>
+      <c r="I31" s="137"/>
     </row>
     <row r="32" spans="2:9">
-      <c r="B32" s="152"/>
-      <c r="C32" s="130"/>
+      <c r="B32" s="188"/>
+      <c r="C32" s="199"/>
       <c r="D32" s="25"/>
       <c r="E32" s="26"/>
-      <c r="F32" s="220"/>
-      <c r="G32" s="143"/>
-      <c r="H32" s="146"/>
-      <c r="I32" s="126"/>
+      <c r="F32" s="123"/>
+      <c r="G32" s="151"/>
+      <c r="H32" s="132"/>
+      <c r="I32" s="137"/>
     </row>
     <row r="33" spans="2:9">
-      <c r="B33" s="152"/>
-      <c r="C33" s="133" t="s">
+      <c r="B33" s="188"/>
+      <c r="C33" s="198" t="s">
         <v>44</v>
       </c>
       <c r="D33" s="23" t="s">
@@ -11181,33 +11244,33 @@
       <c r="E33" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F33" s="139" t="s">
-        <v>176</v>
-      </c>
-      <c r="G33" s="228" t="s">
-        <v>126</v>
-      </c>
-      <c r="H33" s="169" t="s">
-        <v>129</v>
-      </c>
-      <c r="I33" s="126"/>
+      <c r="F33" s="226" t="s">
+        <v>175</v>
+      </c>
+      <c r="G33" s="141" t="s">
+        <v>125</v>
+      </c>
+      <c r="H33" s="131" t="s">
+        <v>128</v>
+      </c>
+      <c r="I33" s="137"/>
     </row>
     <row r="34" spans="2:9" ht="123.4" customHeight="1">
-      <c r="B34" s="152"/>
-      <c r="C34" s="130"/>
+      <c r="B34" s="188"/>
+      <c r="C34" s="199"/>
       <c r="D34" s="27" t="s">
         <v>46</v>
       </c>
       <c r="E34" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="F34" s="140"/>
-      <c r="G34" s="229"/>
-      <c r="H34" s="146"/>
-      <c r="I34" s="126"/>
+      <c r="F34" s="227"/>
+      <c r="G34" s="142"/>
+      <c r="H34" s="132"/>
+      <c r="I34" s="137"/>
     </row>
     <row r="35" spans="2:9" ht="141" customHeight="1">
-      <c r="B35" s="152"/>
+      <c r="B35" s="188"/>
       <c r="C35" s="28" t="s">
         <v>50</v>
       </c>
@@ -11219,15 +11282,15 @@
       </c>
       <c r="F35" s="9"/>
       <c r="G35" s="63" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H35" s="99" t="s">
-        <v>130</v>
-      </c>
-      <c r="I35" s="127"/>
+        <v>129</v>
+      </c>
+      <c r="I35" s="138"/>
     </row>
     <row r="36" spans="2:9" ht="33.75" thickBot="1">
-      <c r="B36" s="153"/>
+      <c r="B36" s="189"/>
       <c r="C36" s="31" t="s">
         <v>54</v>
       </c>
@@ -11253,224 +11316,224 @@
       <c r="I37" s="94"/>
     </row>
     <row r="38" spans="2:9">
-      <c r="B38" s="151" t="s">
+      <c r="B38" s="187" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="129" t="s">
+      <c r="C38" s="213" t="s">
         <v>58</v>
       </c>
       <c r="D38" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="E38" s="154" t="s">
+      <c r="E38" s="214" t="s">
         <v>61</v>
       </c>
-      <c r="F38" s="131" t="s">
-        <v>179</v>
-      </c>
-      <c r="G38" s="201" t="s">
-        <v>143</v>
-      </c>
-      <c r="H38" s="203" t="s">
-        <v>145</v>
-      </c>
-      <c r="I38" s="125" t="s">
-        <v>189</v>
+      <c r="F38" s="124" t="s">
+        <v>178</v>
+      </c>
+      <c r="G38" s="154" t="s">
+        <v>142</v>
+      </c>
+      <c r="H38" s="156" t="s">
+        <v>144</v>
+      </c>
+      <c r="I38" s="134" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="39" spans="2:9" ht="149.1" customHeight="1">
-      <c r="B39" s="152"/>
-      <c r="C39" s="134"/>
+      <c r="B39" s="188"/>
+      <c r="C39" s="202"/>
       <c r="D39" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="E39" s="146"/>
-      <c r="F39" s="132"/>
-      <c r="G39" s="202"/>
-      <c r="H39" s="204"/>
-      <c r="I39" s="224"/>
+      <c r="E39" s="132"/>
+      <c r="F39" s="125"/>
+      <c r="G39" s="155"/>
+      <c r="H39" s="157"/>
+      <c r="I39" s="135"/>
     </row>
     <row r="40" spans="2:9">
-      <c r="B40" s="152"/>
-      <c r="C40" s="134"/>
-      <c r="D40" s="155" t="s">
+      <c r="B40" s="188"/>
+      <c r="C40" s="202"/>
+      <c r="D40" s="215" t="s">
         <v>62</v>
       </c>
       <c r="E40" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F40" s="122" t="s">
-        <v>182</v>
-      </c>
-      <c r="G40" s="163" t="s">
-        <v>144</v>
-      </c>
-      <c r="H40" s="199" t="s">
-        <v>146</v>
-      </c>
-      <c r="I40" s="224"/>
+      <c r="F40" s="126" t="s">
+        <v>181</v>
+      </c>
+      <c r="G40" s="158" t="s">
+        <v>143</v>
+      </c>
+      <c r="H40" s="152" t="s">
+        <v>145</v>
+      </c>
+      <c r="I40" s="135"/>
     </row>
     <row r="41" spans="2:9" ht="119.65" customHeight="1">
-      <c r="B41" s="152"/>
-      <c r="C41" s="130"/>
-      <c r="D41" s="156"/>
+      <c r="B41" s="188"/>
+      <c r="C41" s="199"/>
+      <c r="D41" s="216"/>
       <c r="E41" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="F41" s="138"/>
-      <c r="G41" s="174"/>
-      <c r="H41" s="200"/>
-      <c r="I41" s="224"/>
+      <c r="F41" s="127"/>
+      <c r="G41" s="159"/>
+      <c r="H41" s="153"/>
+      <c r="I41" s="135"/>
     </row>
     <row r="42" spans="2:9">
-      <c r="B42" s="152"/>
-      <c r="C42" s="133" t="s">
+      <c r="B42" s="188"/>
+      <c r="C42" s="198" t="s">
         <v>65</v>
       </c>
-      <c r="D42" s="175" t="s">
+      <c r="D42" s="209" t="s">
         <v>66</v>
       </c>
-      <c r="E42" s="218" t="s">
+      <c r="E42" s="121" t="s">
+        <v>138</v>
+      </c>
+      <c r="F42" s="126" t="s">
+        <v>180</v>
+      </c>
+      <c r="G42" s="158" t="s">
         <v>139</v>
       </c>
-      <c r="F42" s="122" t="s">
-        <v>181</v>
-      </c>
-      <c r="G42" s="163" t="s">
-        <v>140</v>
-      </c>
-      <c r="H42" s="205" t="s">
-        <v>147</v>
-      </c>
-      <c r="I42" s="224"/>
+      <c r="H42" s="160" t="s">
+        <v>146</v>
+      </c>
+      <c r="I42" s="135"/>
     </row>
     <row r="43" spans="2:9" ht="113.65" customHeight="1">
-      <c r="B43" s="152"/>
-      <c r="C43" s="134"/>
-      <c r="D43" s="176"/>
-      <c r="E43" s="220"/>
-      <c r="F43" s="138"/>
-      <c r="G43" s="174"/>
-      <c r="H43" s="205"/>
-      <c r="I43" s="224"/>
+      <c r="B43" s="188"/>
+      <c r="C43" s="202"/>
+      <c r="D43" s="210"/>
+      <c r="E43" s="123"/>
+      <c r="F43" s="127"/>
+      <c r="G43" s="159"/>
+      <c r="H43" s="160"/>
+      <c r="I43" s="135"/>
     </row>
     <row r="44" spans="2:9">
-      <c r="B44" s="152"/>
-      <c r="C44" s="134"/>
-      <c r="D44" s="147" t="s">
+      <c r="B44" s="188"/>
+      <c r="C44" s="202"/>
+      <c r="D44" s="200" t="s">
         <v>67</v>
       </c>
-      <c r="E44" s="122" t="s">
-        <v>180</v>
-      </c>
-      <c r="F44" s="149"/>
-      <c r="G44" s="226" t="s">
-        <v>195</v>
-      </c>
-      <c r="H44" s="205"/>
-      <c r="I44" s="224"/>
+      <c r="E44" s="126" t="s">
+        <v>179</v>
+      </c>
+      <c r="F44" s="211"/>
+      <c r="G44" s="139" t="s">
+        <v>194</v>
+      </c>
+      <c r="H44" s="160"/>
+      <c r="I44" s="135"/>
     </row>
     <row r="45" spans="2:9" ht="317.64999999999998" customHeight="1">
-      <c r="B45" s="152"/>
-      <c r="C45" s="130"/>
-      <c r="D45" s="148"/>
-      <c r="E45" s="138"/>
-      <c r="F45" s="150"/>
-      <c r="G45" s="227"/>
-      <c r="H45" s="200"/>
-      <c r="I45" s="224"/>
+      <c r="B45" s="188"/>
+      <c r="C45" s="199"/>
+      <c r="D45" s="201"/>
+      <c r="E45" s="127"/>
+      <c r="F45" s="212"/>
+      <c r="G45" s="140"/>
+      <c r="H45" s="153"/>
+      <c r="I45" s="135"/>
     </row>
     <row r="46" spans="2:9">
-      <c r="B46" s="152"/>
-      <c r="C46" s="133" t="s">
+      <c r="B46" s="188"/>
+      <c r="C46" s="198" t="s">
         <v>68</v>
       </c>
       <c r="D46" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="E46" s="119" t="s">
+      <c r="E46" s="203" t="s">
+        <v>71</v>
+      </c>
+      <c r="F46" s="131" t="s">
+        <v>182</v>
+      </c>
+      <c r="G46" s="161" t="s">
+        <v>195</v>
+      </c>
+      <c r="H46" s="164"/>
+      <c r="I46" s="135"/>
+    </row>
+    <row r="47" spans="2:9">
+      <c r="B47" s="188"/>
+      <c r="C47" s="202"/>
+      <c r="D47" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="E47" s="204"/>
+      <c r="F47" s="133"/>
+      <c r="G47" s="162"/>
+      <c r="H47" s="164"/>
+      <c r="I47" s="135"/>
+    </row>
+    <row r="48" spans="2:9">
+      <c r="B48" s="188"/>
+      <c r="C48" s="202"/>
+      <c r="D48" s="297" t="s">
+        <v>203</v>
+      </c>
+      <c r="E48" s="204"/>
+      <c r="F48" s="133"/>
+      <c r="G48" s="162"/>
+      <c r="H48" s="164"/>
+      <c r="I48" s="135"/>
+    </row>
+    <row r="49" spans="2:9">
+      <c r="B49" s="188"/>
+      <c r="C49" s="202"/>
+      <c r="D49" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="E49" s="204"/>
+      <c r="F49" s="133"/>
+      <c r="G49" s="162"/>
+      <c r="H49" s="164"/>
+      <c r="I49" s="135"/>
+    </row>
+    <row r="50" spans="2:9">
+      <c r="B50" s="188"/>
+      <c r="C50" s="202"/>
+      <c r="D50" s="37"/>
+      <c r="E50" s="204"/>
+      <c r="F50" s="133"/>
+      <c r="G50" s="162"/>
+      <c r="H50" s="164"/>
+      <c r="I50" s="135"/>
+    </row>
+    <row r="51" spans="2:9" ht="223.5" customHeight="1" thickBot="1">
+      <c r="B51" s="188"/>
+      <c r="C51" s="199"/>
+      <c r="D51" s="37"/>
+      <c r="E51" s="205"/>
+      <c r="F51" s="132"/>
+      <c r="G51" s="163"/>
+      <c r="H51" s="165"/>
+      <c r="I51" s="136"/>
+    </row>
+    <row r="52" spans="2:9" ht="30.75" thickBot="1">
+      <c r="B52" s="189"/>
+      <c r="C52" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="F46" s="169" t="s">
-        <v>183</v>
-      </c>
-      <c r="G46" s="206" t="s">
-        <v>196</v>
-      </c>
-      <c r="H46" s="209"/>
-      <c r="I46" s="224"/>
-    </row>
-    <row r="47" spans="2:9">
-      <c r="B47" s="152"/>
-      <c r="C47" s="134"/>
-      <c r="D47" s="37" t="s">
-        <v>173</v>
-      </c>
-      <c r="E47" s="120"/>
-      <c r="F47" s="145"/>
-      <c r="G47" s="207"/>
-      <c r="H47" s="209"/>
-      <c r="I47" s="224"/>
-    </row>
-    <row r="48" spans="2:9">
-      <c r="B48" s="152"/>
-      <c r="C48" s="134"/>
-      <c r="D48" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="E48" s="120"/>
-      <c r="F48" s="145"/>
-      <c r="G48" s="207"/>
-      <c r="H48" s="209"/>
-      <c r="I48" s="224"/>
-    </row>
-    <row r="49" spans="2:9">
-      <c r="B49" s="152"/>
-      <c r="C49" s="134"/>
-      <c r="D49" s="37" t="s">
-        <v>71</v>
-      </c>
-      <c r="E49" s="120"/>
-      <c r="F49" s="145"/>
-      <c r="G49" s="207"/>
-      <c r="H49" s="209"/>
-      <c r="I49" s="224"/>
-    </row>
-    <row r="50" spans="2:9">
-      <c r="B50" s="152"/>
-      <c r="C50" s="134"/>
-      <c r="D50" s="37"/>
-      <c r="E50" s="120"/>
-      <c r="F50" s="145"/>
-      <c r="G50" s="207"/>
-      <c r="H50" s="209"/>
-      <c r="I50" s="224"/>
-    </row>
-    <row r="51" spans="2:9" ht="204.4" customHeight="1" thickBot="1">
-      <c r="B51" s="152"/>
-      <c r="C51" s="130"/>
-      <c r="D51" s="37"/>
-      <c r="E51" s="170"/>
-      <c r="F51" s="146"/>
-      <c r="G51" s="208"/>
-      <c r="H51" s="210"/>
-      <c r="I51" s="225"/>
-    </row>
-    <row r="52" spans="2:9" ht="30.75" thickBot="1">
-      <c r="B52" s="153"/>
-      <c r="C52" s="38" t="s">
+      <c r="D52" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="D52" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="E52" s="171" t="s">
+      <c r="E52" s="206" t="s">
         <v>56</v>
       </c>
-      <c r="F52" s="172"/>
-      <c r="G52" s="172"/>
-      <c r="H52" s="172"/>
-      <c r="I52" s="173"/>
+      <c r="F52" s="207"/>
+      <c r="G52" s="207"/>
+      <c r="H52" s="207"/>
+      <c r="I52" s="208"/>
     </row>
     <row r="53" spans="2:9" ht="17.25" thickBot="1">
       <c r="B53" s="82"/>
@@ -11483,96 +11546,96 @@
       <c r="I53" s="95"/>
     </row>
     <row r="54" spans="2:9" ht="94.7" customHeight="1">
-      <c r="B54" s="151" t="s">
+      <c r="B54" s="187" t="s">
+        <v>74</v>
+      </c>
+      <c r="C54" s="40" t="s">
         <v>75</v>
       </c>
-      <c r="C54" s="40" t="s">
+      <c r="D54" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D54" s="41" t="s">
+      <c r="E54" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="E54" s="42" t="s">
+      <c r="F54" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G54" s="69" t="s">
+        <v>151</v>
+      </c>
+      <c r="H54" s="111" t="s">
+        <v>148</v>
+      </c>
+      <c r="I54" s="134" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9">
+      <c r="B55" s="188"/>
+      <c r="C55" s="198" t="s">
+        <v>16</v>
+      </c>
+      <c r="D55" s="200" t="s">
         <v>78</v>
       </c>
-      <c r="F54" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="G54" s="69" t="s">
-        <v>152</v>
-      </c>
-      <c r="H54" s="111" t="s">
-        <v>149</v>
-      </c>
-      <c r="I54" s="125" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="55" spans="2:9">
-      <c r="B55" s="152"/>
-      <c r="C55" s="133" t="s">
-        <v>16</v>
-      </c>
-      <c r="D55" s="147" t="s">
+      <c r="E55" s="131" t="s">
+        <v>196</v>
+      </c>
+      <c r="F55" s="131" t="s">
+        <v>183</v>
+      </c>
+      <c r="G55" s="150" t="s">
+        <v>197</v>
+      </c>
+      <c r="H55" s="152" t="s">
+        <v>184</v>
+      </c>
+      <c r="I55" s="135"/>
+    </row>
+    <row r="56" spans="2:9" ht="150.4" customHeight="1">
+      <c r="B56" s="188"/>
+      <c r="C56" s="199"/>
+      <c r="D56" s="201"/>
+      <c r="E56" s="132"/>
+      <c r="F56" s="132"/>
+      <c r="G56" s="151"/>
+      <c r="H56" s="153"/>
+      <c r="I56" s="135"/>
+    </row>
+    <row r="57" spans="2:9" ht="181.7" customHeight="1">
+      <c r="B57" s="188"/>
+      <c r="C57" s="28" t="s">
         <v>79</v>
-      </c>
-      <c r="E55" s="169" t="s">
-        <v>197</v>
-      </c>
-      <c r="F55" s="169" t="s">
-        <v>184</v>
-      </c>
-      <c r="G55" s="141" t="s">
-        <v>198</v>
-      </c>
-      <c r="H55" s="199" t="s">
-        <v>185</v>
-      </c>
-      <c r="I55" s="224"/>
-    </row>
-    <row r="56" spans="2:9" ht="150.4" customHeight="1">
-      <c r="B56" s="152"/>
-      <c r="C56" s="130"/>
-      <c r="D56" s="148"/>
-      <c r="E56" s="146"/>
-      <c r="F56" s="146"/>
-      <c r="G56" s="143"/>
-      <c r="H56" s="200"/>
-      <c r="I56" s="224"/>
-    </row>
-    <row r="57" spans="2:9" ht="181.7" customHeight="1">
-      <c r="B57" s="152"/>
-      <c r="C57" s="28" t="s">
-        <v>80</v>
       </c>
       <c r="D57" s="29" t="s">
         <v>69</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F57" s="9"/>
       <c r="G57" s="90" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H57" s="101"/>
-      <c r="I57" s="225"/>
+      <c r="I57" s="136"/>
     </row>
     <row r="58" spans="2:9" ht="33.75" thickBot="1">
-      <c r="B58" s="153"/>
+      <c r="B58" s="189"/>
       <c r="C58" s="31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D58" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="E58" s="221" t="s">
+        <v>81</v>
+      </c>
+      <c r="E58" s="128" t="s">
         <v>56</v>
       </c>
-      <c r="F58" s="222"/>
-      <c r="G58" s="222"/>
-      <c r="H58" s="222"/>
-      <c r="I58" s="223"/>
+      <c r="F58" s="129"/>
+      <c r="G58" s="129"/>
+      <c r="H58" s="129"/>
+      <c r="I58" s="130"/>
     </row>
     <row r="59" spans="2:9" ht="17.25" thickBot="1">
       <c r="B59" s="78"/>
@@ -11585,134 +11648,164 @@
       <c r="I59" s="96"/>
     </row>
     <row r="60" spans="2:9" ht="66">
-      <c r="B60" s="160" t="s">
+      <c r="B60" s="190" t="s">
+        <v>156</v>
+      </c>
+      <c r="C60" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="D60" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="E60" s="42" t="s">
         <v>157</v>
-      </c>
-      <c r="C60" s="40" t="s">
-        <v>83</v>
-      </c>
-      <c r="D60" s="44" t="s">
-        <v>84</v>
-      </c>
-      <c r="E60" s="42" t="s">
-        <v>158</v>
       </c>
       <c r="F60" s="72"/>
       <c r="G60" s="72" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H60" s="102"/>
-      <c r="I60" s="125" t="s">
-        <v>202</v>
+      <c r="I60" s="134" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="61" spans="2:9" ht="148.5">
-      <c r="B61" s="161"/>
+      <c r="B61" s="191"/>
       <c r="C61" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="D61" s="29" t="s">
         <v>86</v>
-      </c>
-      <c r="D61" s="29" t="s">
-        <v>87</v>
       </c>
       <c r="E61" s="30"/>
       <c r="F61" s="73"/>
       <c r="G61" s="73" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H61" s="103"/>
-      <c r="I61" s="126"/>
+      <c r="I61" s="137"/>
     </row>
     <row r="62" spans="2:9" ht="181.5">
-      <c r="B62" s="161"/>
+      <c r="B62" s="191"/>
       <c r="C62" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="D62" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="D62" s="29" t="s">
+      <c r="E62" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="E62" s="30" t="s">
+      <c r="F62" s="109" t="s">
+        <v>198</v>
+      </c>
+      <c r="G62" s="87" t="s">
+        <v>190</v>
+      </c>
+      <c r="H62" s="112" t="s">
+        <v>202</v>
+      </c>
+      <c r="I62" s="137"/>
+    </row>
+    <row r="63" spans="2:9" ht="33">
+      <c r="B63" s="191"/>
+      <c r="C63" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="F62" s="109" t="s">
+      <c r="D63" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="E63" s="30" t="s">
         <v>199</v>
-      </c>
-      <c r="G62" s="87" t="s">
-        <v>191</v>
-      </c>
-      <c r="H62" s="112" t="s">
-        <v>203</v>
-      </c>
-      <c r="I62" s="126"/>
-    </row>
-    <row r="63" spans="2:9" ht="33">
-      <c r="B63" s="161"/>
-      <c r="C63" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="D63" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="E63" s="30" t="s">
-        <v>200</v>
       </c>
       <c r="F63" s="30"/>
       <c r="G63" s="30" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H63" s="104"/>
-      <c r="I63" s="126"/>
+      <c r="I63" s="137"/>
     </row>
     <row r="64" spans="2:9" ht="82.5">
-      <c r="B64" s="161"/>
+      <c r="B64" s="191"/>
       <c r="C64" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="D64" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="D64" s="29" t="s">
+      <c r="E64" s="30" t="s">
         <v>95</v>
-      </c>
-      <c r="E64" s="30" t="s">
-        <v>96</v>
       </c>
       <c r="F64" s="30"/>
       <c r="G64" s="76" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H64" s="105"/>
-      <c r="I64" s="127"/>
+      <c r="I64" s="138"/>
     </row>
     <row r="65" spans="2:9" ht="33.75" thickBot="1">
-      <c r="B65" s="162"/>
+      <c r="B65" s="192"/>
       <c r="C65" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="D65" s="113" t="s">
         <v>97</v>
       </c>
-      <c r="D65" s="113" t="s">
-        <v>98</v>
-      </c>
-      <c r="E65" s="213" t="s">
+      <c r="E65" s="116" t="s">
         <v>56</v>
       </c>
-      <c r="F65" s="214"/>
-      <c r="G65" s="214"/>
-      <c r="H65" s="214"/>
-      <c r="I65" s="215"/>
+      <c r="F65" s="117"/>
+      <c r="G65" s="117"/>
+      <c r="H65" s="117"/>
+      <c r="I65" s="118"/>
     </row>
   </sheetData>
   <mergeCells count="76">
-    <mergeCell ref="E65:I65"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="F25:F32"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="E58:I58"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="F46:F51"/>
-    <mergeCell ref="I54:I57"/>
-    <mergeCell ref="I38:I51"/>
-    <mergeCell ref="I23:I35"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="G33:G34"/>
-    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="F4:F7"/>
+    <mergeCell ref="I60:I64"/>
+    <mergeCell ref="C14:C21"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="C25:C32"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="G25:G32"/>
+    <mergeCell ref="H25:H32"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="B38:B52"/>
+    <mergeCell ref="C38:C41"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="B3:B21"/>
+    <mergeCell ref="B23:B36"/>
+    <mergeCell ref="B60:B65"/>
+    <mergeCell ref="G4:G7"/>
+    <mergeCell ref="H4:H7"/>
+    <mergeCell ref="B54:B58"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="C46:C51"/>
+    <mergeCell ref="E46:E51"/>
+    <mergeCell ref="E52:I52"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="C42:C45"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="D14:D21"/>
+    <mergeCell ref="G11:G13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="H11:H13"/>
+    <mergeCell ref="G14:G21"/>
+    <mergeCell ref="H14:H21"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="I8:I21"/>
     <mergeCell ref="I4:I7"/>
@@ -11729,51 +11822,21 @@
     <mergeCell ref="G9:G10"/>
     <mergeCell ref="G23:G24"/>
     <mergeCell ref="H23:H24"/>
-    <mergeCell ref="D14:D21"/>
-    <mergeCell ref="G11:G13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="H11:H13"/>
-    <mergeCell ref="G14:G21"/>
-    <mergeCell ref="H14:H21"/>
-    <mergeCell ref="B3:B21"/>
-    <mergeCell ref="B23:B36"/>
-    <mergeCell ref="B60:B65"/>
-    <mergeCell ref="G4:G7"/>
-    <mergeCell ref="H4:H7"/>
-    <mergeCell ref="B54:B58"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="C46:C51"/>
-    <mergeCell ref="E46:E51"/>
-    <mergeCell ref="E52:I52"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="C42:C45"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="B38:B52"/>
-    <mergeCell ref="C38:C41"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="F4:F7"/>
-    <mergeCell ref="I60:I64"/>
-    <mergeCell ref="C14:C21"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="C25:C32"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="G25:G32"/>
-    <mergeCell ref="H25:H32"/>
+    <mergeCell ref="E65:I65"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="F25:F32"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="E58:I58"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="F46:F51"/>
+    <mergeCell ref="I54:I57"/>
+    <mergeCell ref="I38:I51"/>
+    <mergeCell ref="I23:I35"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="H33:H34"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <hyperlinks>
@@ -11812,17 +11875,17 @@
         <v>1</v>
       </c>
       <c r="E4" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="F4" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="F4" s="47" t="s">
-        <v>101</v>
-      </c>
       <c r="G4" s="48" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="2:7" ht="33">
-      <c r="B5" s="233" t="s">
+      <c r="B5" s="242" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="54" t="s">
@@ -11832,55 +11895,55 @@
         <v>7</v>
       </c>
       <c r="E5" s="55" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F5" s="56" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G5" s="57"/>
     </row>
     <row r="6" spans="2:7">
-      <c r="B6" s="234"/>
-      <c r="C6" s="241" t="s">
+      <c r="B6" s="243"/>
+      <c r="C6" s="248" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="119" t="s">
+      <c r="D6" s="203" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="122" t="s">
+      <c r="E6" s="126" t="s">
+        <v>101</v>
+      </c>
+      <c r="F6" s="158" t="s">
         <v>102</v>
       </c>
-      <c r="F6" s="163" t="s">
-        <v>103</v>
-      </c>
-      <c r="G6" s="230"/>
+      <c r="G6" s="239"/>
     </row>
     <row r="7" spans="2:7">
-      <c r="B7" s="234"/>
-      <c r="C7" s="242"/>
-      <c r="D7" s="120"/>
-      <c r="E7" s="123"/>
-      <c r="F7" s="164"/>
-      <c r="G7" s="231"/>
+      <c r="B7" s="243"/>
+      <c r="C7" s="249"/>
+      <c r="D7" s="204"/>
+      <c r="E7" s="170"/>
+      <c r="F7" s="193"/>
+      <c r="G7" s="240"/>
     </row>
     <row r="8" spans="2:7">
-      <c r="B8" s="234"/>
-      <c r="C8" s="242"/>
-      <c r="D8" s="120"/>
-      <c r="E8" s="123"/>
-      <c r="F8" s="164"/>
-      <c r="G8" s="231"/>
+      <c r="B8" s="243"/>
+      <c r="C8" s="249"/>
+      <c r="D8" s="204"/>
+      <c r="E8" s="170"/>
+      <c r="F8" s="193"/>
+      <c r="G8" s="240"/>
     </row>
     <row r="9" spans="2:7">
-      <c r="B9" s="234"/>
-      <c r="C9" s="246"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="138"/>
-      <c r="F9" s="165"/>
-      <c r="G9" s="232"/>
+      <c r="B9" s="243"/>
+      <c r="C9" s="253"/>
+      <c r="D9" s="220"/>
+      <c r="E9" s="127"/>
+      <c r="F9" s="194"/>
+      <c r="G9" s="241"/>
     </row>
     <row r="10" spans="2:7" ht="33">
-      <c r="B10" s="234"/>
+      <c r="B10" s="243"/>
       <c r="C10" s="58" t="s">
         <v>16</v>
       </c>
@@ -11889,169 +11952,164 @@
       </c>
       <c r="E10" s="45"/>
       <c r="F10" s="51" t="s">
+        <v>108</v>
+      </c>
+      <c r="G10" s="52"/>
+    </row>
+    <row r="11" spans="2:7">
+      <c r="B11" s="243"/>
+      <c r="C11" s="248" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="224" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="126" t="s">
+        <v>106</v>
+      </c>
+      <c r="F11" s="230" t="s">
+        <v>118</v>
+      </c>
+      <c r="G11" s="257" t="s">
         <v>109</v>
       </c>
-      <c r="G10" s="52"/>
-    </row>
-    <row r="11" spans="2:7">
-      <c r="B11" s="234"/>
-      <c r="C11" s="241" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="136" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="122" t="s">
+    </row>
+    <row r="12" spans="2:7">
+      <c r="B12" s="243"/>
+      <c r="C12" s="249"/>
+      <c r="D12" s="252"/>
+      <c r="E12" s="170"/>
+      <c r="F12" s="231"/>
+      <c r="G12" s="258"/>
+    </row>
+    <row r="13" spans="2:7" ht="286.7" customHeight="1">
+      <c r="B13" s="243"/>
+      <c r="C13" s="251"/>
+      <c r="D13" s="225"/>
+      <c r="E13" s="127"/>
+      <c r="F13" s="155"/>
+      <c r="G13" s="259"/>
+    </row>
+    <row r="14" spans="2:7" ht="35.1" customHeight="1">
+      <c r="B14" s="243"/>
+      <c r="C14" s="248" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="245" t="s">
+        <v>115</v>
+      </c>
+      <c r="E14" s="126" t="s">
         <v>107</v>
       </c>
-      <c r="F11" s="239" t="s">
-        <v>119</v>
-      </c>
-      <c r="G11" s="250" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7">
-      <c r="B12" s="234"/>
-      <c r="C12" s="242"/>
-      <c r="D12" s="245"/>
-      <c r="E12" s="123"/>
-      <c r="F12" s="240"/>
-      <c r="G12" s="251"/>
-    </row>
-    <row r="13" spans="2:7" ht="286.7" customHeight="1">
-      <c r="B13" s="234"/>
-      <c r="C13" s="244"/>
-      <c r="D13" s="137"/>
-      <c r="E13" s="138"/>
-      <c r="F13" s="202"/>
-      <c r="G13" s="252"/>
-    </row>
-    <row r="14" spans="2:7" ht="35.1" customHeight="1">
-      <c r="B14" s="234"/>
-      <c r="C14" s="241" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="236" t="s">
+      <c r="F14" s="230" t="s">
         <v>116</v>
       </c>
-      <c r="E14" s="122" t="s">
-        <v>108</v>
-      </c>
-      <c r="F14" s="239" t="s">
-        <v>117</v>
-      </c>
-      <c r="G14" s="253" t="s">
-        <v>113</v>
+      <c r="G14" s="232" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="2:7">
-      <c r="B15" s="234"/>
-      <c r="C15" s="242"/>
-      <c r="D15" s="237"/>
-      <c r="E15" s="123"/>
-      <c r="F15" s="240"/>
-      <c r="G15" s="254"/>
+      <c r="B15" s="243"/>
+      <c r="C15" s="249"/>
+      <c r="D15" s="246"/>
+      <c r="E15" s="170"/>
+      <c r="F15" s="231"/>
+      <c r="G15" s="233"/>
     </row>
     <row r="16" spans="2:7" ht="134.65" customHeight="1">
-      <c r="B16" s="234"/>
-      <c r="C16" s="244"/>
-      <c r="D16" s="238"/>
-      <c r="E16" s="138"/>
-      <c r="F16" s="202"/>
-      <c r="G16" s="255"/>
+      <c r="B16" s="243"/>
+      <c r="C16" s="251"/>
+      <c r="D16" s="247"/>
+      <c r="E16" s="127"/>
+      <c r="F16" s="155"/>
+      <c r="G16" s="234"/>
     </row>
     <row r="17" spans="2:7" ht="35.1" customHeight="1">
-      <c r="B17" s="234"/>
-      <c r="C17" s="241" t="s">
+      <c r="B17" s="243"/>
+      <c r="C17" s="248" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="122" t="s">
-        <v>99</v>
-      </c>
-      <c r="E17" s="119" t="s">
-        <v>104</v>
-      </c>
-      <c r="F17" s="247" t="s">
-        <v>122</v>
-      </c>
-      <c r="G17" s="257" t="s">
-        <v>112</v>
+      <c r="D17" s="126" t="s">
+        <v>98</v>
+      </c>
+      <c r="E17" s="203" t="s">
+        <v>103</v>
+      </c>
+      <c r="F17" s="254" t="s">
+        <v>121</v>
+      </c>
+      <c r="G17" s="236" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="234"/>
-      <c r="C18" s="242"/>
-      <c r="D18" s="123"/>
-      <c r="E18" s="120"/>
-      <c r="F18" s="248"/>
-      <c r="G18" s="258"/>
+      <c r="B18" s="243"/>
+      <c r="C18" s="249"/>
+      <c r="D18" s="170"/>
+      <c r="E18" s="204"/>
+      <c r="F18" s="255"/>
+      <c r="G18" s="237"/>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="234"/>
-      <c r="C19" s="242"/>
-      <c r="D19" s="123"/>
-      <c r="E19" s="120"/>
-      <c r="F19" s="248"/>
-      <c r="G19" s="258"/>
+      <c r="B19" s="243"/>
+      <c r="C19" s="249"/>
+      <c r="D19" s="170"/>
+      <c r="E19" s="204"/>
+      <c r="F19" s="255"/>
+      <c r="G19" s="237"/>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="234"/>
-      <c r="C20" s="242"/>
-      <c r="D20" s="123"/>
-      <c r="E20" s="120"/>
-      <c r="F20" s="248"/>
-      <c r="G20" s="258"/>
+      <c r="B20" s="243"/>
+      <c r="C20" s="249"/>
+      <c r="D20" s="170"/>
+      <c r="E20" s="204"/>
+      <c r="F20" s="255"/>
+      <c r="G20" s="237"/>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="234"/>
-      <c r="C21" s="242"/>
-      <c r="D21" s="123"/>
-      <c r="E21" s="120"/>
-      <c r="F21" s="248"/>
-      <c r="G21" s="258"/>
+      <c r="B21" s="243"/>
+      <c r="C21" s="249"/>
+      <c r="D21" s="170"/>
+      <c r="E21" s="204"/>
+      <c r="F21" s="255"/>
+      <c r="G21" s="237"/>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="234"/>
-      <c r="C22" s="242"/>
-      <c r="D22" s="123"/>
-      <c r="E22" s="120"/>
-      <c r="F22" s="248"/>
-      <c r="G22" s="258"/>
+      <c r="B22" s="243"/>
+      <c r="C22" s="249"/>
+      <c r="D22" s="170"/>
+      <c r="E22" s="204"/>
+      <c r="F22" s="255"/>
+      <c r="G22" s="237"/>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="234"/>
-      <c r="C23" s="242"/>
-      <c r="D23" s="123"/>
-      <c r="E23" s="120"/>
-      <c r="F23" s="248"/>
-      <c r="G23" s="258"/>
+      <c r="B23" s="243"/>
+      <c r="C23" s="249"/>
+      <c r="D23" s="170"/>
+      <c r="E23" s="204"/>
+      <c r="F23" s="255"/>
+      <c r="G23" s="237"/>
     </row>
     <row r="24" spans="2:7" ht="85.7" customHeight="1" thickBot="1">
-      <c r="B24" s="235"/>
-      <c r="C24" s="243"/>
-      <c r="D24" s="177"/>
-      <c r="E24" s="256"/>
-      <c r="F24" s="249"/>
-      <c r="G24" s="259"/>
+      <c r="B24" s="244"/>
+      <c r="C24" s="250"/>
+      <c r="D24" s="171"/>
+      <c r="E24" s="235"/>
+      <c r="F24" s="256"/>
+      <c r="G24" s="238"/>
     </row>
     <row r="28" spans="2:7">
       <c r="F28" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="2:7">
       <c r="F29" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="E17:E24"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="G17:G24"/>
     <mergeCell ref="G6:G9"/>
     <mergeCell ref="B5:B24"/>
     <mergeCell ref="D17:D24"/>
@@ -12068,6 +12126,11 @@
     <mergeCell ref="F6:F9"/>
     <mergeCell ref="F17:F24"/>
     <mergeCell ref="G11:G13"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="E17:E24"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="G17:G24"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12097,145 +12160,145 @@
         <v>1</v>
       </c>
       <c r="E2" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="F2" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="F2" s="47" t="s">
-        <v>101</v>
-      </c>
       <c r="G2" s="48" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="70.349999999999994" customHeight="1">
-      <c r="B3" s="160" t="s">
+      <c r="B3" s="190" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="273" t="s">
+      <c r="C3" s="261" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="276" t="s">
-        <v>115</v>
-      </c>
-      <c r="E3" s="278" t="s">
+      <c r="D3" s="265" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" s="267" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" s="154" t="s">
+        <v>132</v>
+      </c>
+      <c r="G3" s="263" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="83.1" customHeight="1">
+      <c r="B4" s="191"/>
+      <c r="C4" s="262"/>
+      <c r="D4" s="266"/>
+      <c r="E4" s="151"/>
+      <c r="F4" s="155"/>
+      <c r="G4" s="264"/>
+    </row>
+    <row r="5" spans="2:7" ht="105.4" customHeight="1">
+      <c r="B5" s="191"/>
+      <c r="C5" s="268" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="209" t="s">
         <v>120</v>
       </c>
-      <c r="F3" s="201" t="s">
-        <v>133</v>
-      </c>
-      <c r="G3" s="274" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="83.1" customHeight="1">
-      <c r="B4" s="161"/>
-      <c r="C4" s="266"/>
-      <c r="D4" s="277"/>
-      <c r="E4" s="143"/>
-      <c r="F4" s="202"/>
-      <c r="G4" s="275"/>
-    </row>
-    <row r="5" spans="2:7" ht="105.4" customHeight="1">
-      <c r="B5" s="161"/>
-      <c r="C5" s="264" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="175" t="s">
-        <v>121</v>
-      </c>
-      <c r="E5" s="260" t="s">
+      <c r="E5" s="272" t="s">
+        <v>126</v>
+      </c>
+      <c r="F5" s="150" t="s">
+        <v>122</v>
+      </c>
+      <c r="G5" s="269" t="s">
         <v>127</v>
       </c>
-      <c r="F5" s="141" t="s">
+    </row>
+    <row r="6" spans="2:7">
+      <c r="B6" s="191"/>
+      <c r="C6" s="276"/>
+      <c r="D6" s="275"/>
+      <c r="E6" s="273"/>
+      <c r="F6" s="228"/>
+      <c r="G6" s="270"/>
+    </row>
+    <row r="7" spans="2:7">
+      <c r="B7" s="191"/>
+      <c r="C7" s="276"/>
+      <c r="D7" s="275"/>
+      <c r="E7" s="273"/>
+      <c r="F7" s="228"/>
+      <c r="G7" s="270"/>
+    </row>
+    <row r="8" spans="2:7">
+      <c r="B8" s="191"/>
+      <c r="C8" s="276"/>
+      <c r="D8" s="275"/>
+      <c r="E8" s="273"/>
+      <c r="F8" s="228"/>
+      <c r="G8" s="270"/>
+    </row>
+    <row r="9" spans="2:7">
+      <c r="B9" s="191"/>
+      <c r="C9" s="276"/>
+      <c r="D9" s="275"/>
+      <c r="E9" s="273"/>
+      <c r="F9" s="228"/>
+      <c r="G9" s="270"/>
+    </row>
+    <row r="10" spans="2:7">
+      <c r="B10" s="191"/>
+      <c r="C10" s="276"/>
+      <c r="D10" s="275"/>
+      <c r="E10" s="273"/>
+      <c r="F10" s="228"/>
+      <c r="G10" s="270"/>
+    </row>
+    <row r="11" spans="2:7">
+      <c r="B11" s="191"/>
+      <c r="C11" s="276"/>
+      <c r="D11" s="275"/>
+      <c r="E11" s="273"/>
+      <c r="F11" s="228"/>
+      <c r="G11" s="270"/>
+    </row>
+    <row r="12" spans="2:7">
+      <c r="B12" s="191"/>
+      <c r="C12" s="262"/>
+      <c r="D12" s="210"/>
+      <c r="E12" s="274"/>
+      <c r="F12" s="151"/>
+      <c r="G12" s="271"/>
+    </row>
+    <row r="13" spans="2:7" ht="138.94999999999999" customHeight="1">
+      <c r="B13" s="191"/>
+      <c r="C13" s="268" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="209" t="s">
+        <v>124</v>
+      </c>
+      <c r="E13" s="203" t="s">
         <v>123</v>
       </c>
-      <c r="G5" s="279" t="s">
+      <c r="F13" s="141" t="s">
+        <v>125</v>
+      </c>
+      <c r="G13" s="280" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
-      <c r="B6" s="161"/>
-      <c r="C6" s="265"/>
-      <c r="D6" s="263"/>
-      <c r="E6" s="261"/>
-      <c r="F6" s="142"/>
-      <c r="G6" s="280"/>
-    </row>
-    <row r="7" spans="2:7">
-      <c r="B7" s="161"/>
-      <c r="C7" s="265"/>
-      <c r="D7" s="263"/>
-      <c r="E7" s="261"/>
-      <c r="F7" s="142"/>
-      <c r="G7" s="280"/>
-    </row>
-    <row r="8" spans="2:7">
-      <c r="B8" s="161"/>
-      <c r="C8" s="265"/>
-      <c r="D8" s="263"/>
-      <c r="E8" s="261"/>
-      <c r="F8" s="142"/>
-      <c r="G8" s="280"/>
-    </row>
-    <row r="9" spans="2:7">
-      <c r="B9" s="161"/>
-      <c r="C9" s="265"/>
-      <c r="D9" s="263"/>
-      <c r="E9" s="261"/>
-      <c r="F9" s="142"/>
-      <c r="G9" s="280"/>
-    </row>
-    <row r="10" spans="2:7">
-      <c r="B10" s="161"/>
-      <c r="C10" s="265"/>
-      <c r="D10" s="263"/>
-      <c r="E10" s="261"/>
-      <c r="F10" s="142"/>
-      <c r="G10" s="280"/>
-    </row>
-    <row r="11" spans="2:7">
-      <c r="B11" s="161"/>
-      <c r="C11" s="265"/>
-      <c r="D11" s="263"/>
-      <c r="E11" s="261"/>
-      <c r="F11" s="142"/>
-      <c r="G11" s="280"/>
-    </row>
-    <row r="12" spans="2:7">
-      <c r="B12" s="161"/>
-      <c r="C12" s="266"/>
-      <c r="D12" s="176"/>
-      <c r="E12" s="262"/>
-      <c r="F12" s="143"/>
-      <c r="G12" s="271"/>
-    </row>
-    <row r="13" spans="2:7" ht="138.94999999999999" customHeight="1">
-      <c r="B13" s="161"/>
-      <c r="C13" s="264" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="175" t="s">
-        <v>125</v>
-      </c>
-      <c r="E13" s="119" t="s">
-        <v>124</v>
-      </c>
-      <c r="F13" s="228" t="s">
-        <v>126</v>
-      </c>
-      <c r="G13" s="270" t="s">
-        <v>129</v>
-      </c>
-    </row>
     <row r="14" spans="2:7">
-      <c r="B14" s="161"/>
-      <c r="C14" s="266"/>
-      <c r="D14" s="176"/>
-      <c r="E14" s="170"/>
-      <c r="F14" s="229"/>
+      <c r="B14" s="191"/>
+      <c r="C14" s="262"/>
+      <c r="D14" s="210"/>
+      <c r="E14" s="205"/>
+      <c r="F14" s="142"/>
       <c r="G14" s="271"/>
     </row>
     <row r="15" spans="2:7" ht="95.65" customHeight="1">
-      <c r="B15" s="161"/>
+      <c r="B15" s="191"/>
       <c r="C15" s="28" t="s">
         <v>50</v>
       </c>
@@ -12246,66 +12309,66 @@
         <v>52</v>
       </c>
       <c r="F15" s="63" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G15" s="64" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="17.25" thickBot="1">
-      <c r="B16" s="162"/>
+      <c r="B16" s="192"/>
       <c r="C16" s="31" t="s">
         <v>54</v>
       </c>
       <c r="D16" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="E16" s="267" t="s">
+      <c r="E16" s="277" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="268"/>
-      <c r="G16" s="269"/>
+      <c r="F16" s="278"/>
+      <c r="G16" s="279"/>
     </row>
     <row r="32" ht="17.25" thickBot="1"/>
     <row r="33" spans="8:8">
-      <c r="H33" s="125" t="s">
+      <c r="H33" s="134" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="34" spans="8:8">
-      <c r="H34" s="126"/>
+      <c r="H34" s="137"/>
     </row>
     <row r="35" spans="8:8">
-      <c r="H35" s="126"/>
+      <c r="H35" s="137"/>
     </row>
     <row r="36" spans="8:8">
-      <c r="H36" s="126"/>
+      <c r="H36" s="137"/>
     </row>
     <row r="37" spans="8:8">
-      <c r="H37" s="126"/>
+      <c r="H37" s="137"/>
     </row>
     <row r="38" spans="8:8">
-      <c r="H38" s="126"/>
+      <c r="H38" s="137"/>
     </row>
     <row r="39" spans="8:8">
-      <c r="H39" s="126"/>
+      <c r="H39" s="137"/>
     </row>
     <row r="40" spans="8:8">
-      <c r="H40" s="126"/>
+      <c r="H40" s="137"/>
     </row>
     <row r="41" spans="8:8">
-      <c r="H41" s="126"/>
+      <c r="H41" s="137"/>
     </row>
     <row r="42" spans="8:8">
-      <c r="H42" s="127"/>
+      <c r="H42" s="138"/>
     </row>
     <row r="43" spans="8:8">
-      <c r="H43" s="272" t="s">
+      <c r="H43" s="260" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="44" spans="8:8">
-      <c r="H44" s="127"/>
+      <c r="H44" s="138"/>
     </row>
     <row r="45" spans="8:8">
       <c r="H45" s="59" t="s">
@@ -12317,6 +12380,12 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B3:B16"/>
+    <mergeCell ref="E5:E12"/>
+    <mergeCell ref="D5:D12"/>
+    <mergeCell ref="C5:C12"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="G13:G14"/>
     <mergeCell ref="H33:H42"/>
     <mergeCell ref="H43:H44"/>
     <mergeCell ref="C3:C4"/>
@@ -12330,12 +12399,6 @@
     <mergeCell ref="E13:E14"/>
     <mergeCell ref="F13:F14"/>
     <mergeCell ref="G5:G12"/>
-    <mergeCell ref="B3:B16"/>
-    <mergeCell ref="E5:E12"/>
-    <mergeCell ref="D5:D12"/>
-    <mergeCell ref="C5:C12"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="G13:G14"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <hyperlinks>
@@ -12368,184 +12431,174 @@
         <v>1</v>
       </c>
       <c r="E2" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="F2" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="F2" s="47" t="s">
-        <v>101</v>
-      </c>
       <c r="G2" s="48" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="35.1" customHeight="1">
-      <c r="B3" s="160" t="s">
+      <c r="B3" s="190" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="273" t="s">
+      <c r="C3" s="261" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="283" t="s">
+      <c r="D3" s="287" t="s">
+        <v>137</v>
+      </c>
+      <c r="E3" s="214" t="s">
+        <v>133</v>
+      </c>
+      <c r="F3" s="154" t="s">
+        <v>142</v>
+      </c>
+      <c r="G3" s="285" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="182.1" customHeight="1">
+      <c r="B4" s="191"/>
+      <c r="C4" s="276"/>
+      <c r="D4" s="288"/>
+      <c r="E4" s="132"/>
+      <c r="F4" s="155"/>
+      <c r="G4" s="286"/>
+    </row>
+    <row r="5" spans="2:7">
+      <c r="B5" s="191"/>
+      <c r="C5" s="276"/>
+      <c r="D5" s="215" t="s">
+        <v>135</v>
+      </c>
+      <c r="E5" s="173" t="s">
+        <v>136</v>
+      </c>
+      <c r="F5" s="158" t="s">
+        <v>143</v>
+      </c>
+      <c r="G5" s="257" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="86.1" customHeight="1">
+      <c r="B6" s="191"/>
+      <c r="C6" s="262"/>
+      <c r="D6" s="216"/>
+      <c r="E6" s="125"/>
+      <c r="F6" s="159"/>
+      <c r="G6" s="292"/>
+    </row>
+    <row r="7" spans="2:7">
+      <c r="B7" s="191"/>
+      <c r="C7" s="268" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="209" t="s">
+        <v>134</v>
+      </c>
+      <c r="E7" s="121" t="s">
         <v>138</v>
       </c>
-      <c r="E3" s="154" t="s">
-        <v>134</v>
-      </c>
-      <c r="F3" s="201" t="s">
-        <v>143</v>
-      </c>
-      <c r="G3" s="281" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="182.1" customHeight="1">
-      <c r="B4" s="161"/>
-      <c r="C4" s="265"/>
-      <c r="D4" s="284"/>
-      <c r="E4" s="146"/>
-      <c r="F4" s="202"/>
-      <c r="G4" s="282"/>
-    </row>
-    <row r="5" spans="2:7">
-      <c r="B5" s="161"/>
-      <c r="C5" s="265"/>
-      <c r="D5" s="155" t="s">
-        <v>136</v>
-      </c>
-      <c r="E5" s="181" t="s">
-        <v>137</v>
-      </c>
-      <c r="F5" s="163" t="s">
-        <v>144</v>
-      </c>
-      <c r="G5" s="250" t="s">
+      <c r="F7" s="158" t="s">
+        <v>139</v>
+      </c>
+      <c r="G7" s="291" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="86.1" customHeight="1">
-      <c r="B6" s="161"/>
-      <c r="C6" s="266"/>
-      <c r="D6" s="156"/>
-      <c r="E6" s="132"/>
-      <c r="F6" s="174"/>
-      <c r="G6" s="288"/>
-    </row>
-    <row r="7" spans="2:7">
-      <c r="B7" s="161"/>
-      <c r="C7" s="264" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="175" t="s">
-        <v>135</v>
-      </c>
-      <c r="E7" s="218" t="s">
-        <v>139</v>
-      </c>
-      <c r="F7" s="163" t="s">
+    <row r="8" spans="2:7" ht="102.95" customHeight="1">
+      <c r="B8" s="191"/>
+      <c r="C8" s="276"/>
+      <c r="D8" s="210"/>
+      <c r="E8" s="123"/>
+      <c r="F8" s="159"/>
+      <c r="G8" s="291"/>
+    </row>
+    <row r="9" spans="2:7">
+      <c r="B9" s="191"/>
+      <c r="C9" s="276"/>
+      <c r="D9" s="200" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="126" t="s">
         <v>140</v>
       </c>
-      <c r="G7" s="287" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" ht="102.95" customHeight="1">
-      <c r="B8" s="161"/>
-      <c r="C8" s="265"/>
-      <c r="D8" s="176"/>
-      <c r="E8" s="220"/>
-      <c r="F8" s="174"/>
-      <c r="G8" s="287"/>
-    </row>
-    <row r="9" spans="2:7">
-      <c r="B9" s="161"/>
-      <c r="C9" s="265"/>
-      <c r="D9" s="147" t="s">
-        <v>67</v>
-      </c>
-      <c r="E9" s="122" t="s">
+      <c r="F9" s="139" t="s">
+        <v>185</v>
+      </c>
+      <c r="G9" s="291"/>
+    </row>
+    <row r="10" spans="2:7" ht="175.35" customHeight="1">
+      <c r="B10" s="191"/>
+      <c r="C10" s="262"/>
+      <c r="D10" s="201"/>
+      <c r="E10" s="127"/>
+      <c r="F10" s="140"/>
+      <c r="G10" s="292"/>
+    </row>
+    <row r="11" spans="2:7" ht="17.649999999999999" customHeight="1">
+      <c r="B11" s="191"/>
+      <c r="C11" s="268" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" s="281" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="203" t="s">
         <v>141</v>
       </c>
-      <c r="F9" s="226" t="s">
-        <v>186</v>
-      </c>
-      <c r="G9" s="287"/>
-    </row>
-    <row r="10" spans="2:7" ht="175.35" customHeight="1">
-      <c r="B10" s="161"/>
-      <c r="C10" s="266"/>
-      <c r="D10" s="148"/>
-      <c r="E10" s="138"/>
-      <c r="F10" s="227"/>
-      <c r="G10" s="288"/>
-    </row>
-    <row r="11" spans="2:7" ht="17.649999999999999" customHeight="1">
-      <c r="B11" s="161"/>
-      <c r="C11" s="264" t="s">
-        <v>68</v>
-      </c>
-      <c r="D11" s="289" t="s">
-        <v>69</v>
-      </c>
-      <c r="E11" s="119" t="s">
-        <v>142</v>
-      </c>
-      <c r="F11" s="206" t="s">
-        <v>193</v>
-      </c>
-      <c r="G11" s="285"/>
+      <c r="F11" s="161" t="s">
+        <v>192</v>
+      </c>
+      <c r="G11" s="289"/>
     </row>
     <row r="12" spans="2:7" ht="28.35" customHeight="1">
-      <c r="B12" s="161"/>
-      <c r="C12" s="265"/>
-      <c r="D12" s="290"/>
-      <c r="E12" s="120"/>
-      <c r="F12" s="207"/>
-      <c r="G12" s="285"/>
+      <c r="B12" s="191"/>
+      <c r="C12" s="276"/>
+      <c r="D12" s="282"/>
+      <c r="E12" s="204"/>
+      <c r="F12" s="162"/>
+      <c r="G12" s="289"/>
     </row>
     <row r="13" spans="2:7" ht="42.4" customHeight="1">
-      <c r="B13" s="161"/>
-      <c r="C13" s="265"/>
-      <c r="D13" s="290"/>
-      <c r="E13" s="120"/>
-      <c r="F13" s="207"/>
-      <c r="G13" s="285"/>
+      <c r="B13" s="191"/>
+      <c r="C13" s="276"/>
+      <c r="D13" s="282"/>
+      <c r="E13" s="204"/>
+      <c r="F13" s="162"/>
+      <c r="G13" s="289"/>
     </row>
     <row r="14" spans="2:7">
-      <c r="B14" s="161"/>
-      <c r="C14" s="265"/>
-      <c r="D14" s="290"/>
-      <c r="E14" s="120"/>
-      <c r="F14" s="207"/>
-      <c r="G14" s="285"/>
+      <c r="B14" s="191"/>
+      <c r="C14" s="276"/>
+      <c r="D14" s="282"/>
+      <c r="E14" s="204"/>
+      <c r="F14" s="162"/>
+      <c r="G14" s="289"/>
     </row>
     <row r="15" spans="2:7">
-      <c r="B15" s="161"/>
-      <c r="C15" s="265"/>
-      <c r="D15" s="290"/>
-      <c r="E15" s="120"/>
-      <c r="F15" s="207"/>
-      <c r="G15" s="285"/>
+      <c r="B15" s="191"/>
+      <c r="C15" s="276"/>
+      <c r="D15" s="282"/>
+      <c r="E15" s="204"/>
+      <c r="F15" s="162"/>
+      <c r="G15" s="289"/>
     </row>
     <row r="16" spans="2:7" ht="115.35" customHeight="1" thickBot="1">
-      <c r="B16" s="162"/>
-      <c r="C16" s="292"/>
-      <c r="D16" s="291"/>
-      <c r="E16" s="256"/>
-      <c r="F16" s="208"/>
-      <c r="G16" s="286"/>
+      <c r="B16" s="192"/>
+      <c r="C16" s="284"/>
+      <c r="D16" s="283"/>
+      <c r="E16" s="235"/>
+      <c r="F16" s="163"/>
+      <c r="G16" s="290"/>
     </row>
     <row r="17" ht="17.649999999999999" customHeight="1"/>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="B3:B16"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="D11:D16"/>
-    <mergeCell ref="F11:F16"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="C11:C16"/>
-    <mergeCell ref="C7:C10"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="F5:F6"/>
@@ -12559,6 +12612,16 @@
     <mergeCell ref="E11:E16"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="F7:F8"/>
+    <mergeCell ref="B3:B16"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="D11:D16"/>
+    <mergeCell ref="F11:F16"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="C11:C16"/>
+    <mergeCell ref="C7:C10"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12587,84 +12650,84 @@
         <v>1</v>
       </c>
       <c r="E2" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="F2" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="F2" s="47" t="s">
-        <v>101</v>
-      </c>
       <c r="G2" s="48" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="103.35" customHeight="1">
-      <c r="B3" s="160" t="s">
+      <c r="B3" s="190" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="40" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="D3" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="41" t="s">
+      <c r="E3" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="42" t="s">
-        <v>78</v>
-      </c>
       <c r="F3" s="69" t="s">
+        <v>151</v>
+      </c>
+      <c r="G3" s="70" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="69.95" customHeight="1">
+      <c r="B4" s="191"/>
+      <c r="C4" s="268" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="71" t="s">
+        <v>150</v>
+      </c>
+      <c r="E4" s="131" t="s">
         <v>152</v>
       </c>
-      <c r="G3" s="70" t="s">
+      <c r="F4" s="150" t="s">
+        <v>153</v>
+      </c>
+      <c r="G4" s="257" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="98.1" customHeight="1">
+      <c r="B5" s="191"/>
+      <c r="C5" s="262"/>
+      <c r="D5" s="67" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="4" spans="2:7" ht="69.95" customHeight="1">
-      <c r="B4" s="161"/>
-      <c r="C4" s="264" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="71" t="s">
-        <v>151</v>
-      </c>
-      <c r="E4" s="169" t="s">
-        <v>153</v>
-      </c>
-      <c r="F4" s="141" t="s">
+      <c r="E5" s="132"/>
+      <c r="F5" s="151"/>
+      <c r="G5" s="292"/>
+    </row>
+    <row r="6" spans="2:7" ht="125.25" customHeight="1">
+      <c r="B6" s="191"/>
+      <c r="C6" s="268" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="281" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="293" t="s">
+        <v>161</v>
+      </c>
+      <c r="F6" s="150" t="s">
         <v>154</v>
       </c>
-      <c r="G4" s="250" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="98.1" customHeight="1">
-      <c r="B5" s="161"/>
-      <c r="C5" s="266"/>
-      <c r="D5" s="67" t="s">
-        <v>150</v>
-      </c>
-      <c r="E5" s="146"/>
-      <c r="F5" s="143"/>
-      <c r="G5" s="288"/>
-    </row>
-    <row r="6" spans="2:7" ht="125.25" customHeight="1">
-      <c r="B6" s="161"/>
-      <c r="C6" s="264" t="s">
-        <v>80</v>
-      </c>
-      <c r="D6" s="289" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" s="293" t="s">
-        <v>162</v>
-      </c>
-      <c r="F6" s="141" t="s">
-        <v>155</v>
-      </c>
       <c r="G6" s="295"/>
     </row>
     <row r="7" spans="2:7" ht="17.25" thickBot="1">
-      <c r="B7" s="162"/>
-      <c r="C7" s="292"/>
-      <c r="D7" s="291"/>
-      <c r="E7" s="171"/>
+      <c r="B7" s="192"/>
+      <c r="C7" s="284"/>
+      <c r="D7" s="283"/>
+      <c r="E7" s="206"/>
       <c r="F7" s="294"/>
       <c r="G7" s="296"/>
     </row>
@@ -12708,121 +12771,121 @@
         <v>1</v>
       </c>
       <c r="E2" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="F2" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="F2" s="47" t="s">
-        <v>101</v>
-      </c>
       <c r="G2" s="48" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="165.4" customHeight="1">
-      <c r="B3" s="160" t="s">
+      <c r="B3" s="190" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" s="42" t="s">
         <v>157</v>
       </c>
-      <c r="C3" s="40" t="s">
-        <v>83</v>
-      </c>
-      <c r="D3" s="44" t="s">
-        <v>84</v>
-      </c>
-      <c r="E3" s="42" t="s">
+      <c r="F3" s="72" t="s">
+        <v>167</v>
+      </c>
+      <c r="G3" s="68"/>
+    </row>
+    <row r="4" spans="2:7" ht="162.94999999999999" customHeight="1">
+      <c r="B4" s="191"/>
+      <c r="C4" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" s="77" t="s">
+        <v>163</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>162</v>
+      </c>
+      <c r="F4" s="73" t="s">
+        <v>166</v>
+      </c>
+      <c r="G4" s="65"/>
+    </row>
+    <row r="5" spans="2:7" ht="176.65" customHeight="1">
+      <c r="B5" s="191"/>
+      <c r="C5" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="F5" s="87" t="s">
+        <v>190</v>
+      </c>
+      <c r="G5" s="114" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="94.35" customHeight="1">
+      <c r="B6" s="191"/>
+      <c r="C6" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="F6" s="75" t="s">
+        <v>191</v>
+      </c>
+      <c r="G6" s="66"/>
+    </row>
+    <row r="7" spans="2:7" ht="82.5">
+      <c r="B7" s="191"/>
+      <c r="C7" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="F3" s="72" t="s">
-        <v>168</v>
-      </c>
-      <c r="G3" s="68"/>
-    </row>
-    <row r="4" spans="2:7" ht="162.94999999999999" customHeight="1">
-      <c r="B4" s="161"/>
-      <c r="C4" s="28" t="s">
-        <v>86</v>
-      </c>
-      <c r="D4" s="77" t="s">
-        <v>164</v>
-      </c>
-      <c r="E4" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="F4" s="73" t="s">
-        <v>167</v>
-      </c>
-      <c r="G4" s="65"/>
-    </row>
-    <row r="5" spans="2:7" ht="176.65" customHeight="1">
-      <c r="B5" s="161"/>
-      <c r="C5" s="28" t="s">
-        <v>88</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>89</v>
-      </c>
-      <c r="E5" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="F5" s="87" t="s">
-        <v>191</v>
-      </c>
-      <c r="G5" s="114" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="94.35" customHeight="1">
-      <c r="B6" s="161"/>
-      <c r="C6" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="E6" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="F6" s="75" t="s">
-        <v>192</v>
-      </c>
-      <c r="G6" s="66"/>
-    </row>
-    <row r="7" spans="2:7" ht="82.5">
-      <c r="B7" s="161"/>
-      <c r="C7" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="E7" s="30" t="s">
+      <c r="F7" s="76" t="s">
         <v>159</v>
       </c>
-      <c r="F7" s="76" t="s">
-        <v>160</v>
-      </c>
       <c r="G7" s="74"/>
     </row>
     <row r="8" spans="2:7" ht="17.25" thickBot="1">
-      <c r="B8" s="162"/>
+      <c r="B8" s="192"/>
       <c r="C8" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="D8" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="E8" s="213" t="s">
+      <c r="E8" s="116" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="214"/>
-      <c r="G8" s="215"/>
+      <c r="F8" s="117"/>
+      <c r="G8" s="118"/>
     </row>
     <row r="11" spans="2:7">
       <c r="F11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="2:7">
       <c r="F12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/16기_스타트캠프_강사 가이드 문서.xlsx
+++ b/16기_스타트캠프_강사 가이드 문서.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ed\ai-onboarding\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SSAFY\Local_Workspace\16g_Local\00_startcamp\share_ai-onboarding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB1C0B49-7033-4DA5-ADBE-7ECF870551E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91158C1-4F4E-4245-86D6-1D0C034F18A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FD3BB604-1650-4EBB-871F-9010366B35B1}"/>
+    <workbookView xWindow="40020" yWindow="1395" windowWidth="26640" windowHeight="18975" activeTab="4" xr2:uid="{FD3BB604-1650-4EBB-871F-9010366B35B1}"/>
   </bookViews>
   <sheets>
     <sheet name="교육 목표 및 방향" sheetId="7" r:id="rId1"/>
@@ -1769,9 +1769,6 @@
     </r>
   </si>
   <si>
-    <t>AI Studio 활용</t>
-  </si>
-  <si>
     <t>17:00 – 17:30</t>
   </si>
   <si>
@@ -4193,106 +4190,6 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">모든 기능이 잘 동작하는 지 테스트할 수 있도록 유도해주세요. 
-* 배포까지 되어야 하기에 전체적인 진행상황을 살펴봐주세요.
-  - 배포되기에 많은 것이 남지 않도록 잘 잘 살펴봐주시기 바랍니다. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-* API Key </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">사용이 마무리된 교육생은 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Readme </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">문서를 정리하고 배포 준비를 할 수 있도록 안내해주세요. 
-  - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>ender</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>의 배포 횟수도 제한되어 있어 잦은 배포를 하지 않도록 안내</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 부탁드립니다. </t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">* </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
         <rFont val="Malgun Gothic"/>
         <family val="2"/>
         <charset val="129"/>
@@ -5419,156 +5316,6 @@
   </si>
   <si>
     <t>VS Code Copilot BYOK 설정 가이드</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">* 욕심내서 많은 내용을 시도하려고 하진 않는지 확인 부탁드립니다. 
-* </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>왜 MVP를 이렇게 결정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">했는지, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>역할 분배는 어떻게 했는지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>일정에 있어 무리는 없는지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">를 각 팀들과 회의 하여 체크해주시기 바랍니다. 
-* 추가 데이터 수집은 하지 않고 주어진 데이터 기반으로 할 수 있도록 안내해주세요. 
-* 개발 진행하기 앞서 </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Copilot Ask모드 활용만 허가받은 상태</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">이기에 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>프로젝트를 어떻게 시작할지 ChatGPT로 확인하고 시작할 수 있도록 교육생들 안내</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 부탁드립니다. 
-  - AI 를 활용하여 프로젝트 시작하는 방법 (FastAPI 시작하는 방법, Vue 시작하는 방법 등등)을 조사하고 시작할 수 있도록 안내해주세요. 
-* Claude Code, Codex와 같은 툴로 한 번에 끝내려는 교육생이 없도록 감독이 필요합니다. 
-* </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>개발 의뢰 문서에 언급된 정해진 스펙 외에는 사용할 수 없음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>을 안내해주세요.  (MySQL 불가, Flask 불가, Express.js 불가, React 불가 등)</t>
-    </r>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
@@ -5612,471 +5359,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">* 발표 진행시 AI Studio의 화면 공유(Zoom) 을 활용해주세요.
-* 우수작 선정은 google form을 활용해서 투표로 진행하는 것을 추천합니다. 
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>- 우수팀에게는 기프티콘 지급 예정 (커피 X)</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">* </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">바로 개발을 진행하지 말고 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>팀 규칙</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">git branch, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">코드 스타일, 커뮤니케이션 방식) 에 대해 어느 정도 결정하고 진행할 수 있도록 유도 부탁해주세요. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">
-* Copilot </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>전체</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>프로젝트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>구조를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>확인하고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>기능을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>추가하기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>위한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>방법을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> ask</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>모드로 물어보는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>형태로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사용할</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있도록</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>해주세요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">. 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">* </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">최대한 OpenAI API 키를 배포하지 않고 무료 사용량을 소모하도록 안내해주세요. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">
-  - 무료 사용량을 다 사용한 경우 개발한 내용을 문서로 정리할 수 있도록 유도 부탁드립니다. 
-  - Readme 문서 템플릿을 ChatGPT를 활용하여 안내 받고 그 곳에 내용을 채우는 방식으로 안내 부탁드립니다. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">* </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">기능 개발 시 git branch 를 활용하도록 안내해주세요. 
-* merge conflict 발생하는 경우 도움을 줄 수 있도록 살펴봐주세요. 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>* 우수팀에게는 기프티콘 지급 예정이라고 합니다. (커피 X)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">* ask </t>
     </r>
     <r>
@@ -7266,463 +6548,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">* </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">바로 개발을 진행하지 말고 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>팀 규칙</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">git branch, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">코드 스타일, 커뮤니케이션 방식) 에 대해 어느 정도 결정하고 진행할 수 있도록 유도 부탁해주세요. 
- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">
-* Copilot </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>전체</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>프로젝트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>구조를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>확인하고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>기능을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>추가하기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>위한</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>방법을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> ask</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>모드로 물어보는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>형태로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사용할</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>있도록</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>해주세요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">. 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">* </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">최대한 OpenAI API 키를 배포하지 않고 무료 사용량을 소모하도록 안내해주세요. 
- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">
-  - 무료 사용량을 다 사용한 경우 지금까지 개발한 내용을 Readme 문서로 정리할 수 있도록 유도 부탁드립니다. 
-  - Readme 문서 템플릿을 ChatGPT를 활용하여 안내 받고 그 곳에 내용을 채우는 방식으로 안내 부탁드립니다. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">* </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">기능 개발 시 git branch 를 활용하도록 안내해주세요. 
-* merge conflict 발생하는 경우 도움을 줄 수 있도록 살펴봐주세요. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">* </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>우수팀에게는 기프티콘 지급 예정이라고 합니다. (커피 X)</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">to do </t>
     </r>
     <r>
@@ -8116,6 +6941,1276 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">  </t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">* </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">모든 기능이 잘 동작하는 지 테스트할 수 있도록 유도해주세요. 
+* 배포까지 되어야 하기에 전체적인 진행상황을 살펴봐주세요.
+  - 배포되기에 많은 것이 남지 않도록 잘 잘 살펴봐주시기 바랍니다. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+* API Key </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">사용이 마무리된 교육생은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Readme </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">문서를 정리하고 배포 준비를 할 수 있도록 안내해주세요. 
+  - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ender</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>의 배포 횟수도 제한되어 있어 잦은 배포를 하지 않도록 안내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 부탁드립니다. 
+* Render 배포시 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>CORS 이슈, PYTHON_VERSION</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>을 3.11로 환경변수 설정해줘야 정상적으로 배포 및 Netlify 와 연동이 되기 때문에 혹시나 배포에 어려움이 있는 팀은 해당 부분을 우선적으로 확인해주시면 되겠습니다.</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Webex</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">* 발표 진행시 Webex를 활용해주세요.
+* 우수작 선정은 기준은 주어지며 강사님들께서 선정해주시면 되겠습니다. (google Form 활용, 기타 방식)
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- 우수팀에게는 기프티콘 지급 예정 (커피 X)</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">* </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">바로 개발을 진행하지 말고 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>팀 규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">git branch, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">코드 스타일, 커뮤니케이션 방식) 에 대해 어느 정도 결정하고 진행할 수 있도록 유도 부탁해주세요. 
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">
+* Copilot </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>프로젝트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구조를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>확인하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기능을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>추가하기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>방법을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ask</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모드로 물어보는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>형태로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사용할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있도록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해주세요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">* </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">최대한 OpenAI API 키를 배포하지 않고 무료 사용량을 소모하도록 안내해주세요. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+  - 무료 사용량을 다 사용한 경우 지금까지 개발한 내용을 Readme 문서로 정리할 수 있도록 유도 부탁드립니다. 
+  - Readme 문서 템플릿을 ChatGPT를 활용하여 안내 받고 그 곳에 내용을 채우는 방식으로 안내 부탁드립니다. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">* </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">기능 개발 시 git branch 를 활용하도록 안내해주세요.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">* Vue에서 챗봇 기능을 구현하는 경우 Netlify 배포할 때 OPEN_AI_API 키 관련해서 빌드 에러가 발생하니 미리 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>Netlify Functions를 사용해서 LLM 챗봇 기능을 구성</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>할 수 있도록 미리 안내해주세요. (비전공 필수)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+* merge conflict 발생하는 경우 도움을 줄 수 있도록 살펴봐주세요. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">* </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우수팀에게는 기프티콘 지급 예정이라고 합니다. (커피 X)</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">* </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">바로 개발을 진행하지 말고 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>팀 규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">git branch, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">코드 스타일, 커뮤니케이션 방식) 에 대해 어느 정도 결정하고 진행할 수 있도록 유도 부탁해주세요. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">
+* Copilot </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>프로젝트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구조를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>확인하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기능을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>추가하기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>방법을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ask</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모드로 물어보는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>형태로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사용할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있도록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해주세요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">* </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">최대한 OpenAI API 키를 배포하지 않고 무료 사용량을 소모하도록 안내해주세요. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+  - 무료 사용량을 다 사용한 경우 개발한 내용을 문서로 정리할 수 있도록 유도 부탁드립니다. 
+  - Readme 문서 템플릿을 ChatGPT를 활용하여 안내 받고 그 곳에 내용을 채우는 방식으로 안내 부탁드립니다. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>* Vue에서 챗봇 기능을 구현하는 경우 Netlify 배포할 때 OPEN_AI_API 키 관련해서 빌드 에러가 발생하니 미리 Netlify Functions를 사용해서 LLM 챗봇 기능을 구성할 수 있도록 미리 안내해주세요. (비전공 필수)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">* </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">기능 개발 시 git branch 를 활용하도록 안내해주세요. 
+* merge conflict 발생하는 경우 도움을 줄 수 있도록 살펴봐주세요. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>* 우수팀에게는 기프티콘 지급 예정이라고 합니다. (커피 X)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">* 욕심내서 많은 내용을 시도하려고 하진 않는지 확인 부탁드립니다. 
+* </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>왜 MVP를 이렇게 결정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">했는지, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>역할 분배는 어떻게 했는지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>일정에 있어 무리는 없는지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">를 각 팀들과 회의 하여 체크해주시기 바랍니다. 
+* 추가 데이터 수집은 하지 않고 주어진 데이터 기반으로 할 수 있도록 안내해주세요. 
+* 개발 진행하기 앞서 </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Copilot Ask모드 활용해야 하기에 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>프로젝트를 어떻게 시작할지 ChatGPT로 확인하고 시작할 수 있도록 교육생들 안내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 부탁드립니다. 
+  - AI 를 활용하여 프로젝트 시작하는 방법 (FastAPI 시작하는 방법, Vue 시작하는 방법 등등)을 조사하고 시작할 수 있도록 안내해주세요. 
+* Claude Code, Codex와 같은 툴로 한 번에 끝내려는 교육생이 없도록 감독이 필요합니다. 
+* </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>개발 의뢰 문서에 언급된 정해진 스펙 외에는 사용할 수 없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">을 안내해주세요.  (MySQL 불가, Flask 불가, Express.js 불가, React 불가 등)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>* Ask 모드를 사용하는 이유</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- 전반적인 코드 작성 흐름을 하나씩 알아볼 수 있고, 흐름 중에 모르는 내용을 학습 목록으로 가져가볼 수 있기 때문
+- Agent 수업은 AI I 과목에서 진행되기 때문
+- 토큰 사용이 제한되어 있기 때문 (반 공유)</t>
     </r>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
@@ -8124,7 +8219,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="45">
+  <fonts count="47">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8466,6 +8561,23 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -9590,9 +9702,6 @@
     <xf numFmtId="0" fontId="18" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -9644,9 +9753,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="51" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -9782,6 +9888,153 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="51" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9797,27 +10050,12 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -9828,9 +10066,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -9851,12 +10086,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -9896,36 +10125,15 @@
     <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9953,9 +10161,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -10004,15 +10209,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -10034,21 +10230,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -10059,12 +10243,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10076,15 +10254,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -10130,34 +10299,31 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="46" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="43" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10205,24 +10371,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -10238,9 +10395,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -10262,9 +10416,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -10276,42 +10427,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -10319,14 +10434,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -10757,7 +10869,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F735B4F9-89DF-4562-B374-7F3189E766EF}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <sheetData/>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10768,18 +10880,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2CBD596-7E3B-4236-AC37-387FA1537CFC}">
   <dimension ref="B1:I65"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="4" max="4" width="34.125" customWidth="1"/>
-    <col min="5" max="5" width="41.375" customWidth="1"/>
-    <col min="6" max="6" width="71.625" customWidth="1"/>
+    <col min="4" max="4" width="34.08203125" customWidth="1"/>
+    <col min="5" max="5" width="41.33203125" customWidth="1"/>
+    <col min="6" max="6" width="71.58203125" customWidth="1"/>
     <col min="7" max="7" width="53.5" customWidth="1"/>
-    <col min="8" max="8" width="41.125" customWidth="1"/>
-    <col min="9" max="9" width="43.375" customWidth="1"/>
+    <col min="8" max="8" width="41.08203125" customWidth="1"/>
+    <col min="9" max="9" width="43.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="17.25" thickBot="1"/>
-    <row r="2" spans="2:9" ht="17.25" thickBot="1">
+    <row r="1" spans="2:9" ht="17.5" thickBot="1"/>
+    <row r="2" spans="2:9" ht="17.5" thickBot="1">
       <c r="B2" s="46"/>
       <c r="C2" s="47" t="s">
         <v>0</v>
@@ -10794,18 +10906,18 @@
         <v>3</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H2" s="47" t="s">
-        <v>110</v>
-      </c>
-      <c r="I2" s="106" t="s">
+        <v>109</v>
+      </c>
+      <c r="I2" s="104" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="33">
-      <c r="B3" s="184" t="s">
-        <v>164</v>
+    <row r="3" spans="2:9" ht="34">
+      <c r="B3" s="215" t="s">
+        <v>163</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>6</v>
@@ -10813,22 +10925,22 @@
       <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="143" t="s">
+      <c r="E3" s="182" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="144"/>
-      <c r="G3" s="56" t="s">
-        <v>102</v>
-      </c>
-      <c r="H3" s="56"/>
-      <c r="I3" s="53"/>
+      <c r="F3" s="183"/>
+      <c r="G3" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="H3" s="55"/>
+      <c r="I3" s="52"/>
     </row>
     <row r="4" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B4" s="185"/>
-      <c r="C4" s="217" t="s">
+      <c r="B4" s="216"/>
+      <c r="C4" s="236" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="203" t="s">
+      <c r="D4" s="158" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="4" t="s">
@@ -10837,50 +10949,50 @@
       <c r="F4" s="126" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="158" t="s">
-        <v>102</v>
-      </c>
-      <c r="H4" s="195"/>
-      <c r="I4" s="148"/>
+      <c r="G4" s="143" t="s">
+        <v>101</v>
+      </c>
+      <c r="H4" s="223"/>
+      <c r="I4" s="187"/>
     </row>
     <row r="5" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B5" s="185"/>
-      <c r="C5" s="218"/>
-      <c r="D5" s="204"/>
+      <c r="B5" s="216"/>
+      <c r="C5" s="237"/>
+      <c r="D5" s="159"/>
       <c r="E5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="170"/>
-      <c r="G5" s="193"/>
-      <c r="H5" s="196"/>
-      <c r="I5" s="146"/>
+      <c r="F5" s="202"/>
+      <c r="G5" s="221"/>
+      <c r="H5" s="224"/>
+      <c r="I5" s="185"/>
     </row>
     <row r="6" spans="2:9">
-      <c r="B6" s="185"/>
-      <c r="C6" s="218"/>
-      <c r="D6" s="204"/>
+      <c r="B6" s="216"/>
+      <c r="C6" s="237"/>
+      <c r="D6" s="159"/>
       <c r="E6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="170"/>
-      <c r="G6" s="193"/>
-      <c r="H6" s="196"/>
-      <c r="I6" s="146"/>
+      <c r="F6" s="202"/>
+      <c r="G6" s="221"/>
+      <c r="H6" s="224"/>
+      <c r="I6" s="185"/>
     </row>
     <row r="7" spans="2:9">
-      <c r="B7" s="185"/>
-      <c r="C7" s="219"/>
-      <c r="D7" s="220"/>
+      <c r="B7" s="216"/>
+      <c r="C7" s="238"/>
+      <c r="D7" s="239"/>
       <c r="E7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="221"/>
-      <c r="G7" s="194"/>
-      <c r="H7" s="197"/>
-      <c r="I7" s="149"/>
-    </row>
-    <row r="8" spans="2:9" ht="53.1" customHeight="1">
-      <c r="B8" s="185"/>
+      <c r="F7" s="240"/>
+      <c r="G7" s="222"/>
+      <c r="H7" s="225"/>
+      <c r="I7" s="188"/>
+    </row>
+    <row r="8" spans="2:9" ht="53.15" customHeight="1">
+      <c r="B8" s="216"/>
       <c r="C8" s="7" t="s">
         <v>16</v>
       </c>
@@ -10889,49 +11001,49 @@
       </c>
       <c r="E8" s="45"/>
       <c r="F8" s="9"/>
-      <c r="G8" s="91" t="s">
-        <v>108</v>
-      </c>
-      <c r="H8" s="97"/>
-      <c r="I8" s="145" t="s">
-        <v>186</v>
+      <c r="G8" s="89" t="s">
+        <v>107</v>
+      </c>
+      <c r="H8" s="95"/>
+      <c r="I8" s="184" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="9" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B9" s="185"/>
-      <c r="C9" s="217" t="s">
+      <c r="B9" s="216"/>
+      <c r="C9" s="236" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="224" t="s">
+      <c r="D9" s="243" t="s">
         <v>19</v>
       </c>
       <c r="E9" s="126" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="119" t="s">
-        <v>173</v>
-      </c>
-      <c r="G9" s="168" t="s">
-        <v>118</v>
-      </c>
-      <c r="H9" s="166" t="s">
-        <v>109</v>
-      </c>
-      <c r="I9" s="146"/>
+      <c r="F9" s="166" t="s">
+        <v>171</v>
+      </c>
+      <c r="G9" s="200" t="s">
+        <v>117</v>
+      </c>
+      <c r="H9" s="198" t="s">
+        <v>108</v>
+      </c>
+      <c r="I9" s="185"/>
     </row>
     <row r="10" spans="2:9" ht="385.5" customHeight="1">
-      <c r="B10" s="185"/>
-      <c r="C10" s="223"/>
-      <c r="D10" s="225"/>
+      <c r="B10" s="216"/>
+      <c r="C10" s="242"/>
+      <c r="D10" s="244"/>
       <c r="E10" s="127"/>
-      <c r="F10" s="120"/>
-      <c r="G10" s="169"/>
-      <c r="H10" s="167"/>
-      <c r="I10" s="146"/>
+      <c r="F10" s="167"/>
+      <c r="G10" s="201"/>
+      <c r="H10" s="199"/>
+      <c r="I10" s="185"/>
     </row>
     <row r="11" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B11" s="185"/>
-      <c r="C11" s="217" t="s">
+      <c r="B11" s="216"/>
+      <c r="C11" s="236" t="s">
         <v>21</v>
       </c>
       <c r="D11" s="10" t="s">
@@ -10940,50 +11052,50 @@
       <c r="E11" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="173" t="s">
-        <v>170</v>
-      </c>
-      <c r="G11" s="168" t="s">
-        <v>116</v>
-      </c>
-      <c r="H11" s="175" t="s">
-        <v>112</v>
-      </c>
-      <c r="I11" s="146"/>
+      <c r="F11" s="120" t="s">
+        <v>168</v>
+      </c>
+      <c r="G11" s="200" t="s">
+        <v>115</v>
+      </c>
+      <c r="H11" s="206" t="s">
+        <v>111</v>
+      </c>
+      <c r="I11" s="185"/>
     </row>
     <row r="12" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B12" s="185"/>
-      <c r="C12" s="218"/>
+      <c r="B12" s="216"/>
+      <c r="C12" s="237"/>
       <c r="D12" s="11" t="s">
         <v>23</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="F12" s="174"/>
-      <c r="G12" s="172"/>
-      <c r="H12" s="176"/>
-      <c r="I12" s="146"/>
-    </row>
-    <row r="13" spans="2:9" ht="123.95" customHeight="1">
-      <c r="B13" s="185"/>
-      <c r="C13" s="223"/>
+        <v>166</v>
+      </c>
+      <c r="F12" s="205"/>
+      <c r="G12" s="204"/>
+      <c r="H12" s="207"/>
+      <c r="I12" s="185"/>
+    </row>
+    <row r="13" spans="2:9" ht="124" customHeight="1">
+      <c r="B13" s="216"/>
+      <c r="C13" s="242"/>
       <c r="D13" s="11"/>
       <c r="E13" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F13" s="125"/>
-      <c r="G13" s="169"/>
-      <c r="H13" s="177"/>
-      <c r="I13" s="146"/>
+      <c r="F13" s="121"/>
+      <c r="G13" s="201"/>
+      <c r="H13" s="208"/>
+      <c r="I13" s="185"/>
     </row>
     <row r="14" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B14" s="185"/>
-      <c r="C14" s="217" t="s">
+      <c r="B14" s="216"/>
+      <c r="C14" s="236" t="s">
         <v>26</v>
       </c>
       <c r="D14" s="126" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>27</v>
@@ -10991,147 +11103,147 @@
       <c r="F14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="178" t="s">
-        <v>121</v>
-      </c>
-      <c r="H14" s="181" t="s">
-        <v>111</v>
-      </c>
-      <c r="I14" s="146"/>
-    </row>
-    <row r="15" spans="2:9" ht="35.1" customHeight="1">
-      <c r="B15" s="185"/>
-      <c r="C15" s="218"/>
-      <c r="D15" s="170"/>
+      <c r="G14" s="209" t="s">
+        <v>120</v>
+      </c>
+      <c r="H14" s="212" t="s">
+        <v>110</v>
+      </c>
+      <c r="I14" s="185"/>
+    </row>
+    <row r="15" spans="2:9" ht="35.15" customHeight="1">
+      <c r="B15" s="216"/>
+      <c r="C15" s="237"/>
+      <c r="D15" s="202"/>
       <c r="E15" s="13" t="s">
         <v>28</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="G15" s="179"/>
-      <c r="H15" s="182"/>
-      <c r="I15" s="146"/>
+        <v>167</v>
+      </c>
+      <c r="G15" s="210"/>
+      <c r="H15" s="213"/>
+      <c r="I15" s="185"/>
     </row>
     <row r="16" spans="2:9">
-      <c r="B16" s="185"/>
-      <c r="C16" s="218"/>
-      <c r="D16" s="170"/>
+      <c r="B16" s="216"/>
+      <c r="C16" s="237"/>
+      <c r="D16" s="202"/>
       <c r="E16" s="14"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="179"/>
-      <c r="H16" s="182"/>
-      <c r="I16" s="146"/>
-    </row>
-    <row r="17" spans="2:9" ht="49.5">
-      <c r="B17" s="185"/>
-      <c r="C17" s="218"/>
-      <c r="D17" s="170"/>
+      <c r="G16" s="210"/>
+      <c r="H16" s="213"/>
+      <c r="I16" s="185"/>
+    </row>
+    <row r="17" spans="2:9" ht="51">
+      <c r="B17" s="216"/>
+      <c r="C17" s="237"/>
+      <c r="D17" s="202"/>
       <c r="E17" s="13" t="s">
         <v>29</v>
       </c>
       <c r="F17" s="5"/>
-      <c r="G17" s="179"/>
-      <c r="H17" s="182"/>
-      <c r="I17" s="146"/>
+      <c r="G17" s="210"/>
+      <c r="H17" s="213"/>
+      <c r="I17" s="185"/>
     </row>
     <row r="18" spans="2:9">
-      <c r="B18" s="185"/>
-      <c r="C18" s="218"/>
-      <c r="D18" s="170"/>
+      <c r="B18" s="216"/>
+      <c r="C18" s="237"/>
+      <c r="D18" s="202"/>
       <c r="E18" s="14"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="179"/>
-      <c r="H18" s="182"/>
-      <c r="I18" s="146"/>
+      <c r="G18" s="210"/>
+      <c r="H18" s="213"/>
+      <c r="I18" s="185"/>
     </row>
     <row r="19" spans="2:9">
-      <c r="B19" s="185"/>
-      <c r="C19" s="218"/>
-      <c r="D19" s="170"/>
-      <c r="E19" s="115" t="s">
+      <c r="B19" s="216"/>
+      <c r="C19" s="237"/>
+      <c r="D19" s="202"/>
+      <c r="E19" s="113" t="s">
         <v>30</v>
       </c>
       <c r="F19" s="5"/>
-      <c r="G19" s="179"/>
-      <c r="H19" s="182"/>
-      <c r="I19" s="146"/>
+      <c r="G19" s="210"/>
+      <c r="H19" s="213"/>
+      <c r="I19" s="185"/>
     </row>
     <row r="20" spans="2:9">
-      <c r="B20" s="185"/>
-      <c r="C20" s="218"/>
-      <c r="D20" s="170"/>
-      <c r="E20" s="115" t="s">
-        <v>104</v>
+      <c r="B20" s="216"/>
+      <c r="C20" s="237"/>
+      <c r="D20" s="202"/>
+      <c r="E20" s="113" t="s">
+        <v>103</v>
       </c>
       <c r="F20" s="5"/>
-      <c r="G20" s="179"/>
-      <c r="H20" s="182"/>
-      <c r="I20" s="146"/>
+      <c r="G20" s="210"/>
+      <c r="H20" s="213"/>
+      <c r="I20" s="185"/>
     </row>
     <row r="21" spans="2:9" ht="84.4" customHeight="1" thickBot="1">
-      <c r="B21" s="186"/>
-      <c r="C21" s="222"/>
-      <c r="D21" s="171"/>
+      <c r="B21" s="217"/>
+      <c r="C21" s="241"/>
+      <c r="D21" s="203"/>
       <c r="E21" s="50"/>
       <c r="F21" s="49"/>
-      <c r="G21" s="180"/>
-      <c r="H21" s="183"/>
-      <c r="I21" s="147"/>
-    </row>
-    <row r="22" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B22" s="107"/>
+      <c r="G21" s="211"/>
+      <c r="H21" s="214"/>
+      <c r="I21" s="186"/>
+    </row>
+    <row r="22" spans="2:9" ht="17.5" thickBot="1">
+      <c r="B22" s="105"/>
       <c r="C22" s="15"/>
       <c r="D22" s="16"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
-      <c r="G22" s="92"/>
-      <c r="H22" s="98"/>
-      <c r="I22" s="108"/>
-    </row>
-    <row r="23" spans="2:9" ht="32.1" customHeight="1">
-      <c r="B23" s="187" t="s">
-        <v>165</v>
-      </c>
-      <c r="C23" s="213" t="s">
+      <c r="G22" s="90"/>
+      <c r="H22" s="96"/>
+      <c r="I22" s="106"/>
+    </row>
+    <row r="23" spans="2:9" ht="32.15" customHeight="1">
+      <c r="B23" s="218" t="s">
+        <v>164</v>
+      </c>
+      <c r="C23" s="235" t="s">
         <v>33</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E23" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="F23" s="124" t="s">
-        <v>174</v>
-      </c>
-      <c r="G23" s="154" t="s">
-        <v>132</v>
-      </c>
-      <c r="H23" s="124" t="s">
+      <c r="F23" s="169" t="s">
+        <v>172</v>
+      </c>
+      <c r="G23" s="122" t="s">
         <v>131</v>
       </c>
-      <c r="I23" s="134" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" ht="70.7" customHeight="1">
-      <c r="B24" s="188"/>
-      <c r="C24" s="199"/>
+      <c r="H23" s="169" t="s">
+        <v>130</v>
+      </c>
+      <c r="I23" s="175" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" ht="70.75" customHeight="1">
+      <c r="B24" s="219"/>
+      <c r="C24" s="227"/>
       <c r="D24" s="20" t="s">
         <v>23</v>
       </c>
       <c r="E24" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="F24" s="125"/>
-      <c r="G24" s="155"/>
-      <c r="H24" s="125"/>
-      <c r="I24" s="137"/>
-    </row>
-    <row r="25" spans="2:9" ht="35.1" customHeight="1">
-      <c r="B25" s="188"/>
-      <c r="C25" s="198" t="s">
+      <c r="F24" s="121"/>
+      <c r="G24" s="123"/>
+      <c r="H24" s="121"/>
+      <c r="I24" s="178"/>
+    </row>
+    <row r="25" spans="2:9" ht="35.15" customHeight="1">
+      <c r="B25" s="219"/>
+      <c r="C25" s="226" t="s">
         <v>37</v>
       </c>
       <c r="D25" s="23" t="s">
@@ -11140,102 +11252,102 @@
       <c r="E25" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F25" s="121" t="s">
-        <v>176</v>
-      </c>
-      <c r="G25" s="150" t="s">
-        <v>122</v>
-      </c>
-      <c r="H25" s="229" t="s">
-        <v>177</v>
-      </c>
-      <c r="I25" s="137"/>
+      <c r="F25" s="124" t="s">
+        <v>174</v>
+      </c>
+      <c r="G25" s="189" t="s">
+        <v>121</v>
+      </c>
+      <c r="H25" s="248" t="s">
+        <v>175</v>
+      </c>
+      <c r="I25" s="178"/>
     </row>
     <row r="26" spans="2:9">
-      <c r="B26" s="188"/>
-      <c r="C26" s="202"/>
+      <c r="B26" s="219"/>
+      <c r="C26" s="228"/>
       <c r="D26" s="24" t="s">
         <v>39</v>
       </c>
       <c r="E26" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F26" s="122"/>
-      <c r="G26" s="228"/>
-      <c r="H26" s="133"/>
-      <c r="I26" s="137"/>
+      <c r="F26" s="168"/>
+      <c r="G26" s="247"/>
+      <c r="H26" s="174"/>
+      <c r="I26" s="178"/>
     </row>
     <row r="27" spans="2:9">
-      <c r="B27" s="188"/>
-      <c r="C27" s="202"/>
+      <c r="B27" s="219"/>
+      <c r="C27" s="228"/>
       <c r="D27" s="24"/>
       <c r="E27" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F27" s="122"/>
-      <c r="G27" s="228"/>
-      <c r="H27" s="133"/>
-      <c r="I27" s="137"/>
+      <c r="F27" s="168"/>
+      <c r="G27" s="247"/>
+      <c r="H27" s="174"/>
+      <c r="I27" s="178"/>
     </row>
     <row r="28" spans="2:9">
-      <c r="B28" s="188"/>
-      <c r="C28" s="202"/>
+      <c r="B28" s="219"/>
+      <c r="C28" s="228"/>
       <c r="D28" s="24"/>
       <c r="E28" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F28" s="122"/>
-      <c r="G28" s="228"/>
-      <c r="H28" s="133"/>
-      <c r="I28" s="137"/>
+      <c r="F28" s="168"/>
+      <c r="G28" s="247"/>
+      <c r="H28" s="174"/>
+      <c r="I28" s="178"/>
     </row>
     <row r="29" spans="2:9">
-      <c r="B29" s="188"/>
-      <c r="C29" s="202"/>
+      <c r="B29" s="219"/>
+      <c r="C29" s="228"/>
       <c r="D29" s="24"/>
       <c r="E29" s="14"/>
-      <c r="F29" s="122"/>
-      <c r="G29" s="228"/>
-      <c r="H29" s="133"/>
-      <c r="I29" s="137"/>
+      <c r="F29" s="168"/>
+      <c r="G29" s="247"/>
+      <c r="H29" s="174"/>
+      <c r="I29" s="178"/>
     </row>
     <row r="30" spans="2:9">
-      <c r="B30" s="188"/>
-      <c r="C30" s="202"/>
+      <c r="B30" s="219"/>
+      <c r="C30" s="228"/>
       <c r="D30" s="24"/>
-      <c r="E30" s="115" t="s">
+      <c r="E30" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="F30" s="122"/>
-      <c r="G30" s="228"/>
-      <c r="H30" s="133"/>
-      <c r="I30" s="137"/>
+      <c r="F30" s="168"/>
+      <c r="G30" s="247"/>
+      <c r="H30" s="174"/>
+      <c r="I30" s="178"/>
     </row>
     <row r="31" spans="2:9">
-      <c r="B31" s="188"/>
-      <c r="C31" s="202"/>
+      <c r="B31" s="219"/>
+      <c r="C31" s="228"/>
       <c r="D31" s="24"/>
-      <c r="E31" s="115" t="s">
-        <v>104</v>
-      </c>
-      <c r="F31" s="122"/>
-      <c r="G31" s="228"/>
-      <c r="H31" s="133"/>
-      <c r="I31" s="137"/>
+      <c r="E31" s="113" t="s">
+        <v>103</v>
+      </c>
+      <c r="F31" s="168"/>
+      <c r="G31" s="247"/>
+      <c r="H31" s="174"/>
+      <c r="I31" s="178"/>
     </row>
     <row r="32" spans="2:9">
-      <c r="B32" s="188"/>
-      <c r="C32" s="199"/>
+      <c r="B32" s="219"/>
+      <c r="C32" s="227"/>
       <c r="D32" s="25"/>
       <c r="E32" s="26"/>
-      <c r="F32" s="123"/>
-      <c r="G32" s="151"/>
-      <c r="H32" s="132"/>
-      <c r="I32" s="137"/>
+      <c r="F32" s="125"/>
+      <c r="G32" s="190"/>
+      <c r="H32" s="157"/>
+      <c r="I32" s="178"/>
     </row>
     <row r="33" spans="2:9">
-      <c r="B33" s="188"/>
-      <c r="C33" s="198" t="s">
+      <c r="B33" s="219"/>
+      <c r="C33" s="226" t="s">
         <v>44</v>
       </c>
       <c r="D33" s="23" t="s">
@@ -11244,33 +11356,33 @@
       <c r="E33" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F33" s="226" t="s">
-        <v>175</v>
-      </c>
-      <c r="G33" s="141" t="s">
-        <v>125</v>
-      </c>
-      <c r="H33" s="131" t="s">
-        <v>128</v>
-      </c>
-      <c r="I33" s="137"/>
+      <c r="F33" s="245" t="s">
+        <v>173</v>
+      </c>
+      <c r="G33" s="180" t="s">
+        <v>124</v>
+      </c>
+      <c r="H33" s="173" t="s">
+        <v>127</v>
+      </c>
+      <c r="I33" s="178"/>
     </row>
     <row r="34" spans="2:9" ht="123.4" customHeight="1">
-      <c r="B34" s="188"/>
-      <c r="C34" s="199"/>
+      <c r="B34" s="219"/>
+      <c r="C34" s="227"/>
       <c r="D34" s="27" t="s">
         <v>46</v>
       </c>
       <c r="E34" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="F34" s="227"/>
-      <c r="G34" s="142"/>
-      <c r="H34" s="132"/>
-      <c r="I34" s="137"/>
+      <c r="F34" s="246"/>
+      <c r="G34" s="181"/>
+      <c r="H34" s="157"/>
+      <c r="I34" s="178"/>
     </row>
     <row r="35" spans="2:9" ht="141" customHeight="1">
-      <c r="B35" s="188"/>
+      <c r="B35" s="219"/>
       <c r="C35" s="28" t="s">
         <v>50</v>
       </c>
@@ -11281,272 +11393,272 @@
         <v>52</v>
       </c>
       <c r="F35" s="9"/>
-      <c r="G35" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="H35" s="99" t="s">
+      <c r="G35" s="62" t="s">
         <v>129</v>
       </c>
-      <c r="I35" s="138"/>
-    </row>
-    <row r="36" spans="2:9" ht="33.75" thickBot="1">
-      <c r="B36" s="189"/>
+      <c r="H35" s="97" t="s">
+        <v>128</v>
+      </c>
+      <c r="I35" s="179"/>
+    </row>
+    <row r="36" spans="2:9" ht="34.5" thickBot="1">
+      <c r="B36" s="220"/>
       <c r="C36" s="31" t="s">
         <v>54</v>
       </c>
       <c r="D36" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="E36" s="60" t="s">
+      <c r="E36" s="59" t="s">
         <v>56</v>
       </c>
-      <c r="F36" s="61"/>
-      <c r="G36" s="88"/>
-      <c r="H36" s="88"/>
-      <c r="I36" s="110"/>
-    </row>
-    <row r="37" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B37" s="82"/>
-      <c r="C37" s="83"/>
-      <c r="D37" s="84"/>
-      <c r="E37" s="85"/>
-      <c r="F37" s="89"/>
-      <c r="G37" s="93"/>
-      <c r="H37" s="100"/>
-      <c r="I37" s="94"/>
+      <c r="F36" s="60"/>
+      <c r="G36" s="86"/>
+      <c r="H36" s="86"/>
+      <c r="I36" s="108"/>
+    </row>
+    <row r="37" spans="2:9" ht="17.5" thickBot="1">
+      <c r="B37" s="80"/>
+      <c r="C37" s="81"/>
+      <c r="D37" s="82"/>
+      <c r="E37" s="83"/>
+      <c r="F37" s="87"/>
+      <c r="G37" s="91"/>
+      <c r="H37" s="98"/>
+      <c r="I37" s="92"/>
     </row>
     <row r="38" spans="2:9">
-      <c r="B38" s="187" t="s">
+      <c r="B38" s="218" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="213" t="s">
+      <c r="C38" s="235" t="s">
         <v>58</v>
       </c>
       <c r="D38" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="E38" s="214" t="s">
+      <c r="E38" s="156" t="s">
         <v>61</v>
       </c>
-      <c r="F38" s="124" t="s">
-        <v>178</v>
-      </c>
-      <c r="G38" s="154" t="s">
-        <v>142</v>
-      </c>
-      <c r="H38" s="156" t="s">
-        <v>144</v>
-      </c>
-      <c r="I38" s="134" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="39" spans="2:9" ht="149.1" customHeight="1">
-      <c r="B39" s="188"/>
-      <c r="C39" s="202"/>
+      <c r="F38" s="169" t="s">
+        <v>176</v>
+      </c>
+      <c r="G38" s="122" t="s">
+        <v>141</v>
+      </c>
+      <c r="H38" s="193" t="s">
+        <v>143</v>
+      </c>
+      <c r="I38" s="175" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" ht="149.15" customHeight="1">
+      <c r="B39" s="219"/>
+      <c r="C39" s="228"/>
       <c r="D39" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="E39" s="132"/>
-      <c r="F39" s="125"/>
-      <c r="G39" s="155"/>
-      <c r="H39" s="157"/>
-      <c r="I39" s="135"/>
+      <c r="E39" s="157"/>
+      <c r="F39" s="121"/>
+      <c r="G39" s="123"/>
+      <c r="H39" s="194"/>
+      <c r="I39" s="176"/>
     </row>
     <row r="40" spans="2:9">
-      <c r="B40" s="188"/>
-      <c r="C40" s="202"/>
-      <c r="D40" s="215" t="s">
+      <c r="B40" s="219"/>
+      <c r="C40" s="228"/>
+      <c r="D40" s="141" t="s">
         <v>62</v>
       </c>
       <c r="E40" s="12" t="s">
         <v>63</v>
       </c>
       <c r="F40" s="126" t="s">
-        <v>181</v>
-      </c>
-      <c r="G40" s="158" t="s">
-        <v>143</v>
-      </c>
-      <c r="H40" s="152" t="s">
-        <v>145</v>
-      </c>
-      <c r="I40" s="135"/>
+        <v>179</v>
+      </c>
+      <c r="G40" s="143" t="s">
+        <v>142</v>
+      </c>
+      <c r="H40" s="191" t="s">
+        <v>144</v>
+      </c>
+      <c r="I40" s="176"/>
     </row>
     <row r="41" spans="2:9" ht="119.65" customHeight="1">
-      <c r="B41" s="188"/>
-      <c r="C41" s="199"/>
-      <c r="D41" s="216"/>
+      <c r="B41" s="219"/>
+      <c r="C41" s="227"/>
+      <c r="D41" s="142"/>
       <c r="E41" s="35" t="s">
         <v>64</v>
       </c>
       <c r="F41" s="127"/>
-      <c r="G41" s="159"/>
-      <c r="H41" s="153"/>
-      <c r="I41" s="135"/>
+      <c r="G41" s="144"/>
+      <c r="H41" s="192"/>
+      <c r="I41" s="176"/>
     </row>
     <row r="42" spans="2:9">
-      <c r="B42" s="188"/>
-      <c r="C42" s="198" t="s">
+      <c r="B42" s="219"/>
+      <c r="C42" s="226" t="s">
         <v>65</v>
       </c>
-      <c r="D42" s="209" t="s">
+      <c r="D42" s="161" t="s">
         <v>66</v>
       </c>
-      <c r="E42" s="121" t="s">
+      <c r="E42" s="124" t="s">
+        <v>137</v>
+      </c>
+      <c r="F42" s="126" t="s">
+        <v>178</v>
+      </c>
+      <c r="G42" s="143" t="s">
         <v>138</v>
       </c>
-      <c r="F42" s="126" t="s">
-        <v>180</v>
-      </c>
-      <c r="G42" s="158" t="s">
-        <v>139</v>
-      </c>
-      <c r="H42" s="160" t="s">
-        <v>146</v>
-      </c>
-      <c r="I42" s="135"/>
+      <c r="H42" s="195" t="s">
+        <v>145</v>
+      </c>
+      <c r="I42" s="176"/>
     </row>
     <row r="43" spans="2:9" ht="113.65" customHeight="1">
-      <c r="B43" s="188"/>
-      <c r="C43" s="202"/>
-      <c r="D43" s="210"/>
-      <c r="E43" s="123"/>
+      <c r="B43" s="219"/>
+      <c r="C43" s="228"/>
+      <c r="D43" s="162"/>
+      <c r="E43" s="125"/>
       <c r="F43" s="127"/>
-      <c r="G43" s="159"/>
-      <c r="H43" s="160"/>
-      <c r="I43" s="135"/>
+      <c r="G43" s="144"/>
+      <c r="H43" s="195"/>
+      <c r="I43" s="176"/>
     </row>
     <row r="44" spans="2:9">
-      <c r="B44" s="188"/>
-      <c r="C44" s="202"/>
-      <c r="D44" s="200" t="s">
+      <c r="B44" s="219"/>
+      <c r="C44" s="228"/>
+      <c r="D44" s="152" t="s">
         <v>67</v>
       </c>
       <c r="E44" s="126" t="s">
-        <v>179</v>
-      </c>
-      <c r="F44" s="211"/>
-      <c r="G44" s="139" t="s">
-        <v>194</v>
-      </c>
-      <c r="H44" s="160"/>
-      <c r="I44" s="135"/>
+        <v>177</v>
+      </c>
+      <c r="F44" s="233"/>
+      <c r="G44" s="154" t="s">
+        <v>189</v>
+      </c>
+      <c r="H44" s="195"/>
+      <c r="I44" s="176"/>
     </row>
     <row r="45" spans="2:9" ht="317.64999999999998" customHeight="1">
-      <c r="B45" s="188"/>
-      <c r="C45" s="199"/>
-      <c r="D45" s="201"/>
+      <c r="B45" s="219"/>
+      <c r="C45" s="227"/>
+      <c r="D45" s="153"/>
       <c r="E45" s="127"/>
-      <c r="F45" s="212"/>
-      <c r="G45" s="140"/>
-      <c r="H45" s="153"/>
-      <c r="I45" s="135"/>
+      <c r="F45" s="234"/>
+      <c r="G45" s="155"/>
+      <c r="H45" s="192"/>
+      <c r="I45" s="176"/>
     </row>
     <row r="46" spans="2:9">
-      <c r="B46" s="188"/>
-      <c r="C46" s="198" t="s">
+      <c r="B46" s="219"/>
+      <c r="C46" s="226" t="s">
         <v>68</v>
       </c>
       <c r="D46" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="E46" s="203" t="s">
+      <c r="E46" s="158" t="s">
         <v>71</v>
       </c>
-      <c r="F46" s="131" t="s">
-        <v>182</v>
-      </c>
-      <c r="G46" s="161" t="s">
-        <v>195</v>
-      </c>
-      <c r="H46" s="164"/>
-      <c r="I46" s="135"/>
+      <c r="F46" s="173" t="s">
+        <v>180</v>
+      </c>
+      <c r="G46" s="131" t="s">
+        <v>201</v>
+      </c>
+      <c r="H46" s="196"/>
+      <c r="I46" s="176"/>
     </row>
     <row r="47" spans="2:9">
-      <c r="B47" s="188"/>
-      <c r="C47" s="202"/>
+      <c r="B47" s="219"/>
+      <c r="C47" s="228"/>
       <c r="D47" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="E47" s="204"/>
-      <c r="F47" s="133"/>
-      <c r="G47" s="162"/>
-      <c r="H47" s="164"/>
-      <c r="I47" s="135"/>
+        <v>170</v>
+      </c>
+      <c r="E47" s="159"/>
+      <c r="F47" s="174"/>
+      <c r="G47" s="132"/>
+      <c r="H47" s="196"/>
+      <c r="I47" s="176"/>
     </row>
     <row r="48" spans="2:9">
-      <c r="B48" s="188"/>
-      <c r="C48" s="202"/>
-      <c r="D48" s="297" t="s">
-        <v>203</v>
-      </c>
-      <c r="E48" s="204"/>
-      <c r="F48" s="133"/>
-      <c r="G48" s="162"/>
-      <c r="H48" s="164"/>
-      <c r="I48" s="135"/>
+      <c r="B48" s="219"/>
+      <c r="C48" s="228"/>
+      <c r="D48" s="114" t="s">
+        <v>197</v>
+      </c>
+      <c r="E48" s="159"/>
+      <c r="F48" s="174"/>
+      <c r="G48" s="132"/>
+      <c r="H48" s="196"/>
+      <c r="I48" s="176"/>
     </row>
     <row r="49" spans="2:9">
-      <c r="B49" s="188"/>
-      <c r="C49" s="202"/>
+      <c r="B49" s="219"/>
+      <c r="C49" s="228"/>
       <c r="D49" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="E49" s="204"/>
-      <c r="F49" s="133"/>
-      <c r="G49" s="162"/>
-      <c r="H49" s="164"/>
-      <c r="I49" s="135"/>
+      <c r="E49" s="159"/>
+      <c r="F49" s="174"/>
+      <c r="G49" s="132"/>
+      <c r="H49" s="196"/>
+      <c r="I49" s="176"/>
     </row>
     <row r="50" spans="2:9">
-      <c r="B50" s="188"/>
-      <c r="C50" s="202"/>
+      <c r="B50" s="219"/>
+      <c r="C50" s="228"/>
       <c r="D50" s="37"/>
-      <c r="E50" s="204"/>
-      <c r="F50" s="133"/>
-      <c r="G50" s="162"/>
-      <c r="H50" s="164"/>
-      <c r="I50" s="135"/>
-    </row>
-    <row r="51" spans="2:9" ht="223.5" customHeight="1" thickBot="1">
-      <c r="B51" s="188"/>
-      <c r="C51" s="199"/>
+      <c r="E50" s="159"/>
+      <c r="F50" s="174"/>
+      <c r="G50" s="132"/>
+      <c r="H50" s="196"/>
+      <c r="I50" s="176"/>
+    </row>
+    <row r="51" spans="2:9" ht="317.5" customHeight="1" thickBot="1">
+      <c r="B51" s="219"/>
+      <c r="C51" s="227"/>
       <c r="D51" s="37"/>
-      <c r="E51" s="205"/>
-      <c r="F51" s="132"/>
-      <c r="G51" s="163"/>
-      <c r="H51" s="165"/>
-      <c r="I51" s="136"/>
-    </row>
-    <row r="52" spans="2:9" ht="30.75" thickBot="1">
-      <c r="B52" s="189"/>
+      <c r="E51" s="229"/>
+      <c r="F51" s="157"/>
+      <c r="G51" s="133"/>
+      <c r="H51" s="197"/>
+      <c r="I51" s="177"/>
+    </row>
+    <row r="52" spans="2:9" ht="29.5" thickBot="1">
+      <c r="B52" s="220"/>
       <c r="C52" s="38" t="s">
         <v>72</v>
       </c>
       <c r="D52" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="E52" s="206" t="s">
+      <c r="E52" s="230" t="s">
         <v>56</v>
       </c>
-      <c r="F52" s="207"/>
-      <c r="G52" s="207"/>
-      <c r="H52" s="207"/>
-      <c r="I52" s="208"/>
-    </row>
-    <row r="53" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B53" s="82"/>
-      <c r="C53" s="83"/>
-      <c r="D53" s="84"/>
-      <c r="E53" s="85"/>
-      <c r="F53" s="86"/>
-      <c r="G53" s="93"/>
-      <c r="H53" s="100"/>
-      <c r="I53" s="95"/>
-    </row>
-    <row r="54" spans="2:9" ht="94.7" customHeight="1">
-      <c r="B54" s="187" t="s">
+      <c r="F52" s="231"/>
+      <c r="G52" s="231"/>
+      <c r="H52" s="231"/>
+      <c r="I52" s="232"/>
+    </row>
+    <row r="53" spans="2:9" ht="17.5" thickBot="1">
+      <c r="B53" s="80"/>
+      <c r="C53" s="81"/>
+      <c r="D53" s="82"/>
+      <c r="E53" s="83"/>
+      <c r="F53" s="84"/>
+      <c r="G53" s="91"/>
+      <c r="H53" s="98"/>
+      <c r="I53" s="93"/>
+    </row>
+    <row r="54" spans="2:9" ht="94.75" customHeight="1">
+      <c r="B54" s="218" t="s">
         <v>74</v>
       </c>
       <c r="C54" s="40" t="s">
@@ -11559,52 +11671,52 @@
         <v>77</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G54" s="69" t="s">
-        <v>151</v>
-      </c>
-      <c r="H54" s="111" t="s">
-        <v>148</v>
-      </c>
-      <c r="I54" s="134" t="s">
-        <v>189</v>
+        <v>147</v>
+      </c>
+      <c r="G54" s="68" t="s">
+        <v>150</v>
+      </c>
+      <c r="H54" s="109" t="s">
+        <v>147</v>
+      </c>
+      <c r="I54" s="175" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="55" spans="2:9">
-      <c r="B55" s="188"/>
-      <c r="C55" s="198" t="s">
+      <c r="B55" s="219"/>
+      <c r="C55" s="226" t="s">
         <v>16</v>
       </c>
-      <c r="D55" s="200" t="s">
+      <c r="D55" s="152" t="s">
         <v>78</v>
       </c>
-      <c r="E55" s="131" t="s">
-        <v>196</v>
-      </c>
-      <c r="F55" s="131" t="s">
-        <v>183</v>
-      </c>
-      <c r="G55" s="150" t="s">
-        <v>197</v>
-      </c>
-      <c r="H55" s="152" t="s">
-        <v>184</v>
-      </c>
-      <c r="I55" s="135"/>
-    </row>
-    <row r="56" spans="2:9" ht="150.4" customHeight="1">
-      <c r="B56" s="188"/>
-      <c r="C56" s="199"/>
-      <c r="D56" s="201"/>
-      <c r="E56" s="132"/>
-      <c r="F56" s="132"/>
-      <c r="G56" s="151"/>
-      <c r="H56" s="153"/>
-      <c r="I56" s="135"/>
-    </row>
-    <row r="57" spans="2:9" ht="181.7" customHeight="1">
-      <c r="B57" s="188"/>
+      <c r="E55" s="173" t="s">
+        <v>190</v>
+      </c>
+      <c r="F55" s="173" t="s">
+        <v>181</v>
+      </c>
+      <c r="G55" s="189" t="s">
+        <v>191</v>
+      </c>
+      <c r="H55" s="191" t="s">
+        <v>182</v>
+      </c>
+      <c r="I55" s="176"/>
+    </row>
+    <row r="56" spans="2:9" ht="207" customHeight="1">
+      <c r="B56" s="219"/>
+      <c r="C56" s="227"/>
+      <c r="D56" s="153"/>
+      <c r="E56" s="157"/>
+      <c r="F56" s="157"/>
+      <c r="G56" s="190"/>
+      <c r="H56" s="192"/>
+      <c r="I56" s="176"/>
+    </row>
+    <row r="57" spans="2:9" ht="181.75" customHeight="1">
+      <c r="B57" s="219"/>
       <c r="C57" s="28" t="s">
         <v>79</v>
       </c>
@@ -11615,41 +11727,41 @@
         <v>80</v>
       </c>
       <c r="F57" s="9"/>
-      <c r="G57" s="90" t="s">
-        <v>193</v>
-      </c>
-      <c r="H57" s="101"/>
-      <c r="I57" s="136"/>
-    </row>
-    <row r="58" spans="2:9" ht="33.75" thickBot="1">
-      <c r="B58" s="189"/>
+      <c r="G57" s="88" t="s">
+        <v>188</v>
+      </c>
+      <c r="H57" s="99"/>
+      <c r="I57" s="177"/>
+    </row>
+    <row r="58" spans="2:9" ht="34.5" thickBot="1">
+      <c r="B58" s="220"/>
       <c r="C58" s="31" t="s">
         <v>72</v>
       </c>
       <c r="D58" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="E58" s="128" t="s">
+      <c r="E58" s="170" t="s">
         <v>56</v>
       </c>
-      <c r="F58" s="129"/>
-      <c r="G58" s="129"/>
-      <c r="H58" s="129"/>
-      <c r="I58" s="130"/>
-    </row>
-    <row r="59" spans="2:9" ht="17.25" thickBot="1">
-      <c r="B59" s="78"/>
-      <c r="C59" s="79"/>
-      <c r="D59" s="80"/>
-      <c r="E59" s="81"/>
-      <c r="F59" s="81"/>
-      <c r="G59" s="93"/>
-      <c r="H59" s="100"/>
-      <c r="I59" s="96"/>
-    </row>
-    <row r="60" spans="2:9" ht="66">
-      <c r="B60" s="190" t="s">
-        <v>156</v>
+      <c r="F58" s="171"/>
+      <c r="G58" s="171"/>
+      <c r="H58" s="171"/>
+      <c r="I58" s="172"/>
+    </row>
+    <row r="59" spans="2:9" ht="17.5" thickBot="1">
+      <c r="B59" s="76"/>
+      <c r="C59" s="77"/>
+      <c r="D59" s="78"/>
+      <c r="E59" s="79"/>
+      <c r="F59" s="79"/>
+      <c r="G59" s="91"/>
+      <c r="H59" s="98"/>
+      <c r="I59" s="94"/>
+    </row>
+    <row r="60" spans="2:9" ht="68">
+      <c r="B60" s="117" t="s">
+        <v>155</v>
       </c>
       <c r="C60" s="40" t="s">
         <v>82</v>
@@ -11658,19 +11770,19 @@
         <v>83</v>
       </c>
       <c r="E60" s="42" t="s">
-        <v>157</v>
-      </c>
-      <c r="F60" s="72"/>
-      <c r="G60" s="72" t="s">
-        <v>171</v>
-      </c>
-      <c r="H60" s="102"/>
-      <c r="I60" s="134" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="61" spans="2:9" ht="148.5">
-      <c r="B61" s="191"/>
+        <v>156</v>
+      </c>
+      <c r="F60" s="70"/>
+      <c r="G60" s="70" t="s">
+        <v>169</v>
+      </c>
+      <c r="H60" s="100"/>
+      <c r="I60" s="175" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" ht="228.5" customHeight="1">
+      <c r="B61" s="118"/>
       <c r="C61" s="28" t="s">
         <v>85</v>
       </c>
@@ -11678,15 +11790,15 @@
         <v>86</v>
       </c>
       <c r="E61" s="30"/>
-      <c r="F61" s="73"/>
-      <c r="G61" s="73" t="s">
-        <v>166</v>
-      </c>
-      <c r="H61" s="103"/>
-      <c r="I61" s="137"/>
-    </row>
-    <row r="62" spans="2:9" ht="181.5">
-      <c r="B62" s="191"/>
+      <c r="F61" s="71"/>
+      <c r="G61" s="71" t="s">
+        <v>198</v>
+      </c>
+      <c r="H61" s="101"/>
+      <c r="I61" s="178"/>
+    </row>
+    <row r="62" spans="2:9" ht="170">
+      <c r="B62" s="118"/>
       <c r="C62" s="28" t="s">
         <v>87</v>
       </c>
@@ -11696,19 +11808,19 @@
       <c r="E62" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="F62" s="109" t="s">
-        <v>198</v>
-      </c>
-      <c r="G62" s="87" t="s">
-        <v>190</v>
-      </c>
-      <c r="H62" s="112" t="s">
-        <v>202</v>
-      </c>
-      <c r="I62" s="137"/>
-    </row>
-    <row r="63" spans="2:9" ht="33">
-      <c r="B63" s="191"/>
+      <c r="F62" s="107" t="s">
+        <v>192</v>
+      </c>
+      <c r="G62" s="85" t="s">
+        <v>187</v>
+      </c>
+      <c r="H62" s="110" t="s">
+        <v>196</v>
+      </c>
+      <c r="I62" s="178"/>
+    </row>
+    <row r="63" spans="2:9" ht="34">
+      <c r="B63" s="118"/>
       <c r="C63" s="28" t="s">
         <v>90</v>
       </c>
@@ -11716,48 +11828,48 @@
         <v>91</v>
       </c>
       <c r="E63" s="30" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="F63" s="30"/>
-      <c r="G63" s="30" t="s">
-        <v>200</v>
-      </c>
-      <c r="H63" s="104"/>
-      <c r="I63" s="137"/>
-    </row>
-    <row r="64" spans="2:9" ht="82.5">
-      <c r="B64" s="191"/>
+      <c r="G63" s="73" t="s">
+        <v>194</v>
+      </c>
+      <c r="H63" s="102"/>
+      <c r="I63" s="178"/>
+    </row>
+    <row r="64" spans="2:9" ht="85">
+      <c r="B64" s="118"/>
       <c r="C64" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="D64" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="D64" s="29" t="s">
+      <c r="E64" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="E64" s="30" t="s">
+      <c r="F64" s="30"/>
+      <c r="G64" s="74" t="s">
+        <v>158</v>
+      </c>
+      <c r="H64" s="103"/>
+      <c r="I64" s="179"/>
+    </row>
+    <row r="65" spans="2:9" ht="34.5" thickBot="1">
+      <c r="B65" s="119"/>
+      <c r="C65" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="F64" s="30"/>
-      <c r="G64" s="76" t="s">
-        <v>159</v>
-      </c>
-      <c r="H64" s="105"/>
-      <c r="I64" s="138"/>
-    </row>
-    <row r="65" spans="2:9" ht="33.75" thickBot="1">
-      <c r="B65" s="192"/>
-      <c r="C65" s="31" t="s">
+      <c r="D65" s="111" t="s">
         <v>96</v>
       </c>
-      <c r="D65" s="113" t="s">
-        <v>97</v>
-      </c>
-      <c r="E65" s="116" t="s">
+      <c r="E65" s="163" t="s">
         <v>56</v>
       </c>
-      <c r="F65" s="117"/>
-      <c r="G65" s="117"/>
-      <c r="H65" s="117"/>
-      <c r="I65" s="118"/>
+      <c r="F65" s="164"/>
+      <c r="G65" s="164"/>
+      <c r="H65" s="164"/>
+      <c r="I65" s="165"/>
     </row>
   </sheetData>
   <mergeCells count="76">
@@ -11857,16 +11969,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84E26AAC-33B4-4831-8771-3672B1AF7BF1}">
   <dimension ref="B3:G29"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="4" max="4" width="31.625" customWidth="1"/>
+    <col min="4" max="4" width="31.58203125" customWidth="1"/>
     <col min="5" max="5" width="61.75" customWidth="1"/>
-    <col min="6" max="6" width="72.625" customWidth="1"/>
+    <col min="6" max="6" width="72.58203125" customWidth="1"/>
     <col min="7" max="7" width="38.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:7" ht="17.25" thickBot="1"/>
-    <row r="4" spans="2:7" ht="17.25" thickBot="1">
+    <row r="3" spans="2:7" ht="17.5" thickBot="1"/>
+    <row r="4" spans="2:7" ht="17.5" thickBot="1">
       <c r="B4" s="46"/>
       <c r="C4" s="47" t="s">
         <v>0</v>
@@ -11875,76 +11987,76 @@
         <v>1</v>
       </c>
       <c r="E4" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="F4" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="F4" s="47" t="s">
-        <v>100</v>
-      </c>
       <c r="G4" s="48" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="33">
-      <c r="B5" s="242" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="34">
+      <c r="B5" s="260" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="53" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="55" t="s">
-        <v>113</v>
-      </c>
-      <c r="F5" s="56" t="s">
-        <v>102</v>
-      </c>
-      <c r="G5" s="57"/>
+      <c r="E5" s="54" t="s">
+        <v>112</v>
+      </c>
+      <c r="F5" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="G5" s="56"/>
     </row>
     <row r="6" spans="2:7">
-      <c r="B6" s="243"/>
-      <c r="C6" s="248" t="s">
+      <c r="B6" s="261"/>
+      <c r="C6" s="266" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="203" t="s">
+      <c r="D6" s="158" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="126" t="s">
+        <v>100</v>
+      </c>
+      <c r="F6" s="143" t="s">
         <v>101</v>
       </c>
-      <c r="F6" s="158" t="s">
-        <v>102</v>
-      </c>
-      <c r="G6" s="239"/>
+      <c r="G6" s="257"/>
     </row>
     <row r="7" spans="2:7">
-      <c r="B7" s="243"/>
-      <c r="C7" s="249"/>
-      <c r="D7" s="204"/>
-      <c r="E7" s="170"/>
-      <c r="F7" s="193"/>
-      <c r="G7" s="240"/>
+      <c r="B7" s="261"/>
+      <c r="C7" s="267"/>
+      <c r="D7" s="159"/>
+      <c r="E7" s="202"/>
+      <c r="F7" s="221"/>
+      <c r="G7" s="258"/>
     </row>
     <row r="8" spans="2:7">
-      <c r="B8" s="243"/>
-      <c r="C8" s="249"/>
-      <c r="D8" s="204"/>
-      <c r="E8" s="170"/>
-      <c r="F8" s="193"/>
-      <c r="G8" s="240"/>
+      <c r="B8" s="261"/>
+      <c r="C8" s="267"/>
+      <c r="D8" s="159"/>
+      <c r="E8" s="202"/>
+      <c r="F8" s="221"/>
+      <c r="G8" s="258"/>
     </row>
     <row r="9" spans="2:7">
-      <c r="B9" s="243"/>
-      <c r="C9" s="253"/>
-      <c r="D9" s="220"/>
+      <c r="B9" s="261"/>
+      <c r="C9" s="271"/>
+      <c r="D9" s="239"/>
       <c r="E9" s="127"/>
-      <c r="F9" s="194"/>
-      <c r="G9" s="241"/>
-    </row>
-    <row r="10" spans="2:7" ht="33">
-      <c r="B10" s="243"/>
-      <c r="C10" s="58" t="s">
+      <c r="F9" s="222"/>
+      <c r="G9" s="259"/>
+    </row>
+    <row r="10" spans="2:7" ht="34">
+      <c r="B10" s="261"/>
+      <c r="C10" s="57" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="8" t="s">
@@ -11952,160 +12064,160 @@
       </c>
       <c r="E10" s="45"/>
       <c r="F10" s="51" t="s">
+        <v>107</v>
+      </c>
+      <c r="G10" s="116"/>
+    </row>
+    <row r="11" spans="2:7">
+      <c r="B11" s="261"/>
+      <c r="C11" s="266" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="243" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="126" t="s">
+        <v>105</v>
+      </c>
+      <c r="F11" s="249" t="s">
+        <v>117</v>
+      </c>
+      <c r="G11" s="151" t="s">
         <v>108</v>
       </c>
-      <c r="G10" s="52"/>
-    </row>
-    <row r="11" spans="2:7">
-      <c r="B11" s="243"/>
-      <c r="C11" s="248" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="224" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="126" t="s">
+    </row>
+    <row r="12" spans="2:7">
+      <c r="B12" s="261"/>
+      <c r="C12" s="267"/>
+      <c r="D12" s="270"/>
+      <c r="E12" s="202"/>
+      <c r="F12" s="250"/>
+      <c r="G12" s="275"/>
+    </row>
+    <row r="13" spans="2:7" ht="286.75" customHeight="1">
+      <c r="B13" s="261"/>
+      <c r="C13" s="269"/>
+      <c r="D13" s="244"/>
+      <c r="E13" s="127"/>
+      <c r="F13" s="123"/>
+      <c r="G13" s="276"/>
+    </row>
+    <row r="14" spans="2:7" ht="35.15" customHeight="1">
+      <c r="B14" s="261"/>
+      <c r="C14" s="266" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="263" t="s">
+        <v>114</v>
+      </c>
+      <c r="E14" s="126" t="s">
         <v>106</v>
       </c>
-      <c r="F11" s="230" t="s">
-        <v>118</v>
-      </c>
-      <c r="G11" s="257" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7">
-      <c r="B12" s="243"/>
-      <c r="C12" s="249"/>
-      <c r="D12" s="252"/>
-      <c r="E12" s="170"/>
-      <c r="F12" s="231"/>
-      <c r="G12" s="258"/>
-    </row>
-    <row r="13" spans="2:7" ht="286.7" customHeight="1">
-      <c r="B13" s="243"/>
-      <c r="C13" s="251"/>
-      <c r="D13" s="225"/>
-      <c r="E13" s="127"/>
-      <c r="F13" s="155"/>
-      <c r="G13" s="259"/>
-    </row>
-    <row r="14" spans="2:7" ht="35.1" customHeight="1">
-      <c r="B14" s="243"/>
-      <c r="C14" s="248" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="245" t="s">
+      <c r="F14" s="249" t="s">
         <v>115</v>
       </c>
-      <c r="E14" s="126" t="s">
-        <v>107</v>
-      </c>
-      <c r="F14" s="230" t="s">
-        <v>116</v>
-      </c>
-      <c r="G14" s="232" t="s">
-        <v>112</v>
+      <c r="G14" s="251" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="2:7">
-      <c r="B15" s="243"/>
-      <c r="C15" s="249"/>
-      <c r="D15" s="246"/>
-      <c r="E15" s="170"/>
-      <c r="F15" s="231"/>
-      <c r="G15" s="233"/>
+      <c r="B15" s="261"/>
+      <c r="C15" s="267"/>
+      <c r="D15" s="264"/>
+      <c r="E15" s="202"/>
+      <c r="F15" s="250"/>
+      <c r="G15" s="252"/>
     </row>
     <row r="16" spans="2:7" ht="134.65" customHeight="1">
-      <c r="B16" s="243"/>
-      <c r="C16" s="251"/>
-      <c r="D16" s="247"/>
+      <c r="B16" s="261"/>
+      <c r="C16" s="269"/>
+      <c r="D16" s="265"/>
       <c r="E16" s="127"/>
-      <c r="F16" s="155"/>
-      <c r="G16" s="234"/>
-    </row>
-    <row r="17" spans="2:7" ht="35.1" customHeight="1">
-      <c r="B17" s="243"/>
-      <c r="C17" s="248" t="s">
+      <c r="F16" s="123"/>
+      <c r="G16" s="253"/>
+    </row>
+    <row r="17" spans="2:7" ht="35.15" customHeight="1">
+      <c r="B17" s="261"/>
+      <c r="C17" s="266" t="s">
         <v>26</v>
       </c>
       <c r="D17" s="126" t="s">
-        <v>98</v>
-      </c>
-      <c r="E17" s="203" t="s">
-        <v>103</v>
-      </c>
-      <c r="F17" s="254" t="s">
-        <v>121</v>
-      </c>
-      <c r="G17" s="236" t="s">
-        <v>111</v>
+        <v>97</v>
+      </c>
+      <c r="E17" s="158" t="s">
+        <v>102</v>
+      </c>
+      <c r="F17" s="272" t="s">
+        <v>120</v>
+      </c>
+      <c r="G17" s="254" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="243"/>
-      <c r="C18" s="249"/>
-      <c r="D18" s="170"/>
-      <c r="E18" s="204"/>
-      <c r="F18" s="255"/>
-      <c r="G18" s="237"/>
+      <c r="B18" s="261"/>
+      <c r="C18" s="267"/>
+      <c r="D18" s="202"/>
+      <c r="E18" s="159"/>
+      <c r="F18" s="273"/>
+      <c r="G18" s="255"/>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="243"/>
-      <c r="C19" s="249"/>
-      <c r="D19" s="170"/>
-      <c r="E19" s="204"/>
-      <c r="F19" s="255"/>
-      <c r="G19" s="237"/>
+      <c r="B19" s="261"/>
+      <c r="C19" s="267"/>
+      <c r="D19" s="202"/>
+      <c r="E19" s="159"/>
+      <c r="F19" s="273"/>
+      <c r="G19" s="255"/>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="243"/>
-      <c r="C20" s="249"/>
-      <c r="D20" s="170"/>
-      <c r="E20" s="204"/>
-      <c r="F20" s="255"/>
-      <c r="G20" s="237"/>
+      <c r="B20" s="261"/>
+      <c r="C20" s="267"/>
+      <c r="D20" s="202"/>
+      <c r="E20" s="159"/>
+      <c r="F20" s="273"/>
+      <c r="G20" s="255"/>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="243"/>
-      <c r="C21" s="249"/>
-      <c r="D21" s="170"/>
-      <c r="E21" s="204"/>
-      <c r="F21" s="255"/>
-      <c r="G21" s="237"/>
+      <c r="B21" s="261"/>
+      <c r="C21" s="267"/>
+      <c r="D21" s="202"/>
+      <c r="E21" s="159"/>
+      <c r="F21" s="273"/>
+      <c r="G21" s="255"/>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="243"/>
-      <c r="C22" s="249"/>
-      <c r="D22" s="170"/>
-      <c r="E22" s="204"/>
-      <c r="F22" s="255"/>
-      <c r="G22" s="237"/>
+      <c r="B22" s="261"/>
+      <c r="C22" s="267"/>
+      <c r="D22" s="202"/>
+      <c r="E22" s="159"/>
+      <c r="F22" s="273"/>
+      <c r="G22" s="255"/>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="243"/>
-      <c r="C23" s="249"/>
-      <c r="D23" s="170"/>
-      <c r="E23" s="204"/>
-      <c r="F23" s="255"/>
-      <c r="G23" s="237"/>
-    </row>
-    <row r="24" spans="2:7" ht="85.7" customHeight="1" thickBot="1">
-      <c r="B24" s="244"/>
-      <c r="C24" s="250"/>
-      <c r="D24" s="171"/>
-      <c r="E24" s="235"/>
-      <c r="F24" s="256"/>
-      <c r="G24" s="238"/>
+      <c r="B23" s="261"/>
+      <c r="C23" s="267"/>
+      <c r="D23" s="202"/>
+      <c r="E23" s="159"/>
+      <c r="F23" s="273"/>
+      <c r="G23" s="255"/>
+    </row>
+    <row r="24" spans="2:7" ht="85.75" customHeight="1" thickBot="1">
+      <c r="B24" s="262"/>
+      <c r="C24" s="268"/>
+      <c r="D24" s="203"/>
+      <c r="E24" s="160"/>
+      <c r="F24" s="274"/>
+      <c r="G24" s="256"/>
     </row>
     <row r="28" spans="2:7">
       <c r="F28" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="2:7">
       <c r="F29" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -12140,18 +12252,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A81E2051-FA1D-49F8-BE92-D7970D343145}">
   <dimension ref="B1:H46"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="3" max="3" width="33.125" customWidth="1"/>
+    <col min="3" max="3" width="33.08203125" customWidth="1"/>
     <col min="4" max="4" width="31.25" customWidth="1"/>
-    <col min="5" max="5" width="49.625" customWidth="1"/>
+    <col min="5" max="5" width="49.58203125" customWidth="1"/>
     <col min="6" max="6" width="67.25" customWidth="1"/>
-    <col min="7" max="7" width="46.125" customWidth="1"/>
-    <col min="8" max="8" width="63.125" customWidth="1"/>
+    <col min="7" max="7" width="46.08203125" customWidth="1"/>
+    <col min="8" max="8" width="63.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="17.25" thickBot="1"/>
-    <row r="2" spans="2:7" ht="17.25" thickBot="1">
+    <row r="1" spans="2:7" ht="17.5" thickBot="1"/>
+    <row r="2" spans="2:7" ht="17.5" thickBot="1">
       <c r="B2" s="46"/>
       <c r="C2" s="47" t="s">
         <v>0</v>
@@ -12160,145 +12272,145 @@
         <v>1</v>
       </c>
       <c r="E2" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="F2" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="F2" s="47" t="s">
-        <v>100</v>
-      </c>
       <c r="G2" s="48" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" ht="70.349999999999994" customHeight="1">
-      <c r="B3" s="190" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="70.400000000000006" customHeight="1">
+      <c r="B3" s="117" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="261" t="s">
+      <c r="C3" s="134" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="265" t="s">
-        <v>114</v>
-      </c>
-      <c r="E3" s="267" t="s">
+      <c r="D3" s="280" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="282" t="s">
+        <v>118</v>
+      </c>
+      <c r="F3" s="122" t="s">
+        <v>131</v>
+      </c>
+      <c r="G3" s="278" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="83.15" customHeight="1">
+      <c r="B4" s="118"/>
+      <c r="C4" s="136"/>
+      <c r="D4" s="281"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="279"/>
+    </row>
+    <row r="5" spans="2:7" ht="105.4" customHeight="1">
+      <c r="B5" s="118"/>
+      <c r="C5" s="137" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="161" t="s">
         <v>119</v>
       </c>
-      <c r="F3" s="154" t="s">
-        <v>132</v>
-      </c>
-      <c r="G3" s="263" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="83.1" customHeight="1">
-      <c r="B4" s="191"/>
-      <c r="C4" s="262"/>
-      <c r="D4" s="266"/>
-      <c r="E4" s="151"/>
-      <c r="F4" s="155"/>
-      <c r="G4" s="264"/>
-    </row>
-    <row r="5" spans="2:7" ht="105.4" customHeight="1">
-      <c r="B5" s="191"/>
-      <c r="C5" s="268" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="209" t="s">
-        <v>120</v>
-      </c>
-      <c r="E5" s="272" t="s">
+      <c r="E5" s="286" t="s">
+        <v>125</v>
+      </c>
+      <c r="F5" s="189" t="s">
+        <v>121</v>
+      </c>
+      <c r="G5" s="283" t="s">
         <v>126</v>
       </c>
-      <c r="F5" s="150" t="s">
+    </row>
+    <row r="6" spans="2:7">
+      <c r="B6" s="118"/>
+      <c r="C6" s="135"/>
+      <c r="D6" s="289"/>
+      <c r="E6" s="287"/>
+      <c r="F6" s="247"/>
+      <c r="G6" s="284"/>
+    </row>
+    <row r="7" spans="2:7">
+      <c r="B7" s="118"/>
+      <c r="C7" s="135"/>
+      <c r="D7" s="289"/>
+      <c r="E7" s="287"/>
+      <c r="F7" s="247"/>
+      <c r="G7" s="284"/>
+    </row>
+    <row r="8" spans="2:7">
+      <c r="B8" s="118"/>
+      <c r="C8" s="135"/>
+      <c r="D8" s="289"/>
+      <c r="E8" s="287"/>
+      <c r="F8" s="247"/>
+      <c r="G8" s="284"/>
+    </row>
+    <row r="9" spans="2:7">
+      <c r="B9" s="118"/>
+      <c r="C9" s="135"/>
+      <c r="D9" s="289"/>
+      <c r="E9" s="287"/>
+      <c r="F9" s="247"/>
+      <c r="G9" s="284"/>
+    </row>
+    <row r="10" spans="2:7">
+      <c r="B10" s="118"/>
+      <c r="C10" s="135"/>
+      <c r="D10" s="289"/>
+      <c r="E10" s="287"/>
+      <c r="F10" s="247"/>
+      <c r="G10" s="284"/>
+    </row>
+    <row r="11" spans="2:7">
+      <c r="B11" s="118"/>
+      <c r="C11" s="135"/>
+      <c r="D11" s="289"/>
+      <c r="E11" s="287"/>
+      <c r="F11" s="247"/>
+      <c r="G11" s="284"/>
+    </row>
+    <row r="12" spans="2:7">
+      <c r="B12" s="118"/>
+      <c r="C12" s="136"/>
+      <c r="D12" s="162"/>
+      <c r="E12" s="288"/>
+      <c r="F12" s="190"/>
+      <c r="G12" s="285"/>
+    </row>
+    <row r="13" spans="2:7" ht="139" customHeight="1">
+      <c r="B13" s="118"/>
+      <c r="C13" s="137" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="161" t="s">
+        <v>123</v>
+      </c>
+      <c r="E13" s="158" t="s">
         <v>122</v>
       </c>
-      <c r="G5" s="269" t="s">
+      <c r="F13" s="180" t="s">
+        <v>124</v>
+      </c>
+      <c r="G13" s="293" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
-      <c r="B6" s="191"/>
-      <c r="C6" s="276"/>
-      <c r="D6" s="275"/>
-      <c r="E6" s="273"/>
-      <c r="F6" s="228"/>
-      <c r="G6" s="270"/>
-    </row>
-    <row r="7" spans="2:7">
-      <c r="B7" s="191"/>
-      <c r="C7" s="276"/>
-      <c r="D7" s="275"/>
-      <c r="E7" s="273"/>
-      <c r="F7" s="228"/>
-      <c r="G7" s="270"/>
-    </row>
-    <row r="8" spans="2:7">
-      <c r="B8" s="191"/>
-      <c r="C8" s="276"/>
-      <c r="D8" s="275"/>
-      <c r="E8" s="273"/>
-      <c r="F8" s="228"/>
-      <c r="G8" s="270"/>
-    </row>
-    <row r="9" spans="2:7">
-      <c r="B9" s="191"/>
-      <c r="C9" s="276"/>
-      <c r="D9" s="275"/>
-      <c r="E9" s="273"/>
-      <c r="F9" s="228"/>
-      <c r="G9" s="270"/>
-    </row>
-    <row r="10" spans="2:7">
-      <c r="B10" s="191"/>
-      <c r="C10" s="276"/>
-      <c r="D10" s="275"/>
-      <c r="E10" s="273"/>
-      <c r="F10" s="228"/>
-      <c r="G10" s="270"/>
-    </row>
-    <row r="11" spans="2:7">
-      <c r="B11" s="191"/>
-      <c r="C11" s="276"/>
-      <c r="D11" s="275"/>
-      <c r="E11" s="273"/>
-      <c r="F11" s="228"/>
-      <c r="G11" s="270"/>
-    </row>
-    <row r="12" spans="2:7">
-      <c r="B12" s="191"/>
-      <c r="C12" s="262"/>
-      <c r="D12" s="210"/>
-      <c r="E12" s="274"/>
-      <c r="F12" s="151"/>
-      <c r="G12" s="271"/>
-    </row>
-    <row r="13" spans="2:7" ht="138.94999999999999" customHeight="1">
-      <c r="B13" s="191"/>
-      <c r="C13" s="268" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="209" t="s">
-        <v>124</v>
-      </c>
-      <c r="E13" s="203" t="s">
-        <v>123</v>
-      </c>
-      <c r="F13" s="141" t="s">
-        <v>125</v>
-      </c>
-      <c r="G13" s="280" t="s">
-        <v>128</v>
-      </c>
-    </row>
     <row r="14" spans="2:7">
-      <c r="B14" s="191"/>
-      <c r="C14" s="262"/>
-      <c r="D14" s="210"/>
-      <c r="E14" s="205"/>
-      <c r="F14" s="142"/>
-      <c r="G14" s="271"/>
+      <c r="B14" s="118"/>
+      <c r="C14" s="136"/>
+      <c r="D14" s="162"/>
+      <c r="E14" s="229"/>
+      <c r="F14" s="181"/>
+      <c r="G14" s="285"/>
     </row>
     <row r="15" spans="2:7" ht="95.65" customHeight="1">
-      <c r="B15" s="191"/>
+      <c r="B15" s="118"/>
       <c r="C15" s="28" t="s">
         <v>50</v>
       </c>
@@ -12308,75 +12420,75 @@
       <c r="E15" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="F15" s="63" t="s">
-        <v>130</v>
-      </c>
-      <c r="G15" s="64" t="s">
+      <c r="F15" s="62" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="16" spans="2:7" ht="17.25" thickBot="1">
-      <c r="B16" s="192"/>
+      <c r="G15" s="63" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" ht="17.5" thickBot="1">
+      <c r="B16" s="119"/>
       <c r="C16" s="31" t="s">
         <v>54</v>
       </c>
       <c r="D16" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="E16" s="277" t="s">
+      <c r="E16" s="290" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="278"/>
-      <c r="G16" s="279"/>
-    </row>
-    <row r="32" ht="17.25" thickBot="1"/>
+      <c r="F16" s="291"/>
+      <c r="G16" s="292"/>
+    </row>
+    <row r="32" ht="17.5" thickBot="1"/>
     <row r="33" spans="8:8">
-      <c r="H33" s="134" t="s">
+      <c r="H33" s="175" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="34" spans="8:8">
-      <c r="H34" s="137"/>
+      <c r="H34" s="178"/>
     </row>
     <row r="35" spans="8:8">
-      <c r="H35" s="137"/>
+      <c r="H35" s="178"/>
     </row>
     <row r="36" spans="8:8">
-      <c r="H36" s="137"/>
+      <c r="H36" s="178"/>
     </row>
     <row r="37" spans="8:8">
-      <c r="H37" s="137"/>
+      <c r="H37" s="178"/>
     </row>
     <row r="38" spans="8:8">
-      <c r="H38" s="137"/>
+      <c r="H38" s="178"/>
     </row>
     <row r="39" spans="8:8">
-      <c r="H39" s="137"/>
+      <c r="H39" s="178"/>
     </row>
     <row r="40" spans="8:8">
-      <c r="H40" s="137"/>
+      <c r="H40" s="178"/>
     </row>
     <row r="41" spans="8:8">
-      <c r="H41" s="137"/>
+      <c r="H41" s="178"/>
     </row>
     <row r="42" spans="8:8">
-      <c r="H42" s="138"/>
+      <c r="H42" s="179"/>
     </row>
     <row r="43" spans="8:8">
-      <c r="H43" s="260" t="s">
+      <c r="H43" s="277" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="44" spans="8:8">
-      <c r="H44" s="138"/>
+      <c r="H44" s="179"/>
     </row>
     <row r="45" spans="8:8">
-      <c r="H45" s="59" t="s">
+      <c r="H45" s="58" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="8:8" ht="17.25" thickBot="1">
-      <c r="H46" s="62"/>
+    <row r="46" spans="8:8" ht="17.5" thickBot="1">
+      <c r="H46" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -12413,16 +12525,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04021987-DBDC-46EB-B15B-B1DD935E8DAA}">
   <dimension ref="B1:G17"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="4" max="4" width="35.375" customWidth="1"/>
+    <col min="4" max="4" width="35.33203125" customWidth="1"/>
     <col min="5" max="5" width="43.75" customWidth="1"/>
     <col min="6" max="6" width="81" customWidth="1"/>
-    <col min="7" max="7" width="59.375" customWidth="1"/>
+    <col min="7" max="7" width="59.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="17.25" thickBot="1"/>
-    <row r="2" spans="2:7" ht="17.25" thickBot="1">
+    <row r="1" spans="2:7" ht="17.5" thickBot="1"/>
+    <row r="2" spans="2:7" ht="17.5" thickBot="1">
       <c r="B2" s="46"/>
       <c r="C2" s="47" t="s">
         <v>0</v>
@@ -12431,170 +12543,170 @@
         <v>1</v>
       </c>
       <c r="E2" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="F2" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="F2" s="47" t="s">
-        <v>100</v>
-      </c>
       <c r="G2" s="48" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" ht="35.1" customHeight="1">
-      <c r="B3" s="190" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="35.15" customHeight="1">
+      <c r="B3" s="117" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="261" t="s">
+      <c r="C3" s="134" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="287" t="s">
+      <c r="D3" s="145" t="s">
+        <v>136</v>
+      </c>
+      <c r="E3" s="156" t="s">
+        <v>132</v>
+      </c>
+      <c r="F3" s="122" t="s">
+        <v>141</v>
+      </c>
+      <c r="G3" s="139" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="182.15" customHeight="1">
+      <c r="B4" s="118"/>
+      <c r="C4" s="135"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="157"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="140"/>
+    </row>
+    <row r="5" spans="2:7">
+      <c r="B5" s="118"/>
+      <c r="C5" s="135"/>
+      <c r="D5" s="141" t="s">
+        <v>134</v>
+      </c>
+      <c r="E5" s="120" t="s">
+        <v>135</v>
+      </c>
+      <c r="F5" s="143" t="s">
+        <v>142</v>
+      </c>
+      <c r="G5" s="151" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="86.15" customHeight="1">
+      <c r="B6" s="118"/>
+      <c r="C6" s="136"/>
+      <c r="D6" s="142"/>
+      <c r="E6" s="121"/>
+      <c r="F6" s="144"/>
+      <c r="G6" s="150"/>
+    </row>
+    <row r="7" spans="2:7">
+      <c r="B7" s="118"/>
+      <c r="C7" s="137" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="161" t="s">
+        <v>133</v>
+      </c>
+      <c r="E7" s="124" t="s">
         <v>137</v>
       </c>
-      <c r="E3" s="214" t="s">
-        <v>133</v>
-      </c>
-      <c r="F3" s="154" t="s">
-        <v>142</v>
-      </c>
-      <c r="G3" s="285" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="182.1" customHeight="1">
-      <c r="B4" s="191"/>
-      <c r="C4" s="276"/>
-      <c r="D4" s="288"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="155"/>
-      <c r="G4" s="286"/>
-    </row>
-    <row r="5" spans="2:7">
-      <c r="B5" s="191"/>
-      <c r="C5" s="276"/>
-      <c r="D5" s="215" t="s">
-        <v>135</v>
-      </c>
-      <c r="E5" s="173" t="s">
-        <v>136</v>
-      </c>
-      <c r="F5" s="158" t="s">
-        <v>143</v>
-      </c>
-      <c r="G5" s="257" t="s">
+      <c r="F7" s="143" t="s">
+        <v>138</v>
+      </c>
+      <c r="G7" s="149" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="86.1" customHeight="1">
-      <c r="B6" s="191"/>
-      <c r="C6" s="262"/>
-      <c r="D6" s="216"/>
-      <c r="E6" s="125"/>
-      <c r="F6" s="159"/>
-      <c r="G6" s="292"/>
-    </row>
-    <row r="7" spans="2:7">
-      <c r="B7" s="191"/>
-      <c r="C7" s="268" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="209" t="s">
-        <v>134</v>
-      </c>
-      <c r="E7" s="121" t="s">
-        <v>138</v>
-      </c>
-      <c r="F7" s="158" t="s">
+    <row r="8" spans="2:7" ht="103" customHeight="1">
+      <c r="B8" s="118"/>
+      <c r="C8" s="135"/>
+      <c r="D8" s="162"/>
+      <c r="E8" s="125"/>
+      <c r="F8" s="144"/>
+      <c r="G8" s="149"/>
+    </row>
+    <row r="9" spans="2:7">
+      <c r="B9" s="118"/>
+      <c r="C9" s="135"/>
+      <c r="D9" s="152" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="126" t="s">
         <v>139</v>
       </c>
-      <c r="G7" s="291" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" ht="102.95" customHeight="1">
-      <c r="B8" s="191"/>
-      <c r="C8" s="276"/>
-      <c r="D8" s="210"/>
-      <c r="E8" s="123"/>
-      <c r="F8" s="159"/>
-      <c r="G8" s="291"/>
-    </row>
-    <row r="9" spans="2:7">
-      <c r="B9" s="191"/>
-      <c r="C9" s="276"/>
-      <c r="D9" s="200" t="s">
-        <v>67</v>
-      </c>
-      <c r="E9" s="126" t="s">
+      <c r="F9" s="154" t="s">
+        <v>203</v>
+      </c>
+      <c r="G9" s="149"/>
+    </row>
+    <row r="10" spans="2:7" ht="274.5" customHeight="1">
+      <c r="B10" s="118"/>
+      <c r="C10" s="136"/>
+      <c r="D10" s="153"/>
+      <c r="E10" s="127"/>
+      <c r="F10" s="155"/>
+      <c r="G10" s="150"/>
+    </row>
+    <row r="11" spans="2:7" ht="17.649999999999999" customHeight="1">
+      <c r="B11" s="118"/>
+      <c r="C11" s="137" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" s="128" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="158" t="s">
         <v>140</v>
       </c>
-      <c r="F9" s="139" t="s">
-        <v>185</v>
-      </c>
-      <c r="G9" s="291"/>
-    </row>
-    <row r="10" spans="2:7" ht="175.35" customHeight="1">
-      <c r="B10" s="191"/>
-      <c r="C10" s="262"/>
-      <c r="D10" s="201"/>
-      <c r="E10" s="127"/>
-      <c r="F10" s="140"/>
-      <c r="G10" s="292"/>
-    </row>
-    <row r="11" spans="2:7" ht="17.649999999999999" customHeight="1">
-      <c r="B11" s="191"/>
-      <c r="C11" s="268" t="s">
-        <v>68</v>
-      </c>
-      <c r="D11" s="281" t="s">
-        <v>69</v>
-      </c>
-      <c r="E11" s="203" t="s">
-        <v>141</v>
-      </c>
-      <c r="F11" s="161" t="s">
-        <v>192</v>
-      </c>
-      <c r="G11" s="289"/>
-    </row>
-    <row r="12" spans="2:7" ht="28.35" customHeight="1">
-      <c r="B12" s="191"/>
-      <c r="C12" s="276"/>
-      <c r="D12" s="282"/>
-      <c r="E12" s="204"/>
-      <c r="F12" s="162"/>
-      <c r="G12" s="289"/>
+      <c r="F11" s="131" t="s">
+        <v>202</v>
+      </c>
+      <c r="G11" s="147"/>
+    </row>
+    <row r="12" spans="2:7" ht="28.4" customHeight="1">
+      <c r="B12" s="118"/>
+      <c r="C12" s="135"/>
+      <c r="D12" s="129"/>
+      <c r="E12" s="159"/>
+      <c r="F12" s="132"/>
+      <c r="G12" s="147"/>
     </row>
     <row r="13" spans="2:7" ht="42.4" customHeight="1">
-      <c r="B13" s="191"/>
-      <c r="C13" s="276"/>
-      <c r="D13" s="282"/>
-      <c r="E13" s="204"/>
-      <c r="F13" s="162"/>
-      <c r="G13" s="289"/>
+      <c r="B13" s="118"/>
+      <c r="C13" s="135"/>
+      <c r="D13" s="129"/>
+      <c r="E13" s="159"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="147"/>
     </row>
     <row r="14" spans="2:7">
-      <c r="B14" s="191"/>
-      <c r="C14" s="276"/>
-      <c r="D14" s="282"/>
-      <c r="E14" s="204"/>
-      <c r="F14" s="162"/>
-      <c r="G14" s="289"/>
+      <c r="B14" s="118"/>
+      <c r="C14" s="135"/>
+      <c r="D14" s="129"/>
+      <c r="E14" s="159"/>
+      <c r="F14" s="132"/>
+      <c r="G14" s="147"/>
     </row>
     <row r="15" spans="2:7">
-      <c r="B15" s="191"/>
-      <c r="C15" s="276"/>
-      <c r="D15" s="282"/>
-      <c r="E15" s="204"/>
-      <c r="F15" s="162"/>
-      <c r="G15" s="289"/>
-    </row>
-    <row r="16" spans="2:7" ht="115.35" customHeight="1" thickBot="1">
-      <c r="B16" s="192"/>
-      <c r="C16" s="284"/>
-      <c r="D16" s="283"/>
-      <c r="E16" s="235"/>
-      <c r="F16" s="163"/>
-      <c r="G16" s="290"/>
+      <c r="B15" s="118"/>
+      <c r="C15" s="135"/>
+      <c r="D15" s="129"/>
+      <c r="E15" s="159"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="147"/>
+    </row>
+    <row r="16" spans="2:7" ht="158" customHeight="1" thickBot="1">
+      <c r="B16" s="119"/>
+      <c r="C16" s="138"/>
+      <c r="D16" s="130"/>
+      <c r="E16" s="160"/>
+      <c r="F16" s="133"/>
+      <c r="G16" s="148"/>
     </row>
     <row r="17" ht="17.649999999999999" customHeight="1"/>
   </sheetData>
@@ -12631,17 +12743,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70E3C3FB-0E54-4ECF-BDE5-7A10C9F7ACB4}">
   <dimension ref="B1:G7"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="3" max="3" width="13.5" customWidth="1"/>
-    <col min="4" max="4" width="34.125" customWidth="1"/>
-    <col min="5" max="5" width="47.625" customWidth="1"/>
-    <col min="6" max="6" width="69.375" customWidth="1"/>
-    <col min="7" max="7" width="55.625" customWidth="1"/>
+    <col min="4" max="4" width="34.08203125" customWidth="1"/>
+    <col min="5" max="5" width="47.58203125" customWidth="1"/>
+    <col min="6" max="6" width="69.33203125" customWidth="1"/>
+    <col min="7" max="7" width="55.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="17.25" thickBot="1"/>
-    <row r="2" spans="2:7" ht="17.25" thickBot="1">
+    <row r="1" spans="2:7" ht="17.5" thickBot="1"/>
+    <row r="2" spans="2:7" ht="17.5" thickBot="1">
       <c r="B2" s="46"/>
       <c r="C2" s="47" t="s">
         <v>0</v>
@@ -12650,17 +12762,17 @@
         <v>1</v>
       </c>
       <c r="E2" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="F2" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="F2" s="47" t="s">
-        <v>100</v>
-      </c>
       <c r="G2" s="48" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" ht="103.35" customHeight="1">
-      <c r="B3" s="190" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="103.4" customHeight="1">
+      <c r="B3" s="117" t="s">
         <v>74</v>
       </c>
       <c r="C3" s="40" t="s">
@@ -12672,64 +12784,64 @@
       <c r="E3" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="F3" s="69" t="s">
+      <c r="F3" s="68" t="s">
+        <v>150</v>
+      </c>
+      <c r="G3" s="115" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="70" customHeight="1">
+      <c r="B4" s="118"/>
+      <c r="C4" s="137" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="69" t="s">
+        <v>149</v>
+      </c>
+      <c r="E4" s="173" t="s">
         <v>151</v>
       </c>
-      <c r="G3" s="70" t="s">
+      <c r="F4" s="189" t="s">
+        <v>152</v>
+      </c>
+      <c r="G4" s="151" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="148.5" customHeight="1">
+      <c r="B5" s="118"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="66" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="4" spans="2:7" ht="69.95" customHeight="1">
-      <c r="B4" s="191"/>
-      <c r="C4" s="268" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="71" t="s">
-        <v>150</v>
-      </c>
-      <c r="E4" s="131" t="s">
-        <v>152</v>
-      </c>
-      <c r="F4" s="150" t="s">
+      <c r="E5" s="157"/>
+      <c r="F5" s="190"/>
+      <c r="G5" s="150"/>
+    </row>
+    <row r="6" spans="2:7" ht="125.25" customHeight="1">
+      <c r="B6" s="118"/>
+      <c r="C6" s="137" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="128" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="294" t="s">
+        <v>160</v>
+      </c>
+      <c r="F6" s="189" t="s">
         <v>153</v>
       </c>
-      <c r="G4" s="257" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="98.1" customHeight="1">
-      <c r="B5" s="191"/>
-      <c r="C5" s="262"/>
-      <c r="D5" s="67" t="s">
-        <v>149</v>
-      </c>
-      <c r="E5" s="132"/>
-      <c r="F5" s="151"/>
-      <c r="G5" s="292"/>
-    </row>
-    <row r="6" spans="2:7" ht="125.25" customHeight="1">
-      <c r="B6" s="191"/>
-      <c r="C6" s="268" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" s="281" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" s="293" t="s">
-        <v>161</v>
-      </c>
-      <c r="F6" s="150" t="s">
-        <v>154</v>
-      </c>
-      <c r="G6" s="295"/>
-    </row>
-    <row r="7" spans="2:7" ht="17.25" thickBot="1">
-      <c r="B7" s="192"/>
-      <c r="C7" s="284"/>
-      <c r="D7" s="283"/>
-      <c r="E7" s="206"/>
-      <c r="F7" s="294"/>
-      <c r="G7" s="296"/>
+      <c r="G6" s="296"/>
+    </row>
+    <row r="7" spans="2:7" ht="17.5" thickBot="1">
+      <c r="B7" s="119"/>
+      <c r="C7" s="138"/>
+      <c r="D7" s="130"/>
+      <c r="E7" s="230"/>
+      <c r="F7" s="295"/>
+      <c r="G7" s="297"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -12752,17 +12864,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECA8A220-10DE-488F-966E-CC2D9B9E3E1E}">
   <dimension ref="B1:G12"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="3" max="3" width="13.875" customWidth="1"/>
-    <col min="4" max="4" width="21.625" customWidth="1"/>
-    <col min="5" max="5" width="26.375" customWidth="1"/>
-    <col min="6" max="6" width="53.875" customWidth="1"/>
-    <col min="7" max="7" width="35.625" customWidth="1"/>
+    <col min="3" max="3" width="13.83203125" customWidth="1"/>
+    <col min="4" max="4" width="21.58203125" customWidth="1"/>
+    <col min="5" max="5" width="26.33203125" customWidth="1"/>
+    <col min="6" max="6" width="53.83203125" customWidth="1"/>
+    <col min="7" max="7" width="35.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="17.25" thickBot="1"/>
-    <row r="2" spans="2:7" ht="17.25" thickBot="1">
+    <row r="1" spans="2:7" ht="17.5" thickBot="1"/>
+    <row r="2" spans="2:7" ht="17.5" thickBot="1">
       <c r="B2" s="46"/>
       <c r="C2" s="47" t="s">
         <v>0</v>
@@ -12771,18 +12883,18 @@
         <v>1</v>
       </c>
       <c r="E2" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="F2" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="F2" s="47" t="s">
-        <v>100</v>
-      </c>
       <c r="G2" s="48" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="165.4" customHeight="1">
-      <c r="B3" s="190" t="s">
-        <v>156</v>
+      <c r="B3" s="117" t="s">
+        <v>155</v>
       </c>
       <c r="C3" s="40" t="s">
         <v>82</v>
@@ -12791,31 +12903,31 @@
         <v>83</v>
       </c>
       <c r="E3" s="42" t="s">
-        <v>157</v>
-      </c>
-      <c r="F3" s="72" t="s">
-        <v>167</v>
-      </c>
-      <c r="G3" s="68"/>
-    </row>
-    <row r="4" spans="2:7" ht="162.94999999999999" customHeight="1">
-      <c r="B4" s="191"/>
+        <v>156</v>
+      </c>
+      <c r="F3" s="70" t="s">
+        <v>165</v>
+      </c>
+      <c r="G3" s="67"/>
+    </row>
+    <row r="4" spans="2:7" ht="256.5" customHeight="1">
+      <c r="B4" s="118"/>
       <c r="C4" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="D4" s="77" t="s">
-        <v>163</v>
+      <c r="D4" s="75" t="s">
+        <v>162</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>162</v>
-      </c>
-      <c r="F4" s="73" t="s">
-        <v>166</v>
-      </c>
-      <c r="G4" s="65"/>
+        <v>161</v>
+      </c>
+      <c r="F4" s="71" t="s">
+        <v>198</v>
+      </c>
+      <c r="G4" s="64"/>
     </row>
     <row r="5" spans="2:7" ht="176.65" customHeight="1">
-      <c r="B5" s="191"/>
+      <c r="B5" s="118"/>
       <c r="C5" s="28" t="s">
         <v>87</v>
       </c>
@@ -12825,15 +12937,15 @@
       <c r="E5" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="F5" s="87" t="s">
-        <v>190</v>
-      </c>
-      <c r="G5" s="114" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="94.35" customHeight="1">
-      <c r="B6" s="191"/>
+      <c r="F5" s="85" t="s">
+        <v>187</v>
+      </c>
+      <c r="G5" s="112" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="94.4" customHeight="1">
+      <c r="B6" s="118"/>
       <c r="C6" s="28" t="s">
         <v>90</v>
       </c>
@@ -12841,42 +12953,42 @@
         <v>91</v>
       </c>
       <c r="E6" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="F6" s="73" t="s">
+        <v>200</v>
+      </c>
+      <c r="G6" s="65"/>
+    </row>
+    <row r="7" spans="2:7" ht="85">
+      <c r="B7" s="118"/>
+      <c r="C7" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="F6" s="75" t="s">
-        <v>191</v>
-      </c>
-      <c r="G6" s="66"/>
-    </row>
-    <row r="7" spans="2:7" ht="82.5">
-      <c r="B7" s="191"/>
-      <c r="C7" s="28" t="s">
+      <c r="D7" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="D7" s="29" t="s">
-        <v>94</v>
-      </c>
       <c r="E7" s="30" t="s">
+        <v>157</v>
+      </c>
+      <c r="F7" s="74" t="s">
         <v>158</v>
       </c>
-      <c r="F7" s="76" t="s">
-        <v>159</v>
-      </c>
-      <c r="G7" s="74"/>
-    </row>
-    <row r="8" spans="2:7" ht="17.25" thickBot="1">
-      <c r="B8" s="192"/>
+      <c r="G7" s="72"/>
+    </row>
+    <row r="8" spans="2:7" ht="17.5" thickBot="1">
+      <c r="B8" s="119"/>
       <c r="C8" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="D8" s="39" t="s">
-        <v>97</v>
-      </c>
-      <c r="E8" s="116" t="s">
+      <c r="E8" s="163" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="117"/>
-      <c r="G8" s="118"/>
+      <c r="F8" s="164"/>
+      <c r="G8" s="165"/>
     </row>
     <row r="11" spans="2:7">
       <c r="F11" t="s">
@@ -12885,7 +12997,7 @@
     </row>
     <row r="12" spans="2:7">
       <c r="F12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/16기_스타트캠프_강사 가이드 문서.xlsx
+++ b/16기_스타트캠프_강사 가이드 문서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SSAFY\Local_Workspace\16g_Local\00_startcamp\share_ai-onboarding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91158C1-4F4E-4245-86D6-1D0C034F18A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF801E5-3F1C-45EC-8CEA-7BCF50F534EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40020" yWindow="1395" windowWidth="26640" windowHeight="18975" activeTab="4" xr2:uid="{FD3BB604-1650-4EBB-871F-9010366B35B1}"/>
+    <workbookView xWindow="40020" yWindow="1395" windowWidth="26640" windowHeight="18975" activeTab="6" xr2:uid="{FD3BB604-1650-4EBB-871F-9010366B35B1}"/>
   </bookViews>
   <sheets>
     <sheet name="교육 목표 및 방향" sheetId="7" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="205">
   <si>
     <t>시간</t>
   </si>
@@ -8211,6 +8211,129 @@
 - 전반적인 코드 작성 흐름을 하나씩 알아볼 수 있고, 흐름 중에 모르는 내용을 학습 목록으로 가져가볼 수 있기 때문
 - Agent 수업은 AI I 과목에서 진행되기 때문
 - 토큰 사용이 제한되어 있기 때문 (반 공유)</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">* </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">모든 기능이 잘 동작하는 지 테스트할 수 있도록 유도해주세요. 
+* 배포까지 되어야 하기에 전체적인 진행상황을 살펴봐주세요.
+  - 배포되기에 많은 것이 남지 않도록 잘 잘 살펴봐주시기 바랍니다. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+* API Key </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">사용이 마무리된 교육생은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Readme </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">문서를 정리하고 배포 준비를 할 수 있도록 안내해주세요. 
+  - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ender</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>의 배포 횟수도 제한되어 있어 잦은 배포를 하지 않도록 안내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 부탁드립니다. 
+* 배포는 비전공 (Netlify), 전공 (Netlify + Render) 조합을 사용하는점 안내 부탁드립니다.
+* Render 배포시 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>CORS 이슈, PYTHON_VERSION</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>을 3.11로 환경변수 설정해줘야 정상적으로 배포 및 Netlify 와 연동이 되기 때문에 혹시나 배포에 어려움이 있는 팀은 해당 부분을 우선적으로 확인해주시면 되겠습니다.</t>
     </r>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
@@ -9897,6 +10020,78 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -9963,77 +10158,224 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -10053,9 +10395,6 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -10064,15 +10403,6 @@
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -10080,217 +10410,37 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10299,6 +10449,39 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -10317,65 +10500,32 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -10399,33 +10549,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10916,7 +11039,7 @@
       </c>
     </row>
     <row r="3" spans="2:9" ht="34">
-      <c r="B3" s="215" t="s">
+      <c r="B3" s="193" t="s">
         <v>163</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -10925,10 +11048,10 @@
       <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="182" t="s">
+      <c r="E3" s="220" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="183"/>
+      <c r="F3" s="221"/>
       <c r="G3" s="55" t="s">
         <v>101</v>
       </c>
@@ -10936,63 +11059,63 @@
       <c r="I3" s="52"/>
     </row>
     <row r="4" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B4" s="216"/>
-      <c r="C4" s="236" t="s">
+      <c r="B4" s="194"/>
+      <c r="C4" s="163" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="158" t="s">
+      <c r="D4" s="136" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="126" t="s">
+      <c r="F4" s="150" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="143" t="s">
+      <c r="G4" s="121" t="s">
         <v>101</v>
       </c>
-      <c r="H4" s="223"/>
-      <c r="I4" s="187"/>
+      <c r="H4" s="198"/>
+      <c r="I4" s="225"/>
     </row>
     <row r="5" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B5" s="216"/>
-      <c r="C5" s="237"/>
-      <c r="D5" s="159"/>
+      <c r="B5" s="194"/>
+      <c r="C5" s="164"/>
+      <c r="D5" s="137"/>
       <c r="E5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="202"/>
-      <c r="G5" s="221"/>
-      <c r="H5" s="224"/>
-      <c r="I5" s="185"/>
+      <c r="F5" s="167"/>
+      <c r="G5" s="196"/>
+      <c r="H5" s="199"/>
+      <c r="I5" s="223"/>
     </row>
     <row r="6" spans="2:9">
-      <c r="B6" s="216"/>
-      <c r="C6" s="237"/>
-      <c r="D6" s="159"/>
+      <c r="B6" s="194"/>
+      <c r="C6" s="164"/>
+      <c r="D6" s="137"/>
       <c r="E6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="202"/>
-      <c r="G6" s="221"/>
-      <c r="H6" s="224"/>
-      <c r="I6" s="185"/>
+      <c r="F6" s="167"/>
+      <c r="G6" s="196"/>
+      <c r="H6" s="199"/>
+      <c r="I6" s="223"/>
     </row>
     <row r="7" spans="2:9">
-      <c r="B7" s="216"/>
-      <c r="C7" s="238"/>
-      <c r="D7" s="239"/>
+      <c r="B7" s="194"/>
+      <c r="C7" s="165"/>
+      <c r="D7" s="166"/>
       <c r="E7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="240"/>
-      <c r="G7" s="222"/>
-      <c r="H7" s="225"/>
-      <c r="I7" s="188"/>
+      <c r="F7" s="168"/>
+      <c r="G7" s="197"/>
+      <c r="H7" s="200"/>
+      <c r="I7" s="226"/>
     </row>
     <row r="8" spans="2:9" ht="53.15" customHeight="1">
-      <c r="B8" s="216"/>
+      <c r="B8" s="194"/>
       <c r="C8" s="7" t="s">
         <v>16</v>
       </c>
@@ -11005,45 +11128,45 @@
         <v>107</v>
       </c>
       <c r="H8" s="95"/>
-      <c r="I8" s="184" t="s">
+      <c r="I8" s="222" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="9" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B9" s="216"/>
-      <c r="C9" s="236" t="s">
+      <c r="B9" s="194"/>
+      <c r="C9" s="163" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="243" t="s">
+      <c r="D9" s="179" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="126" t="s">
+      <c r="E9" s="150" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="166" t="s">
+      <c r="F9" s="239" t="s">
         <v>171</v>
       </c>
-      <c r="G9" s="200" t="s">
+      <c r="G9" s="207" t="s">
         <v>117</v>
       </c>
-      <c r="H9" s="198" t="s">
+      <c r="H9" s="234" t="s">
         <v>108</v>
       </c>
-      <c r="I9" s="185"/>
+      <c r="I9" s="223"/>
     </row>
     <row r="10" spans="2:9" ht="385.5" customHeight="1">
-      <c r="B10" s="216"/>
-      <c r="C10" s="242"/>
-      <c r="D10" s="244"/>
-      <c r="E10" s="127"/>
-      <c r="F10" s="167"/>
-      <c r="G10" s="201"/>
-      <c r="H10" s="199"/>
-      <c r="I10" s="185"/>
+      <c r="B10" s="194"/>
+      <c r="C10" s="178"/>
+      <c r="D10" s="180"/>
+      <c r="E10" s="151"/>
+      <c r="F10" s="240"/>
+      <c r="G10" s="209"/>
+      <c r="H10" s="235"/>
+      <c r="I10" s="223"/>
     </row>
     <row r="11" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B11" s="216"/>
-      <c r="C11" s="236" t="s">
+      <c r="B11" s="194"/>
+      <c r="C11" s="163" t="s">
         <v>21</v>
       </c>
       <c r="D11" s="10" t="s">
@@ -11052,49 +11175,49 @@
       <c r="E11" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="120" t="s">
+      <c r="F11" s="144" t="s">
         <v>168</v>
       </c>
-      <c r="G11" s="200" t="s">
+      <c r="G11" s="207" t="s">
         <v>115</v>
       </c>
-      <c r="H11" s="206" t="s">
+      <c r="H11" s="211" t="s">
         <v>111</v>
       </c>
-      <c r="I11" s="185"/>
+      <c r="I11" s="223"/>
     </row>
     <row r="12" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B12" s="216"/>
-      <c r="C12" s="237"/>
+      <c r="B12" s="194"/>
+      <c r="C12" s="164"/>
       <c r="D12" s="11" t="s">
         <v>23</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F12" s="205"/>
-      <c r="G12" s="204"/>
-      <c r="H12" s="207"/>
-      <c r="I12" s="185"/>
+      <c r="F12" s="210"/>
+      <c r="G12" s="208"/>
+      <c r="H12" s="212"/>
+      <c r="I12" s="223"/>
     </row>
     <row r="13" spans="2:9" ht="124" customHeight="1">
-      <c r="B13" s="216"/>
-      <c r="C13" s="242"/>
+      <c r="B13" s="194"/>
+      <c r="C13" s="178"/>
       <c r="D13" s="11"/>
       <c r="E13" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F13" s="121"/>
-      <c r="G13" s="201"/>
-      <c r="H13" s="208"/>
-      <c r="I13" s="185"/>
+      <c r="F13" s="145"/>
+      <c r="G13" s="209"/>
+      <c r="H13" s="213"/>
+      <c r="I13" s="223"/>
     </row>
     <row r="14" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B14" s="216"/>
-      <c r="C14" s="236" t="s">
+      <c r="B14" s="194"/>
+      <c r="C14" s="163" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="126" t="s">
+      <c r="D14" s="150" t="s">
         <v>97</v>
       </c>
       <c r="E14" s="3" t="s">
@@ -11103,93 +11226,93 @@
       <c r="F14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="209" t="s">
+      <c r="G14" s="214" t="s">
         <v>120</v>
       </c>
-      <c r="H14" s="212" t="s">
+      <c r="H14" s="217" t="s">
         <v>110</v>
       </c>
-      <c r="I14" s="185"/>
+      <c r="I14" s="223"/>
     </row>
     <row r="15" spans="2:9" ht="35.15" customHeight="1">
-      <c r="B15" s="216"/>
-      <c r="C15" s="237"/>
-      <c r="D15" s="202"/>
+      <c r="B15" s="194"/>
+      <c r="C15" s="164"/>
+      <c r="D15" s="167"/>
       <c r="E15" s="13" t="s">
         <v>28</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G15" s="210"/>
-      <c r="H15" s="213"/>
-      <c r="I15" s="185"/>
+      <c r="G15" s="215"/>
+      <c r="H15" s="218"/>
+      <c r="I15" s="223"/>
     </row>
     <row r="16" spans="2:9">
-      <c r="B16" s="216"/>
-      <c r="C16" s="237"/>
-      <c r="D16" s="202"/>
+      <c r="B16" s="194"/>
+      <c r="C16" s="164"/>
+      <c r="D16" s="167"/>
       <c r="E16" s="14"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="210"/>
-      <c r="H16" s="213"/>
-      <c r="I16" s="185"/>
+      <c r="G16" s="215"/>
+      <c r="H16" s="218"/>
+      <c r="I16" s="223"/>
     </row>
     <row r="17" spans="2:9" ht="51">
-      <c r="B17" s="216"/>
-      <c r="C17" s="237"/>
-      <c r="D17" s="202"/>
+      <c r="B17" s="194"/>
+      <c r="C17" s="164"/>
+      <c r="D17" s="167"/>
       <c r="E17" s="13" t="s">
         <v>29</v>
       </c>
       <c r="F17" s="5"/>
-      <c r="G17" s="210"/>
-      <c r="H17" s="213"/>
-      <c r="I17" s="185"/>
+      <c r="G17" s="215"/>
+      <c r="H17" s="218"/>
+      <c r="I17" s="223"/>
     </row>
     <row r="18" spans="2:9">
-      <c r="B18" s="216"/>
-      <c r="C18" s="237"/>
-      <c r="D18" s="202"/>
+      <c r="B18" s="194"/>
+      <c r="C18" s="164"/>
+      <c r="D18" s="167"/>
       <c r="E18" s="14"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="210"/>
-      <c r="H18" s="213"/>
-      <c r="I18" s="185"/>
+      <c r="G18" s="215"/>
+      <c r="H18" s="218"/>
+      <c r="I18" s="223"/>
     </row>
     <row r="19" spans="2:9">
-      <c r="B19" s="216"/>
-      <c r="C19" s="237"/>
-      <c r="D19" s="202"/>
+      <c r="B19" s="194"/>
+      <c r="C19" s="164"/>
+      <c r="D19" s="167"/>
       <c r="E19" s="113" t="s">
         <v>30</v>
       </c>
       <c r="F19" s="5"/>
-      <c r="G19" s="210"/>
-      <c r="H19" s="213"/>
-      <c r="I19" s="185"/>
+      <c r="G19" s="215"/>
+      <c r="H19" s="218"/>
+      <c r="I19" s="223"/>
     </row>
     <row r="20" spans="2:9">
-      <c r="B20" s="216"/>
-      <c r="C20" s="237"/>
-      <c r="D20" s="202"/>
+      <c r="B20" s="194"/>
+      <c r="C20" s="164"/>
+      <c r="D20" s="167"/>
       <c r="E20" s="113" t="s">
         <v>103</v>
       </c>
       <c r="F20" s="5"/>
-      <c r="G20" s="210"/>
-      <c r="H20" s="213"/>
-      <c r="I20" s="185"/>
+      <c r="G20" s="215"/>
+      <c r="H20" s="218"/>
+      <c r="I20" s="223"/>
     </row>
     <row r="21" spans="2:9" ht="84.4" customHeight="1" thickBot="1">
-      <c r="B21" s="217"/>
-      <c r="C21" s="241"/>
-      <c r="D21" s="203"/>
+      <c r="B21" s="195"/>
+      <c r="C21" s="172"/>
+      <c r="D21" s="206"/>
       <c r="E21" s="50"/>
       <c r="F21" s="49"/>
-      <c r="G21" s="211"/>
-      <c r="H21" s="214"/>
-      <c r="I21" s="186"/>
+      <c r="G21" s="216"/>
+      <c r="H21" s="219"/>
+      <c r="I21" s="224"/>
     </row>
     <row r="22" spans="2:9" ht="17.5" thickBot="1">
       <c r="B22" s="105"/>
@@ -11202,10 +11325,10 @@
       <c r="I22" s="106"/>
     </row>
     <row r="23" spans="2:9" ht="32.15" customHeight="1">
-      <c r="B23" s="218" t="s">
+      <c r="B23" s="190" t="s">
         <v>164</v>
       </c>
-      <c r="C23" s="235" t="s">
+      <c r="C23" s="173" t="s">
         <v>33</v>
       </c>
       <c r="D23" s="19" t="s">
@@ -11214,36 +11337,36 @@
       <c r="E23" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="F23" s="169" t="s">
+      <c r="F23" s="175" t="s">
         <v>172</v>
       </c>
-      <c r="G23" s="122" t="s">
+      <c r="G23" s="146" t="s">
         <v>131</v>
       </c>
-      <c r="H23" s="169" t="s">
+      <c r="H23" s="175" t="s">
         <v>130</v>
       </c>
-      <c r="I23" s="175" t="s">
+      <c r="I23" s="169" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="24" spans="2:9" ht="70.75" customHeight="1">
-      <c r="B24" s="219"/>
-      <c r="C24" s="227"/>
+      <c r="B24" s="191"/>
+      <c r="C24" s="174"/>
       <c r="D24" s="20" t="s">
         <v>23</v>
       </c>
       <c r="E24" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="F24" s="121"/>
-      <c r="G24" s="123"/>
-      <c r="H24" s="121"/>
-      <c r="I24" s="178"/>
+      <c r="F24" s="145"/>
+      <c r="G24" s="147"/>
+      <c r="H24" s="145"/>
+      <c r="I24" s="170"/>
     </row>
     <row r="25" spans="2:9" ht="35.15" customHeight="1">
-      <c r="B25" s="219"/>
-      <c r="C25" s="226" t="s">
+      <c r="B25" s="191"/>
+      <c r="C25" s="176" t="s">
         <v>37</v>
       </c>
       <c r="D25" s="23" t="s">
@@ -11252,102 +11375,102 @@
       <c r="E25" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F25" s="124" t="s">
+      <c r="F25" s="148" t="s">
         <v>174</v>
       </c>
-      <c r="G25" s="189" t="s">
+      <c r="G25" s="183" t="s">
         <v>121</v>
       </c>
-      <c r="H25" s="248" t="s">
+      <c r="H25" s="186" t="s">
         <v>175</v>
       </c>
-      <c r="I25" s="178"/>
+      <c r="I25" s="170"/>
     </row>
     <row r="26" spans="2:9">
-      <c r="B26" s="219"/>
-      <c r="C26" s="228"/>
+      <c r="B26" s="191"/>
+      <c r="C26" s="177"/>
       <c r="D26" s="24" t="s">
         <v>39</v>
       </c>
       <c r="E26" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F26" s="168"/>
-      <c r="G26" s="247"/>
-      <c r="H26" s="174"/>
-      <c r="I26" s="178"/>
+      <c r="F26" s="241"/>
+      <c r="G26" s="184"/>
+      <c r="H26" s="187"/>
+      <c r="I26" s="170"/>
     </row>
     <row r="27" spans="2:9">
-      <c r="B27" s="219"/>
-      <c r="C27" s="228"/>
+      <c r="B27" s="191"/>
+      <c r="C27" s="177"/>
       <c r="D27" s="24"/>
       <c r="E27" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F27" s="168"/>
-      <c r="G27" s="247"/>
-      <c r="H27" s="174"/>
-      <c r="I27" s="178"/>
+      <c r="F27" s="241"/>
+      <c r="G27" s="184"/>
+      <c r="H27" s="187"/>
+      <c r="I27" s="170"/>
     </row>
     <row r="28" spans="2:9">
-      <c r="B28" s="219"/>
-      <c r="C28" s="228"/>
+      <c r="B28" s="191"/>
+      <c r="C28" s="177"/>
       <c r="D28" s="24"/>
       <c r="E28" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F28" s="168"/>
-      <c r="G28" s="247"/>
-      <c r="H28" s="174"/>
-      <c r="I28" s="178"/>
+      <c r="F28" s="241"/>
+      <c r="G28" s="184"/>
+      <c r="H28" s="187"/>
+      <c r="I28" s="170"/>
     </row>
     <row r="29" spans="2:9">
-      <c r="B29" s="219"/>
-      <c r="C29" s="228"/>
+      <c r="B29" s="191"/>
+      <c r="C29" s="177"/>
       <c r="D29" s="24"/>
       <c r="E29" s="14"/>
-      <c r="F29" s="168"/>
-      <c r="G29" s="247"/>
-      <c r="H29" s="174"/>
-      <c r="I29" s="178"/>
+      <c r="F29" s="241"/>
+      <c r="G29" s="184"/>
+      <c r="H29" s="187"/>
+      <c r="I29" s="170"/>
     </row>
     <row r="30" spans="2:9">
-      <c r="B30" s="219"/>
-      <c r="C30" s="228"/>
+      <c r="B30" s="191"/>
+      <c r="C30" s="177"/>
       <c r="D30" s="24"/>
       <c r="E30" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="F30" s="168"/>
-      <c r="G30" s="247"/>
-      <c r="H30" s="174"/>
-      <c r="I30" s="178"/>
+      <c r="F30" s="241"/>
+      <c r="G30" s="184"/>
+      <c r="H30" s="187"/>
+      <c r="I30" s="170"/>
     </row>
     <row r="31" spans="2:9">
-      <c r="B31" s="219"/>
-      <c r="C31" s="228"/>
+      <c r="B31" s="191"/>
+      <c r="C31" s="177"/>
       <c r="D31" s="24"/>
       <c r="E31" s="113" t="s">
         <v>103</v>
       </c>
-      <c r="F31" s="168"/>
-      <c r="G31" s="247"/>
-      <c r="H31" s="174"/>
-      <c r="I31" s="178"/>
+      <c r="F31" s="241"/>
+      <c r="G31" s="184"/>
+      <c r="H31" s="187"/>
+      <c r="I31" s="170"/>
     </row>
     <row r="32" spans="2:9">
-      <c r="B32" s="219"/>
-      <c r="C32" s="227"/>
+      <c r="B32" s="191"/>
+      <c r="C32" s="174"/>
       <c r="D32" s="25"/>
       <c r="E32" s="26"/>
-      <c r="F32" s="125"/>
-      <c r="G32" s="190"/>
-      <c r="H32" s="157"/>
-      <c r="I32" s="178"/>
+      <c r="F32" s="149"/>
+      <c r="G32" s="185"/>
+      <c r="H32" s="135"/>
+      <c r="I32" s="170"/>
     </row>
     <row r="33" spans="2:9">
-      <c r="B33" s="219"/>
-      <c r="C33" s="226" t="s">
+      <c r="B33" s="191"/>
+      <c r="C33" s="176" t="s">
         <v>44</v>
       </c>
       <c r="D33" s="23" t="s">
@@ -11356,33 +11479,33 @@
       <c r="E33" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F33" s="245" t="s">
+      <c r="F33" s="181" t="s">
         <v>173</v>
       </c>
-      <c r="G33" s="180" t="s">
+      <c r="G33" s="247" t="s">
         <v>124</v>
       </c>
-      <c r="H33" s="173" t="s">
+      <c r="H33" s="201" t="s">
         <v>127</v>
       </c>
-      <c r="I33" s="178"/>
+      <c r="I33" s="170"/>
     </row>
     <row r="34" spans="2:9" ht="123.4" customHeight="1">
-      <c r="B34" s="219"/>
-      <c r="C34" s="227"/>
+      <c r="B34" s="191"/>
+      <c r="C34" s="174"/>
       <c r="D34" s="27" t="s">
         <v>46</v>
       </c>
       <c r="E34" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="F34" s="246"/>
-      <c r="G34" s="181"/>
-      <c r="H34" s="157"/>
-      <c r="I34" s="178"/>
+      <c r="F34" s="182"/>
+      <c r="G34" s="248"/>
+      <c r="H34" s="135"/>
+      <c r="I34" s="170"/>
     </row>
     <row r="35" spans="2:9" ht="141" customHeight="1">
-      <c r="B35" s="219"/>
+      <c r="B35" s="191"/>
       <c r="C35" s="28" t="s">
         <v>50</v>
       </c>
@@ -11399,10 +11522,10 @@
       <c r="H35" s="97" t="s">
         <v>128</v>
       </c>
-      <c r="I35" s="179"/>
+      <c r="I35" s="171"/>
     </row>
     <row r="36" spans="2:9" ht="34.5" thickBot="1">
-      <c r="B36" s="220"/>
+      <c r="B36" s="192"/>
       <c r="C36" s="31" t="s">
         <v>54</v>
       </c>
@@ -11428,224 +11551,224 @@
       <c r="I37" s="92"/>
     </row>
     <row r="38" spans="2:9">
-      <c r="B38" s="218" t="s">
+      <c r="B38" s="190" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="235" t="s">
+      <c r="C38" s="173" t="s">
         <v>58</v>
       </c>
       <c r="D38" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="E38" s="156" t="s">
+      <c r="E38" s="134" t="s">
         <v>61</v>
       </c>
-      <c r="F38" s="169" t="s">
+      <c r="F38" s="175" t="s">
         <v>176</v>
       </c>
-      <c r="G38" s="122" t="s">
+      <c r="G38" s="146" t="s">
         <v>141</v>
       </c>
-      <c r="H38" s="193" t="s">
+      <c r="H38" s="229" t="s">
         <v>143</v>
       </c>
-      <c r="I38" s="175" t="s">
+      <c r="I38" s="169" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="39" spans="2:9" ht="149.15" customHeight="1">
-      <c r="B39" s="219"/>
-      <c r="C39" s="228"/>
+      <c r="B39" s="191"/>
+      <c r="C39" s="177"/>
       <c r="D39" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="E39" s="157"/>
-      <c r="F39" s="121"/>
-      <c r="G39" s="123"/>
-      <c r="H39" s="194"/>
-      <c r="I39" s="176"/>
+      <c r="E39" s="135"/>
+      <c r="F39" s="145"/>
+      <c r="G39" s="147"/>
+      <c r="H39" s="230"/>
+      <c r="I39" s="245"/>
     </row>
     <row r="40" spans="2:9">
-      <c r="B40" s="219"/>
-      <c r="C40" s="228"/>
-      <c r="D40" s="141" t="s">
+      <c r="B40" s="191"/>
+      <c r="C40" s="177"/>
+      <c r="D40" s="119" t="s">
         <v>62</v>
       </c>
       <c r="E40" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F40" s="126" t="s">
+      <c r="F40" s="150" t="s">
         <v>179</v>
       </c>
-      <c r="G40" s="143" t="s">
+      <c r="G40" s="121" t="s">
         <v>142</v>
       </c>
-      <c r="H40" s="191" t="s">
+      <c r="H40" s="227" t="s">
         <v>144</v>
       </c>
-      <c r="I40" s="176"/>
+      <c r="I40" s="245"/>
     </row>
     <row r="41" spans="2:9" ht="119.65" customHeight="1">
-      <c r="B41" s="219"/>
-      <c r="C41" s="227"/>
-      <c r="D41" s="142"/>
+      <c r="B41" s="191"/>
+      <c r="C41" s="174"/>
+      <c r="D41" s="120"/>
       <c r="E41" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="F41" s="127"/>
-      <c r="G41" s="144"/>
-      <c r="H41" s="192"/>
-      <c r="I41" s="176"/>
+      <c r="F41" s="151"/>
+      <c r="G41" s="122"/>
+      <c r="H41" s="228"/>
+      <c r="I41" s="245"/>
     </row>
     <row r="42" spans="2:9">
-      <c r="B42" s="219"/>
-      <c r="C42" s="226" t="s">
+      <c r="B42" s="191"/>
+      <c r="C42" s="176" t="s">
         <v>65</v>
       </c>
-      <c r="D42" s="161" t="s">
+      <c r="D42" s="139" t="s">
         <v>66</v>
       </c>
-      <c r="E42" s="124" t="s">
+      <c r="E42" s="148" t="s">
         <v>137</v>
       </c>
-      <c r="F42" s="126" t="s">
+      <c r="F42" s="150" t="s">
         <v>178</v>
       </c>
-      <c r="G42" s="143" t="s">
+      <c r="G42" s="121" t="s">
         <v>138</v>
       </c>
-      <c r="H42" s="195" t="s">
+      <c r="H42" s="231" t="s">
         <v>145</v>
       </c>
-      <c r="I42" s="176"/>
+      <c r="I42" s="245"/>
     </row>
     <row r="43" spans="2:9" ht="113.65" customHeight="1">
-      <c r="B43" s="219"/>
-      <c r="C43" s="228"/>
-      <c r="D43" s="162"/>
-      <c r="E43" s="125"/>
-      <c r="F43" s="127"/>
-      <c r="G43" s="144"/>
-      <c r="H43" s="195"/>
-      <c r="I43" s="176"/>
+      <c r="B43" s="191"/>
+      <c r="C43" s="177"/>
+      <c r="D43" s="140"/>
+      <c r="E43" s="149"/>
+      <c r="F43" s="151"/>
+      <c r="G43" s="122"/>
+      <c r="H43" s="231"/>
+      <c r="I43" s="245"/>
     </row>
     <row r="44" spans="2:9">
-      <c r="B44" s="219"/>
-      <c r="C44" s="228"/>
-      <c r="D44" s="152" t="s">
+      <c r="B44" s="191"/>
+      <c r="C44" s="177"/>
+      <c r="D44" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="E44" s="126" t="s">
+      <c r="E44" s="150" t="s">
         <v>177</v>
       </c>
-      <c r="F44" s="233"/>
-      <c r="G44" s="154" t="s">
+      <c r="F44" s="188"/>
+      <c r="G44" s="132" t="s">
         <v>189</v>
       </c>
-      <c r="H44" s="195"/>
-      <c r="I44" s="176"/>
+      <c r="H44" s="231"/>
+      <c r="I44" s="245"/>
     </row>
     <row r="45" spans="2:9" ht="317.64999999999998" customHeight="1">
-      <c r="B45" s="219"/>
-      <c r="C45" s="227"/>
-      <c r="D45" s="153"/>
-      <c r="E45" s="127"/>
-      <c r="F45" s="234"/>
-      <c r="G45" s="155"/>
-      <c r="H45" s="192"/>
-      <c r="I45" s="176"/>
+      <c r="B45" s="191"/>
+      <c r="C45" s="174"/>
+      <c r="D45" s="131"/>
+      <c r="E45" s="151"/>
+      <c r="F45" s="189"/>
+      <c r="G45" s="133"/>
+      <c r="H45" s="228"/>
+      <c r="I45" s="245"/>
     </row>
     <row r="46" spans="2:9">
-      <c r="B46" s="219"/>
-      <c r="C46" s="226" t="s">
+      <c r="B46" s="191"/>
+      <c r="C46" s="176" t="s">
         <v>68</v>
       </c>
       <c r="D46" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="E46" s="158" t="s">
+      <c r="E46" s="136" t="s">
         <v>71</v>
       </c>
-      <c r="F46" s="173" t="s">
+      <c r="F46" s="201" t="s">
         <v>180</v>
       </c>
-      <c r="G46" s="131" t="s">
+      <c r="G46" s="155" t="s">
         <v>201</v>
       </c>
-      <c r="H46" s="196"/>
-      <c r="I46" s="176"/>
+      <c r="H46" s="232"/>
+      <c r="I46" s="245"/>
     </row>
     <row r="47" spans="2:9">
-      <c r="B47" s="219"/>
-      <c r="C47" s="228"/>
+      <c r="B47" s="191"/>
+      <c r="C47" s="177"/>
       <c r="D47" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="E47" s="159"/>
-      <c r="F47" s="174"/>
-      <c r="G47" s="132"/>
-      <c r="H47" s="196"/>
-      <c r="I47" s="176"/>
+      <c r="E47" s="137"/>
+      <c r="F47" s="187"/>
+      <c r="G47" s="156"/>
+      <c r="H47" s="232"/>
+      <c r="I47" s="245"/>
     </row>
     <row r="48" spans="2:9">
-      <c r="B48" s="219"/>
-      <c r="C48" s="228"/>
+      <c r="B48" s="191"/>
+      <c r="C48" s="177"/>
       <c r="D48" s="114" t="s">
         <v>197</v>
       </c>
-      <c r="E48" s="159"/>
-      <c r="F48" s="174"/>
-      <c r="G48" s="132"/>
-      <c r="H48" s="196"/>
-      <c r="I48" s="176"/>
+      <c r="E48" s="137"/>
+      <c r="F48" s="187"/>
+      <c r="G48" s="156"/>
+      <c r="H48" s="232"/>
+      <c r="I48" s="245"/>
     </row>
     <row r="49" spans="2:9">
-      <c r="B49" s="219"/>
-      <c r="C49" s="228"/>
+      <c r="B49" s="191"/>
+      <c r="C49" s="177"/>
       <c r="D49" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="E49" s="159"/>
-      <c r="F49" s="174"/>
-      <c r="G49" s="132"/>
-      <c r="H49" s="196"/>
-      <c r="I49" s="176"/>
+      <c r="E49" s="137"/>
+      <c r="F49" s="187"/>
+      <c r="G49" s="156"/>
+      <c r="H49" s="232"/>
+      <c r="I49" s="245"/>
     </row>
     <row r="50" spans="2:9">
-      <c r="B50" s="219"/>
-      <c r="C50" s="228"/>
+      <c r="B50" s="191"/>
+      <c r="C50" s="177"/>
       <c r="D50" s="37"/>
-      <c r="E50" s="159"/>
-      <c r="F50" s="174"/>
-      <c r="G50" s="132"/>
-      <c r="H50" s="196"/>
-      <c r="I50" s="176"/>
+      <c r="E50" s="137"/>
+      <c r="F50" s="187"/>
+      <c r="G50" s="156"/>
+      <c r="H50" s="232"/>
+      <c r="I50" s="245"/>
     </row>
     <row r="51" spans="2:9" ht="317.5" customHeight="1" thickBot="1">
-      <c r="B51" s="219"/>
-      <c r="C51" s="227"/>
+      <c r="B51" s="191"/>
+      <c r="C51" s="174"/>
       <c r="D51" s="37"/>
-      <c r="E51" s="229"/>
-      <c r="F51" s="157"/>
-      <c r="G51" s="133"/>
-      <c r="H51" s="197"/>
-      <c r="I51" s="177"/>
+      <c r="E51" s="202"/>
+      <c r="F51" s="135"/>
+      <c r="G51" s="157"/>
+      <c r="H51" s="233"/>
+      <c r="I51" s="246"/>
     </row>
     <row r="52" spans="2:9" ht="29.5" thickBot="1">
-      <c r="B52" s="220"/>
+      <c r="B52" s="192"/>
       <c r="C52" s="38" t="s">
         <v>72</v>
       </c>
       <c r="D52" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="E52" s="230" t="s">
+      <c r="E52" s="203" t="s">
         <v>56</v>
       </c>
-      <c r="F52" s="231"/>
-      <c r="G52" s="231"/>
-      <c r="H52" s="231"/>
-      <c r="I52" s="232"/>
+      <c r="F52" s="204"/>
+      <c r="G52" s="204"/>
+      <c r="H52" s="204"/>
+      <c r="I52" s="205"/>
     </row>
     <row r="53" spans="2:9" ht="17.5" thickBot="1">
       <c r="B53" s="80"/>
@@ -11658,7 +11781,7 @@
       <c r="I53" s="93"/>
     </row>
     <row r="54" spans="2:9" ht="94.75" customHeight="1">
-      <c r="B54" s="218" t="s">
+      <c r="B54" s="190" t="s">
         <v>74</v>
       </c>
       <c r="C54" s="40" t="s">
@@ -11679,44 +11802,44 @@
       <c r="H54" s="109" t="s">
         <v>147</v>
       </c>
-      <c r="I54" s="175" t="s">
+      <c r="I54" s="169" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="55" spans="2:9">
-      <c r="B55" s="219"/>
-      <c r="C55" s="226" t="s">
+      <c r="B55" s="191"/>
+      <c r="C55" s="176" t="s">
         <v>16</v>
       </c>
-      <c r="D55" s="152" t="s">
+      <c r="D55" s="130" t="s">
         <v>78</v>
       </c>
-      <c r="E55" s="173" t="s">
+      <c r="E55" s="201" t="s">
         <v>190</v>
       </c>
-      <c r="F55" s="173" t="s">
+      <c r="F55" s="201" t="s">
         <v>181</v>
       </c>
-      <c r="G55" s="189" t="s">
+      <c r="G55" s="183" t="s">
         <v>191</v>
       </c>
-      <c r="H55" s="191" t="s">
+      <c r="H55" s="227" t="s">
         <v>182</v>
       </c>
-      <c r="I55" s="176"/>
+      <c r="I55" s="245"/>
     </row>
     <row r="56" spans="2:9" ht="207" customHeight="1">
-      <c r="B56" s="219"/>
-      <c r="C56" s="227"/>
-      <c r="D56" s="153"/>
-      <c r="E56" s="157"/>
-      <c r="F56" s="157"/>
-      <c r="G56" s="190"/>
-      <c r="H56" s="192"/>
-      <c r="I56" s="176"/>
+      <c r="B56" s="191"/>
+      <c r="C56" s="174"/>
+      <c r="D56" s="131"/>
+      <c r="E56" s="135"/>
+      <c r="F56" s="135"/>
+      <c r="G56" s="185"/>
+      <c r="H56" s="228"/>
+      <c r="I56" s="245"/>
     </row>
     <row r="57" spans="2:9" ht="181.75" customHeight="1">
-      <c r="B57" s="219"/>
+      <c r="B57" s="191"/>
       <c r="C57" s="28" t="s">
         <v>79</v>
       </c>
@@ -11731,23 +11854,23 @@
         <v>188</v>
       </c>
       <c r="H57" s="99"/>
-      <c r="I57" s="177"/>
+      <c r="I57" s="246"/>
     </row>
     <row r="58" spans="2:9" ht="34.5" thickBot="1">
-      <c r="B58" s="220"/>
+      <c r="B58" s="192"/>
       <c r="C58" s="31" t="s">
         <v>72</v>
       </c>
       <c r="D58" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="E58" s="170" t="s">
+      <c r="E58" s="242" t="s">
         <v>56</v>
       </c>
-      <c r="F58" s="171"/>
-      <c r="G58" s="171"/>
-      <c r="H58" s="171"/>
-      <c r="I58" s="172"/>
+      <c r="F58" s="243"/>
+      <c r="G58" s="243"/>
+      <c r="H58" s="243"/>
+      <c r="I58" s="244"/>
     </row>
     <row r="59" spans="2:9" ht="17.5" thickBot="1">
       <c r="B59" s="76"/>
@@ -11760,7 +11883,7 @@
       <c r="I59" s="94"/>
     </row>
     <row r="60" spans="2:9" ht="68">
-      <c r="B60" s="117" t="s">
+      <c r="B60" s="141" t="s">
         <v>155</v>
       </c>
       <c r="C60" s="40" t="s">
@@ -11777,12 +11900,12 @@
         <v>169</v>
       </c>
       <c r="H60" s="100"/>
-      <c r="I60" s="175" t="s">
+      <c r="I60" s="169" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="61" spans="2:9" ht="228.5" customHeight="1">
-      <c r="B61" s="118"/>
+      <c r="B61" s="142"/>
       <c r="C61" s="28" t="s">
         <v>85</v>
       </c>
@@ -11795,10 +11918,10 @@
         <v>198</v>
       </c>
       <c r="H61" s="101"/>
-      <c r="I61" s="178"/>
+      <c r="I61" s="170"/>
     </row>
     <row r="62" spans="2:9" ht="170">
-      <c r="B62" s="118"/>
+      <c r="B62" s="142"/>
       <c r="C62" s="28" t="s">
         <v>87</v>
       </c>
@@ -11817,10 +11940,10 @@
       <c r="H62" s="110" t="s">
         <v>196</v>
       </c>
-      <c r="I62" s="178"/>
+      <c r="I62" s="170"/>
     </row>
     <row r="63" spans="2:9" ht="34">
-      <c r="B63" s="118"/>
+      <c r="B63" s="142"/>
       <c r="C63" s="28" t="s">
         <v>90</v>
       </c>
@@ -11835,10 +11958,10 @@
         <v>194</v>
       </c>
       <c r="H63" s="102"/>
-      <c r="I63" s="178"/>
+      <c r="I63" s="170"/>
     </row>
     <row r="64" spans="2:9" ht="85">
-      <c r="B64" s="118"/>
+      <c r="B64" s="142"/>
       <c r="C64" s="28" t="s">
         <v>92</v>
       </c>
@@ -11853,26 +11976,86 @@
         <v>158</v>
       </c>
       <c r="H64" s="103"/>
-      <c r="I64" s="179"/>
+      <c r="I64" s="171"/>
     </row>
     <row r="65" spans="2:9" ht="34.5" thickBot="1">
-      <c r="B65" s="119"/>
+      <c r="B65" s="143"/>
       <c r="C65" s="31" t="s">
         <v>95</v>
       </c>
       <c r="D65" s="111" t="s">
         <v>96</v>
       </c>
-      <c r="E65" s="163" t="s">
+      <c r="E65" s="236" t="s">
         <v>56</v>
       </c>
-      <c r="F65" s="164"/>
-      <c r="G65" s="164"/>
-      <c r="H65" s="164"/>
-      <c r="I65" s="165"/>
+      <c r="F65" s="237"/>
+      <c r="G65" s="237"/>
+      <c r="H65" s="237"/>
+      <c r="I65" s="238"/>
     </row>
   </sheetData>
   <mergeCells count="76">
+    <mergeCell ref="E65:I65"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="F25:F32"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="E58:I58"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="F46:F51"/>
+    <mergeCell ref="I54:I57"/>
+    <mergeCell ref="I38:I51"/>
+    <mergeCell ref="I23:I35"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="I8:I21"/>
+    <mergeCell ref="I4:I7"/>
+    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="H55:H56"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="H42:H45"/>
+    <mergeCell ref="G46:G51"/>
+    <mergeCell ref="H46:H51"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="D14:D21"/>
+    <mergeCell ref="G11:G13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="H11:H13"/>
+    <mergeCell ref="G14:G21"/>
+    <mergeCell ref="H14:H21"/>
+    <mergeCell ref="B3:B21"/>
+    <mergeCell ref="B23:B36"/>
+    <mergeCell ref="B60:B65"/>
+    <mergeCell ref="G4:G7"/>
+    <mergeCell ref="H4:H7"/>
+    <mergeCell ref="B54:B58"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="C46:C51"/>
+    <mergeCell ref="E46:E51"/>
+    <mergeCell ref="E52:I52"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="C42:C45"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="B38:B52"/>
+    <mergeCell ref="C38:C41"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="F40:F41"/>
     <mergeCell ref="C4:C7"/>
     <mergeCell ref="D4:D7"/>
     <mergeCell ref="F4:F7"/>
@@ -11889,66 +12072,6 @@
     <mergeCell ref="F33:F34"/>
     <mergeCell ref="G25:G32"/>
     <mergeCell ref="H25:H32"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="B38:B52"/>
-    <mergeCell ref="C38:C41"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="B3:B21"/>
-    <mergeCell ref="B23:B36"/>
-    <mergeCell ref="B60:B65"/>
-    <mergeCell ref="G4:G7"/>
-    <mergeCell ref="H4:H7"/>
-    <mergeCell ref="B54:B58"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="C46:C51"/>
-    <mergeCell ref="E46:E51"/>
-    <mergeCell ref="E52:I52"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="C42:C45"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="D14:D21"/>
-    <mergeCell ref="G11:G13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="H11:H13"/>
-    <mergeCell ref="G14:G21"/>
-    <mergeCell ref="H14:H21"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="I8:I21"/>
-    <mergeCell ref="I4:I7"/>
-    <mergeCell ref="G55:G56"/>
-    <mergeCell ref="H55:H56"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="H40:H41"/>
-    <mergeCell ref="H42:H45"/>
-    <mergeCell ref="G46:G51"/>
-    <mergeCell ref="H46:H51"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="E65:I65"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="F25:F32"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="E58:I58"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="F46:F51"/>
-    <mergeCell ref="I54:I57"/>
-    <mergeCell ref="I38:I51"/>
-    <mergeCell ref="I23:I35"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="G33:G34"/>
-    <mergeCell ref="H33:H34"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <hyperlinks>
@@ -11997,7 +12120,7 @@
       </c>
     </row>
     <row r="5" spans="2:7" ht="34">
-      <c r="B5" s="260" t="s">
+      <c r="B5" s="252" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="53" t="s">
@@ -12015,47 +12138,47 @@
       <c r="G5" s="56"/>
     </row>
     <row r="6" spans="2:7">
-      <c r="B6" s="261"/>
-      <c r="C6" s="266" t="s">
+      <c r="B6" s="253"/>
+      <c r="C6" s="260" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="158" t="s">
+      <c r="D6" s="136" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="126" t="s">
+      <c r="E6" s="150" t="s">
         <v>100</v>
       </c>
-      <c r="F6" s="143" t="s">
+      <c r="F6" s="121" t="s">
         <v>101</v>
       </c>
-      <c r="G6" s="257"/>
+      <c r="G6" s="249"/>
     </row>
     <row r="7" spans="2:7">
-      <c r="B7" s="261"/>
-      <c r="C7" s="267"/>
-      <c r="D7" s="159"/>
-      <c r="E7" s="202"/>
-      <c r="F7" s="221"/>
-      <c r="G7" s="258"/>
+      <c r="B7" s="253"/>
+      <c r="C7" s="261"/>
+      <c r="D7" s="137"/>
+      <c r="E7" s="167"/>
+      <c r="F7" s="196"/>
+      <c r="G7" s="250"/>
     </row>
     <row r="8" spans="2:7">
-      <c r="B8" s="261"/>
-      <c r="C8" s="267"/>
-      <c r="D8" s="159"/>
-      <c r="E8" s="202"/>
-      <c r="F8" s="221"/>
-      <c r="G8" s="258"/>
+      <c r="B8" s="253"/>
+      <c r="C8" s="261"/>
+      <c r="D8" s="137"/>
+      <c r="E8" s="167"/>
+      <c r="F8" s="196"/>
+      <c r="G8" s="250"/>
     </row>
     <row r="9" spans="2:7">
-      <c r="B9" s="261"/>
-      <c r="C9" s="271"/>
-      <c r="D9" s="239"/>
-      <c r="E9" s="127"/>
-      <c r="F9" s="222"/>
-      <c r="G9" s="259"/>
+      <c r="B9" s="253"/>
+      <c r="C9" s="265"/>
+      <c r="D9" s="166"/>
+      <c r="E9" s="151"/>
+      <c r="F9" s="197"/>
+      <c r="G9" s="251"/>
     </row>
     <row r="10" spans="2:7" ht="34">
-      <c r="B10" s="261"/>
+      <c r="B10" s="253"/>
       <c r="C10" s="57" t="s">
         <v>16</v>
       </c>
@@ -12069,146 +12192,146 @@
       <c r="G10" s="116"/>
     </row>
     <row r="11" spans="2:7">
-      <c r="B11" s="261"/>
-      <c r="C11" s="266" t="s">
+      <c r="B11" s="253"/>
+      <c r="C11" s="260" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="243" t="s">
+      <c r="D11" s="179" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="126" t="s">
+      <c r="E11" s="150" t="s">
         <v>105</v>
       </c>
-      <c r="F11" s="249" t="s">
+      <c r="F11" s="258" t="s">
         <v>117</v>
       </c>
-      <c r="G11" s="151" t="s">
+      <c r="G11" s="129" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="12" spans="2:7">
-      <c r="B12" s="261"/>
-      <c r="C12" s="267"/>
-      <c r="D12" s="270"/>
-      <c r="E12" s="202"/>
-      <c r="F12" s="250"/>
-      <c r="G12" s="275"/>
+      <c r="B12" s="253"/>
+      <c r="C12" s="261"/>
+      <c r="D12" s="264"/>
+      <c r="E12" s="167"/>
+      <c r="F12" s="259"/>
+      <c r="G12" s="269"/>
     </row>
     <row r="13" spans="2:7" ht="286.75" customHeight="1">
-      <c r="B13" s="261"/>
-      <c r="C13" s="269"/>
-      <c r="D13" s="244"/>
-      <c r="E13" s="127"/>
-      <c r="F13" s="123"/>
-      <c r="G13" s="276"/>
+      <c r="B13" s="253"/>
+      <c r="C13" s="263"/>
+      <c r="D13" s="180"/>
+      <c r="E13" s="151"/>
+      <c r="F13" s="147"/>
+      <c r="G13" s="270"/>
     </row>
     <row r="14" spans="2:7" ht="35.15" customHeight="1">
-      <c r="B14" s="261"/>
-      <c r="C14" s="266" t="s">
+      <c r="B14" s="253"/>
+      <c r="C14" s="260" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="263" t="s">
+      <c r="D14" s="255" t="s">
         <v>114</v>
       </c>
-      <c r="E14" s="126" t="s">
+      <c r="E14" s="150" t="s">
         <v>106</v>
       </c>
-      <c r="F14" s="249" t="s">
+      <c r="F14" s="258" t="s">
         <v>115</v>
       </c>
-      <c r="G14" s="251" t="s">
+      <c r="G14" s="271" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="15" spans="2:7">
-      <c r="B15" s="261"/>
-      <c r="C15" s="267"/>
-      <c r="D15" s="264"/>
-      <c r="E15" s="202"/>
-      <c r="F15" s="250"/>
-      <c r="G15" s="252"/>
+      <c r="B15" s="253"/>
+      <c r="C15" s="261"/>
+      <c r="D15" s="256"/>
+      <c r="E15" s="167"/>
+      <c r="F15" s="259"/>
+      <c r="G15" s="272"/>
     </row>
     <row r="16" spans="2:7" ht="134.65" customHeight="1">
-      <c r="B16" s="261"/>
-      <c r="C16" s="269"/>
-      <c r="D16" s="265"/>
-      <c r="E16" s="127"/>
-      <c r="F16" s="123"/>
-      <c r="G16" s="253"/>
+      <c r="B16" s="253"/>
+      <c r="C16" s="263"/>
+      <c r="D16" s="257"/>
+      <c r="E16" s="151"/>
+      <c r="F16" s="147"/>
+      <c r="G16" s="273"/>
     </row>
     <row r="17" spans="2:7" ht="35.15" customHeight="1">
-      <c r="B17" s="261"/>
-      <c r="C17" s="266" t="s">
+      <c r="B17" s="253"/>
+      <c r="C17" s="260" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="126" t="s">
+      <c r="D17" s="150" t="s">
         <v>97</v>
       </c>
-      <c r="E17" s="158" t="s">
+      <c r="E17" s="136" t="s">
         <v>102</v>
       </c>
-      <c r="F17" s="272" t="s">
+      <c r="F17" s="266" t="s">
         <v>120</v>
       </c>
-      <c r="G17" s="254" t="s">
+      <c r="G17" s="274" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="261"/>
-      <c r="C18" s="267"/>
-      <c r="D18" s="202"/>
-      <c r="E18" s="159"/>
-      <c r="F18" s="273"/>
-      <c r="G18" s="255"/>
+      <c r="B18" s="253"/>
+      <c r="C18" s="261"/>
+      <c r="D18" s="167"/>
+      <c r="E18" s="137"/>
+      <c r="F18" s="267"/>
+      <c r="G18" s="275"/>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="261"/>
-      <c r="C19" s="267"/>
-      <c r="D19" s="202"/>
-      <c r="E19" s="159"/>
-      <c r="F19" s="273"/>
-      <c r="G19" s="255"/>
+      <c r="B19" s="253"/>
+      <c r="C19" s="261"/>
+      <c r="D19" s="167"/>
+      <c r="E19" s="137"/>
+      <c r="F19" s="267"/>
+      <c r="G19" s="275"/>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="261"/>
-      <c r="C20" s="267"/>
-      <c r="D20" s="202"/>
-      <c r="E20" s="159"/>
-      <c r="F20" s="273"/>
-      <c r="G20" s="255"/>
+      <c r="B20" s="253"/>
+      <c r="C20" s="261"/>
+      <c r="D20" s="167"/>
+      <c r="E20" s="137"/>
+      <c r="F20" s="267"/>
+      <c r="G20" s="275"/>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="261"/>
-      <c r="C21" s="267"/>
-      <c r="D21" s="202"/>
-      <c r="E21" s="159"/>
-      <c r="F21" s="273"/>
-      <c r="G21" s="255"/>
+      <c r="B21" s="253"/>
+      <c r="C21" s="261"/>
+      <c r="D21" s="167"/>
+      <c r="E21" s="137"/>
+      <c r="F21" s="267"/>
+      <c r="G21" s="275"/>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="261"/>
-      <c r="C22" s="267"/>
-      <c r="D22" s="202"/>
-      <c r="E22" s="159"/>
-      <c r="F22" s="273"/>
-      <c r="G22" s="255"/>
+      <c r="B22" s="253"/>
+      <c r="C22" s="261"/>
+      <c r="D22" s="167"/>
+      <c r="E22" s="137"/>
+      <c r="F22" s="267"/>
+      <c r="G22" s="275"/>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="261"/>
-      <c r="C23" s="267"/>
-      <c r="D23" s="202"/>
-      <c r="E23" s="159"/>
-      <c r="F23" s="273"/>
-      <c r="G23" s="255"/>
+      <c r="B23" s="253"/>
+      <c r="C23" s="261"/>
+      <c r="D23" s="167"/>
+      <c r="E23" s="137"/>
+      <c r="F23" s="267"/>
+      <c r="G23" s="275"/>
     </row>
     <row r="24" spans="2:7" ht="85.75" customHeight="1" thickBot="1">
-      <c r="B24" s="262"/>
-      <c r="C24" s="268"/>
-      <c r="D24" s="203"/>
-      <c r="E24" s="160"/>
-      <c r="F24" s="274"/>
-      <c r="G24" s="256"/>
+      <c r="B24" s="254"/>
+      <c r="C24" s="262"/>
+      <c r="D24" s="206"/>
+      <c r="E24" s="138"/>
+      <c r="F24" s="268"/>
+      <c r="G24" s="276"/>
     </row>
     <row r="28" spans="2:7">
       <c r="F28" t="s">
@@ -12222,6 +12345,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="E17:E24"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="G17:G24"/>
     <mergeCell ref="G6:G9"/>
     <mergeCell ref="B5:B24"/>
     <mergeCell ref="D17:D24"/>
@@ -12238,11 +12366,6 @@
     <mergeCell ref="F6:F9"/>
     <mergeCell ref="F17:F24"/>
     <mergeCell ref="G11:G13"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="E17:E24"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="G17:G24"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12282,135 +12405,135 @@
       </c>
     </row>
     <row r="3" spans="2:7" ht="70.400000000000006" customHeight="1">
-      <c r="B3" s="117" t="s">
+      <c r="B3" s="141" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="134" t="s">
+      <c r="C3" s="158" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="280" t="s">
+      <c r="D3" s="289" t="s">
         <v>113</v>
       </c>
-      <c r="E3" s="282" t="s">
+      <c r="E3" s="291" t="s">
         <v>118</v>
       </c>
-      <c r="F3" s="122" t="s">
+      <c r="F3" s="146" t="s">
         <v>131</v>
       </c>
-      <c r="G3" s="278" t="s">
+      <c r="G3" s="287" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="83.15" customHeight="1">
-      <c r="B4" s="118"/>
-      <c r="C4" s="136"/>
-      <c r="D4" s="281"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="123"/>
-      <c r="G4" s="279"/>
+      <c r="B4" s="142"/>
+      <c r="C4" s="160"/>
+      <c r="D4" s="290"/>
+      <c r="E4" s="185"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="288"/>
     </row>
     <row r="5" spans="2:7" ht="105.4" customHeight="1">
-      <c r="B5" s="118"/>
-      <c r="C5" s="137" t="s">
+      <c r="B5" s="142"/>
+      <c r="C5" s="161" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="161" t="s">
+      <c r="D5" s="139" t="s">
         <v>119</v>
       </c>
-      <c r="E5" s="286" t="s">
+      <c r="E5" s="277" t="s">
         <v>125</v>
       </c>
-      <c r="F5" s="189" t="s">
+      <c r="F5" s="183" t="s">
         <v>121</v>
       </c>
-      <c r="G5" s="283" t="s">
+      <c r="G5" s="292" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="6" spans="2:7">
-      <c r="B6" s="118"/>
-      <c r="C6" s="135"/>
-      <c r="D6" s="289"/>
-      <c r="E6" s="287"/>
-      <c r="F6" s="247"/>
-      <c r="G6" s="284"/>
+      <c r="B6" s="142"/>
+      <c r="C6" s="159"/>
+      <c r="D6" s="280"/>
+      <c r="E6" s="278"/>
+      <c r="F6" s="184"/>
+      <c r="G6" s="293"/>
     </row>
     <row r="7" spans="2:7">
-      <c r="B7" s="118"/>
-      <c r="C7" s="135"/>
-      <c r="D7" s="289"/>
-      <c r="E7" s="287"/>
-      <c r="F7" s="247"/>
-      <c r="G7" s="284"/>
+      <c r="B7" s="142"/>
+      <c r="C7" s="159"/>
+      <c r="D7" s="280"/>
+      <c r="E7" s="278"/>
+      <c r="F7" s="184"/>
+      <c r="G7" s="293"/>
     </row>
     <row r="8" spans="2:7">
-      <c r="B8" s="118"/>
-      <c r="C8" s="135"/>
-      <c r="D8" s="289"/>
-      <c r="E8" s="287"/>
-      <c r="F8" s="247"/>
-      <c r="G8" s="284"/>
+      <c r="B8" s="142"/>
+      <c r="C8" s="159"/>
+      <c r="D8" s="280"/>
+      <c r="E8" s="278"/>
+      <c r="F8" s="184"/>
+      <c r="G8" s="293"/>
     </row>
     <row r="9" spans="2:7">
-      <c r="B9" s="118"/>
-      <c r="C9" s="135"/>
-      <c r="D9" s="289"/>
-      <c r="E9" s="287"/>
-      <c r="F9" s="247"/>
-      <c r="G9" s="284"/>
+      <c r="B9" s="142"/>
+      <c r="C9" s="159"/>
+      <c r="D9" s="280"/>
+      <c r="E9" s="278"/>
+      <c r="F9" s="184"/>
+      <c r="G9" s="293"/>
     </row>
     <row r="10" spans="2:7">
-      <c r="B10" s="118"/>
-      <c r="C10" s="135"/>
-      <c r="D10" s="289"/>
-      <c r="E10" s="287"/>
-      <c r="F10" s="247"/>
-      <c r="G10" s="284"/>
+      <c r="B10" s="142"/>
+      <c r="C10" s="159"/>
+      <c r="D10" s="280"/>
+      <c r="E10" s="278"/>
+      <c r="F10" s="184"/>
+      <c r="G10" s="293"/>
     </row>
     <row r="11" spans="2:7">
-      <c r="B11" s="118"/>
-      <c r="C11" s="135"/>
-      <c r="D11" s="289"/>
-      <c r="E11" s="287"/>
-      <c r="F11" s="247"/>
-      <c r="G11" s="284"/>
+      <c r="B11" s="142"/>
+      <c r="C11" s="159"/>
+      <c r="D11" s="280"/>
+      <c r="E11" s="278"/>
+      <c r="F11" s="184"/>
+      <c r="G11" s="293"/>
     </row>
     <row r="12" spans="2:7">
-      <c r="B12" s="118"/>
-      <c r="C12" s="136"/>
-      <c r="D12" s="162"/>
-      <c r="E12" s="288"/>
-      <c r="F12" s="190"/>
+      <c r="B12" s="142"/>
+      <c r="C12" s="160"/>
+      <c r="D12" s="140"/>
+      <c r="E12" s="279"/>
+      <c r="F12" s="185"/>
       <c r="G12" s="285"/>
     </row>
     <row r="13" spans="2:7" ht="139" customHeight="1">
-      <c r="B13" s="118"/>
-      <c r="C13" s="137" t="s">
+      <c r="B13" s="142"/>
+      <c r="C13" s="161" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="161" t="s">
+      <c r="D13" s="139" t="s">
         <v>123</v>
       </c>
-      <c r="E13" s="158" t="s">
+      <c r="E13" s="136" t="s">
         <v>122</v>
       </c>
-      <c r="F13" s="180" t="s">
+      <c r="F13" s="247" t="s">
         <v>124</v>
       </c>
-      <c r="G13" s="293" t="s">
+      <c r="G13" s="284" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="14" spans="2:7">
-      <c r="B14" s="118"/>
-      <c r="C14" s="136"/>
-      <c r="D14" s="162"/>
-      <c r="E14" s="229"/>
-      <c r="F14" s="181"/>
+      <c r="B14" s="142"/>
+      <c r="C14" s="160"/>
+      <c r="D14" s="140"/>
+      <c r="E14" s="202"/>
+      <c r="F14" s="248"/>
       <c r="G14" s="285"/>
     </row>
     <row r="15" spans="2:7" ht="95.65" customHeight="1">
-      <c r="B15" s="118"/>
+      <c r="B15" s="142"/>
       <c r="C15" s="28" t="s">
         <v>50</v>
       </c>
@@ -12428,59 +12551,59 @@
       </c>
     </row>
     <row r="16" spans="2:7" ht="17.5" thickBot="1">
-      <c r="B16" s="119"/>
+      <c r="B16" s="143"/>
       <c r="C16" s="31" t="s">
         <v>54</v>
       </c>
       <c r="D16" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="E16" s="290" t="s">
+      <c r="E16" s="281" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="291"/>
-      <c r="G16" s="292"/>
+      <c r="F16" s="282"/>
+      <c r="G16" s="283"/>
     </row>
     <row r="32" ht="17.5" thickBot="1"/>
     <row r="33" spans="8:8">
-      <c r="H33" s="175" t="s">
+      <c r="H33" s="169" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="34" spans="8:8">
-      <c r="H34" s="178"/>
+      <c r="H34" s="170"/>
     </row>
     <row r="35" spans="8:8">
-      <c r="H35" s="178"/>
+      <c r="H35" s="170"/>
     </row>
     <row r="36" spans="8:8">
-      <c r="H36" s="178"/>
+      <c r="H36" s="170"/>
     </row>
     <row r="37" spans="8:8">
-      <c r="H37" s="178"/>
+      <c r="H37" s="170"/>
     </row>
     <row r="38" spans="8:8">
-      <c r="H38" s="178"/>
+      <c r="H38" s="170"/>
     </row>
     <row r="39" spans="8:8">
-      <c r="H39" s="178"/>
+      <c r="H39" s="170"/>
     </row>
     <row r="40" spans="8:8">
-      <c r="H40" s="178"/>
+      <c r="H40" s="170"/>
     </row>
     <row r="41" spans="8:8">
-      <c r="H41" s="178"/>
+      <c r="H41" s="170"/>
     </row>
     <row r="42" spans="8:8">
-      <c r="H42" s="179"/>
+      <c r="H42" s="171"/>
     </row>
     <row r="43" spans="8:8">
-      <c r="H43" s="277" t="s">
+      <c r="H43" s="286" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="44" spans="8:8">
-      <c r="H44" s="179"/>
+      <c r="H44" s="171"/>
     </row>
     <row r="45" spans="8:8">
       <c r="H45" s="58" t="s">
@@ -12492,12 +12615,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B3:B16"/>
-    <mergeCell ref="E5:E12"/>
-    <mergeCell ref="D5:D12"/>
-    <mergeCell ref="C5:C12"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="G13:G14"/>
     <mergeCell ref="H33:H42"/>
     <mergeCell ref="H43:H44"/>
     <mergeCell ref="C3:C4"/>
@@ -12511,6 +12628,12 @@
     <mergeCell ref="E13:E14"/>
     <mergeCell ref="F13:F14"/>
     <mergeCell ref="G5:G12"/>
+    <mergeCell ref="B3:B16"/>
+    <mergeCell ref="E5:E12"/>
+    <mergeCell ref="D5:D12"/>
+    <mergeCell ref="C5:C12"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="G13:G14"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <hyperlinks>
@@ -12553,164 +12676,174 @@
       </c>
     </row>
     <row r="3" spans="2:7" ht="35.15" customHeight="1">
-      <c r="B3" s="117" t="s">
+      <c r="B3" s="141" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="134" t="s">
+      <c r="C3" s="158" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="145" t="s">
+      <c r="D3" s="123" t="s">
         <v>136</v>
       </c>
-      <c r="E3" s="156" t="s">
+      <c r="E3" s="134" t="s">
         <v>132</v>
       </c>
-      <c r="F3" s="122" t="s">
+      <c r="F3" s="146" t="s">
         <v>141</v>
       </c>
-      <c r="G3" s="139" t="s">
+      <c r="G3" s="117" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="182.15" customHeight="1">
-      <c r="B4" s="118"/>
-      <c r="C4" s="135"/>
-      <c r="D4" s="146"/>
-      <c r="E4" s="157"/>
-      <c r="F4" s="123"/>
-      <c r="G4" s="140"/>
+      <c r="B4" s="142"/>
+      <c r="C4" s="159"/>
+      <c r="D4" s="124"/>
+      <c r="E4" s="135"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="118"/>
     </row>
     <row r="5" spans="2:7">
-      <c r="B5" s="118"/>
-      <c r="C5" s="135"/>
-      <c r="D5" s="141" t="s">
+      <c r="B5" s="142"/>
+      <c r="C5" s="159"/>
+      <c r="D5" s="119" t="s">
         <v>134</v>
       </c>
-      <c r="E5" s="120" t="s">
+      <c r="E5" s="144" t="s">
         <v>135</v>
       </c>
-      <c r="F5" s="143" t="s">
+      <c r="F5" s="121" t="s">
         <v>142</v>
       </c>
-      <c r="G5" s="151" t="s">
+      <c r="G5" s="129" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="6" spans="2:7" ht="86.15" customHeight="1">
-      <c r="B6" s="118"/>
-      <c r="C6" s="136"/>
-      <c r="D6" s="142"/>
-      <c r="E6" s="121"/>
-      <c r="F6" s="144"/>
-      <c r="G6" s="150"/>
+      <c r="B6" s="142"/>
+      <c r="C6" s="160"/>
+      <c r="D6" s="120"/>
+      <c r="E6" s="145"/>
+      <c r="F6" s="122"/>
+      <c r="G6" s="128"/>
     </row>
     <row r="7" spans="2:7">
-      <c r="B7" s="118"/>
-      <c r="C7" s="137" t="s">
+      <c r="B7" s="142"/>
+      <c r="C7" s="161" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="161" t="s">
+      <c r="D7" s="139" t="s">
         <v>133</v>
       </c>
-      <c r="E7" s="124" t="s">
+      <c r="E7" s="148" t="s">
         <v>137</v>
       </c>
-      <c r="F7" s="143" t="s">
+      <c r="F7" s="121" t="s">
         <v>138</v>
       </c>
-      <c r="G7" s="149" t="s">
+      <c r="G7" s="127" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="103" customHeight="1">
-      <c r="B8" s="118"/>
-      <c r="C8" s="135"/>
-      <c r="D8" s="162"/>
-      <c r="E8" s="125"/>
-      <c r="F8" s="144"/>
-      <c r="G8" s="149"/>
+      <c r="B8" s="142"/>
+      <c r="C8" s="159"/>
+      <c r="D8" s="140"/>
+      <c r="E8" s="149"/>
+      <c r="F8" s="122"/>
+      <c r="G8" s="127"/>
     </row>
     <row r="9" spans="2:7">
-      <c r="B9" s="118"/>
-      <c r="C9" s="135"/>
-      <c r="D9" s="152" t="s">
+      <c r="B9" s="142"/>
+      <c r="C9" s="159"/>
+      <c r="D9" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="126" t="s">
+      <c r="E9" s="150" t="s">
         <v>139</v>
       </c>
-      <c r="F9" s="154" t="s">
+      <c r="F9" s="132" t="s">
         <v>203</v>
       </c>
-      <c r="G9" s="149"/>
+      <c r="G9" s="127"/>
     </row>
     <row r="10" spans="2:7" ht="274.5" customHeight="1">
-      <c r="B10" s="118"/>
-      <c r="C10" s="136"/>
-      <c r="D10" s="153"/>
-      <c r="E10" s="127"/>
-      <c r="F10" s="155"/>
-      <c r="G10" s="150"/>
+      <c r="B10" s="142"/>
+      <c r="C10" s="160"/>
+      <c r="D10" s="131"/>
+      <c r="E10" s="151"/>
+      <c r="F10" s="133"/>
+      <c r="G10" s="128"/>
     </row>
     <row r="11" spans="2:7" ht="17.649999999999999" customHeight="1">
-      <c r="B11" s="118"/>
-      <c r="C11" s="137" t="s">
+      <c r="B11" s="142"/>
+      <c r="C11" s="161" t="s">
         <v>68</v>
       </c>
-      <c r="D11" s="128" t="s">
+      <c r="D11" s="152" t="s">
         <v>69</v>
       </c>
-      <c r="E11" s="158" t="s">
+      <c r="E11" s="136" t="s">
         <v>140</v>
       </c>
-      <c r="F11" s="131" t="s">
+      <c r="F11" s="155" t="s">
         <v>202</v>
       </c>
-      <c r="G11" s="147"/>
+      <c r="G11" s="125"/>
     </row>
     <row r="12" spans="2:7" ht="28.4" customHeight="1">
-      <c r="B12" s="118"/>
-      <c r="C12" s="135"/>
-      <c r="D12" s="129"/>
-      <c r="E12" s="159"/>
-      <c r="F12" s="132"/>
-      <c r="G12" s="147"/>
+      <c r="B12" s="142"/>
+      <c r="C12" s="159"/>
+      <c r="D12" s="153"/>
+      <c r="E12" s="137"/>
+      <c r="F12" s="156"/>
+      <c r="G12" s="125"/>
     </row>
     <row r="13" spans="2:7" ht="42.4" customHeight="1">
-      <c r="B13" s="118"/>
-      <c r="C13" s="135"/>
-      <c r="D13" s="129"/>
-      <c r="E13" s="159"/>
-      <c r="F13" s="132"/>
-      <c r="G13" s="147"/>
+      <c r="B13" s="142"/>
+      <c r="C13" s="159"/>
+      <c r="D13" s="153"/>
+      <c r="E13" s="137"/>
+      <c r="F13" s="156"/>
+      <c r="G13" s="125"/>
     </row>
     <row r="14" spans="2:7">
-      <c r="B14" s="118"/>
-      <c r="C14" s="135"/>
-      <c r="D14" s="129"/>
-      <c r="E14" s="159"/>
-      <c r="F14" s="132"/>
-      <c r="G14" s="147"/>
+      <c r="B14" s="142"/>
+      <c r="C14" s="159"/>
+      <c r="D14" s="153"/>
+      <c r="E14" s="137"/>
+      <c r="F14" s="156"/>
+      <c r="G14" s="125"/>
     </row>
     <row r="15" spans="2:7">
-      <c r="B15" s="118"/>
-      <c r="C15" s="135"/>
-      <c r="D15" s="129"/>
-      <c r="E15" s="159"/>
-      <c r="F15" s="132"/>
-      <c r="G15" s="147"/>
+      <c r="B15" s="142"/>
+      <c r="C15" s="159"/>
+      <c r="D15" s="153"/>
+      <c r="E15" s="137"/>
+      <c r="F15" s="156"/>
+      <c r="G15" s="125"/>
     </row>
     <row r="16" spans="2:7" ht="158" customHeight="1" thickBot="1">
-      <c r="B16" s="119"/>
-      <c r="C16" s="138"/>
-      <c r="D16" s="130"/>
-      <c r="E16" s="160"/>
-      <c r="F16" s="133"/>
-      <c r="G16" s="148"/>
+      <c r="B16" s="143"/>
+      <c r="C16" s="162"/>
+      <c r="D16" s="154"/>
+      <c r="E16" s="138"/>
+      <c r="F16" s="157"/>
+      <c r="G16" s="126"/>
     </row>
     <row r="17" ht="17.649999999999999" customHeight="1"/>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="B3:B16"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="D11:D16"/>
+    <mergeCell ref="F11:F16"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="C11:C16"/>
+    <mergeCell ref="C7:C10"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="F5:F6"/>
@@ -12724,16 +12857,6 @@
     <mergeCell ref="E11:E16"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="F7:F8"/>
-    <mergeCell ref="B3:B16"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="D11:D16"/>
-    <mergeCell ref="F11:F16"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="C11:C16"/>
-    <mergeCell ref="C7:C10"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12772,7 +12895,7 @@
       </c>
     </row>
     <row r="3" spans="2:7" ht="103.4" customHeight="1">
-      <c r="B3" s="117" t="s">
+      <c r="B3" s="141" t="s">
         <v>74</v>
       </c>
       <c r="C3" s="40" t="s">
@@ -12792,54 +12915,54 @@
       </c>
     </row>
     <row r="4" spans="2:7" ht="70" customHeight="1">
-      <c r="B4" s="118"/>
-      <c r="C4" s="137" t="s">
+      <c r="B4" s="142"/>
+      <c r="C4" s="161" t="s">
         <v>16</v>
       </c>
       <c r="D4" s="69" t="s">
         <v>149</v>
       </c>
-      <c r="E4" s="173" t="s">
+      <c r="E4" s="201" t="s">
         <v>151</v>
       </c>
-      <c r="F4" s="189" t="s">
+      <c r="F4" s="183" t="s">
         <v>152</v>
       </c>
-      <c r="G4" s="151" t="s">
+      <c r="G4" s="129" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="5" spans="2:7" ht="148.5" customHeight="1">
-      <c r="B5" s="118"/>
-      <c r="C5" s="136"/>
+      <c r="B5" s="142"/>
+      <c r="C5" s="160"/>
       <c r="D5" s="66" t="s">
         <v>148</v>
       </c>
-      <c r="E5" s="157"/>
-      <c r="F5" s="190"/>
-      <c r="G5" s="150"/>
+      <c r="E5" s="135"/>
+      <c r="F5" s="185"/>
+      <c r="G5" s="128"/>
     </row>
     <row r="6" spans="2:7" ht="125.25" customHeight="1">
-      <c r="B6" s="118"/>
-      <c r="C6" s="137" t="s">
+      <c r="B6" s="142"/>
+      <c r="C6" s="161" t="s">
         <v>79</v>
       </c>
-      <c r="D6" s="128" t="s">
+      <c r="D6" s="152" t="s">
         <v>69</v>
       </c>
       <c r="E6" s="294" t="s">
         <v>160</v>
       </c>
-      <c r="F6" s="189" t="s">
+      <c r="F6" s="183" t="s">
         <v>153</v>
       </c>
       <c r="G6" s="296"/>
     </row>
     <row r="7" spans="2:7" ht="17.5" thickBot="1">
-      <c r="B7" s="119"/>
-      <c r="C7" s="138"/>
-      <c r="D7" s="130"/>
-      <c r="E7" s="230"/>
+      <c r="B7" s="143"/>
+      <c r="C7" s="162"/>
+      <c r="D7" s="154"/>
+      <c r="E7" s="203"/>
       <c r="F7" s="295"/>
       <c r="G7" s="297"/>
     </row>
@@ -12893,7 +13016,7 @@
       </c>
     </row>
     <row r="3" spans="2:7" ht="165.4" customHeight="1">
-      <c r="B3" s="117" t="s">
+      <c r="B3" s="141" t="s">
         <v>155</v>
       </c>
       <c r="C3" s="40" t="s">
@@ -12911,7 +13034,7 @@
       <c r="G3" s="67"/>
     </row>
     <row r="4" spans="2:7" ht="256.5" customHeight="1">
-      <c r="B4" s="118"/>
+      <c r="B4" s="142"/>
       <c r="C4" s="28" t="s">
         <v>85</v>
       </c>
@@ -12922,12 +13045,12 @@
         <v>161</v>
       </c>
       <c r="F4" s="71" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="G4" s="64"/>
     </row>
     <row r="5" spans="2:7" ht="176.65" customHeight="1">
-      <c r="B5" s="118"/>
+      <c r="B5" s="142"/>
       <c r="C5" s="28" t="s">
         <v>87</v>
       </c>
@@ -12945,7 +13068,7 @@
       </c>
     </row>
     <row r="6" spans="2:7" ht="94.4" customHeight="1">
-      <c r="B6" s="118"/>
+      <c r="B6" s="142"/>
       <c r="C6" s="28" t="s">
         <v>90</v>
       </c>
@@ -12961,7 +13084,7 @@
       <c r="G6" s="65"/>
     </row>
     <row r="7" spans="2:7" ht="85">
-      <c r="B7" s="118"/>
+      <c r="B7" s="142"/>
       <c r="C7" s="28" t="s">
         <v>92</v>
       </c>
@@ -12977,18 +13100,18 @@
       <c r="G7" s="72"/>
     </row>
     <row r="8" spans="2:7" ht="17.5" thickBot="1">
-      <c r="B8" s="119"/>
+      <c r="B8" s="143"/>
       <c r="C8" s="31" t="s">
         <v>95</v>
       </c>
       <c r="D8" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="E8" s="163" t="s">
+      <c r="E8" s="236" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="164"/>
-      <c r="G8" s="165"/>
+      <c r="F8" s="237"/>
+      <c r="G8" s="238"/>
     </row>
     <row r="11" spans="2:7">
       <c r="F11" t="s">

--- a/16기_스타트캠프_강사 가이드 문서.xlsx
+++ b/16기_스타트캠프_강사 가이드 문서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SSAFY\Local_Workspace\16g_Local\00_startcamp\share_ai-onboarding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF801E5-3F1C-45EC-8CEA-7BCF50F534EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639FFBE6-C1C4-4A1A-A77F-A27C1E92028A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40020" yWindow="1395" windowWidth="26640" windowHeight="18975" activeTab="6" xr2:uid="{FD3BB604-1650-4EBB-871F-9010366B35B1}"/>
+    <workbookView xWindow="62490" yWindow="645" windowWidth="26640" windowHeight="18975" activeTab="6" xr2:uid="{FD3BB604-1650-4EBB-871F-9010366B35B1}"/>
   </bookViews>
   <sheets>
     <sheet name="교육 목표 및 방향" sheetId="7" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="208">
   <si>
     <t>시간</t>
   </si>
@@ -65,12 +65,6 @@
     <t>7/10 (금)</t>
   </si>
   <si>
-    <t>9:30 ~ 10:30</t>
-  </si>
-  <si>
-    <t>AI 거버넌스 특강</t>
-  </si>
-  <si>
     <r>
       <t>해당</t>
     </r>
@@ -95,9 +89,6 @@
     </r>
   </si>
   <si>
-    <t>10:30 ~ 12:00</t>
-  </si>
-  <si>
     <r>
       <t>AI 온보딩</t>
     </r>
@@ -122,18 +113,6 @@
     </r>
   </si>
   <si>
-    <t>AI 온보딩 소개</t>
-  </si>
-  <si>
-    <t>바이브 코딩 소개</t>
-  </si>
-  <si>
-    <t>개발 절차(기획-구현 - 배포)  소개</t>
-  </si>
-  <si>
-    <t>프로젝트 안내 및 산출물 예시</t>
-  </si>
-  <si>
     <t>라이브 교안</t>
   </si>
   <si>
@@ -161,33 +140,6 @@
         <family val="2"/>
       </rPr>
       <t>브레이킹</t>
-    </r>
-  </si>
-  <si>
-    <t>13:30 – 14:00</t>
-  </si>
-  <si>
-    <r>
-      <t>환경</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>셋팅</t>
     </r>
   </si>
   <si>
@@ -1195,11 +1147,19 @@
     <t>10:30 – 12:00</t>
   </si>
   <si>
-    <t>git branch 수업</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">(git bash  </t>
+    <r>
+      <t>기획과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -1209,7 +1169,161 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>터미널</t>
+      <t>설계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수업</t>
+    </r>
+  </si>
+  <si>
+    <t>프로젝트 기획과 설계</t>
+  </si>
+  <si>
+    <r>
+      <t>팀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>명세서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>방법</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안내</t>
+    </r>
+  </si>
+  <si>
+    <t>13:00 – 16:00</t>
+  </si>
+  <si>
+    <t>서비스 개발 요청 문서(RFP) 배포</t>
+  </si>
+  <si>
+    <r>
+      <t>팀별 강사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미팅</t>
+    </r>
+  </si>
+  <si>
+    <t>16:00 – 17:00</t>
+  </si>
+  <si>
+    <r>
+      <t>개발</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -1218,7 +1332,98 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">, vscode </t>
+      <t>진행</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>팀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>프로젝트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개발</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">시작, </t>
+    </r>
+  </si>
+  <si>
+    <t>17:00 – 18:00</t>
+  </si>
+  <si>
+    <t>7/15 (수) (day4)</t>
+  </si>
+  <si>
+    <t>11:00 – 12:00</t>
+  </si>
+  <si>
+    <t>Unit 테스트 수업</t>
+  </si>
+  <si>
+    <t>unit test 학습 및 실습</t>
+  </si>
+  <si>
+    <r>
+      <t>팀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -1228,7 +1433,109 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>터미널</t>
+      <t>스크럼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> + OpenAI API 키 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>배포</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 및 사용 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안내</t>
+    </r>
+  </si>
+  <si>
+    <t>13:30 – 17:00</t>
+  </si>
+  <si>
+    <t>팀 프로젝트 개발 진행</t>
+  </si>
+  <si>
+    <t>현직개발자 특강</t>
+  </si>
+  <si>
+    <t>09:30 – 10:00</t>
+  </si>
+  <si>
+    <t>팀 스크럼 회의</t>
+  </si>
+  <si>
+    <t>비전공: https://localhub-sc16-1.netlify.app/</t>
+  </si>
+  <si>
+    <t>10:00 – 12:00</t>
+  </si>
+  <si>
+    <t>개발 진행</t>
+  </si>
+  <si>
+    <t>13:00 – 14:30</t>
+  </si>
+  <si>
+    <r>
+      <t>배포</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 및 </t>
     </r>
     <r>
       <rPr>
@@ -1237,180 +1544,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>Git branch ·</t>
-  </si>
-  <si>
-    <r>
-      <t>기획과</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B2E3A"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B2E3A"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>설계</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B2E3A"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B2E3A"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수업</t>
-    </r>
-  </si>
-  <si>
-    <t>프로젝트 기획과 설계</t>
-  </si>
-  <si>
-    <r>
-      <t>팀</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>명세서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>작성</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>방법</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>안내</t>
-    </r>
-  </si>
-  <si>
-    <t>13:00 – 16:00</t>
-  </si>
-  <si>
-    <t>서비스 개발 요청 문서(RFP) 배포</t>
-  </si>
-  <si>
-    <r>
-      <t>팀별 강사</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B2E3A"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B2E3A"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>미팅</t>
-    </r>
-  </si>
-  <si>
-    <t>16:00 – 17:00</t>
-  </si>
-  <si>
-    <r>
-      <t>개발</t>
+      <t>발표</t>
     </r>
     <r>
       <rPr>
@@ -1429,126 +1563,28 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>진행</t>
-    </r>
-  </si>
-  <si>
-    <t>-  github 신규 계정 필요)</t>
-  </si>
-  <si>
-    <r>
-      <t>팀</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>프로젝트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>개발</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">시작, </t>
-    </r>
-  </si>
-  <si>
-    <t>17:00 – 18:00</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF44607A"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>거버넌스</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF44607A"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF44607A"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>특강</t>
-    </r>
-  </si>
-  <si>
-    <t>7/15 (수) (day4)</t>
-  </si>
-  <si>
-    <t>11:00 – 12:00</t>
-  </si>
-  <si>
-    <t>Unit 테스트 수업</t>
-  </si>
-  <si>
-    <t>unit test 학습 및 실습</t>
-  </si>
-  <si>
-    <r>
-      <t>팀</t>
+      <t>준비</t>
+    </r>
+  </si>
+  <si>
+    <t>서비스 배포, 발표 준비(with AI)</t>
+  </si>
+  <si>
+    <t>14:30 – 17:00</t>
+  </si>
+  <si>
+    <r>
+      <t>발표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -1557,109 +1593,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B2E3A"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>스크럼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B2E3A"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B2E3A"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>회의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B2E3A"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> + OpenAI API 키 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B2E3A"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>배포</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B2E3A"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 및 사용 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B2E3A"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>안내</t>
-    </r>
-  </si>
-  <si>
-    <t>13:30 – 17:00</t>
-  </si>
-  <si>
-    <t>팀 프로젝트 개발 진행</t>
-  </si>
-  <si>
-    <t>현직개발자 특강</t>
-  </si>
-  <si>
-    <t>09:30 – 10:00</t>
-  </si>
-  <si>
-    <t>팀 스크럼 회의</t>
-  </si>
-  <si>
-    <t>비전공: https://localhub-sc16-1.netlify.app/</t>
-  </si>
-  <si>
-    <t>10:00 – 12:00</t>
-  </si>
-  <si>
-    <t>개발 진행</t>
-  </si>
-  <si>
-    <t>13:00 – 14:30</t>
-  </si>
-  <si>
-    <r>
-      <t>배포</t>
+      <t>진행</t>
     </r>
     <r>
       <rPr>
@@ -1678,7 +1612,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>발표</t>
+      <t>우수작</t>
     </r>
     <r>
       <rPr>
@@ -1697,18 +1631,15 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>준비</t>
-    </r>
-  </si>
-  <si>
-    <t>서비스 배포, 발표 준비(with AI)</t>
-  </si>
-  <si>
-    <t>14:30 – 17:00</t>
-  </si>
-  <si>
-    <r>
-      <t>발표</t>
+      <t>선정</t>
+    </r>
+  </si>
+  <si>
+    <t>17:00 – 17:30</t>
+  </si>
+  <si>
+    <r>
+      <t>전체</t>
     </r>
     <r>
       <rPr>
@@ -1727,7 +1658,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>진행</t>
+      <t>회고</t>
     </r>
     <r>
       <rPr>
@@ -1737,7 +1668,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 및 </t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -1746,71 +1677,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>우수작</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B2E3A"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B2E3A"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>선정</t>
-    </r>
-  </si>
-  <si>
-    <t>17:00 – 17:30</t>
-  </si>
-  <si>
-    <r>
-      <t>전체</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B2E3A"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B2E3A"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>회고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B2E3A"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B2E3A"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>진행</t>
     </r>
   </si>
@@ -1902,78 +1768,15 @@
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <t>AI 온보딩 소개, 바이브 코딩 소개, 
-개발 절차(기획-구현 - 배포)  소개, 프로젝트 안내 및 산출물 예시</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
     <t>오전 라이브 방송</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>프로젝트명</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>: I AM (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>아이엠</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">
--내가 좋아하는 주제(나 자신, 포트폴리오, 취미, 반려동물, 등)를 매력적으로 소개하는 웹 서비스
--자신이 보여주고 싶은 내용을 AI를 활용하여 화면을 구현하고, 그 과정에서 개발의 재미와 성취를 느끼기</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
     <t>전공 : https://check-sc16-mpa.netlify.app/</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>비전공: https://check-sc16-spa.netlify.app/</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>개발 환경 구성 (git vscode, python, node)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>Git 기초 안내 및 실습
-git 의 기본적인 이론과 기초 명령어 중 commit 까지 진행 
-(Push 관련 내용은 2일차에 준비되어 있습니다.)</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
@@ -1998,10 +1801,6 @@
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <t>AI 거버넌스 특강</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">git remote </t>
     </r>
@@ -2014,55 +1813,6 @@
         <charset val="129"/>
       </rPr>
       <t>수업 (clone, push)</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">CLI &amp; Git </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>기본</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수업 (add, commit)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-(git bash  터미널, vscode 터미널)</t>
     </r>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
@@ -2094,22 +1844,6 @@
 * CLI 수업의 경우 강사님들의 판단아래 진행해주시면 됩니다. 
  - 비전공의 경우 필수로 진행하는 것을 추천드립니다.
 * 교안을 따라하면 실습이 가능하며 별도로 준비한 git/cli 실습자료는 없습니다. </t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">git remote / reset, revert </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B2E3A"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>수업</t>
     </r>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
@@ -4914,41 +4648,6 @@
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">( Copilot  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B2E3A"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>무료</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B2E3A"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B2E3A"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>티어</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">파이썬,  vscode, node 설치 가이드
 Git 설치 및 git 환경 설정 가이드 </t>
     <phoneticPr fontId="17" type="noConversion"/>
@@ -6871,77 +6570,10 @@
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">* 발표 진행시 Webex 화면 공유를 활용해주세요. </t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
     <t>https://github.com/mulcamp-ed/ai-onboarding/tree/master/Day05</t>
   </si>
   <si>
     <t>render 서비스 배포 가이드 문서</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B2E3A"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>첫</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B2E3A"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B2E3A"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>가입자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B2E3A"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B2E3A"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>크레딧</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF2B2E3A"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
@@ -7068,26 +6700,6 @@
   </si>
   <si>
     <t>Webex</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">* 발표 진행시 Webex를 활용해주세요.
-* 우수작 선정은 기준은 주어지며 강사님들께서 선정해주시면 되겠습니다. (google Form 활용, 기타 방식)
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>- 우수팀에게는 기프티콘 지급 예정 (커피 X)</t>
-    </r>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
@@ -8335,6 +7947,495 @@
       </rPr>
       <t>을 3.11로 환경변수 설정해줘야 정상적으로 배포 및 Netlify 와 연동이 되기 때문에 혹시나 배포에 어려움이 있는 팀은 해당 부분을 우선적으로 확인해주시면 되겠습니다.</t>
     </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">* 발표 진행시 Webex를 활용해주세요.
+* 우수작 선정은 기준은 주어지며 강사님들께서 선정해주시면 되겠습니다.
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- 우수팀에게는 기프티콘 지급 예정 (커피 X)</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>* 발표 진행시 Webex 화면 공유를 활용해주세요. 
+* 우수작 선정은 기준은 주어지며 강사님들께서 선정해주시면 되겠습니다.</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>17:00 - 18:00</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI 인사이트 특강</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>라이브 방송</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI 온보딩 소개
+바이브 코딩 소개
+개발 절차(기획-구현 - 배포)  소개
+프로젝트 안내 및 산출물 예시</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>9:30 ~ 11:00</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>11:00 – 12:00</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>13:00 – 14:00</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>환경 셋팅</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CLI &amp; Git </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기본</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+(git bash  터미널, vscode 터미널)</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">git branch </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(git bash  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>터미널</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, vscode </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>터미널</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">선택기수 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>프로젝트 체험</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 없음</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>09:30 – 10:30</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:30 – 12:00</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>13:00 – 16:00</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개발 진행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+( Copilot  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>무료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>티어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>첫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가입자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>크레딧</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  
+-  github </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>신규</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>계정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>필요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>거버넌스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>특강</t>
+    </r>
+  </si>
+  <si>
+    <t>메토링 소개</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>싸피셜 소개</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>슬기로운 싸피생활</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>09:30 - 10:00</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:00 - 10:30</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:30 - 11:00</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">git remote / reset, revert </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF2B2E3A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+(git bash  터미널, vscode 터미널)</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>9:30 - 11:00</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>17:00 – 18:00</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
@@ -8342,7 +8443,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="47">
+  <fonts count="50">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8701,6 +8802,26 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2B2E3A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2B2E3A"/>
+      <name val="Malgun Gothic"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -8746,7 +8867,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="74">
+  <borders count="66">
     <border>
       <left/>
       <right/>
@@ -9039,7 +9160,7 @@
       </right>
       <top/>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -9050,20 +9171,20 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom/>
@@ -9073,8 +9194,82 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
       <top/>
       <bottom/>
@@ -9082,12 +9277,62 @@
     </border>
     <border>
       <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom/>
@@ -9097,142 +9342,61 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
@@ -9243,211 +9407,11 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
       <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -9659,6 +9623,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -9668,16 +9697,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="298">
+  <cellXfs count="308">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -9705,30 +9728,12 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -9768,24 +9773,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -9804,764 +9794,833 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="40" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="55" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="60" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="57" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="46" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="51" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="73" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="70" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="59" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="51" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -11002,7 +11061,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2CBD596-7E3B-4236-AC37-387FA1537CFC}">
-  <dimension ref="B1:I65"/>
+  <dimension ref="B1:I69"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="4" max="4" width="34.08203125" customWidth="1"/>
@@ -11015,1077 +11074,1126 @@
   <sheetData>
     <row r="1" spans="2:9" ht="17.5" thickBot="1"/>
     <row r="2" spans="2:9" ht="17.5" thickBot="1">
-      <c r="B2" s="46"/>
-      <c r="C2" s="47" t="s">
+      <c r="B2" s="32"/>
+      <c r="C2" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="47" t="s">
+      <c r="D2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="47" t="s">
+      <c r="E2" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="47" t="s">
+      <c r="F2" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="47" t="s">
+      <c r="G2" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="H2" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="I2" s="82" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" ht="68.5" customHeight="1">
+      <c r="B3" s="154" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3" s="246" t="s">
+        <v>206</v>
+      </c>
+      <c r="D3" s="238" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="103" t="s">
+        <v>185</v>
+      </c>
+      <c r="F3" s="239" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="242" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3" s="103"/>
+      <c r="I3" s="36"/>
+    </row>
+    <row r="4" spans="2:9" ht="17.649999999999999" customHeight="1">
+      <c r="B4" s="155"/>
+      <c r="C4" s="181"/>
+      <c r="D4" s="167"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="240"/>
+      <c r="G4" s="143"/>
+      <c r="H4" s="146"/>
+      <c r="I4" s="243"/>
+    </row>
+    <row r="5" spans="2:9" ht="17.649999999999999" customHeight="1">
+      <c r="B5" s="155"/>
+      <c r="C5" s="181"/>
+      <c r="D5" s="167"/>
+      <c r="E5" s="146"/>
+      <c r="F5" s="240"/>
+      <c r="G5" s="143"/>
+      <c r="H5" s="146"/>
+      <c r="I5" s="244"/>
+    </row>
+    <row r="6" spans="2:9">
+      <c r="B6" s="155"/>
+      <c r="C6" s="181"/>
+      <c r="D6" s="167"/>
+      <c r="E6" s="146"/>
+      <c r="F6" s="240"/>
+      <c r="G6" s="143"/>
+      <c r="H6" s="146"/>
+      <c r="I6" s="244"/>
+    </row>
+    <row r="7" spans="2:9">
+      <c r="B7" s="155"/>
+      <c r="C7" s="182"/>
+      <c r="D7" s="168"/>
+      <c r="E7" s="104"/>
+      <c r="F7" s="241"/>
+      <c r="G7" s="106"/>
+      <c r="H7" s="104"/>
+      <c r="I7" s="245"/>
+    </row>
+    <row r="8" spans="2:9" ht="53.15" customHeight="1">
+      <c r="B8" s="155"/>
+      <c r="C8" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="235"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="68" t="s">
+        <v>89</v>
+      </c>
+      <c r="H8" s="73"/>
+      <c r="I8" s="122" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="17.649999999999999" customHeight="1">
+      <c r="B9" s="155"/>
+      <c r="C9" s="180" t="s">
+        <v>188</v>
+      </c>
+      <c r="D9" s="166" t="s">
+        <v>189</v>
+      </c>
+      <c r="E9" s="105" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="306" t="s">
+        <v>149</v>
+      </c>
+      <c r="G9" s="300" t="s">
+        <v>96</v>
+      </c>
+      <c r="H9" s="139" t="s">
+        <v>90</v>
+      </c>
+      <c r="I9" s="123"/>
+    </row>
+    <row r="10" spans="2:9" ht="385.5" customHeight="1">
+      <c r="B10" s="155"/>
+      <c r="C10" s="182"/>
+      <c r="D10" s="183"/>
+      <c r="E10" s="106"/>
+      <c r="F10" s="307"/>
+      <c r="G10" s="301"/>
+      <c r="H10" s="140"/>
+      <c r="I10" s="123"/>
+    </row>
+    <row r="11" spans="2:9" ht="17.649999999999999" customHeight="1">
+      <c r="B11" s="155"/>
+      <c r="C11" s="180" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="189" t="s">
+        <v>190</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="145" t="s">
+        <v>147</v>
+      </c>
+      <c r="G11" s="300" t="s">
+        <v>95</v>
+      </c>
+      <c r="H11" s="147" t="s">
+        <v>93</v>
+      </c>
+      <c r="I11" s="123"/>
+    </row>
+    <row r="12" spans="2:9" ht="17.649999999999999" customHeight="1">
+      <c r="B12" s="155"/>
+      <c r="C12" s="181"/>
+      <c r="D12" s="190"/>
+      <c r="E12" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F12" s="146"/>
+      <c r="G12" s="302"/>
+      <c r="H12" s="148"/>
+      <c r="I12" s="123"/>
+    </row>
+    <row r="13" spans="2:9" ht="124" customHeight="1">
+      <c r="B13" s="155"/>
+      <c r="C13" s="182"/>
+      <c r="D13" s="191"/>
+      <c r="E13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="104"/>
+      <c r="G13" s="301"/>
+      <c r="H13" s="149"/>
+      <c r="I13" s="123"/>
+    </row>
+    <row r="14" spans="2:9" ht="17.649999999999999" customHeight="1">
+      <c r="B14" s="155"/>
+      <c r="C14" s="180" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="105" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="303" t="s">
         <v>99</v>
       </c>
-      <c r="H2" s="47" t="s">
+      <c r="H14" s="152" t="s">
+        <v>92</v>
+      </c>
+      <c r="I14" s="123"/>
+    </row>
+    <row r="15" spans="2:9" ht="35.15" customHeight="1">
+      <c r="B15" s="155"/>
+      <c r="C15" s="181"/>
+      <c r="D15" s="143"/>
+      <c r="E15" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G15" s="304"/>
+      <c r="H15" s="153"/>
+      <c r="I15" s="123"/>
+    </row>
+    <row r="16" spans="2:9">
+      <c r="B16" s="155"/>
+      <c r="C16" s="181"/>
+      <c r="D16" s="143"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="304"/>
+      <c r="H16" s="153"/>
+      <c r="I16" s="123"/>
+    </row>
+    <row r="17" spans="2:9" ht="51">
+      <c r="B17" s="155"/>
+      <c r="C17" s="181"/>
+      <c r="D17" s="143"/>
+      <c r="E17" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="304"/>
+      <c r="H17" s="153"/>
+      <c r="I17" s="123"/>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" s="155"/>
+      <c r="C18" s="181"/>
+      <c r="D18" s="143"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="304"/>
+      <c r="H18" s="153"/>
+      <c r="I18" s="123"/>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19" s="155"/>
+      <c r="C19" s="181"/>
+      <c r="D19" s="143"/>
+      <c r="E19" s="88" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="304"/>
+      <c r="H19" s="153"/>
+      <c r="I19" s="123"/>
+    </row>
+    <row r="20" spans="2:9">
+      <c r="B20" s="155"/>
+      <c r="C20" s="181"/>
+      <c r="D20" s="143"/>
+      <c r="E20" s="88" t="s">
+        <v>87</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="304"/>
+      <c r="H20" s="153"/>
+      <c r="I20" s="123"/>
+    </row>
+    <row r="21" spans="2:9" ht="84.4" customHeight="1">
+      <c r="B21" s="155"/>
+      <c r="C21" s="182"/>
+      <c r="D21" s="106"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="305"/>
+      <c r="H21" s="237"/>
+      <c r="I21" s="124"/>
+    </row>
+    <row r="22" spans="2:9" ht="34.5" thickBot="1">
+      <c r="B22" s="156"/>
+      <c r="C22" s="227" t="s">
+        <v>182</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E22" s="247" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" s="248"/>
+      <c r="G22" s="233" t="s">
+        <v>184</v>
+      </c>
+      <c r="H22" s="233"/>
+      <c r="I22" s="234"/>
+    </row>
+    <row r="23" spans="2:9" ht="17.5" thickBot="1">
+      <c r="B23" s="228"/>
+      <c r="C23" s="229"/>
+      <c r="D23" s="230"/>
+      <c r="E23" s="231"/>
+      <c r="F23" s="232"/>
+      <c r="G23" s="69"/>
+      <c r="H23" s="74"/>
+      <c r="I23" s="71"/>
+    </row>
+    <row r="24" spans="2:9" ht="32.15" customHeight="1">
+      <c r="B24" s="157" t="s">
+        <v>143</v>
+      </c>
+      <c r="C24" s="176" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" s="198" t="s">
+        <v>205</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="103" t="s">
+        <v>150</v>
+      </c>
+      <c r="G24" s="129" t="s">
+        <v>110</v>
+      </c>
+      <c r="H24" s="103" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="104" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" ht="34">
-      <c r="B3" s="193" t="s">
+      <c r="I24" s="113" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" ht="70.75" customHeight="1">
+      <c r="B25" s="158"/>
+      <c r="C25" s="162"/>
+      <c r="D25" s="199"/>
+      <c r="E25" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="104"/>
+      <c r="G25" s="130"/>
+      <c r="H25" s="104"/>
+      <c r="I25" s="116"/>
+    </row>
+    <row r="26" spans="2:9" ht="35.15" customHeight="1">
+      <c r="B26" s="158"/>
+      <c r="C26" s="161" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F26" s="100" t="s">
+        <v>152</v>
+      </c>
+      <c r="G26" s="125" t="s">
+        <v>100</v>
+      </c>
+      <c r="H26" s="187" t="s">
+        <v>153</v>
+      </c>
+      <c r="I26" s="116"/>
+    </row>
+    <row r="27" spans="2:9">
+      <c r="B27" s="158"/>
+      <c r="C27" s="165"/>
+      <c r="D27" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F27" s="101"/>
+      <c r="G27" s="186"/>
+      <c r="H27" s="112"/>
+      <c r="I27" s="116"/>
+    </row>
+    <row r="28" spans="2:9">
+      <c r="B28" s="158"/>
+      <c r="C28" s="165"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F28" s="101"/>
+      <c r="G28" s="186"/>
+      <c r="H28" s="112"/>
+      <c r="I28" s="116"/>
+    </row>
+    <row r="29" spans="2:9">
+      <c r="B29" s="158"/>
+      <c r="C29" s="165"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F29" s="101"/>
+      <c r="G29" s="186"/>
+      <c r="H29" s="112"/>
+      <c r="I29" s="116"/>
+    </row>
+    <row r="30" spans="2:9">
+      <c r="B30" s="158"/>
+      <c r="C30" s="165"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="101"/>
+      <c r="G30" s="186"/>
+      <c r="H30" s="112"/>
+      <c r="I30" s="116"/>
+    </row>
+    <row r="31" spans="2:9">
+      <c r="B31" s="158"/>
+      <c r="C31" s="165"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="88" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="101"/>
+      <c r="G31" s="186"/>
+      <c r="H31" s="112"/>
+      <c r="I31" s="116"/>
+    </row>
+    <row r="32" spans="2:9">
+      <c r="B32" s="158"/>
+      <c r="C32" s="165"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="88" t="s">
+        <v>87</v>
+      </c>
+      <c r="F32" s="101"/>
+      <c r="G32" s="186"/>
+      <c r="H32" s="112"/>
+      <c r="I32" s="116"/>
+    </row>
+    <row r="33" spans="2:9">
+      <c r="B33" s="158"/>
+      <c r="C33" s="162"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="102"/>
+      <c r="G33" s="126"/>
+      <c r="H33" s="111"/>
+      <c r="I33" s="116"/>
+    </row>
+    <row r="34" spans="2:9">
+      <c r="B34" s="158"/>
+      <c r="C34" s="161" t="s">
+        <v>35</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F34" s="184" t="s">
+        <v>151</v>
+      </c>
+      <c r="G34" s="120" t="s">
+        <v>103</v>
+      </c>
+      <c r="H34" s="110" t="s">
+        <v>106</v>
+      </c>
+      <c r="I34" s="116"/>
+    </row>
+    <row r="35" spans="2:9" ht="123.4" customHeight="1">
+      <c r="B35" s="158"/>
+      <c r="C35" s="162"/>
+      <c r="D35" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="F35" s="185"/>
+      <c r="G35" s="121"/>
+      <c r="H35" s="111"/>
+      <c r="I35" s="116"/>
+    </row>
+    <row r="36" spans="2:9" ht="141" customHeight="1">
+      <c r="B36" s="158"/>
+      <c r="C36" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="E36" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="F36" s="7"/>
+      <c r="G36" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="H36" s="75" t="s">
+        <v>107</v>
+      </c>
+      <c r="I36" s="117"/>
+    </row>
+    <row r="37" spans="2:9" ht="34.5" thickBot="1">
+      <c r="B37" s="159"/>
+      <c r="C37" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="D37" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="E37" s="107" t="s">
+        <v>47</v>
+      </c>
+      <c r="F37" s="280"/>
+      <c r="G37" s="65"/>
+      <c r="H37" s="65"/>
+      <c r="I37" s="84"/>
+    </row>
+    <row r="38" spans="2:9" ht="17.5" thickBot="1">
+      <c r="B38" s="60"/>
+      <c r="C38" s="61"/>
+      <c r="D38" s="62"/>
+      <c r="E38" s="63"/>
+      <c r="F38" s="66"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="76"/>
+      <c r="I38" s="71"/>
+    </row>
+    <row r="39" spans="2:9" ht="34">
+      <c r="B39" s="157" t="s">
+        <v>48</v>
+      </c>
+      <c r="C39" s="283" t="s">
+        <v>194</v>
+      </c>
+      <c r="D39" s="277" t="s">
+        <v>192</v>
+      </c>
+      <c r="E39" s="279" t="s">
+        <v>193</v>
+      </c>
+      <c r="F39" s="278"/>
+      <c r="G39" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="H39" s="272"/>
+      <c r="I39" s="113" t="s">
         <v>163</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="220" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="221"/>
-      <c r="G3" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="H3" s="55"/>
-      <c r="I3" s="52"/>
-    </row>
-    <row r="4" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B4" s="194"/>
-      <c r="C4" s="163" t="s">
+    </row>
+    <row r="40" spans="2:9" ht="149.15" customHeight="1">
+      <c r="B40" s="158"/>
+      <c r="C40" s="282" t="s">
+        <v>195</v>
+      </c>
+      <c r="D40" s="274" t="s">
+        <v>191</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="F40" s="281" t="s">
+        <v>154</v>
+      </c>
+      <c r="G40" s="275" t="s">
+        <v>120</v>
+      </c>
+      <c r="H40" s="276" t="s">
+        <v>122</v>
+      </c>
+      <c r="I40" s="114"/>
+    </row>
+    <row r="41" spans="2:9" ht="34" customHeight="1">
+      <c r="B41" s="158"/>
+      <c r="C41" s="270"/>
+      <c r="D41" s="273" t="s">
+        <v>50</v>
+      </c>
+      <c r="E41" s="92" t="s">
+        <v>51</v>
+      </c>
+      <c r="F41" s="143" t="s">
+        <v>157</v>
+      </c>
+      <c r="G41" s="160" t="s">
+        <v>121</v>
+      </c>
+      <c r="H41" s="133" t="s">
+        <v>123</v>
+      </c>
+      <c r="I41" s="114"/>
+    </row>
+    <row r="42" spans="2:9" ht="100" customHeight="1">
+      <c r="B42" s="158"/>
+      <c r="C42" s="271"/>
+      <c r="D42" s="179"/>
+      <c r="E42" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="F42" s="106"/>
+      <c r="G42" s="132"/>
+      <c r="H42" s="128"/>
+      <c r="I42" s="114"/>
+    </row>
+    <row r="43" spans="2:9">
+      <c r="B43" s="158"/>
+      <c r="C43" s="161" t="s">
+        <v>196</v>
+      </c>
+      <c r="D43" s="172" t="s">
+        <v>54</v>
+      </c>
+      <c r="E43" s="100" t="s">
+        <v>116</v>
+      </c>
+      <c r="F43" s="105" t="s">
+        <v>156</v>
+      </c>
+      <c r="G43" s="131" t="s">
+        <v>117</v>
+      </c>
+      <c r="H43" s="133" t="s">
+        <v>124</v>
+      </c>
+      <c r="I43" s="114"/>
+    </row>
+    <row r="44" spans="2:9" ht="113.65" customHeight="1">
+      <c r="B44" s="158"/>
+      <c r="C44" s="165"/>
+      <c r="D44" s="173"/>
+      <c r="E44" s="102"/>
+      <c r="F44" s="106"/>
+      <c r="G44" s="132"/>
+      <c r="H44" s="133"/>
+      <c r="I44" s="114"/>
+    </row>
+    <row r="45" spans="2:9">
+      <c r="B45" s="158"/>
+      <c r="C45" s="165"/>
+      <c r="D45" s="163" t="s">
+        <v>55</v>
+      </c>
+      <c r="E45" s="105" t="s">
+        <v>155</v>
+      </c>
+      <c r="F45" s="174"/>
+      <c r="G45" s="118" t="s">
+        <v>167</v>
+      </c>
+      <c r="H45" s="133"/>
+      <c r="I45" s="114"/>
+    </row>
+    <row r="46" spans="2:9" ht="317.64999999999998" customHeight="1">
+      <c r="B46" s="158"/>
+      <c r="C46" s="162"/>
+      <c r="D46" s="164"/>
+      <c r="E46" s="106"/>
+      <c r="F46" s="175"/>
+      <c r="G46" s="119"/>
+      <c r="H46" s="128"/>
+      <c r="I46" s="114"/>
+    </row>
+    <row r="47" spans="2:9" ht="82" customHeight="1">
+      <c r="B47" s="158"/>
+      <c r="C47" s="161" t="s">
+        <v>56</v>
+      </c>
+      <c r="D47" s="284" t="s">
+        <v>197</v>
+      </c>
+      <c r="E47" s="166" t="s">
+        <v>58</v>
+      </c>
+      <c r="F47" s="110" t="s">
+        <v>158</v>
+      </c>
+      <c r="G47" s="134" t="s">
+        <v>176</v>
+      </c>
+      <c r="H47" s="137"/>
+      <c r="I47" s="114"/>
+    </row>
+    <row r="48" spans="2:9">
+      <c r="B48" s="158"/>
+      <c r="C48" s="165"/>
+      <c r="D48" s="285"/>
+      <c r="E48" s="167"/>
+      <c r="F48" s="112"/>
+      <c r="G48" s="135"/>
+      <c r="H48" s="137"/>
+      <c r="I48" s="114"/>
+    </row>
+    <row r="49" spans="2:9">
+      <c r="B49" s="158"/>
+      <c r="C49" s="165"/>
+      <c r="D49" s="285"/>
+      <c r="E49" s="167"/>
+      <c r="F49" s="112"/>
+      <c r="G49" s="135"/>
+      <c r="H49" s="137"/>
+      <c r="I49" s="114"/>
+    </row>
+    <row r="50" spans="2:9">
+      <c r="B50" s="158"/>
+      <c r="C50" s="165"/>
+      <c r="D50" s="285"/>
+      <c r="E50" s="167"/>
+      <c r="F50" s="112"/>
+      <c r="G50" s="135"/>
+      <c r="H50" s="137"/>
+      <c r="I50" s="114"/>
+    </row>
+    <row r="51" spans="2:9">
+      <c r="B51" s="158"/>
+      <c r="C51" s="165"/>
+      <c r="D51" s="285"/>
+      <c r="E51" s="167"/>
+      <c r="F51" s="112"/>
+      <c r="G51" s="135"/>
+      <c r="H51" s="137"/>
+      <c r="I51" s="114"/>
+    </row>
+    <row r="52" spans="2:9" ht="317.5" customHeight="1" thickBot="1">
+      <c r="B52" s="158"/>
+      <c r="C52" s="162"/>
+      <c r="D52" s="286"/>
+      <c r="E52" s="168"/>
+      <c r="F52" s="111"/>
+      <c r="G52" s="136"/>
+      <c r="H52" s="138"/>
+      <c r="I52" s="115"/>
+    </row>
+    <row r="53" spans="2:9" ht="34.5" thickBot="1">
+      <c r="B53" s="159"/>
+      <c r="C53" s="91" t="s">
+        <v>207</v>
+      </c>
+      <c r="D53" s="86" t="s">
+        <v>198</v>
+      </c>
+      <c r="E53" s="169" t="s">
+        <v>47</v>
+      </c>
+      <c r="F53" s="170"/>
+      <c r="G53" s="170"/>
+      <c r="H53" s="170"/>
+      <c r="I53" s="171"/>
+    </row>
+    <row r="54" spans="2:9" ht="17.5" thickBot="1">
+      <c r="B54" s="296"/>
+      <c r="C54" s="298"/>
+      <c r="D54" s="230"/>
+      <c r="E54" s="231"/>
+      <c r="F54" s="232"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="76"/>
+      <c r="I54" s="299"/>
+    </row>
+    <row r="55" spans="2:9" ht="29.5" customHeight="1">
+      <c r="B55" s="157" t="s">
+        <v>60</v>
+      </c>
+      <c r="C55" s="91" t="s">
+        <v>202</v>
+      </c>
+      <c r="D55" s="297" t="s">
+        <v>201</v>
+      </c>
+      <c r="E55" s="288" t="s">
+        <v>193</v>
+      </c>
+      <c r="F55" s="289"/>
+      <c r="G55" s="292" t="s">
+        <v>193</v>
+      </c>
+      <c r="H55" s="293"/>
+      <c r="I55" s="116" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" ht="29.5" customHeight="1">
+      <c r="B56" s="158"/>
+      <c r="C56" s="91" t="s">
+        <v>203</v>
+      </c>
+      <c r="D56" s="287" t="s">
+        <v>200</v>
+      </c>
+      <c r="E56" s="288"/>
+      <c r="F56" s="289"/>
+      <c r="G56" s="292"/>
+      <c r="H56" s="293"/>
+      <c r="I56" s="116"/>
+    </row>
+    <row r="57" spans="2:9" ht="34">
+      <c r="B57" s="158"/>
+      <c r="C57" s="91" t="s">
+        <v>204</v>
+      </c>
+      <c r="D57" s="287" t="s">
+        <v>199</v>
+      </c>
+      <c r="E57" s="290"/>
+      <c r="F57" s="291"/>
+      <c r="G57" s="294"/>
+      <c r="H57" s="295"/>
+      <c r="I57" s="116"/>
+    </row>
+    <row r="58" spans="2:9" ht="94.75" customHeight="1">
+      <c r="B58" s="158"/>
+      <c r="C58" s="91" t="s">
+        <v>61</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E58" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G58" s="90" t="s">
+        <v>129</v>
+      </c>
+      <c r="H58" s="93" t="s">
+        <v>126</v>
+      </c>
+      <c r="I58" s="116"/>
+    </row>
+    <row r="59" spans="2:9">
+      <c r="B59" s="158"/>
+      <c r="C59" s="161" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="136" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="150" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="121" t="s">
-        <v>101</v>
-      </c>
-      <c r="H4" s="198"/>
-      <c r="I4" s="225"/>
-    </row>
-    <row r="5" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B5" s="194"/>
-      <c r="C5" s="164"/>
-      <c r="D5" s="137"/>
-      <c r="E5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="167"/>
-      <c r="G5" s="196"/>
-      <c r="H5" s="199"/>
-      <c r="I5" s="223"/>
-    </row>
-    <row r="6" spans="2:9">
-      <c r="B6" s="194"/>
-      <c r="C6" s="164"/>
-      <c r="D6" s="137"/>
-      <c r="E6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="167"/>
-      <c r="G6" s="196"/>
-      <c r="H6" s="199"/>
-      <c r="I6" s="223"/>
-    </row>
-    <row r="7" spans="2:9">
-      <c r="B7" s="194"/>
-      <c r="C7" s="165"/>
-      <c r="D7" s="166"/>
-      <c r="E7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="168"/>
-      <c r="G7" s="197"/>
-      <c r="H7" s="200"/>
-      <c r="I7" s="226"/>
-    </row>
-    <row r="8" spans="2:9" ht="53.15" customHeight="1">
-      <c r="B8" s="194"/>
-      <c r="C8" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="45"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="89" t="s">
-        <v>107</v>
-      </c>
-      <c r="H8" s="95"/>
-      <c r="I8" s="222" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B9" s="194"/>
-      <c r="C9" s="163" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="179" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="150" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="239" t="s">
+      <c r="D59" s="163" t="s">
+        <v>64</v>
+      </c>
+      <c r="E59" s="110" t="s">
+        <v>168</v>
+      </c>
+      <c r="F59" s="110" t="s">
+        <v>159</v>
+      </c>
+      <c r="G59" s="125" t="s">
+        <v>169</v>
+      </c>
+      <c r="H59" s="127" t="s">
+        <v>160</v>
+      </c>
+      <c r="I59" s="116"/>
+    </row>
+    <row r="60" spans="2:9" ht="207" customHeight="1">
+      <c r="B60" s="158"/>
+      <c r="C60" s="162"/>
+      <c r="D60" s="164"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="126"/>
+      <c r="H60" s="128"/>
+      <c r="I60" s="116"/>
+    </row>
+    <row r="61" spans="2:9" ht="181.75" customHeight="1">
+      <c r="B61" s="158"/>
+      <c r="C61" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="D61" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F61" s="7"/>
+      <c r="G61" s="67" t="s">
+        <v>166</v>
+      </c>
+      <c r="H61" s="77"/>
+      <c r="I61" s="117"/>
+    </row>
+    <row r="62" spans="2:9" ht="34.5" thickBot="1">
+      <c r="B62" s="159"/>
+      <c r="C62" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D62" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="E62" s="107" t="s">
+        <v>47</v>
+      </c>
+      <c r="F62" s="108"/>
+      <c r="G62" s="108"/>
+      <c r="H62" s="108"/>
+      <c r="I62" s="109"/>
+    </row>
+    <row r="63" spans="2:9" ht="17.5" thickBot="1">
+      <c r="B63" s="56"/>
+      <c r="C63" s="57"/>
+      <c r="D63" s="58"/>
+      <c r="E63" s="59"/>
+      <c r="F63" s="59"/>
+      <c r="G63" s="70"/>
+      <c r="H63" s="76"/>
+      <c r="I63" s="72"/>
+    </row>
+    <row r="64" spans="2:9" ht="68">
+      <c r="B64" s="94" t="s">
+        <v>134</v>
+      </c>
+      <c r="C64" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="D64" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="E64" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="F64" s="50"/>
+      <c r="G64" s="50" t="s">
+        <v>148</v>
+      </c>
+      <c r="H64" s="78"/>
+      <c r="I64" s="113" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="65" spans="2:9" ht="228.5" customHeight="1">
+      <c r="B65" s="95"/>
+      <c r="C65" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D65" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="E65" s="22"/>
+      <c r="F65" s="51"/>
+      <c r="G65" s="51" t="s">
+        <v>174</v>
+      </c>
+      <c r="H65" s="79"/>
+      <c r="I65" s="116"/>
+    </row>
+    <row r="66" spans="2:9" ht="170">
+      <c r="B66" s="95"/>
+      <c r="C66" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="D66" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="E66" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F66" s="83" t="s">
+        <v>170</v>
+      </c>
+      <c r="G66" s="64" t="s">
+        <v>165</v>
+      </c>
+      <c r="H66" s="85" t="s">
+        <v>173</v>
+      </c>
+      <c r="I66" s="116"/>
+    </row>
+    <row r="67" spans="2:9" ht="70.5" customHeight="1">
+      <c r="B67" s="95"/>
+      <c r="C67" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D67" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="E67" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="G9" s="207" t="s">
-        <v>117</v>
-      </c>
-      <c r="H9" s="234" t="s">
-        <v>108</v>
-      </c>
-      <c r="I9" s="223"/>
-    </row>
-    <row r="10" spans="2:9" ht="385.5" customHeight="1">
-      <c r="B10" s="194"/>
-      <c r="C10" s="178"/>
-      <c r="D10" s="180"/>
-      <c r="E10" s="151"/>
-      <c r="F10" s="240"/>
-      <c r="G10" s="209"/>
-      <c r="H10" s="235"/>
-      <c r="I10" s="223"/>
-    </row>
-    <row r="11" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B11" s="194"/>
-      <c r="C11" s="163" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="144" t="s">
-        <v>168</v>
-      </c>
-      <c r="G11" s="207" t="s">
-        <v>115</v>
-      </c>
-      <c r="H11" s="211" t="s">
-        <v>111</v>
-      </c>
-      <c r="I11" s="223"/>
-    </row>
-    <row r="12" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B12" s="194"/>
-      <c r="C12" s="164"/>
-      <c r="D12" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="F12" s="210"/>
-      <c r="G12" s="208"/>
-      <c r="H12" s="212"/>
-      <c r="I12" s="223"/>
-    </row>
-    <row r="13" spans="2:9" ht="124" customHeight="1">
-      <c r="B13" s="194"/>
-      <c r="C13" s="178"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="145"/>
-      <c r="G13" s="209"/>
-      <c r="H13" s="213"/>
-      <c r="I13" s="223"/>
-    </row>
-    <row r="14" spans="2:9" ht="17.649999999999999" customHeight="1">
-      <c r="B14" s="194"/>
-      <c r="C14" s="163" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="150" t="s">
-        <v>97</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G14" s="214" t="s">
-        <v>120</v>
-      </c>
-      <c r="H14" s="217" t="s">
-        <v>110</v>
-      </c>
-      <c r="I14" s="223"/>
-    </row>
-    <row r="15" spans="2:9" ht="35.15" customHeight="1">
-      <c r="B15" s="194"/>
-      <c r="C15" s="164"/>
-      <c r="D15" s="167"/>
-      <c r="E15" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="G15" s="215"/>
-      <c r="H15" s="218"/>
-      <c r="I15" s="223"/>
-    </row>
-    <row r="16" spans="2:9">
-      <c r="B16" s="194"/>
-      <c r="C16" s="164"/>
-      <c r="D16" s="167"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="215"/>
-      <c r="H16" s="218"/>
-      <c r="I16" s="223"/>
-    </row>
-    <row r="17" spans="2:9" ht="51">
-      <c r="B17" s="194"/>
-      <c r="C17" s="164"/>
-      <c r="D17" s="167"/>
-      <c r="E17" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="F17" s="5"/>
-      <c r="G17" s="215"/>
-      <c r="H17" s="218"/>
-      <c r="I17" s="223"/>
-    </row>
-    <row r="18" spans="2:9">
-      <c r="B18" s="194"/>
-      <c r="C18" s="164"/>
-      <c r="D18" s="167"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="215"/>
-      <c r="H18" s="218"/>
-      <c r="I18" s="223"/>
-    </row>
-    <row r="19" spans="2:9">
-      <c r="B19" s="194"/>
-      <c r="C19" s="164"/>
-      <c r="D19" s="167"/>
-      <c r="E19" s="113" t="s">
-        <v>30</v>
-      </c>
-      <c r="F19" s="5"/>
-      <c r="G19" s="215"/>
-      <c r="H19" s="218"/>
-      <c r="I19" s="223"/>
-    </row>
-    <row r="20" spans="2:9">
-      <c r="B20" s="194"/>
-      <c r="C20" s="164"/>
-      <c r="D20" s="167"/>
-      <c r="E20" s="113" t="s">
-        <v>103</v>
-      </c>
-      <c r="F20" s="5"/>
-      <c r="G20" s="215"/>
-      <c r="H20" s="218"/>
-      <c r="I20" s="223"/>
-    </row>
-    <row r="21" spans="2:9" ht="84.4" customHeight="1" thickBot="1">
-      <c r="B21" s="195"/>
-      <c r="C21" s="172"/>
-      <c r="D21" s="206"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="49"/>
-      <c r="G21" s="216"/>
-      <c r="H21" s="219"/>
-      <c r="I21" s="224"/>
-    </row>
-    <row r="22" spans="2:9" ht="17.5" thickBot="1">
-      <c r="B22" s="105"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="90"/>
-      <c r="H22" s="96"/>
-      <c r="I22" s="106"/>
-    </row>
-    <row r="23" spans="2:9" ht="32.15" customHeight="1">
-      <c r="B23" s="190" t="s">
-        <v>164</v>
-      </c>
-      <c r="C23" s="173" t="s">
-        <v>33</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="E23" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="F23" s="175" t="s">
-        <v>172</v>
-      </c>
-      <c r="G23" s="146" t="s">
-        <v>131</v>
-      </c>
-      <c r="H23" s="175" t="s">
-        <v>130</v>
-      </c>
-      <c r="I23" s="169" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" ht="70.75" customHeight="1">
-      <c r="B24" s="191"/>
-      <c r="C24" s="174"/>
-      <c r="D24" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="F24" s="145"/>
-      <c r="G24" s="147"/>
-      <c r="H24" s="145"/>
-      <c r="I24" s="170"/>
-    </row>
-    <row r="25" spans="2:9" ht="35.15" customHeight="1">
-      <c r="B25" s="191"/>
-      <c r="C25" s="176" t="s">
-        <v>37</v>
-      </c>
-      <c r="D25" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F25" s="148" t="s">
-        <v>174</v>
-      </c>
-      <c r="G25" s="183" t="s">
-        <v>121</v>
-      </c>
-      <c r="H25" s="186" t="s">
-        <v>175</v>
-      </c>
-      <c r="I25" s="170"/>
-    </row>
-    <row r="26" spans="2:9">
-      <c r="B26" s="191"/>
-      <c r="C26" s="177"/>
-      <c r="D26" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F26" s="241"/>
-      <c r="G26" s="184"/>
-      <c r="H26" s="187"/>
-      <c r="I26" s="170"/>
-    </row>
-    <row r="27" spans="2:9">
-      <c r="B27" s="191"/>
-      <c r="C27" s="177"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="F27" s="241"/>
-      <c r="G27" s="184"/>
-      <c r="H27" s="187"/>
-      <c r="I27" s="170"/>
-    </row>
-    <row r="28" spans="2:9">
-      <c r="B28" s="191"/>
-      <c r="C28" s="177"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="F28" s="241"/>
-      <c r="G28" s="184"/>
-      <c r="H28" s="187"/>
-      <c r="I28" s="170"/>
-    </row>
-    <row r="29" spans="2:9">
-      <c r="B29" s="191"/>
-      <c r="C29" s="177"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="241"/>
-      <c r="G29" s="184"/>
-      <c r="H29" s="187"/>
-      <c r="I29" s="170"/>
-    </row>
-    <row r="30" spans="2:9">
-      <c r="B30" s="191"/>
-      <c r="C30" s="177"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="113" t="s">
-        <v>30</v>
-      </c>
-      <c r="F30" s="241"/>
-      <c r="G30" s="184"/>
-      <c r="H30" s="187"/>
-      <c r="I30" s="170"/>
-    </row>
-    <row r="31" spans="2:9">
-      <c r="B31" s="191"/>
-      <c r="C31" s="177"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="113" t="s">
-        <v>103</v>
-      </c>
-      <c r="F31" s="241"/>
-      <c r="G31" s="184"/>
-      <c r="H31" s="187"/>
-      <c r="I31" s="170"/>
-    </row>
-    <row r="32" spans="2:9">
-      <c r="B32" s="191"/>
-      <c r="C32" s="174"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="149"/>
-      <c r="G32" s="185"/>
-      <c r="H32" s="135"/>
-      <c r="I32" s="170"/>
-    </row>
-    <row r="33" spans="2:9">
-      <c r="B33" s="191"/>
-      <c r="C33" s="176" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="E33" s="3" t="s">
+      <c r="F67" s="22"/>
+      <c r="G67" s="53" t="s">
+        <v>181</v>
+      </c>
+      <c r="H67" s="80"/>
+      <c r="I67" s="116"/>
+    </row>
+    <row r="68" spans="2:9" ht="85">
+      <c r="B68" s="95"/>
+      <c r="C68" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D68" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="E68" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="F68" s="22"/>
+      <c r="G68" s="54" t="s">
+        <v>137</v>
+      </c>
+      <c r="H68" s="81"/>
+      <c r="I68" s="117"/>
+    </row>
+    <row r="69" spans="2:9" ht="34.5" thickBot="1">
+      <c r="B69" s="96"/>
+      <c r="C69" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D69" s="86" t="s">
+        <v>82</v>
+      </c>
+      <c r="E69" s="97" t="s">
         <v>47</v>
       </c>
-      <c r="F33" s="181" t="s">
-        <v>173</v>
-      </c>
-      <c r="G33" s="247" t="s">
-        <v>124</v>
-      </c>
-      <c r="H33" s="201" t="s">
-        <v>127</v>
-      </c>
-      <c r="I33" s="170"/>
-    </row>
-    <row r="34" spans="2:9" ht="123.4" customHeight="1">
-      <c r="B34" s="191"/>
-      <c r="C34" s="174"/>
-      <c r="D34" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="E34" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="F34" s="182"/>
-      <c r="G34" s="248"/>
-      <c r="H34" s="135"/>
-      <c r="I34" s="170"/>
-    </row>
-    <row r="35" spans="2:9" ht="141" customHeight="1">
-      <c r="B35" s="191"/>
-      <c r="C35" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="D35" s="29" t="s">
-        <v>51</v>
-      </c>
-      <c r="E35" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="F35" s="9"/>
-      <c r="G35" s="62" t="s">
-        <v>129</v>
-      </c>
-      <c r="H35" s="97" t="s">
-        <v>128</v>
-      </c>
-      <c r="I35" s="171"/>
-    </row>
-    <row r="36" spans="2:9" ht="34.5" thickBot="1">
-      <c r="B36" s="192"/>
-      <c r="C36" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="D36" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="E36" s="59" t="s">
-        <v>56</v>
-      </c>
-      <c r="F36" s="60"/>
-      <c r="G36" s="86"/>
-      <c r="H36" s="86"/>
-      <c r="I36" s="108"/>
-    </row>
-    <row r="37" spans="2:9" ht="17.5" thickBot="1">
-      <c r="B37" s="80"/>
-      <c r="C37" s="81"/>
-      <c r="D37" s="82"/>
-      <c r="E37" s="83"/>
-      <c r="F37" s="87"/>
-      <c r="G37" s="91"/>
-      <c r="H37" s="98"/>
-      <c r="I37" s="92"/>
-    </row>
-    <row r="38" spans="2:9">
-      <c r="B38" s="190" t="s">
-        <v>57</v>
-      </c>
-      <c r="C38" s="173" t="s">
-        <v>58</v>
-      </c>
-      <c r="D38" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="E38" s="134" t="s">
-        <v>61</v>
-      </c>
-      <c r="F38" s="175" t="s">
-        <v>176</v>
-      </c>
-      <c r="G38" s="146" t="s">
-        <v>141</v>
-      </c>
-      <c r="H38" s="229" t="s">
-        <v>143</v>
-      </c>
-      <c r="I38" s="169" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="39" spans="2:9" ht="149.15" customHeight="1">
-      <c r="B39" s="191"/>
-      <c r="C39" s="177"/>
-      <c r="D39" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="E39" s="135"/>
-      <c r="F39" s="145"/>
-      <c r="G39" s="147"/>
-      <c r="H39" s="230"/>
-      <c r="I39" s="245"/>
-    </row>
-    <row r="40" spans="2:9">
-      <c r="B40" s="191"/>
-      <c r="C40" s="177"/>
-      <c r="D40" s="119" t="s">
-        <v>62</v>
-      </c>
-      <c r="E40" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F40" s="150" t="s">
-        <v>179</v>
-      </c>
-      <c r="G40" s="121" t="s">
-        <v>142</v>
-      </c>
-      <c r="H40" s="227" t="s">
-        <v>144</v>
-      </c>
-      <c r="I40" s="245"/>
-    </row>
-    <row r="41" spans="2:9" ht="119.65" customHeight="1">
-      <c r="B41" s="191"/>
-      <c r="C41" s="174"/>
-      <c r="D41" s="120"/>
-      <c r="E41" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="F41" s="151"/>
-      <c r="G41" s="122"/>
-      <c r="H41" s="228"/>
-      <c r="I41" s="245"/>
-    </row>
-    <row r="42" spans="2:9">
-      <c r="B42" s="191"/>
-      <c r="C42" s="176" t="s">
-        <v>65</v>
-      </c>
-      <c r="D42" s="139" t="s">
-        <v>66</v>
-      </c>
-      <c r="E42" s="148" t="s">
-        <v>137</v>
-      </c>
-      <c r="F42" s="150" t="s">
-        <v>178</v>
-      </c>
-      <c r="G42" s="121" t="s">
-        <v>138</v>
-      </c>
-      <c r="H42" s="231" t="s">
-        <v>145</v>
-      </c>
-      <c r="I42" s="245"/>
-    </row>
-    <row r="43" spans="2:9" ht="113.65" customHeight="1">
-      <c r="B43" s="191"/>
-      <c r="C43" s="177"/>
-      <c r="D43" s="140"/>
-      <c r="E43" s="149"/>
-      <c r="F43" s="151"/>
-      <c r="G43" s="122"/>
-      <c r="H43" s="231"/>
-      <c r="I43" s="245"/>
-    </row>
-    <row r="44" spans="2:9">
-      <c r="B44" s="191"/>
-      <c r="C44" s="177"/>
-      <c r="D44" s="130" t="s">
-        <v>67</v>
-      </c>
-      <c r="E44" s="150" t="s">
-        <v>177</v>
-      </c>
-      <c r="F44" s="188"/>
-      <c r="G44" s="132" t="s">
-        <v>189</v>
-      </c>
-      <c r="H44" s="231"/>
-      <c r="I44" s="245"/>
-    </row>
-    <row r="45" spans="2:9" ht="317.64999999999998" customHeight="1">
-      <c r="B45" s="191"/>
-      <c r="C45" s="174"/>
-      <c r="D45" s="131"/>
-      <c r="E45" s="151"/>
-      <c r="F45" s="189"/>
-      <c r="G45" s="133"/>
-      <c r="H45" s="228"/>
-      <c r="I45" s="245"/>
-    </row>
-    <row r="46" spans="2:9">
-      <c r="B46" s="191"/>
-      <c r="C46" s="176" t="s">
-        <v>68</v>
-      </c>
-      <c r="D46" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="E46" s="136" t="s">
-        <v>71</v>
-      </c>
-      <c r="F46" s="201" t="s">
-        <v>180</v>
-      </c>
-      <c r="G46" s="155" t="s">
-        <v>201</v>
-      </c>
-      <c r="H46" s="232"/>
-      <c r="I46" s="245"/>
-    </row>
-    <row r="47" spans="2:9">
-      <c r="B47" s="191"/>
-      <c r="C47" s="177"/>
-      <c r="D47" s="37" t="s">
-        <v>170</v>
-      </c>
-      <c r="E47" s="137"/>
-      <c r="F47" s="187"/>
-      <c r="G47" s="156"/>
-      <c r="H47" s="232"/>
-      <c r="I47" s="245"/>
-    </row>
-    <row r="48" spans="2:9">
-      <c r="B48" s="191"/>
-      <c r="C48" s="177"/>
-      <c r="D48" s="114" t="s">
-        <v>197</v>
-      </c>
-      <c r="E48" s="137"/>
-      <c r="F48" s="187"/>
-      <c r="G48" s="156"/>
-      <c r="H48" s="232"/>
-      <c r="I48" s="245"/>
-    </row>
-    <row r="49" spans="2:9">
-      <c r="B49" s="191"/>
-      <c r="C49" s="177"/>
-      <c r="D49" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="E49" s="137"/>
-      <c r="F49" s="187"/>
-      <c r="G49" s="156"/>
-      <c r="H49" s="232"/>
-      <c r="I49" s="245"/>
-    </row>
-    <row r="50" spans="2:9">
-      <c r="B50" s="191"/>
-      <c r="C50" s="177"/>
-      <c r="D50" s="37"/>
-      <c r="E50" s="137"/>
-      <c r="F50" s="187"/>
-      <c r="G50" s="156"/>
-      <c r="H50" s="232"/>
-      <c r="I50" s="245"/>
-    </row>
-    <row r="51" spans="2:9" ht="317.5" customHeight="1" thickBot="1">
-      <c r="B51" s="191"/>
-      <c r="C51" s="174"/>
-      <c r="D51" s="37"/>
-      <c r="E51" s="202"/>
-      <c r="F51" s="135"/>
-      <c r="G51" s="157"/>
-      <c r="H51" s="233"/>
-      <c r="I51" s="246"/>
-    </row>
-    <row r="52" spans="2:9" ht="29.5" thickBot="1">
-      <c r="B52" s="192"/>
-      <c r="C52" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="D52" s="39" t="s">
-        <v>73</v>
-      </c>
-      <c r="E52" s="203" t="s">
-        <v>56</v>
-      </c>
-      <c r="F52" s="204"/>
-      <c r="G52" s="204"/>
-      <c r="H52" s="204"/>
-      <c r="I52" s="205"/>
-    </row>
-    <row r="53" spans="2:9" ht="17.5" thickBot="1">
-      <c r="B53" s="80"/>
-      <c r="C53" s="81"/>
-      <c r="D53" s="82"/>
-      <c r="E53" s="83"/>
-      <c r="F53" s="84"/>
-      <c r="G53" s="91"/>
-      <c r="H53" s="98"/>
-      <c r="I53" s="93"/>
-    </row>
-    <row r="54" spans="2:9" ht="94.75" customHeight="1">
-      <c r="B54" s="190" t="s">
-        <v>74</v>
-      </c>
-      <c r="C54" s="40" t="s">
-        <v>75</v>
-      </c>
-      <c r="D54" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="E54" s="42" t="s">
-        <v>77</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="G54" s="68" t="s">
-        <v>150</v>
-      </c>
-      <c r="H54" s="109" t="s">
-        <v>147</v>
-      </c>
-      <c r="I54" s="169" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="55" spans="2:9">
-      <c r="B55" s="191"/>
-      <c r="C55" s="176" t="s">
-        <v>16</v>
-      </c>
-      <c r="D55" s="130" t="s">
-        <v>78</v>
-      </c>
-      <c r="E55" s="201" t="s">
-        <v>190</v>
-      </c>
-      <c r="F55" s="201" t="s">
-        <v>181</v>
-      </c>
-      <c r="G55" s="183" t="s">
-        <v>191</v>
-      </c>
-      <c r="H55" s="227" t="s">
-        <v>182</v>
-      </c>
-      <c r="I55" s="245"/>
-    </row>
-    <row r="56" spans="2:9" ht="207" customHeight="1">
-      <c r="B56" s="191"/>
-      <c r="C56" s="174"/>
-      <c r="D56" s="131"/>
-      <c r="E56" s="135"/>
-      <c r="F56" s="135"/>
-      <c r="G56" s="185"/>
-      <c r="H56" s="228"/>
-      <c r="I56" s="245"/>
-    </row>
-    <row r="57" spans="2:9" ht="181.75" customHeight="1">
-      <c r="B57" s="191"/>
-      <c r="C57" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="D57" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="E57" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F57" s="9"/>
-      <c r="G57" s="88" t="s">
-        <v>188</v>
-      </c>
-      <c r="H57" s="99"/>
-      <c r="I57" s="246"/>
-    </row>
-    <row r="58" spans="2:9" ht="34.5" thickBot="1">
-      <c r="B58" s="192"/>
-      <c r="C58" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="D58" s="43" t="s">
-        <v>81</v>
-      </c>
-      <c r="E58" s="242" t="s">
-        <v>56</v>
-      </c>
-      <c r="F58" s="243"/>
-      <c r="G58" s="243"/>
-      <c r="H58" s="243"/>
-      <c r="I58" s="244"/>
-    </row>
-    <row r="59" spans="2:9" ht="17.5" thickBot="1">
-      <c r="B59" s="76"/>
-      <c r="C59" s="77"/>
-      <c r="D59" s="78"/>
-      <c r="E59" s="79"/>
-      <c r="F59" s="79"/>
-      <c r="G59" s="91"/>
-      <c r="H59" s="98"/>
-      <c r="I59" s="94"/>
-    </row>
-    <row r="60" spans="2:9" ht="68">
-      <c r="B60" s="141" t="s">
-        <v>155</v>
-      </c>
-      <c r="C60" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="D60" s="44" t="s">
-        <v>83</v>
-      </c>
-      <c r="E60" s="42" t="s">
-        <v>156</v>
-      </c>
-      <c r="F60" s="70"/>
-      <c r="G60" s="70" t="s">
-        <v>169</v>
-      </c>
-      <c r="H60" s="100"/>
-      <c r="I60" s="169" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="61" spans="2:9" ht="228.5" customHeight="1">
-      <c r="B61" s="142"/>
-      <c r="C61" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="D61" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="E61" s="30"/>
-      <c r="F61" s="71"/>
-      <c r="G61" s="71" t="s">
-        <v>198</v>
-      </c>
-      <c r="H61" s="101"/>
-      <c r="I61" s="170"/>
-    </row>
-    <row r="62" spans="2:9" ht="170">
-      <c r="B62" s="142"/>
-      <c r="C62" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="D62" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E62" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="F62" s="107" t="s">
-        <v>192</v>
-      </c>
-      <c r="G62" s="85" t="s">
-        <v>187</v>
-      </c>
-      <c r="H62" s="110" t="s">
-        <v>196</v>
-      </c>
-      <c r="I62" s="170"/>
-    </row>
-    <row r="63" spans="2:9" ht="34">
-      <c r="B63" s="142"/>
-      <c r="C63" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="D63" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="E63" s="30" t="s">
-        <v>193</v>
-      </c>
-      <c r="F63" s="30"/>
-      <c r="G63" s="73" t="s">
-        <v>194</v>
-      </c>
-      <c r="H63" s="102"/>
-      <c r="I63" s="170"/>
-    </row>
-    <row r="64" spans="2:9" ht="85">
-      <c r="B64" s="142"/>
-      <c r="C64" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="D64" s="29" t="s">
-        <v>93</v>
-      </c>
-      <c r="E64" s="30" t="s">
-        <v>94</v>
-      </c>
-      <c r="F64" s="30"/>
-      <c r="G64" s="74" t="s">
-        <v>158</v>
-      </c>
-      <c r="H64" s="103"/>
-      <c r="I64" s="171"/>
-    </row>
-    <row r="65" spans="2:9" ht="34.5" thickBot="1">
-      <c r="B65" s="143"/>
-      <c r="C65" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="D65" s="111" t="s">
-        <v>96</v>
-      </c>
-      <c r="E65" s="236" t="s">
-        <v>56</v>
-      </c>
-      <c r="F65" s="237"/>
-      <c r="G65" s="237"/>
-      <c r="H65" s="237"/>
-      <c r="I65" s="238"/>
+      <c r="F69" s="98"/>
+      <c r="G69" s="98"/>
+      <c r="H69" s="98"/>
+      <c r="I69" s="99"/>
     </row>
   </sheetData>
-  <mergeCells count="76">
-    <mergeCell ref="E65:I65"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="F25:F32"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="E58:I58"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="F46:F51"/>
-    <mergeCell ref="I54:I57"/>
-    <mergeCell ref="I38:I51"/>
-    <mergeCell ref="I23:I35"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="G33:G34"/>
-    <mergeCell ref="H33:H34"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="I8:I21"/>
-    <mergeCell ref="I4:I7"/>
-    <mergeCell ref="G55:G56"/>
-    <mergeCell ref="H55:H56"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="H40:H41"/>
-    <mergeCell ref="H42:H45"/>
-    <mergeCell ref="G46:G51"/>
-    <mergeCell ref="H46:H51"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="H23:H24"/>
+  <mergeCells count="78">
+    <mergeCell ref="G55:H57"/>
+    <mergeCell ref="I55:I61"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="D47:D52"/>
+    <mergeCell ref="B55:B62"/>
+    <mergeCell ref="E55:F57"/>
+    <mergeCell ref="B3:B22"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="D3:D7"/>
+    <mergeCell ref="E3:E7"/>
+    <mergeCell ref="H3:H7"/>
+    <mergeCell ref="F3:F7"/>
+    <mergeCell ref="G3:G7"/>
+    <mergeCell ref="I64:I68"/>
+    <mergeCell ref="C14:C21"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="C26:C33"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="G26:G33"/>
+    <mergeCell ref="H26:H33"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="B39:B53"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="B24:B37"/>
+    <mergeCell ref="B64:B69"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="D59:D60"/>
+    <mergeCell ref="E59:E60"/>
+    <mergeCell ref="C47:C52"/>
+    <mergeCell ref="E47:E52"/>
+    <mergeCell ref="E53:I53"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="C43:C46"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="F43:F44"/>
     <mergeCell ref="D14:D21"/>
     <mergeCell ref="G11:G13"/>
     <mergeCell ref="F11:F13"/>
     <mergeCell ref="H11:H13"/>
     <mergeCell ref="G14:G21"/>
     <mergeCell ref="H14:H21"/>
-    <mergeCell ref="B3:B21"/>
-    <mergeCell ref="B23:B36"/>
-    <mergeCell ref="B60:B65"/>
-    <mergeCell ref="G4:G7"/>
-    <mergeCell ref="H4:H7"/>
-    <mergeCell ref="B54:B58"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="C46:C51"/>
-    <mergeCell ref="E46:E51"/>
-    <mergeCell ref="E52:I52"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="C42:C45"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="B38:B52"/>
-    <mergeCell ref="C38:C41"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="F4:F7"/>
-    <mergeCell ref="I60:I64"/>
-    <mergeCell ref="C14:C21"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="C25:C32"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="G25:G32"/>
-    <mergeCell ref="H25:H32"/>
+    <mergeCell ref="I8:I21"/>
+    <mergeCell ref="G59:G60"/>
+    <mergeCell ref="H59:H60"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="H43:H46"/>
+    <mergeCell ref="G47:G52"/>
+    <mergeCell ref="H47:H52"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="E69:I69"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="F26:F33"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="E62:I62"/>
+    <mergeCell ref="F59:F60"/>
+    <mergeCell ref="F47:F52"/>
+    <mergeCell ref="I39:I52"/>
+    <mergeCell ref="I24:I36"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="H34:H35"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I8" r:id="rId1" xr:uid="{F90B7A6D-277A-4C51-914E-6F998CCC576E}"/>
-    <hyperlink ref="I23" r:id="rId2" xr:uid="{48C188C7-7A34-4753-891F-6AFB7AA82563}"/>
-    <hyperlink ref="I38" r:id="rId3" xr:uid="{EC9FD26B-5901-42E8-BC47-4FA90402A688}"/>
-    <hyperlink ref="I54" r:id="rId4" xr:uid="{DBCE87F3-DC8B-4CB2-B7E7-2C179D59A9DD}"/>
+    <hyperlink ref="I24" r:id="rId2" xr:uid="{48C188C7-7A34-4753-891F-6AFB7AA82563}"/>
+    <hyperlink ref="I39" r:id="rId3" xr:uid="{EC9FD26B-5901-42E8-BC47-4FA90402A688}"/>
+    <hyperlink ref="I55" r:id="rId4" xr:uid="{DBCE87F3-DC8B-4CB2-B7E7-2C179D59A9DD}"/>
     <hyperlink ref="E19" r:id="rId5" xr:uid="{E01D2651-D930-4355-A0F8-FA470948D355}"/>
     <hyperlink ref="E20" r:id="rId6" xr:uid="{E640EF3B-D28F-4372-820C-21868F7D842B}"/>
-    <hyperlink ref="E30" r:id="rId7" xr:uid="{55CB4F8D-79D6-4086-834E-A7B97BDD0E0A}"/>
-    <hyperlink ref="E31" r:id="rId8" xr:uid="{AAAAFA55-A7A9-4D9F-AA48-6828AF2613D3}"/>
-    <hyperlink ref="I60:I64" r:id="rId9" display="https://github.com/mulcamp-ed/ai-onboarding/tree/master/Day05" xr:uid="{311D5629-79A4-40B8-9A92-B2A35AB221AD}"/>
+    <hyperlink ref="E31" r:id="rId7" xr:uid="{55CB4F8D-79D6-4086-834E-A7B97BDD0E0A}"/>
+    <hyperlink ref="E32" r:id="rId8" xr:uid="{AAAAFA55-A7A9-4D9F-AA48-6828AF2613D3}"/>
+    <hyperlink ref="I64:I68" r:id="rId9" display="https://github.com/mulcamp-ed/ai-onboarding/tree/master/Day05" xr:uid="{311D5629-79A4-40B8-9A92-B2A35AB221AD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
 </worksheet>
 </file>
 
@@ -12102,272 +12210,287 @@
   <sheetData>
     <row r="3" spans="2:7" ht="17.5" thickBot="1"/>
     <row r="4" spans="2:7" ht="17.5" thickBot="1">
-      <c r="B4" s="46"/>
-      <c r="C4" s="47" t="s">
+      <c r="B4" s="32"/>
+      <c r="C4" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="D4" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="47" t="s">
-        <v>98</v>
-      </c>
-      <c r="F4" s="47" t="s">
+      <c r="E4" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="F4" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="G4" s="34" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="17" customHeight="1">
+      <c r="B5" s="267" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="262" t="s">
+        <v>186</v>
+      </c>
+      <c r="D5" s="238" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="103" t="s">
+        <v>185</v>
+      </c>
+      <c r="F5" s="242" t="s">
+        <v>86</v>
+      </c>
+      <c r="G5" s="196"/>
+    </row>
+    <row r="6" spans="2:7" ht="17" customHeight="1">
+      <c r="B6" s="268"/>
+      <c r="C6" s="263"/>
+      <c r="D6" s="167"/>
+      <c r="E6" s="146"/>
+      <c r="F6" s="143"/>
+      <c r="G6" s="249"/>
+    </row>
+    <row r="7" spans="2:7">
+      <c r="B7" s="268"/>
+      <c r="C7" s="263"/>
+      <c r="D7" s="167"/>
+      <c r="E7" s="146"/>
+      <c r="F7" s="143"/>
+      <c r="G7" s="249"/>
+    </row>
+    <row r="8" spans="2:7">
+      <c r="B8" s="268"/>
+      <c r="C8" s="263"/>
+      <c r="D8" s="167"/>
+      <c r="E8" s="146"/>
+      <c r="F8" s="143"/>
+      <c r="G8" s="249"/>
+    </row>
+    <row r="9" spans="2:7">
+      <c r="B9" s="268"/>
+      <c r="C9" s="264"/>
+      <c r="D9" s="168"/>
+      <c r="E9" s="104"/>
+      <c r="F9" s="106"/>
+      <c r="G9" s="197"/>
+    </row>
+    <row r="10" spans="2:7" ht="51" customHeight="1">
+      <c r="B10" s="268"/>
+      <c r="C10" s="265" t="s">
+        <v>187</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="235"/>
+      <c r="F10" s="68" t="s">
+        <v>89</v>
+      </c>
+      <c r="G10" s="250"/>
+    </row>
+    <row r="11" spans="2:7" ht="17" customHeight="1">
+      <c r="B11" s="268"/>
+      <c r="C11" s="266" t="s">
+        <v>188</v>
+      </c>
+      <c r="D11" s="166" t="s">
+        <v>189</v>
+      </c>
+      <c r="E11" s="105" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="141" t="s">
+        <v>96</v>
+      </c>
+      <c r="G11" s="251" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7">
+      <c r="B12" s="268"/>
+      <c r="C12" s="264"/>
+      <c r="D12" s="183"/>
+      <c r="E12" s="106"/>
+      <c r="F12" s="142"/>
+      <c r="G12" s="252"/>
+    </row>
+    <row r="13" spans="2:7" ht="286.75" customHeight="1">
+      <c r="B13" s="268"/>
+      <c r="C13" s="266" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="141" t="s">
+        <v>95</v>
+      </c>
+      <c r="G13" s="253" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="35.15" customHeight="1">
+      <c r="B14" s="268"/>
+      <c r="C14" s="263"/>
+      <c r="D14" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F14" s="144"/>
+      <c r="G14" s="254"/>
+    </row>
+    <row r="15" spans="2:7">
+      <c r="B15" s="268"/>
+      <c r="C15" s="264"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="142"/>
+      <c r="G15" s="255"/>
+    </row>
+    <row r="16" spans="2:7" ht="134.65" customHeight="1">
+      <c r="B16" s="268"/>
+      <c r="C16" s="266" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="105" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="150" t="s">
         <v>99</v>
       </c>
-      <c r="G4" s="48" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="34">
-      <c r="B5" s="252" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="53" t="s">
+      <c r="G16" s="256" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" ht="35.15" customHeight="1">
+      <c r="B17" s="268"/>
+      <c r="C17" s="263"/>
+      <c r="D17" s="143"/>
+      <c r="E17" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" s="151"/>
+      <c r="G17" s="257"/>
+    </row>
+    <row r="18" spans="2:7">
+      <c r="B18" s="268"/>
+      <c r="C18" s="263"/>
+      <c r="D18" s="143"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="151"/>
+      <c r="G18" s="257"/>
+    </row>
+    <row r="19" spans="2:7" ht="34">
+      <c r="B19" s="268"/>
+      <c r="C19" s="263"/>
+      <c r="D19" s="143"/>
+      <c r="E19" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="151"/>
+      <c r="G19" s="257"/>
+    </row>
+    <row r="20" spans="2:7">
+      <c r="B20" s="268"/>
+      <c r="C20" s="263"/>
+      <c r="D20" s="143"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="151"/>
+      <c r="G20" s="257"/>
+    </row>
+    <row r="21" spans="2:7">
+      <c r="B21" s="268"/>
+      <c r="C21" s="263"/>
+      <c r="D21" s="143"/>
+      <c r="E21" s="88" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="151"/>
+      <c r="G21" s="257"/>
+    </row>
+    <row r="22" spans="2:7">
+      <c r="B22" s="268"/>
+      <c r="C22" s="263"/>
+      <c r="D22" s="143"/>
+      <c r="E22" s="88" t="s">
+        <v>87</v>
+      </c>
+      <c r="F22" s="151"/>
+      <c r="G22" s="257"/>
+    </row>
+    <row r="23" spans="2:7">
+      <c r="B23" s="268"/>
+      <c r="C23" s="264"/>
+      <c r="D23" s="106"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="236"/>
+      <c r="G23" s="258"/>
+    </row>
+    <row r="24" spans="2:7" ht="85.75" customHeight="1" thickBot="1">
+      <c r="B24" s="269"/>
+      <c r="C24" s="259" t="s">
+        <v>182</v>
+      </c>
+      <c r="D24" s="35" t="s">
+        <v>183</v>
+      </c>
+      <c r="E24" s="247" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="54" t="s">
-        <v>112</v>
-      </c>
-      <c r="F5" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="G5" s="56"/>
-    </row>
-    <row r="6" spans="2:7">
-      <c r="B6" s="253"/>
-      <c r="C6" s="260" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="136" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="150" t="s">
-        <v>100</v>
-      </c>
-      <c r="F6" s="121" t="s">
-        <v>101</v>
-      </c>
-      <c r="G6" s="249"/>
-    </row>
-    <row r="7" spans="2:7">
-      <c r="B7" s="253"/>
-      <c r="C7" s="261"/>
-      <c r="D7" s="137"/>
-      <c r="E7" s="167"/>
-      <c r="F7" s="196"/>
-      <c r="G7" s="250"/>
-    </row>
-    <row r="8" spans="2:7">
-      <c r="B8" s="253"/>
-      <c r="C8" s="261"/>
-      <c r="D8" s="137"/>
-      <c r="E8" s="167"/>
-      <c r="F8" s="196"/>
-      <c r="G8" s="250"/>
-    </row>
-    <row r="9" spans="2:7">
-      <c r="B9" s="253"/>
-      <c r="C9" s="265"/>
-      <c r="D9" s="166"/>
-      <c r="E9" s="151"/>
-      <c r="F9" s="197"/>
-      <c r="G9" s="251"/>
-    </row>
-    <row r="10" spans="2:7" ht="34">
-      <c r="B10" s="253"/>
-      <c r="C10" s="57" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="45"/>
-      <c r="F10" s="51" t="s">
-        <v>107</v>
-      </c>
-      <c r="G10" s="116"/>
-    </row>
-    <row r="11" spans="2:7">
-      <c r="B11" s="253"/>
-      <c r="C11" s="260" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="179" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="150" t="s">
-        <v>105</v>
-      </c>
-      <c r="F11" s="258" t="s">
-        <v>117</v>
-      </c>
-      <c r="G11" s="129" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7">
-      <c r="B12" s="253"/>
-      <c r="C12" s="261"/>
-      <c r="D12" s="264"/>
-      <c r="E12" s="167"/>
-      <c r="F12" s="259"/>
-      <c r="G12" s="269"/>
-    </row>
-    <row r="13" spans="2:7" ht="286.75" customHeight="1">
-      <c r="B13" s="253"/>
-      <c r="C13" s="263"/>
-      <c r="D13" s="180"/>
-      <c r="E13" s="151"/>
-      <c r="F13" s="147"/>
-      <c r="G13" s="270"/>
-    </row>
-    <row r="14" spans="2:7" ht="35.15" customHeight="1">
-      <c r="B14" s="253"/>
-      <c r="C14" s="260" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="255" t="s">
-        <v>114</v>
-      </c>
-      <c r="E14" s="150" t="s">
-        <v>106</v>
-      </c>
-      <c r="F14" s="258" t="s">
-        <v>115</v>
-      </c>
-      <c r="G14" s="271" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7">
-      <c r="B15" s="253"/>
-      <c r="C15" s="261"/>
-      <c r="D15" s="256"/>
-      <c r="E15" s="167"/>
-      <c r="F15" s="259"/>
-      <c r="G15" s="272"/>
-    </row>
-    <row r="16" spans="2:7" ht="134.65" customHeight="1">
-      <c r="B16" s="253"/>
-      <c r="C16" s="263"/>
-      <c r="D16" s="257"/>
-      <c r="E16" s="151"/>
-      <c r="F16" s="147"/>
-      <c r="G16" s="273"/>
-    </row>
-    <row r="17" spans="2:7" ht="35.15" customHeight="1">
-      <c r="B17" s="253"/>
-      <c r="C17" s="260" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="150" t="s">
-        <v>97</v>
-      </c>
-      <c r="E17" s="136" t="s">
-        <v>102</v>
-      </c>
-      <c r="F17" s="266" t="s">
-        <v>120</v>
-      </c>
-      <c r="G17" s="274" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="253"/>
-      <c r="C18" s="261"/>
-      <c r="D18" s="167"/>
-      <c r="E18" s="137"/>
-      <c r="F18" s="267"/>
-      <c r="G18" s="275"/>
-    </row>
-    <row r="19" spans="2:7">
-      <c r="B19" s="253"/>
-      <c r="C19" s="261"/>
-      <c r="D19" s="167"/>
-      <c r="E19" s="137"/>
-      <c r="F19" s="267"/>
-      <c r="G19" s="275"/>
-    </row>
-    <row r="20" spans="2:7">
-      <c r="B20" s="253"/>
-      <c r="C20" s="261"/>
-      <c r="D20" s="167"/>
-      <c r="E20" s="137"/>
-      <c r="F20" s="267"/>
-      <c r="G20" s="275"/>
-    </row>
-    <row r="21" spans="2:7">
-      <c r="B21" s="253"/>
-      <c r="C21" s="261"/>
-      <c r="D21" s="167"/>
-      <c r="E21" s="137"/>
-      <c r="F21" s="267"/>
-      <c r="G21" s="275"/>
-    </row>
-    <row r="22" spans="2:7">
-      <c r="B22" s="253"/>
-      <c r="C22" s="261"/>
-      <c r="D22" s="167"/>
-      <c r="E22" s="137"/>
-      <c r="F22" s="267"/>
-      <c r="G22" s="275"/>
-    </row>
-    <row r="23" spans="2:7">
-      <c r="B23" s="253"/>
-      <c r="C23" s="261"/>
-      <c r="D23" s="167"/>
-      <c r="E23" s="137"/>
-      <c r="F23" s="267"/>
-      <c r="G23" s="275"/>
-    </row>
-    <row r="24" spans="2:7" ht="85.75" customHeight="1" thickBot="1">
-      <c r="B24" s="254"/>
-      <c r="C24" s="262"/>
-      <c r="D24" s="206"/>
-      <c r="E24" s="138"/>
-      <c r="F24" s="268"/>
-      <c r="G24" s="276"/>
+      <c r="F24" s="260" t="s">
+        <v>184</v>
+      </c>
+      <c r="G24" s="261"/>
     </row>
     <row r="28" spans="2:7">
       <c r="F28" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="2:7">
       <c r="F29" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="E17:E24"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="G17:G24"/>
-    <mergeCell ref="G6:G9"/>
+  <mergeCells count="18">
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="G13:G15"/>
+    <mergeCell ref="C16:C23"/>
+    <mergeCell ref="D16:D23"/>
+    <mergeCell ref="G16:G23"/>
+    <mergeCell ref="C5:C9"/>
+    <mergeCell ref="D5:D9"/>
+    <mergeCell ref="E5:E9"/>
+    <mergeCell ref="F5:F9"/>
+    <mergeCell ref="G5:G9"/>
     <mergeCell ref="B5:B24"/>
-    <mergeCell ref="D17:D24"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="E6:E9"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="C17:C24"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="E11:E13"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="C6:C9"/>
-    <mergeCell ref="D6:D9"/>
-    <mergeCell ref="F6:F9"/>
-    <mergeCell ref="F17:F24"/>
-    <mergeCell ref="G11:G13"/>
+    <mergeCell ref="F16:F23"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="E21" r:id="rId1" xr:uid="{F28A8AF6-CC27-433B-B268-1AED189D304A}"/>
+    <hyperlink ref="E22" r:id="rId2" xr:uid="{D15C3677-5C1F-4E90-A61F-A6399FB406DE}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -12387,234 +12510,239 @@
   <sheetData>
     <row r="1" spans="2:7" ht="17.5" thickBot="1"/>
     <row r="2" spans="2:7" ht="17.5" thickBot="1">
-      <c r="B2" s="46"/>
-      <c r="C2" s="47" t="s">
+      <c r="B2" s="32"/>
+      <c r="C2" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="47" t="s">
+      <c r="D2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="47" t="s">
+      <c r="E2" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2" s="34" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="70.400000000000006" customHeight="1">
+      <c r="B3" s="94" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="194" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="198" t="s">
+        <v>94</v>
+      </c>
+      <c r="E3" s="200" t="s">
+        <v>97</v>
+      </c>
+      <c r="F3" s="129" t="s">
+        <v>110</v>
+      </c>
+      <c r="G3" s="196" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="83.15" customHeight="1">
+      <c r="B4" s="95"/>
+      <c r="C4" s="195"/>
+      <c r="D4" s="199"/>
+      <c r="E4" s="126"/>
+      <c r="F4" s="130"/>
+      <c r="G4" s="197"/>
+    </row>
+    <row r="5" spans="2:7" ht="105.4" customHeight="1">
+      <c r="B5" s="95"/>
+      <c r="C5" s="201" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="172" t="s">
         <v>98</v>
       </c>
-      <c r="F2" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="G2" s="48" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" ht="70.400000000000006" customHeight="1">
-      <c r="B3" s="141" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="158" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="289" t="s">
-        <v>113</v>
-      </c>
-      <c r="E3" s="291" t="s">
-        <v>118</v>
-      </c>
-      <c r="F3" s="146" t="s">
-        <v>131</v>
-      </c>
-      <c r="G3" s="287" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="83.15" customHeight="1">
-      <c r="B4" s="142"/>
-      <c r="C4" s="160"/>
-      <c r="D4" s="290"/>
-      <c r="E4" s="185"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="288"/>
-    </row>
-    <row r="5" spans="2:7" ht="105.4" customHeight="1">
-      <c r="B5" s="142"/>
-      <c r="C5" s="161" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="139" t="s">
-        <v>119</v>
-      </c>
-      <c r="E5" s="277" t="s">
-        <v>125</v>
-      </c>
-      <c r="F5" s="183" t="s">
-        <v>121</v>
-      </c>
-      <c r="G5" s="292" t="s">
-        <v>126</v>
+      <c r="E5" s="205" t="s">
+        <v>104</v>
+      </c>
+      <c r="F5" s="125" t="s">
+        <v>100</v>
+      </c>
+      <c r="G5" s="202" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="2:7">
-      <c r="B6" s="142"/>
-      <c r="C6" s="159"/>
-      <c r="D6" s="280"/>
-      <c r="E6" s="278"/>
-      <c r="F6" s="184"/>
-      <c r="G6" s="293"/>
+      <c r="B6" s="95"/>
+      <c r="C6" s="209"/>
+      <c r="D6" s="208"/>
+      <c r="E6" s="206"/>
+      <c r="F6" s="186"/>
+      <c r="G6" s="203"/>
     </row>
     <row r="7" spans="2:7">
-      <c r="B7" s="142"/>
-      <c r="C7" s="159"/>
-      <c r="D7" s="280"/>
-      <c r="E7" s="278"/>
-      <c r="F7" s="184"/>
-      <c r="G7" s="293"/>
+      <c r="B7" s="95"/>
+      <c r="C7" s="209"/>
+      <c r="D7" s="208"/>
+      <c r="E7" s="206"/>
+      <c r="F7" s="186"/>
+      <c r="G7" s="203"/>
     </row>
     <row r="8" spans="2:7">
-      <c r="B8" s="142"/>
-      <c r="C8" s="159"/>
-      <c r="D8" s="280"/>
-      <c r="E8" s="278"/>
-      <c r="F8" s="184"/>
-      <c r="G8" s="293"/>
+      <c r="B8" s="95"/>
+      <c r="C8" s="209"/>
+      <c r="D8" s="208"/>
+      <c r="E8" s="206"/>
+      <c r="F8" s="186"/>
+      <c r="G8" s="203"/>
     </row>
     <row r="9" spans="2:7">
-      <c r="B9" s="142"/>
-      <c r="C9" s="159"/>
-      <c r="D9" s="280"/>
-      <c r="E9" s="278"/>
-      <c r="F9" s="184"/>
-      <c r="G9" s="293"/>
+      <c r="B9" s="95"/>
+      <c r="C9" s="209"/>
+      <c r="D9" s="208"/>
+      <c r="E9" s="206"/>
+      <c r="F9" s="186"/>
+      <c r="G9" s="203"/>
     </row>
     <row r="10" spans="2:7">
-      <c r="B10" s="142"/>
-      <c r="C10" s="159"/>
-      <c r="D10" s="280"/>
-      <c r="E10" s="278"/>
-      <c r="F10" s="184"/>
-      <c r="G10" s="293"/>
+      <c r="B10" s="95"/>
+      <c r="C10" s="209"/>
+      <c r="D10" s="208"/>
+      <c r="E10" s="206"/>
+      <c r="F10" s="186"/>
+      <c r="G10" s="203"/>
     </row>
     <row r="11" spans="2:7">
-      <c r="B11" s="142"/>
-      <c r="C11" s="159"/>
-      <c r="D11" s="280"/>
-      <c r="E11" s="278"/>
-      <c r="F11" s="184"/>
-      <c r="G11" s="293"/>
+      <c r="B11" s="95"/>
+      <c r="C11" s="209"/>
+      <c r="D11" s="208"/>
+      <c r="E11" s="206"/>
+      <c r="F11" s="186"/>
+      <c r="G11" s="203"/>
     </row>
     <row r="12" spans="2:7">
-      <c r="B12" s="142"/>
-      <c r="C12" s="160"/>
-      <c r="D12" s="140"/>
-      <c r="E12" s="279"/>
-      <c r="F12" s="185"/>
-      <c r="G12" s="285"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="195"/>
+      <c r="D12" s="173"/>
+      <c r="E12" s="207"/>
+      <c r="F12" s="126"/>
+      <c r="G12" s="204"/>
     </row>
     <row r="13" spans="2:7" ht="139" customHeight="1">
-      <c r="B13" s="142"/>
-      <c r="C13" s="161" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="139" t="s">
-        <v>123</v>
-      </c>
-      <c r="E13" s="136" t="s">
-        <v>122</v>
-      </c>
-      <c r="F13" s="247" t="s">
-        <v>124</v>
-      </c>
-      <c r="G13" s="284" t="s">
-        <v>127</v>
+      <c r="B13" s="95"/>
+      <c r="C13" s="201" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="172" t="s">
+        <v>102</v>
+      </c>
+      <c r="E13" s="166" t="s">
+        <v>101</v>
+      </c>
+      <c r="F13" s="120" t="s">
+        <v>103</v>
+      </c>
+      <c r="G13" s="210" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="2:7">
-      <c r="B14" s="142"/>
-      <c r="C14" s="160"/>
-      <c r="D14" s="140"/>
-      <c r="E14" s="202"/>
-      <c r="F14" s="248"/>
-      <c r="G14" s="285"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="195"/>
+      <c r="D14" s="173"/>
+      <c r="E14" s="168"/>
+      <c r="F14" s="121"/>
+      <c r="G14" s="204"/>
     </row>
     <row r="15" spans="2:7" ht="95.65" customHeight="1">
-      <c r="B15" s="142"/>
-      <c r="C15" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" s="29" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="F15" s="62" t="s">
-        <v>129</v>
-      </c>
-      <c r="G15" s="63" t="s">
-        <v>128</v>
+      <c r="B15" s="95"/>
+      <c r="C15" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="G15" s="43" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="17.5" thickBot="1">
-      <c r="B16" s="143"/>
-      <c r="C16" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="D16" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="E16" s="281" t="s">
-        <v>56</v>
-      </c>
-      <c r="F16" s="282"/>
-      <c r="G16" s="283"/>
+      <c r="B16" s="96"/>
+      <c r="C16" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="40"/>
+      <c r="G16" s="41"/>
     </row>
     <row r="32" ht="17.5" thickBot="1"/>
     <row r="33" spans="8:8">
-      <c r="H33" s="169" t="s">
-        <v>36</v>
+      <c r="H33" s="113" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="8:8">
-      <c r="H34" s="170"/>
+      <c r="H34" s="116"/>
     </row>
     <row r="35" spans="8:8">
-      <c r="H35" s="170"/>
+      <c r="H35" s="116"/>
     </row>
     <row r="36" spans="8:8">
-      <c r="H36" s="170"/>
+      <c r="H36" s="116"/>
     </row>
     <row r="37" spans="8:8">
-      <c r="H37" s="170"/>
+      <c r="H37" s="116"/>
     </row>
     <row r="38" spans="8:8">
-      <c r="H38" s="170"/>
+      <c r="H38" s="116"/>
     </row>
     <row r="39" spans="8:8">
-      <c r="H39" s="170"/>
+      <c r="H39" s="116"/>
     </row>
     <row r="40" spans="8:8">
-      <c r="H40" s="170"/>
+      <c r="H40" s="116"/>
     </row>
     <row r="41" spans="8:8">
-      <c r="H41" s="170"/>
+      <c r="H41" s="116"/>
     </row>
     <row r="42" spans="8:8">
-      <c r="H42" s="171"/>
+      <c r="H42" s="117"/>
     </row>
     <row r="43" spans="8:8">
-      <c r="H43" s="286" t="s">
-        <v>49</v>
+      <c r="H43" s="193" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="44" spans="8:8">
-      <c r="H44" s="171"/>
+      <c r="H44" s="117"/>
     </row>
     <row r="45" spans="8:8">
-      <c r="H45" s="58" t="s">
-        <v>53</v>
+      <c r="H45" s="38" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="46" spans="8:8" ht="17.5" thickBot="1">
-      <c r="H46" s="61"/>
+      <c r="H46" s="41"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="18">
+    <mergeCell ref="B3:B16"/>
+    <mergeCell ref="E5:E12"/>
+    <mergeCell ref="D5:D12"/>
+    <mergeCell ref="C5:C12"/>
+    <mergeCell ref="G13:G14"/>
     <mergeCell ref="H33:H42"/>
     <mergeCell ref="H43:H44"/>
     <mergeCell ref="C3:C4"/>
@@ -12628,12 +12756,6 @@
     <mergeCell ref="E13:E14"/>
     <mergeCell ref="F13:F14"/>
     <mergeCell ref="G5:G12"/>
-    <mergeCell ref="B3:B16"/>
-    <mergeCell ref="E5:E12"/>
-    <mergeCell ref="D5:D12"/>
-    <mergeCell ref="C5:C12"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="G13:G14"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <hyperlinks>
@@ -12658,192 +12780,182 @@
   <sheetData>
     <row r="1" spans="2:7" ht="17.5" thickBot="1"/>
     <row r="2" spans="2:7" ht="17.5" thickBot="1">
-      <c r="B2" s="46"/>
-      <c r="C2" s="47" t="s">
+      <c r="B2" s="32"/>
+      <c r="C2" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="47" t="s">
+      <c r="D2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="47" t="s">
-        <v>98</v>
-      </c>
-      <c r="F2" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="G2" s="48" t="s">
-        <v>109</v>
+      <c r="E2" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2" s="34" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="35.15" customHeight="1">
-      <c r="B3" s="141" t="s">
+      <c r="B3" s="94" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="194" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" s="217" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" s="177" t="s">
+        <v>111</v>
+      </c>
+      <c r="F3" s="129" t="s">
+        <v>120</v>
+      </c>
+      <c r="G3" s="215" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="182.15" customHeight="1">
+      <c r="B4" s="95"/>
+      <c r="C4" s="209"/>
+      <c r="D4" s="218"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="130"/>
+      <c r="G4" s="216"/>
+    </row>
+    <row r="5" spans="2:7">
+      <c r="B5" s="95"/>
+      <c r="C5" s="209"/>
+      <c r="D5" s="178" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="145" t="s">
+        <v>114</v>
+      </c>
+      <c r="F5" s="131" t="s">
+        <v>121</v>
+      </c>
+      <c r="G5" s="192" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="86.15" customHeight="1">
+      <c r="B6" s="95"/>
+      <c r="C6" s="195"/>
+      <c r="D6" s="179"/>
+      <c r="E6" s="104"/>
+      <c r="F6" s="132"/>
+      <c r="G6" s="222"/>
+    </row>
+    <row r="7" spans="2:7">
+      <c r="B7" s="95"/>
+      <c r="C7" s="201" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="172" t="s">
+        <v>112</v>
+      </c>
+      <c r="E7" s="100" t="s">
+        <v>116</v>
+      </c>
+      <c r="F7" s="131" t="s">
+        <v>117</v>
+      </c>
+      <c r="G7" s="221" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" ht="103" customHeight="1">
+      <c r="B8" s="95"/>
+      <c r="C8" s="209"/>
+      <c r="D8" s="173"/>
+      <c r="E8" s="102"/>
+      <c r="F8" s="132"/>
+      <c r="G8" s="221"/>
+    </row>
+    <row r="9" spans="2:7">
+      <c r="B9" s="95"/>
+      <c r="C9" s="209"/>
+      <c r="D9" s="163" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="105" t="s">
+        <v>118</v>
+      </c>
+      <c r="F9" s="118" t="s">
+        <v>178</v>
+      </c>
+      <c r="G9" s="221"/>
+    </row>
+    <row r="10" spans="2:7" ht="274.5" customHeight="1">
+      <c r="B10" s="95"/>
+      <c r="C10" s="195"/>
+      <c r="D10" s="164"/>
+      <c r="E10" s="106"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="222"/>
+    </row>
+    <row r="11" spans="2:7" ht="17.649999999999999" customHeight="1">
+      <c r="B11" s="95"/>
+      <c r="C11" s="201" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="211" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="158" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="123" t="s">
-        <v>136</v>
-      </c>
-      <c r="E3" s="134" t="s">
-        <v>132</v>
-      </c>
-      <c r="F3" s="146" t="s">
-        <v>141</v>
-      </c>
-      <c r="G3" s="117" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="182.15" customHeight="1">
-      <c r="B4" s="142"/>
-      <c r="C4" s="159"/>
-      <c r="D4" s="124"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="118"/>
-    </row>
-    <row r="5" spans="2:7">
-      <c r="B5" s="142"/>
-      <c r="C5" s="159"/>
-      <c r="D5" s="119" t="s">
-        <v>134</v>
-      </c>
-      <c r="E5" s="144" t="s">
-        <v>135</v>
-      </c>
-      <c r="F5" s="121" t="s">
-        <v>142</v>
-      </c>
-      <c r="G5" s="129" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="86.15" customHeight="1">
-      <c r="B6" s="142"/>
-      <c r="C6" s="160"/>
-      <c r="D6" s="120"/>
-      <c r="E6" s="145"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="128"/>
-    </row>
-    <row r="7" spans="2:7">
-      <c r="B7" s="142"/>
-      <c r="C7" s="161" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="139" t="s">
-        <v>133</v>
-      </c>
-      <c r="E7" s="148" t="s">
-        <v>137</v>
-      </c>
-      <c r="F7" s="121" t="s">
-        <v>138</v>
-      </c>
-      <c r="G7" s="127" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" ht="103" customHeight="1">
-      <c r="B8" s="142"/>
-      <c r="C8" s="159"/>
-      <c r="D8" s="140"/>
-      <c r="E8" s="149"/>
-      <c r="F8" s="122"/>
-      <c r="G8" s="127"/>
-    </row>
-    <row r="9" spans="2:7">
-      <c r="B9" s="142"/>
-      <c r="C9" s="159"/>
-      <c r="D9" s="130" t="s">
-        <v>67</v>
-      </c>
-      <c r="E9" s="150" t="s">
-        <v>139</v>
-      </c>
-      <c r="F9" s="132" t="s">
-        <v>203</v>
-      </c>
-      <c r="G9" s="127"/>
-    </row>
-    <row r="10" spans="2:7" ht="274.5" customHeight="1">
-      <c r="B10" s="142"/>
-      <c r="C10" s="160"/>
-      <c r="D10" s="131"/>
-      <c r="E10" s="151"/>
-      <c r="F10" s="133"/>
-      <c r="G10" s="128"/>
-    </row>
-    <row r="11" spans="2:7" ht="17.649999999999999" customHeight="1">
-      <c r="B11" s="142"/>
-      <c r="C11" s="161" t="s">
-        <v>68</v>
-      </c>
-      <c r="D11" s="152" t="s">
-        <v>69</v>
-      </c>
-      <c r="E11" s="136" t="s">
-        <v>140</v>
-      </c>
-      <c r="F11" s="155" t="s">
-        <v>202</v>
-      </c>
-      <c r="G11" s="125"/>
+      <c r="E11" s="166" t="s">
+        <v>119</v>
+      </c>
+      <c r="F11" s="134" t="s">
+        <v>177</v>
+      </c>
+      <c r="G11" s="219"/>
     </row>
     <row r="12" spans="2:7" ht="28.4" customHeight="1">
-      <c r="B12" s="142"/>
-      <c r="C12" s="159"/>
-      <c r="D12" s="153"/>
-      <c r="E12" s="137"/>
-      <c r="F12" s="156"/>
-      <c r="G12" s="125"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="209"/>
+      <c r="D12" s="212"/>
+      <c r="E12" s="167"/>
+      <c r="F12" s="135"/>
+      <c r="G12" s="219"/>
     </row>
     <row r="13" spans="2:7" ht="42.4" customHeight="1">
-      <c r="B13" s="142"/>
-      <c r="C13" s="159"/>
-      <c r="D13" s="153"/>
-      <c r="E13" s="137"/>
-      <c r="F13" s="156"/>
-      <c r="G13" s="125"/>
+      <c r="B13" s="95"/>
+      <c r="C13" s="209"/>
+      <c r="D13" s="212"/>
+      <c r="E13" s="167"/>
+      <c r="F13" s="135"/>
+      <c r="G13" s="219"/>
     </row>
     <row r="14" spans="2:7">
-      <c r="B14" s="142"/>
-      <c r="C14" s="159"/>
-      <c r="D14" s="153"/>
-      <c r="E14" s="137"/>
-      <c r="F14" s="156"/>
-      <c r="G14" s="125"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="209"/>
+      <c r="D14" s="212"/>
+      <c r="E14" s="167"/>
+      <c r="F14" s="135"/>
+      <c r="G14" s="219"/>
     </row>
     <row r="15" spans="2:7">
-      <c r="B15" s="142"/>
-      <c r="C15" s="159"/>
-      <c r="D15" s="153"/>
-      <c r="E15" s="137"/>
-      <c r="F15" s="156"/>
-      <c r="G15" s="125"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="209"/>
+      <c r="D15" s="212"/>
+      <c r="E15" s="167"/>
+      <c r="F15" s="135"/>
+      <c r="G15" s="219"/>
     </row>
     <row r="16" spans="2:7" ht="158" customHeight="1" thickBot="1">
-      <c r="B16" s="143"/>
-      <c r="C16" s="162"/>
-      <c r="D16" s="154"/>
-      <c r="E16" s="138"/>
-      <c r="F16" s="157"/>
-      <c r="G16" s="126"/>
+      <c r="B16" s="96"/>
+      <c r="C16" s="214"/>
+      <c r="D16" s="213"/>
+      <c r="E16" s="188"/>
+      <c r="F16" s="136"/>
+      <c r="G16" s="220"/>
     </row>
     <row r="17" ht="17.649999999999999" customHeight="1"/>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="B3:B16"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="D11:D16"/>
-    <mergeCell ref="F11:F16"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="C11:C16"/>
-    <mergeCell ref="C7:C10"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="F5:F6"/>
@@ -12857,6 +12969,16 @@
     <mergeCell ref="E11:E16"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="F7:F8"/>
+    <mergeCell ref="B3:B16"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="D11:D16"/>
+    <mergeCell ref="F11:F16"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="C11:C16"/>
+    <mergeCell ref="C7:C10"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12877,94 +12999,94 @@
   <sheetData>
     <row r="1" spans="2:7" ht="17.5" thickBot="1"/>
     <row r="2" spans="2:7" ht="17.5" thickBot="1">
-      <c r="B2" s="46"/>
-      <c r="C2" s="47" t="s">
+      <c r="B2" s="32"/>
+      <c r="C2" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="47" t="s">
+      <c r="D2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="47" t="s">
-        <v>98</v>
-      </c>
-      <c r="F2" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="G2" s="48" t="s">
-        <v>109</v>
+      <c r="E2" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2" s="34" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="103.4" customHeight="1">
-      <c r="B3" s="141" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" s="40" t="s">
-        <v>75</v>
-      </c>
-      <c r="D3" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" s="42" t="s">
-        <v>77</v>
-      </c>
-      <c r="F3" s="68" t="s">
-        <v>150</v>
-      </c>
-      <c r="G3" s="115" t="s">
-        <v>147</v>
+      <c r="B3" s="94" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" s="48" t="s">
+        <v>129</v>
+      </c>
+      <c r="G3" s="89" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="70" customHeight="1">
-      <c r="B4" s="142"/>
-      <c r="C4" s="161" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="69" t="s">
-        <v>149</v>
-      </c>
-      <c r="E4" s="201" t="s">
-        <v>151</v>
-      </c>
-      <c r="F4" s="183" t="s">
-        <v>152</v>
-      </c>
-      <c r="G4" s="129" t="s">
-        <v>146</v>
+      <c r="B4" s="95"/>
+      <c r="C4" s="201" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="49" t="s">
+        <v>128</v>
+      </c>
+      <c r="E4" s="110" t="s">
+        <v>130</v>
+      </c>
+      <c r="F4" s="125" t="s">
+        <v>131</v>
+      </c>
+      <c r="G4" s="192" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="2:7" ht="148.5" customHeight="1">
-      <c r="B5" s="142"/>
-      <c r="C5" s="160"/>
-      <c r="D5" s="66" t="s">
-        <v>148</v>
-      </c>
-      <c r="E5" s="135"/>
-      <c r="F5" s="185"/>
-      <c r="G5" s="128"/>
+      <c r="B5" s="95"/>
+      <c r="C5" s="195"/>
+      <c r="D5" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="E5" s="111"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="222"/>
     </row>
     <row r="6" spans="2:7" ht="125.25" customHeight="1">
-      <c r="B6" s="142"/>
-      <c r="C6" s="161" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" s="152" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" s="294" t="s">
-        <v>160</v>
-      </c>
-      <c r="F6" s="183" t="s">
-        <v>153</v>
-      </c>
-      <c r="G6" s="296"/>
+      <c r="B6" s="95"/>
+      <c r="C6" s="201" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="211" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="223" t="s">
+        <v>139</v>
+      </c>
+      <c r="F6" s="125" t="s">
+        <v>132</v>
+      </c>
+      <c r="G6" s="225"/>
     </row>
     <row r="7" spans="2:7" ht="17.5" thickBot="1">
-      <c r="B7" s="143"/>
-      <c r="C7" s="162"/>
-      <c r="D7" s="154"/>
-      <c r="E7" s="203"/>
-      <c r="F7" s="295"/>
-      <c r="G7" s="297"/>
+      <c r="B7" s="96"/>
+      <c r="C7" s="214"/>
+      <c r="D7" s="213"/>
+      <c r="E7" s="169"/>
+      <c r="F7" s="224"/>
+      <c r="G7" s="226"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -12998,129 +13120,129 @@
   <sheetData>
     <row r="1" spans="2:7" ht="17.5" thickBot="1"/>
     <row r="2" spans="2:7" ht="17.5" thickBot="1">
-      <c r="B2" s="46"/>
-      <c r="C2" s="47" t="s">
+      <c r="B2" s="32"/>
+      <c r="C2" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="47" t="s">
+      <c r="D2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="47" t="s">
-        <v>98</v>
-      </c>
-      <c r="F2" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="G2" s="48" t="s">
-        <v>109</v>
+      <c r="E2" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2" s="34" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="165.4" customHeight="1">
-      <c r="B3" s="141" t="s">
-        <v>155</v>
-      </c>
-      <c r="C3" s="40" t="s">
+      <c r="B3" s="94" t="s">
+        <v>134</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="F3" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="G3" s="47"/>
+    </row>
+    <row r="4" spans="2:7" ht="256.5" customHeight="1">
+      <c r="B4" s="95"/>
+      <c r="C4" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" s="55" t="s">
+        <v>141</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="F4" s="51" t="s">
+        <v>179</v>
+      </c>
+      <c r="G4" s="44"/>
+    </row>
+    <row r="5" spans="2:7" ht="176.65" customHeight="1">
+      <c r="B5" s="95"/>
+      <c r="C5" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F5" s="64" t="s">
+        <v>165</v>
+      </c>
+      <c r="G5" s="87" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="94.4" customHeight="1">
+      <c r="B6" s="95"/>
+      <c r="C6" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="F6" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="G6" s="45"/>
+    </row>
+    <row r="7" spans="2:7" ht="85">
+      <c r="B7" s="95"/>
+      <c r="C7" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="F7" s="54" t="s">
+        <v>137</v>
+      </c>
+      <c r="G7" s="52"/>
+    </row>
+    <row r="8" spans="2:7" ht="17.5" thickBot="1">
+      <c r="B8" s="96"/>
+      <c r="C8" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="D3" s="44" t="s">
-        <v>83</v>
-      </c>
-      <c r="E3" s="42" t="s">
-        <v>156</v>
-      </c>
-      <c r="F3" s="70" t="s">
-        <v>165</v>
-      </c>
-      <c r="G3" s="67"/>
-    </row>
-    <row r="4" spans="2:7" ht="256.5" customHeight="1">
-      <c r="B4" s="142"/>
-      <c r="C4" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="D4" s="75" t="s">
-        <v>162</v>
-      </c>
-      <c r="E4" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="F4" s="71" t="s">
-        <v>204</v>
-      </c>
-      <c r="G4" s="64"/>
-    </row>
-    <row r="5" spans="2:7" ht="176.65" customHeight="1">
-      <c r="B5" s="142"/>
-      <c r="C5" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E5" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="F5" s="85" t="s">
-        <v>187</v>
-      </c>
-      <c r="G5" s="112" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="94.4" customHeight="1">
-      <c r="B6" s="142"/>
-      <c r="C6" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="E6" s="30" t="s">
-        <v>199</v>
-      </c>
-      <c r="F6" s="73" t="s">
-        <v>200</v>
-      </c>
-      <c r="G6" s="65"/>
-    </row>
-    <row r="7" spans="2:7" ht="85">
-      <c r="B7" s="142"/>
-      <c r="C7" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>93</v>
-      </c>
-      <c r="E7" s="30" t="s">
-        <v>157</v>
-      </c>
-      <c r="F7" s="74" t="s">
-        <v>158</v>
-      </c>
-      <c r="G7" s="72"/>
-    </row>
-    <row r="8" spans="2:7" ht="17.5" thickBot="1">
-      <c r="B8" s="143"/>
-      <c r="C8" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8" s="39" t="s">
-        <v>96</v>
-      </c>
-      <c r="E8" s="236" t="s">
-        <v>56</v>
-      </c>
-      <c r="F8" s="237"/>
-      <c r="G8" s="238"/>
+      <c r="E8" s="97" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="98"/>
+      <c r="G8" s="99"/>
     </row>
     <row r="11" spans="2:7">
       <c r="F11" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="2:7">
       <c r="F12" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
